--- a/DATA_VENTA26.1.xlsx
+++ b/DATA_VENTA26.1.xlsx
@@ -489,6 +489,10 @@
         <v>BOLETA PROYECTADA</v>
       </c>
       <c r="BC1" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RINDIO EXAMEN")</f>
+        <v>RINDIO EXAMEN</v>
+      </c>
+      <c r="BD1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Respuestas NEE")</f>
         <v>Respuestas NEE</v>
       </c>
@@ -707,7 +711,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),860.0)</f>
         <v>860</v>
       </c>
-      <c r="BC2" s="1" t="str">
+      <c r="BC2" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD2" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -926,7 +934,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1150.0)</f>
         <v>1150</v>
       </c>
-      <c r="BC3" s="1" t="str">
+      <c r="BC3" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BD3" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -1145,7 +1157,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1450.0)</f>
         <v>1450</v>
       </c>
-      <c r="BC4" s="1" t="str">
+      <c r="BC4" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD4" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -1358,7 +1374,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1600.0)</f>
         <v>1600</v>
       </c>
-      <c r="BC5" s="1" t="str">
+      <c r="BC5" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD5" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -1577,7 +1597,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1500.0)</f>
         <v>1500</v>
       </c>
-      <c r="BC6" s="1" t="str">
+      <c r="BC6" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD6" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -1796,7 +1820,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1050.0)</f>
         <v>1050</v>
       </c>
-      <c r="BC7" s="1" t="str">
+      <c r="BC7" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD7" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -2015,7 +2043,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1215.0)</f>
         <v>1215</v>
       </c>
-      <c r="BC8" s="1" t="str">
+      <c r="BC8" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD8" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -2102,8 +2134,8 @@
         <v>45799</v>
       </c>
       <c r="U9" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Pago Link")</f>
-        <v>Pago Link</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO LINK")</f>
+        <v>PAGO LINK</v>
       </c>
       <c r="V9" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
@@ -2234,133 +2266,454 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1215.0)</f>
         <v>1215</v>
       </c>
-      <c r="BC9" s="1" t="str">
+      <c r="BC9" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD9" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-      <c r="Q10" s="1"/>
-      <c r="R10" s="1"/>
-      <c r="S10" s="1"/>
-      <c r="T10" s="1"/>
-      <c r="U10" s="1"/>
-      <c r="V10" s="1"/>
-      <c r="W10" s="1"/>
-      <c r="X10" s="1"/>
-      <c r="Y10" s="1"/>
-      <c r="Z10" s="1"/>
-      <c r="AA10" s="1"/>
+      <c r="A10" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5126740.0)</f>
+        <v>5126740</v>
+      </c>
+      <c r="C10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0000427077")</f>
+        <v>0000427077</v>
+      </c>
+      <c r="D10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESTEBAN SANTIAGO")</f>
+        <v>ESTEBAN SANTIAGO</v>
+      </c>
+      <c r="E10" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GASTANADUI HEREDIA")</f>
+        <v>GASTANADUI HEREDIA</v>
+      </c>
+      <c r="F10" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.1677488E7)</f>
+        <v>71677488</v>
+      </c>
+      <c r="G10" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.75535555E8)</f>
+        <v>975535555</v>
+      </c>
+      <c r="H10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"esteban1606.g.heredia@gmail.com")</f>
+        <v>esteban1606.g.heredia@gmail.com</v>
+      </c>
+      <c r="I10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Diseño Gráfico Publicitario")</f>
+        <v>Diseño Gráfico Publicitario</v>
+      </c>
+      <c r="J10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Diseño")</f>
+        <v>Diseño</v>
+      </c>
+      <c r="K10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Antigua")</f>
+        <v>Antigua</v>
+      </c>
+      <c r="L10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Admisión de Alto Rendimiento")</f>
+        <v>Admisión de Alto Rendimiento</v>
+      </c>
+      <c r="M10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Semi-presencial")</f>
+        <v>Semi-presencial</v>
+      </c>
+      <c r="N10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Diurno")</f>
+        <v>Diurno</v>
+      </c>
+      <c r="O10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NUEVO")</f>
+        <v>NUEVO</v>
+      </c>
+      <c r="P10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCALA REGULAR")</f>
+        <v>ESCALA REGULAR</v>
+      </c>
+      <c r="Q10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="R10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="S10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="T10" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45804.0)</f>
+        <v>45804</v>
+      </c>
+      <c r="U10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARGO")</f>
+        <v>CARGO</v>
+      </c>
+      <c r="V10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="W10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="X10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="Y10" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45804.0)</f>
+        <v>45804</v>
+      </c>
+      <c r="Z10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="AA10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
+        <v>#N/A</v>
+      </c>
       <c r="AB10" s="1"/>
-      <c r="AC10" s="1"/>
-      <c r="AD10" s="1"/>
-      <c r="AE10" s="1"/>
-      <c r="AF10" s="1"/>
-      <c r="AG10" s="1"/>
-      <c r="AH10" s="1"/>
-      <c r="AI10" s="1"/>
-      <c r="AJ10" s="1"/>
-      <c r="AK10" s="1"/>
-      <c r="AL10" s="1"/>
-      <c r="AM10" s="1"/>
-      <c r="AN10" s="1"/>
-      <c r="AO10" s="1"/>
-      <c r="AP10" s="1"/>
-      <c r="AQ10" s="1"/>
-      <c r="AR10" s="1"/>
-      <c r="AS10" s="1"/>
-      <c r="AT10" s="1"/>
-      <c r="AU10" s="1"/>
-      <c r="AV10" s="1"/>
-      <c r="AW10" s="1"/>
-      <c r="AX10" s="1"/>
-      <c r="AY10" s="1"/>
-      <c r="AZ10" s="1"/>
-      <c r="BA10" s="1"/>
-      <c r="BB10" s="1"/>
-      <c r="BC10" s="1" t="str">
+      <c r="AC10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),95.0)</f>
+        <v>95</v>
+      </c>
+      <c r="AD10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
+        <v>50</v>
+      </c>
+      <c r="AE10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1600.0)</f>
+        <v>1600</v>
+      </c>
+      <c r="AF10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1600.0)</f>
+        <v>1600</v>
+      </c>
+      <c r="AG10" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH10" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI10" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),329557.0)</f>
+        <v>329557</v>
+      </c>
+      <c r="AK10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"10 kms a 15 kms")</f>
+        <v>10 kms a 15 kms</v>
+      </c>
+      <c r="AL10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"07 801 a 900")</f>
+        <v>07 801 a 900</v>
+      </c>
+      <c r="AM10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0")</f>
+        <v>0</v>
+      </c>
+      <c r="AN10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="AO10" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2025.0)</f>
+        <v>2025</v>
+      </c>
+      <c r="AP10" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
+        <v>45778</v>
+      </c>
+      <c r="AQ10" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45775.0)</f>
+        <v>45775</v>
+      </c>
+      <c r="AR10" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45804.0)</f>
+        <v>45804</v>
+      </c>
+      <c r="AS10" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
+        <v>45778</v>
+      </c>
+      <c r="AT10" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45775.0)</f>
+        <v>45775</v>
+      </c>
+      <c r="AU10" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AV10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"OUTBOUND")</f>
+        <v>OUTBOUND</v>
+      </c>
+      <c r="AW10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"OUTBOUND")</f>
+        <v>OUTBOUND</v>
+      </c>
+      <c r="AX10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"OUTBOUND")</f>
+        <v>OUTBOUND</v>
+      </c>
+      <c r="AY10" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Daniel Zapata")</f>
+        <v>Daniel Zapata</v>
+      </c>
+      <c r="BA10" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BB10" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1600.0)</f>
+        <v>1600</v>
+      </c>
+      <c r="BC10" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD10" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-      <c r="U11" s="1"/>
-      <c r="V11" s="1"/>
-      <c r="W11" s="1"/>
-      <c r="X11" s="1"/>
+      <c r="A11" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5210779.0)</f>
+        <v>5210779</v>
+      </c>
+      <c r="C11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0000426964")</f>
+        <v>0000426964</v>
+      </c>
+      <c r="D11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUCYA VALERIA")</f>
+        <v>LUCYA VALERIA</v>
+      </c>
+      <c r="E11" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"QUISPE RODRIGUEZ")</f>
+        <v>QUISPE RODRIGUEZ</v>
+      </c>
+      <c r="F11" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.2591665E7)</f>
+        <v>72591665</v>
+      </c>
+      <c r="G11" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.40296595E8)</f>
+        <v>940296595</v>
+      </c>
+      <c r="H11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Valerialucya9@gmail.com")</f>
+        <v>Valerialucya9@gmail.com</v>
+      </c>
+      <c r="I11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Comunicación Audiovisual y Cine")</f>
+        <v>Comunicación Audiovisual y Cine</v>
+      </c>
+      <c r="J11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Comunicaciones")</f>
+        <v>Comunicaciones</v>
+      </c>
+      <c r="K11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Antigua")</f>
+        <v>Antigua</v>
+      </c>
+      <c r="L11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Admisión Ordinaria")</f>
+        <v>Admisión Ordinaria</v>
+      </c>
+      <c r="M11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Semi-presencial")</f>
+        <v>Semi-presencial</v>
+      </c>
+      <c r="N11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Diurno")</f>
+        <v>Diurno</v>
+      </c>
+      <c r="O11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NUEVO")</f>
+        <v>NUEVO</v>
+      </c>
+      <c r="P11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BECA")</f>
+        <v>BECA</v>
+      </c>
+      <c r="Q11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BECA CARRERAS CORE")</f>
+        <v>BECA CARRERAS CORE</v>
+      </c>
+      <c r="R11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="S11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="T11" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45805.0)</f>
+        <v>45805</v>
+      </c>
+      <c r="U11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO LINK")</f>
+        <v>PAGO LINK</v>
+      </c>
+      <c r="V11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO FRACCIONADO")</f>
+        <v>PAGO FRACCIONADO</v>
+      </c>
+      <c r="W11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),600.0)</f>
+        <v>600</v>
+      </c>
+      <c r="X11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"20/06/2025")</f>
+        <v>20/06/2025</v>
+      </c>
       <c r="Y11" s="1"/>
-      <c r="Z11" s="1"/>
-      <c r="AA11" s="1"/>
+      <c r="Z11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO FRACCIONADO")</f>
+        <v>PAGO FRACCIONADO</v>
+      </c>
+      <c r="AA11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
+        <v>#N/A</v>
+      </c>
       <c r="AB11" s="1"/>
-      <c r="AC11" s="1"/>
-      <c r="AD11" s="1"/>
-      <c r="AE11" s="1"/>
-      <c r="AF11" s="1"/>
-      <c r="AG11" s="1"/>
-      <c r="AH11" s="1"/>
-      <c r="AI11" s="1"/>
-      <c r="AJ11" s="1"/>
-      <c r="AK11" s="1"/>
-      <c r="AL11" s="1"/>
-      <c r="AM11" s="1"/>
-      <c r="AN11" s="1"/>
-      <c r="AO11" s="1"/>
-      <c r="AP11" s="1"/>
-      <c r="AQ11" s="1"/>
-      <c r="AR11" s="1"/>
-      <c r="AS11" s="1"/>
-      <c r="AT11" s="1"/>
-      <c r="AU11" s="1"/>
-      <c r="AV11" s="1"/>
-      <c r="AW11" s="1"/>
-      <c r="AX11" s="1"/>
-      <c r="AY11" s="1"/>
-      <c r="AZ11" s="1"/>
-      <c r="BA11" s="1"/>
-      <c r="BB11" s="1"/>
-      <c r="BC11" s="1" t="str">
+      <c r="AC11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),95.0)</f>
+        <v>95</v>
+      </c>
+      <c r="AD11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
+        <v>50</v>
+      </c>
+      <c r="AE11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1400.0)</f>
+        <v>1400</v>
+      </c>
+      <c r="AF11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1200.0)</f>
+        <v>1200</v>
+      </c>
+      <c r="AG11" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH11" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI11" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1541911.0)</f>
+        <v>1541911</v>
+      </c>
+      <c r="AK11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"10 kms a 15 kms")</f>
+        <v>10 kms a 15 kms</v>
+      </c>
+      <c r="AL11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"07 801 a 900")</f>
+        <v>07 801 a 900</v>
+      </c>
+      <c r="AM11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0")</f>
+        <v>0</v>
+      </c>
+      <c r="AN11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="AO11" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2025.0)</f>
+        <v>2025</v>
+      </c>
+      <c r="AP11" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
+        <v>45778</v>
+      </c>
+      <c r="AQ11" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45775.0)</f>
+        <v>45775</v>
+      </c>
+      <c r="AR11" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45798.0)</f>
+        <v>45798</v>
+      </c>
+      <c r="AS11" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
+        <v>45778</v>
+      </c>
+      <c r="AT11" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45775.0)</f>
+        <v>45775</v>
+      </c>
+      <c r="AU11" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
+        <v>7</v>
+      </c>
+      <c r="AV11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIGITAL")</f>
+        <v>DIGITAL</v>
+      </c>
+      <c r="AW11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BIDIRECCIONAL")</f>
+        <v>BIDIRECCIONAL</v>
+      </c>
+      <c r="AX11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ORGANICO")</f>
+        <v>ORGANICO</v>
+      </c>
+      <c r="AY11" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cinthia Mariella Orosco")</f>
+        <v>Cinthia Mariella Orosco</v>
+      </c>
+      <c r="BA11" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5539033457249071)</f>
+        <v>0.5539033457</v>
+      </c>
+      <c r="BB11" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1200.0)</f>
+        <v>1200</v>
+      </c>
+      <c r="BC11" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD11" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -2423,7 +2776,8 @@
       <c r="AZ12" s="1"/>
       <c r="BA12" s="1"/>
       <c r="BB12" s="1"/>
-      <c r="BC12" s="1" t="str">
+      <c r="BC12" s="1"/>
+      <c r="BD12" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -2486,7 +2840,8 @@
       <c r="AZ13" s="1"/>
       <c r="BA13" s="1"/>
       <c r="BB13" s="1"/>
-      <c r="BC13" s="1" t="str">
+      <c r="BC13" s="1"/>
+      <c r="BD13" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -2549,7 +2904,8 @@
       <c r="AZ14" s="1"/>
       <c r="BA14" s="1"/>
       <c r="BB14" s="1"/>
-      <c r="BC14" s="1" t="str">
+      <c r="BC14" s="1"/>
+      <c r="BD14" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -2612,7 +2968,8 @@
       <c r="AZ15" s="1"/>
       <c r="BA15" s="1"/>
       <c r="BB15" s="1"/>
-      <c r="BC15" s="1" t="str">
+      <c r="BC15" s="1"/>
+      <c r="BD15" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -2675,7 +3032,8 @@
       <c r="AZ16" s="1"/>
       <c r="BA16" s="1"/>
       <c r="BB16" s="1"/>
-      <c r="BC16" s="1" t="str">
+      <c r="BC16" s="1"/>
+      <c r="BD16" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -2738,7 +3096,8 @@
       <c r="AZ17" s="1"/>
       <c r="BA17" s="1"/>
       <c r="BB17" s="1"/>
-      <c r="BC17" s="1" t="str">
+      <c r="BC17" s="1"/>
+      <c r="BD17" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -2801,7 +3160,8 @@
       <c r="AZ18" s="1"/>
       <c r="BA18" s="1"/>
       <c r="BB18" s="1"/>
-      <c r="BC18" s="1" t="str">
+      <c r="BC18" s="1"/>
+      <c r="BD18" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -2864,7 +3224,8 @@
       <c r="AZ19" s="1"/>
       <c r="BA19" s="1"/>
       <c r="BB19" s="1"/>
-      <c r="BC19" s="1" t="str">
+      <c r="BC19" s="1"/>
+      <c r="BD19" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -2927,7 +3288,8 @@
       <c r="AZ20" s="1"/>
       <c r="BA20" s="1"/>
       <c r="BB20" s="1"/>
-      <c r="BC20" s="1" t="str">
+      <c r="BC20" s="1"/>
+      <c r="BD20" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -2990,7 +3352,8 @@
       <c r="AZ21" s="1"/>
       <c r="BA21" s="1"/>
       <c r="BB21" s="1"/>
-      <c r="BC21" s="1" t="str">
+      <c r="BC21" s="1"/>
+      <c r="BD21" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -3053,7 +3416,8 @@
       <c r="AZ22" s="1"/>
       <c r="BA22" s="1"/>
       <c r="BB22" s="1"/>
-      <c r="BC22" s="1" t="str">
+      <c r="BC22" s="1"/>
+      <c r="BD22" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -3116,7 +3480,8 @@
       <c r="AZ23" s="1"/>
       <c r="BA23" s="1"/>
       <c r="BB23" s="1"/>
-      <c r="BC23" s="1" t="str">
+      <c r="BC23" s="1"/>
+      <c r="BD23" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -3179,7 +3544,8 @@
       <c r="AZ24" s="1"/>
       <c r="BA24" s="1"/>
       <c r="BB24" s="1"/>
-      <c r="BC24" s="1" t="str">
+      <c r="BC24" s="1"/>
+      <c r="BD24" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -3242,7 +3608,8 @@
       <c r="AZ25" s="1"/>
       <c r="BA25" s="1"/>
       <c r="BB25" s="1"/>
-      <c r="BC25" s="1" t="str">
+      <c r="BC25" s="1"/>
+      <c r="BD25" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -3305,7 +3672,8 @@
       <c r="AZ26" s="1"/>
       <c r="BA26" s="1"/>
       <c r="BB26" s="1"/>
-      <c r="BC26" s="1" t="str">
+      <c r="BC26" s="1"/>
+      <c r="BD26" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -3368,7 +3736,8 @@
       <c r="AZ27" s="1"/>
       <c r="BA27" s="1"/>
       <c r="BB27" s="1"/>
-      <c r="BC27" s="1" t="str">
+      <c r="BC27" s="1"/>
+      <c r="BD27" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -3431,7 +3800,8 @@
       <c r="AZ28" s="1"/>
       <c r="BA28" s="1"/>
       <c r="BB28" s="1"/>
-      <c r="BC28" s="1" t="str">
+      <c r="BC28" s="1"/>
+      <c r="BD28" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -3494,7 +3864,8 @@
       <c r="AZ29" s="1"/>
       <c r="BA29" s="1"/>
       <c r="BB29" s="1"/>
-      <c r="BC29" s="1" t="str">
+      <c r="BC29" s="1"/>
+      <c r="BD29" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -3557,7 +3928,8 @@
       <c r="AZ30" s="1"/>
       <c r="BA30" s="1"/>
       <c r="BB30" s="1"/>
-      <c r="BC30" s="1" t="str">
+      <c r="BC30" s="1"/>
+      <c r="BD30" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -3620,7 +3992,8 @@
       <c r="AZ31" s="1"/>
       <c r="BA31" s="1"/>
       <c r="BB31" s="1"/>
-      <c r="BC31" s="1" t="str">
+      <c r="BC31" s="1"/>
+      <c r="BD31" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -3683,7 +4056,8 @@
       <c r="AZ32" s="1"/>
       <c r="BA32" s="1"/>
       <c r="BB32" s="1"/>
-      <c r="BC32" s="1" t="str">
+      <c r="BC32" s="1"/>
+      <c r="BD32" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -3746,7 +4120,8 @@
       <c r="AZ33" s="1"/>
       <c r="BA33" s="1"/>
       <c r="BB33" s="1"/>
-      <c r="BC33" s="1" t="str">
+      <c r="BC33" s="1"/>
+      <c r="BD33" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -3809,7 +4184,8 @@
       <c r="AZ34" s="1"/>
       <c r="BA34" s="1"/>
       <c r="BB34" s="1"/>
-      <c r="BC34" s="1" t="str">
+      <c r="BC34" s="1"/>
+      <c r="BD34" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -3872,7 +4248,8 @@
       <c r="AZ35" s="1"/>
       <c r="BA35" s="1"/>
       <c r="BB35" s="1"/>
-      <c r="BC35" s="1" t="str">
+      <c r="BC35" s="1"/>
+      <c r="BD35" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -3935,7 +4312,8 @@
       <c r="AZ36" s="1"/>
       <c r="BA36" s="1"/>
       <c r="BB36" s="1"/>
-      <c r="BC36" s="1" t="str">
+      <c r="BC36" s="1"/>
+      <c r="BD36" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -3998,7 +4376,8 @@
       <c r="AZ37" s="1"/>
       <c r="BA37" s="1"/>
       <c r="BB37" s="1"/>
-      <c r="BC37" s="1" t="str">
+      <c r="BC37" s="1"/>
+      <c r="BD37" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4061,7 +4440,8 @@
       <c r="AZ38" s="1"/>
       <c r="BA38" s="1"/>
       <c r="BB38" s="1"/>
-      <c r="BC38" s="1" t="str">
+      <c r="BC38" s="1"/>
+      <c r="BD38" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4124,7 +4504,8 @@
       <c r="AZ39" s="1"/>
       <c r="BA39" s="1"/>
       <c r="BB39" s="1"/>
-      <c r="BC39" s="1" t="str">
+      <c r="BC39" s="1"/>
+      <c r="BD39" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4187,7 +4568,8 @@
       <c r="AZ40" s="1"/>
       <c r="BA40" s="1"/>
       <c r="BB40" s="1"/>
-      <c r="BC40" s="1" t="str">
+      <c r="BC40" s="1"/>
+      <c r="BD40" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4250,7 +4632,8 @@
       <c r="AZ41" s="1"/>
       <c r="BA41" s="1"/>
       <c r="BB41" s="1"/>
-      <c r="BC41" s="1" t="str">
+      <c r="BC41" s="1"/>
+      <c r="BD41" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4313,7 +4696,8 @@
       <c r="AZ42" s="1"/>
       <c r="BA42" s="1"/>
       <c r="BB42" s="1"/>
-      <c r="BC42" s="1" t="str">
+      <c r="BC42" s="1"/>
+      <c r="BD42" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4376,7 +4760,8 @@
       <c r="AZ43" s="1"/>
       <c r="BA43" s="1"/>
       <c r="BB43" s="1"/>
-      <c r="BC43" s="1" t="str">
+      <c r="BC43" s="1"/>
+      <c r="BD43" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4439,7 +4824,8 @@
       <c r="AZ44" s="1"/>
       <c r="BA44" s="1"/>
       <c r="BB44" s="1"/>
-      <c r="BC44" s="1" t="str">
+      <c r="BC44" s="1"/>
+      <c r="BD44" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4502,7 +4888,8 @@
       <c r="AZ45" s="1"/>
       <c r="BA45" s="1"/>
       <c r="BB45" s="1"/>
-      <c r="BC45" s="1" t="str">
+      <c r="BC45" s="1"/>
+      <c r="BD45" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4565,7 +4952,8 @@
       <c r="AZ46" s="1"/>
       <c r="BA46" s="1"/>
       <c r="BB46" s="1"/>
-      <c r="BC46" s="1" t="str">
+      <c r="BC46" s="1"/>
+      <c r="BD46" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4628,7 +5016,8 @@
       <c r="AZ47" s="1"/>
       <c r="BA47" s="1"/>
       <c r="BB47" s="1"/>
-      <c r="BC47" s="1" t="str">
+      <c r="BC47" s="1"/>
+      <c r="BD47" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4691,7 +5080,8 @@
       <c r="AZ48" s="1"/>
       <c r="BA48" s="1"/>
       <c r="BB48" s="1"/>
-      <c r="BC48" s="1" t="str">
+      <c r="BC48" s="1"/>
+      <c r="BD48" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4754,7 +5144,8 @@
       <c r="AZ49" s="1"/>
       <c r="BA49" s="1"/>
       <c r="BB49" s="1"/>
-      <c r="BC49" s="1" t="str">
+      <c r="BC49" s="1"/>
+      <c r="BD49" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4817,7 +5208,8 @@
       <c r="AZ50" s="1"/>
       <c r="BA50" s="1"/>
       <c r="BB50" s="1"/>
-      <c r="BC50" s="1" t="str">
+      <c r="BC50" s="1"/>
+      <c r="BD50" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4880,7 +5272,8 @@
       <c r="AZ51" s="1"/>
       <c r="BA51" s="1"/>
       <c r="BB51" s="1"/>
-      <c r="BC51" s="1" t="str">
+      <c r="BC51" s="1"/>
+      <c r="BD51" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4943,7 +5336,8 @@
       <c r="AZ52" s="1"/>
       <c r="BA52" s="1"/>
       <c r="BB52" s="1"/>
-      <c r="BC52" s="1" t="str">
+      <c r="BC52" s="1"/>
+      <c r="BD52" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5006,7 +5400,8 @@
       <c r="AZ53" s="1"/>
       <c r="BA53" s="1"/>
       <c r="BB53" s="1"/>
-      <c r="BC53" s="1" t="str">
+      <c r="BC53" s="1"/>
+      <c r="BD53" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5069,7 +5464,8 @@
       <c r="AZ54" s="1"/>
       <c r="BA54" s="1"/>
       <c r="BB54" s="1"/>
-      <c r="BC54" s="1" t="str">
+      <c r="BC54" s="1"/>
+      <c r="BD54" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5132,7 +5528,8 @@
       <c r="AZ55" s="1"/>
       <c r="BA55" s="1"/>
       <c r="BB55" s="1"/>
-      <c r="BC55" s="1" t="str">
+      <c r="BC55" s="1"/>
+      <c r="BD55" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5195,7 +5592,8 @@
       <c r="AZ56" s="1"/>
       <c r="BA56" s="1"/>
       <c r="BB56" s="1"/>
-      <c r="BC56" s="1" t="str">
+      <c r="BC56" s="1"/>
+      <c r="BD56" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5258,7 +5656,8 @@
       <c r="AZ57" s="1"/>
       <c r="BA57" s="1"/>
       <c r="BB57" s="1"/>
-      <c r="BC57" s="1" t="str">
+      <c r="BC57" s="1"/>
+      <c r="BD57" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5321,7 +5720,8 @@
       <c r="AZ58" s="1"/>
       <c r="BA58" s="1"/>
       <c r="BB58" s="1"/>
-      <c r="BC58" s="1" t="str">
+      <c r="BC58" s="1"/>
+      <c r="BD58" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5384,7 +5784,8 @@
       <c r="AZ59" s="1"/>
       <c r="BA59" s="1"/>
       <c r="BB59" s="1"/>
-      <c r="BC59" s="1" t="str">
+      <c r="BC59" s="1"/>
+      <c r="BD59" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5447,7 +5848,8 @@
       <c r="AZ60" s="1"/>
       <c r="BA60" s="1"/>
       <c r="BB60" s="1"/>
-      <c r="BC60" s="1" t="str">
+      <c r="BC60" s="1"/>
+      <c r="BD60" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5510,7 +5912,8 @@
       <c r="AZ61" s="1"/>
       <c r="BA61" s="1"/>
       <c r="BB61" s="1"/>
-      <c r="BC61" s="1" t="str">
+      <c r="BC61" s="1"/>
+      <c r="BD61" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5573,7 +5976,8 @@
       <c r="AZ62" s="1"/>
       <c r="BA62" s="1"/>
       <c r="BB62" s="1"/>
-      <c r="BC62" s="1" t="str">
+      <c r="BC62" s="1"/>
+      <c r="BD62" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5636,7 +6040,8 @@
       <c r="AZ63" s="1"/>
       <c r="BA63" s="1"/>
       <c r="BB63" s="1"/>
-      <c r="BC63" s="1" t="str">
+      <c r="BC63" s="1"/>
+      <c r="BD63" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5699,7 +6104,8 @@
       <c r="AZ64" s="1"/>
       <c r="BA64" s="1"/>
       <c r="BB64" s="1"/>
-      <c r="BC64" s="1" t="str">
+      <c r="BC64" s="1"/>
+      <c r="BD64" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5762,7 +6168,8 @@
       <c r="AZ65" s="1"/>
       <c r="BA65" s="1"/>
       <c r="BB65" s="1"/>
-      <c r="BC65" s="1" t="str">
+      <c r="BC65" s="1"/>
+      <c r="BD65" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5825,7 +6232,8 @@
       <c r="AZ66" s="1"/>
       <c r="BA66" s="1"/>
       <c r="BB66" s="1"/>
-      <c r="BC66" s="1" t="str">
+      <c r="BC66" s="1"/>
+      <c r="BD66" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5888,7 +6296,8 @@
       <c r="AZ67" s="1"/>
       <c r="BA67" s="1"/>
       <c r="BB67" s="1"/>
-      <c r="BC67" s="1" t="str">
+      <c r="BC67" s="1"/>
+      <c r="BD67" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5951,7 +6360,8 @@
       <c r="AZ68" s="1"/>
       <c r="BA68" s="1"/>
       <c r="BB68" s="1"/>
-      <c r="BC68" s="1" t="str">
+      <c r="BC68" s="1"/>
+      <c r="BD68" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6014,7 +6424,8 @@
       <c r="AZ69" s="1"/>
       <c r="BA69" s="1"/>
       <c r="BB69" s="1"/>
-      <c r="BC69" s="1" t="str">
+      <c r="BC69" s="1"/>
+      <c r="BD69" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6077,7 +6488,8 @@
       <c r="AZ70" s="1"/>
       <c r="BA70" s="1"/>
       <c r="BB70" s="1"/>
-      <c r="BC70" s="1" t="str">
+      <c r="BC70" s="1"/>
+      <c r="BD70" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6140,7 +6552,8 @@
       <c r="AZ71" s="1"/>
       <c r="BA71" s="1"/>
       <c r="BB71" s="1"/>
-      <c r="BC71" s="1" t="str">
+      <c r="BC71" s="1"/>
+      <c r="BD71" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6203,7 +6616,8 @@
       <c r="AZ72" s="1"/>
       <c r="BA72" s="1"/>
       <c r="BB72" s="1"/>
-      <c r="BC72" s="1" t="str">
+      <c r="BC72" s="1"/>
+      <c r="BD72" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6266,7 +6680,8 @@
       <c r="AZ73" s="1"/>
       <c r="BA73" s="1"/>
       <c r="BB73" s="1"/>
-      <c r="BC73" s="1" t="str">
+      <c r="BC73" s="1"/>
+      <c r="BD73" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6329,7 +6744,8 @@
       <c r="AZ74" s="1"/>
       <c r="BA74" s="1"/>
       <c r="BB74" s="1"/>
-      <c r="BC74" s="1" t="str">
+      <c r="BC74" s="1"/>
+      <c r="BD74" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6392,7 +6808,8 @@
       <c r="AZ75" s="1"/>
       <c r="BA75" s="1"/>
       <c r="BB75" s="1"/>
-      <c r="BC75" s="1" t="str">
+      <c r="BC75" s="1"/>
+      <c r="BD75" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6455,7 +6872,8 @@
       <c r="AZ76" s="1"/>
       <c r="BA76" s="1"/>
       <c r="BB76" s="1"/>
-      <c r="BC76" s="1" t="str">
+      <c r="BC76" s="1"/>
+      <c r="BD76" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6518,7 +6936,8 @@
       <c r="AZ77" s="1"/>
       <c r="BA77" s="1"/>
       <c r="BB77" s="1"/>
-      <c r="BC77" s="1" t="str">
+      <c r="BC77" s="1"/>
+      <c r="BD77" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6581,7 +7000,8 @@
       <c r="AZ78" s="1"/>
       <c r="BA78" s="1"/>
       <c r="BB78" s="1"/>
-      <c r="BC78" s="1" t="str">
+      <c r="BC78" s="1"/>
+      <c r="BD78" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6644,7 +7064,8 @@
       <c r="AZ79" s="1"/>
       <c r="BA79" s="1"/>
       <c r="BB79" s="1"/>
-      <c r="BC79" s="1" t="str">
+      <c r="BC79" s="1"/>
+      <c r="BD79" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6707,7 +7128,8 @@
       <c r="AZ80" s="1"/>
       <c r="BA80" s="1"/>
       <c r="BB80" s="1"/>
-      <c r="BC80" s="1" t="str">
+      <c r="BC80" s="1"/>
+      <c r="BD80" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6770,7 +7192,8 @@
       <c r="AZ81" s="1"/>
       <c r="BA81" s="1"/>
       <c r="BB81" s="1"/>
-      <c r="BC81" s="1" t="str">
+      <c r="BC81" s="1"/>
+      <c r="BD81" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6833,7 +7256,8 @@
       <c r="AZ82" s="1"/>
       <c r="BA82" s="1"/>
       <c r="BB82" s="1"/>
-      <c r="BC82" s="1" t="str">
+      <c r="BC82" s="1"/>
+      <c r="BD82" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6896,7 +7320,8 @@
       <c r="AZ83" s="1"/>
       <c r="BA83" s="1"/>
       <c r="BB83" s="1"/>
-      <c r="BC83" s="1" t="str">
+      <c r="BC83" s="1"/>
+      <c r="BD83" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6959,7 +7384,8 @@
       <c r="AZ84" s="1"/>
       <c r="BA84" s="1"/>
       <c r="BB84" s="1"/>
-      <c r="BC84" s="1" t="str">
+      <c r="BC84" s="1"/>
+      <c r="BD84" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7022,7 +7448,8 @@
       <c r="AZ85" s="1"/>
       <c r="BA85" s="1"/>
       <c r="BB85" s="1"/>
-      <c r="BC85" s="1" t="str">
+      <c r="BC85" s="1"/>
+      <c r="BD85" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7085,7 +7512,8 @@
       <c r="AZ86" s="1"/>
       <c r="BA86" s="1"/>
       <c r="BB86" s="1"/>
-      <c r="BC86" s="1" t="str">
+      <c r="BC86" s="1"/>
+      <c r="BD86" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7148,7 +7576,8 @@
       <c r="AZ87" s="1"/>
       <c r="BA87" s="1"/>
       <c r="BB87" s="1"/>
-      <c r="BC87" s="1" t="str">
+      <c r="BC87" s="1"/>
+      <c r="BD87" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7211,7 +7640,8 @@
       <c r="AZ88" s="1"/>
       <c r="BA88" s="1"/>
       <c r="BB88" s="1"/>
-      <c r="BC88" s="1" t="str">
+      <c r="BC88" s="1"/>
+      <c r="BD88" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7274,7 +7704,8 @@
       <c r="AZ89" s="1"/>
       <c r="BA89" s="1"/>
       <c r="BB89" s="1"/>
-      <c r="BC89" s="1" t="str">
+      <c r="BC89" s="1"/>
+      <c r="BD89" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7337,7 +7768,8 @@
       <c r="AZ90" s="1"/>
       <c r="BA90" s="1"/>
       <c r="BB90" s="1"/>
-      <c r="BC90" s="1" t="str">
+      <c r="BC90" s="1"/>
+      <c r="BD90" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7400,7 +7832,8 @@
       <c r="AZ91" s="1"/>
       <c r="BA91" s="1"/>
       <c r="BB91" s="1"/>
-      <c r="BC91" s="1" t="str">
+      <c r="BC91" s="1"/>
+      <c r="BD91" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7463,7 +7896,8 @@
       <c r="AZ92" s="1"/>
       <c r="BA92" s="1"/>
       <c r="BB92" s="1"/>
-      <c r="BC92" s="1" t="str">
+      <c r="BC92" s="1"/>
+      <c r="BD92" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7526,7 +7960,8 @@
       <c r="AZ93" s="1"/>
       <c r="BA93" s="1"/>
       <c r="BB93" s="1"/>
-      <c r="BC93" s="1" t="str">
+      <c r="BC93" s="1"/>
+      <c r="BD93" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7589,7 +8024,8 @@
       <c r="AZ94" s="1"/>
       <c r="BA94" s="1"/>
       <c r="BB94" s="1"/>
-      <c r="BC94" s="1" t="str">
+      <c r="BC94" s="1"/>
+      <c r="BD94" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7652,7 +8088,8 @@
       <c r="AZ95" s="1"/>
       <c r="BA95" s="1"/>
       <c r="BB95" s="1"/>
-      <c r="BC95" s="1" t="str">
+      <c r="BC95" s="1"/>
+      <c r="BD95" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7715,7 +8152,8 @@
       <c r="AZ96" s="1"/>
       <c r="BA96" s="1"/>
       <c r="BB96" s="1"/>
-      <c r="BC96" s="1" t="str">
+      <c r="BC96" s="1"/>
+      <c r="BD96" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7778,7 +8216,8 @@
       <c r="AZ97" s="1"/>
       <c r="BA97" s="1"/>
       <c r="BB97" s="1"/>
-      <c r="BC97" s="1" t="str">
+      <c r="BC97" s="1"/>
+      <c r="BD97" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7841,7 +8280,8 @@
       <c r="AZ98" s="1"/>
       <c r="BA98" s="1"/>
       <c r="BB98" s="1"/>
-      <c r="BC98" s="1" t="str">
+      <c r="BC98" s="1"/>
+      <c r="BD98" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7904,7 +8344,8 @@
       <c r="AZ99" s="1"/>
       <c r="BA99" s="1"/>
       <c r="BB99" s="1"/>
-      <c r="BC99" s="1" t="str">
+      <c r="BC99" s="1"/>
+      <c r="BD99" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7967,7 +8408,8 @@
       <c r="AZ100" s="1"/>
       <c r="BA100" s="1"/>
       <c r="BB100" s="1"/>
-      <c r="BC100" s="1" t="str">
+      <c r="BC100" s="1"/>
+      <c r="BD100" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8030,7 +8472,8 @@
       <c r="AZ101" s="1"/>
       <c r="BA101" s="1"/>
       <c r="BB101" s="1"/>
-      <c r="BC101" s="1" t="str">
+      <c r="BC101" s="1"/>
+      <c r="BD101" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8093,7 +8536,8 @@
       <c r="AZ102" s="1"/>
       <c r="BA102" s="1"/>
       <c r="BB102" s="1"/>
-      <c r="BC102" s="1" t="str">
+      <c r="BC102" s="1"/>
+      <c r="BD102" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8156,7 +8600,8 @@
       <c r="AZ103" s="1"/>
       <c r="BA103" s="1"/>
       <c r="BB103" s="1"/>
-      <c r="BC103" s="1" t="str">
+      <c r="BC103" s="1"/>
+      <c r="BD103" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8219,7 +8664,8 @@
       <c r="AZ104" s="1"/>
       <c r="BA104" s="1"/>
       <c r="BB104" s="1"/>
-      <c r="BC104" s="1" t="str">
+      <c r="BC104" s="1"/>
+      <c r="BD104" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8282,7 +8728,8 @@
       <c r="AZ105" s="1"/>
       <c r="BA105" s="1"/>
       <c r="BB105" s="1"/>
-      <c r="BC105" s="1" t="str">
+      <c r="BC105" s="1"/>
+      <c r="BD105" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8345,7 +8792,8 @@
       <c r="AZ106" s="1"/>
       <c r="BA106" s="1"/>
       <c r="BB106" s="1"/>
-      <c r="BC106" s="1" t="str">
+      <c r="BC106" s="1"/>
+      <c r="BD106" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8408,7 +8856,8 @@
       <c r="AZ107" s="1"/>
       <c r="BA107" s="1"/>
       <c r="BB107" s="1"/>
-      <c r="BC107" s="1" t="str">
+      <c r="BC107" s="1"/>
+      <c r="BD107" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8471,7 +8920,8 @@
       <c r="AZ108" s="1"/>
       <c r="BA108" s="1"/>
       <c r="BB108" s="1"/>
-      <c r="BC108" s="1" t="str">
+      <c r="BC108" s="1"/>
+      <c r="BD108" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8534,7 +8984,8 @@
       <c r="AZ109" s="1"/>
       <c r="BA109" s="1"/>
       <c r="BB109" s="1"/>
-      <c r="BC109" s="1" t="str">
+      <c r="BC109" s="1"/>
+      <c r="BD109" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8597,7 +9048,8 @@
       <c r="AZ110" s="1"/>
       <c r="BA110" s="1"/>
       <c r="BB110" s="1"/>
-      <c r="BC110" s="1" t="str">
+      <c r="BC110" s="1"/>
+      <c r="BD110" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8660,7 +9112,8 @@
       <c r="AZ111" s="1"/>
       <c r="BA111" s="1"/>
       <c r="BB111" s="1"/>
-      <c r="BC111" s="1" t="str">
+      <c r="BC111" s="1"/>
+      <c r="BD111" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8723,7 +9176,8 @@
       <c r="AZ112" s="1"/>
       <c r="BA112" s="1"/>
       <c r="BB112" s="1"/>
-      <c r="BC112" s="1" t="str">
+      <c r="BC112" s="1"/>
+      <c r="BD112" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8786,7 +9240,8 @@
       <c r="AZ113" s="1"/>
       <c r="BA113" s="1"/>
       <c r="BB113" s="1"/>
-      <c r="BC113" s="1" t="str">
+      <c r="BC113" s="1"/>
+      <c r="BD113" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8849,7 +9304,8 @@
       <c r="AZ114" s="1"/>
       <c r="BA114" s="1"/>
       <c r="BB114" s="1"/>
-      <c r="BC114" s="1" t="str">
+      <c r="BC114" s="1"/>
+      <c r="BD114" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8912,7 +9368,8 @@
       <c r="AZ115" s="1"/>
       <c r="BA115" s="1"/>
       <c r="BB115" s="1"/>
-      <c r="BC115" s="1" t="str">
+      <c r="BC115" s="1"/>
+      <c r="BD115" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8975,7 +9432,8 @@
       <c r="AZ116" s="1"/>
       <c r="BA116" s="1"/>
       <c r="BB116" s="1"/>
-      <c r="BC116" s="1" t="str">
+      <c r="BC116" s="1"/>
+      <c r="BD116" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9038,7 +9496,8 @@
       <c r="AZ117" s="1"/>
       <c r="BA117" s="1"/>
       <c r="BB117" s="1"/>
-      <c r="BC117" s="1" t="str">
+      <c r="BC117" s="1"/>
+      <c r="BD117" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9101,7 +9560,8 @@
       <c r="AZ118" s="1"/>
       <c r="BA118" s="1"/>
       <c r="BB118" s="1"/>
-      <c r="BC118" s="1" t="str">
+      <c r="BC118" s="1"/>
+      <c r="BD118" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9164,7 +9624,8 @@
       <c r="AZ119" s="1"/>
       <c r="BA119" s="1"/>
       <c r="BB119" s="1"/>
-      <c r="BC119" s="1" t="str">
+      <c r="BC119" s="1"/>
+      <c r="BD119" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9227,7 +9688,8 @@
       <c r="AZ120" s="1"/>
       <c r="BA120" s="1"/>
       <c r="BB120" s="1"/>
-      <c r="BC120" s="1" t="str">
+      <c r="BC120" s="1"/>
+      <c r="BD120" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9290,7 +9752,8 @@
       <c r="AZ121" s="1"/>
       <c r="BA121" s="1"/>
       <c r="BB121" s="1"/>
-      <c r="BC121" s="1" t="str">
+      <c r="BC121" s="1"/>
+      <c r="BD121" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9353,7 +9816,8 @@
       <c r="AZ122" s="1"/>
       <c r="BA122" s="1"/>
       <c r="BB122" s="1"/>
-      <c r="BC122" s="1" t="str">
+      <c r="BC122" s="1"/>
+      <c r="BD122" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9416,7 +9880,8 @@
       <c r="AZ123" s="1"/>
       <c r="BA123" s="1"/>
       <c r="BB123" s="1"/>
-      <c r="BC123" s="1" t="str">
+      <c r="BC123" s="1"/>
+      <c r="BD123" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9479,7 +9944,8 @@
       <c r="AZ124" s="1"/>
       <c r="BA124" s="1"/>
       <c r="BB124" s="1"/>
-      <c r="BC124" s="1" t="str">
+      <c r="BC124" s="1"/>
+      <c r="BD124" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9542,7 +10008,8 @@
       <c r="AZ125" s="1"/>
       <c r="BA125" s="1"/>
       <c r="BB125" s="1"/>
-      <c r="BC125" s="1" t="str">
+      <c r="BC125" s="1"/>
+      <c r="BD125" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9605,7 +10072,8 @@
       <c r="AZ126" s="1"/>
       <c r="BA126" s="1"/>
       <c r="BB126" s="1"/>
-      <c r="BC126" s="1" t="str">
+      <c r="BC126" s="1"/>
+      <c r="BD126" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9668,7 +10136,8 @@
       <c r="AZ127" s="1"/>
       <c r="BA127" s="1"/>
       <c r="BB127" s="1"/>
-      <c r="BC127" s="1" t="str">
+      <c r="BC127" s="1"/>
+      <c r="BD127" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9731,7 +10200,8 @@
       <c r="AZ128" s="1"/>
       <c r="BA128" s="1"/>
       <c r="BB128" s="1"/>
-      <c r="BC128" s="1" t="str">
+      <c r="BC128" s="1"/>
+      <c r="BD128" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9794,7 +10264,8 @@
       <c r="AZ129" s="1"/>
       <c r="BA129" s="1"/>
       <c r="BB129" s="1"/>
-      <c r="BC129" s="1" t="str">
+      <c r="BC129" s="1"/>
+      <c r="BD129" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9857,7 +10328,8 @@
       <c r="AZ130" s="1"/>
       <c r="BA130" s="1"/>
       <c r="BB130" s="1"/>
-      <c r="BC130" s="1" t="str">
+      <c r="BC130" s="1"/>
+      <c r="BD130" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9920,7 +10392,8 @@
       <c r="AZ131" s="1"/>
       <c r="BA131" s="1"/>
       <c r="BB131" s="1"/>
-      <c r="BC131" s="1" t="str">
+      <c r="BC131" s="1"/>
+      <c r="BD131" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9983,7 +10456,8 @@
       <c r="AZ132" s="1"/>
       <c r="BA132" s="1"/>
       <c r="BB132" s="1"/>
-      <c r="BC132" s="1" t="str">
+      <c r="BC132" s="1"/>
+      <c r="BD132" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10046,7 +10520,8 @@
       <c r="AZ133" s="1"/>
       <c r="BA133" s="1"/>
       <c r="BB133" s="1"/>
-      <c r="BC133" s="1" t="str">
+      <c r="BC133" s="1"/>
+      <c r="BD133" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10109,7 +10584,8 @@
       <c r="AZ134" s="1"/>
       <c r="BA134" s="1"/>
       <c r="BB134" s="1"/>
-      <c r="BC134" s="1" t="str">
+      <c r="BC134" s="1"/>
+      <c r="BD134" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10172,7 +10648,8 @@
       <c r="AZ135" s="1"/>
       <c r="BA135" s="1"/>
       <c r="BB135" s="1"/>
-      <c r="BC135" s="1" t="str">
+      <c r="BC135" s="1"/>
+      <c r="BD135" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10235,7 +10712,8 @@
       <c r="AZ136" s="1"/>
       <c r="BA136" s="1"/>
       <c r="BB136" s="1"/>
-      <c r="BC136" s="1" t="str">
+      <c r="BC136" s="1"/>
+      <c r="BD136" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10298,7 +10776,8 @@
       <c r="AZ137" s="1"/>
       <c r="BA137" s="1"/>
       <c r="BB137" s="1"/>
-      <c r="BC137" s="1" t="str">
+      <c r="BC137" s="1"/>
+      <c r="BD137" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10361,7 +10840,8 @@
       <c r="AZ138" s="1"/>
       <c r="BA138" s="1"/>
       <c r="BB138" s="1"/>
-      <c r="BC138" s="1" t="str">
+      <c r="BC138" s="1"/>
+      <c r="BD138" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10424,7 +10904,8 @@
       <c r="AZ139" s="1"/>
       <c r="BA139" s="1"/>
       <c r="BB139" s="1"/>
-      <c r="BC139" s="1" t="str">
+      <c r="BC139" s="1"/>
+      <c r="BD139" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10487,7 +10968,8 @@
       <c r="AZ140" s="1"/>
       <c r="BA140" s="1"/>
       <c r="BB140" s="1"/>
-      <c r="BC140" s="1" t="str">
+      <c r="BC140" s="1"/>
+      <c r="BD140" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10550,7 +11032,8 @@
       <c r="AZ141" s="1"/>
       <c r="BA141" s="1"/>
       <c r="BB141" s="1"/>
-      <c r="BC141" s="1" t="str">
+      <c r="BC141" s="1"/>
+      <c r="BD141" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10613,7 +11096,8 @@
       <c r="AZ142" s="1"/>
       <c r="BA142" s="1"/>
       <c r="BB142" s="1"/>
-      <c r="BC142" s="1" t="str">
+      <c r="BC142" s="1"/>
+      <c r="BD142" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10676,7 +11160,8 @@
       <c r="AZ143" s="1"/>
       <c r="BA143" s="1"/>
       <c r="BB143" s="1"/>
-      <c r="BC143" s="1" t="str">
+      <c r="BC143" s="1"/>
+      <c r="BD143" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10739,7 +11224,8 @@
       <c r="AZ144" s="1"/>
       <c r="BA144" s="1"/>
       <c r="BB144" s="1"/>
-      <c r="BC144" s="1" t="str">
+      <c r="BC144" s="1"/>
+      <c r="BD144" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10802,7 +11288,8 @@
       <c r="AZ145" s="1"/>
       <c r="BA145" s="1"/>
       <c r="BB145" s="1"/>
-      <c r="BC145" s="1" t="str">
+      <c r="BC145" s="1"/>
+      <c r="BD145" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10865,7 +11352,8 @@
       <c r="AZ146" s="1"/>
       <c r="BA146" s="1"/>
       <c r="BB146" s="1"/>
-      <c r="BC146" s="1" t="str">
+      <c r="BC146" s="1"/>
+      <c r="BD146" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10928,7 +11416,8 @@
       <c r="AZ147" s="1"/>
       <c r="BA147" s="1"/>
       <c r="BB147" s="1"/>
-      <c r="BC147" s="1" t="str">
+      <c r="BC147" s="1"/>
+      <c r="BD147" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10991,7 +11480,8 @@
       <c r="AZ148" s="1"/>
       <c r="BA148" s="1"/>
       <c r="BB148" s="1"/>
-      <c r="BC148" s="1" t="str">
+      <c r="BC148" s="1"/>
+      <c r="BD148" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11054,7 +11544,8 @@
       <c r="AZ149" s="1"/>
       <c r="BA149" s="1"/>
       <c r="BB149" s="1"/>
-      <c r="BC149" s="1" t="str">
+      <c r="BC149" s="1"/>
+      <c r="BD149" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11117,7 +11608,8 @@
       <c r="AZ150" s="1"/>
       <c r="BA150" s="1"/>
       <c r="BB150" s="1"/>
-      <c r="BC150" s="1" t="str">
+      <c r="BC150" s="1"/>
+      <c r="BD150" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11180,7 +11672,8 @@
       <c r="AZ151" s="1"/>
       <c r="BA151" s="1"/>
       <c r="BB151" s="1"/>
-      <c r="BC151" s="1" t="str">
+      <c r="BC151" s="1"/>
+      <c r="BD151" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11243,7 +11736,8 @@
       <c r="AZ152" s="1"/>
       <c r="BA152" s="1"/>
       <c r="BB152" s="1"/>
-      <c r="BC152" s="1" t="str">
+      <c r="BC152" s="1"/>
+      <c r="BD152" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11306,7 +11800,8 @@
       <c r="AZ153" s="1"/>
       <c r="BA153" s="1"/>
       <c r="BB153" s="1"/>
-      <c r="BC153" s="1" t="str">
+      <c r="BC153" s="1"/>
+      <c r="BD153" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11369,7 +11864,8 @@
       <c r="AZ154" s="1"/>
       <c r="BA154" s="1"/>
       <c r="BB154" s="1"/>
-      <c r="BC154" s="1" t="str">
+      <c r="BC154" s="1"/>
+      <c r="BD154" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11432,7 +11928,8 @@
       <c r="AZ155" s="1"/>
       <c r="BA155" s="1"/>
       <c r="BB155" s="1"/>
-      <c r="BC155" s="1" t="str">
+      <c r="BC155" s="1"/>
+      <c r="BD155" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11495,7 +11992,8 @@
       <c r="AZ156" s="1"/>
       <c r="BA156" s="1"/>
       <c r="BB156" s="1"/>
-      <c r="BC156" s="1" t="str">
+      <c r="BC156" s="1"/>
+      <c r="BD156" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11558,7 +12056,8 @@
       <c r="AZ157" s="1"/>
       <c r="BA157" s="1"/>
       <c r="BB157" s="1"/>
-      <c r="BC157" s="1" t="str">
+      <c r="BC157" s="1"/>
+      <c r="BD157" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11621,7 +12120,8 @@
       <c r="AZ158" s="1"/>
       <c r="BA158" s="1"/>
       <c r="BB158" s="1"/>
-      <c r="BC158" s="1" t="str">
+      <c r="BC158" s="1"/>
+      <c r="BD158" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11684,7 +12184,8 @@
       <c r="AZ159" s="1"/>
       <c r="BA159" s="1"/>
       <c r="BB159" s="1"/>
-      <c r="BC159" s="1" t="str">
+      <c r="BC159" s="1"/>
+      <c r="BD159" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11747,7 +12248,8 @@
       <c r="AZ160" s="1"/>
       <c r="BA160" s="1"/>
       <c r="BB160" s="1"/>
-      <c r="BC160" s="1" t="str">
+      <c r="BC160" s="1"/>
+      <c r="BD160" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11810,7 +12312,8 @@
       <c r="AZ161" s="1"/>
       <c r="BA161" s="1"/>
       <c r="BB161" s="1"/>
-      <c r="BC161" s="1" t="str">
+      <c r="BC161" s="1"/>
+      <c r="BD161" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11873,7 +12376,8 @@
       <c r="AZ162" s="1"/>
       <c r="BA162" s="1"/>
       <c r="BB162" s="1"/>
-      <c r="BC162" s="1" t="str">
+      <c r="BC162" s="1"/>
+      <c r="BD162" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11936,7 +12440,8 @@
       <c r="AZ163" s="1"/>
       <c r="BA163" s="1"/>
       <c r="BB163" s="1"/>
-      <c r="BC163" s="1" t="str">
+      <c r="BC163" s="1"/>
+      <c r="BD163" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11999,7 +12504,8 @@
       <c r="AZ164" s="1"/>
       <c r="BA164" s="1"/>
       <c r="BB164" s="1"/>
-      <c r="BC164" s="1" t="str">
+      <c r="BC164" s="1"/>
+      <c r="BD164" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12062,7 +12568,8 @@
       <c r="AZ165" s="1"/>
       <c r="BA165" s="1"/>
       <c r="BB165" s="1"/>
-      <c r="BC165" s="1" t="str">
+      <c r="BC165" s="1"/>
+      <c r="BD165" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12125,7 +12632,8 @@
       <c r="AZ166" s="1"/>
       <c r="BA166" s="1"/>
       <c r="BB166" s="1"/>
-      <c r="BC166" s="1" t="str">
+      <c r="BC166" s="1"/>
+      <c r="BD166" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12188,7 +12696,8 @@
       <c r="AZ167" s="1"/>
       <c r="BA167" s="1"/>
       <c r="BB167" s="1"/>
-      <c r="BC167" s="1" t="str">
+      <c r="BC167" s="1"/>
+      <c r="BD167" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12251,7 +12760,8 @@
       <c r="AZ168" s="1"/>
       <c r="BA168" s="1"/>
       <c r="BB168" s="1"/>
-      <c r="BC168" s="1" t="str">
+      <c r="BC168" s="1"/>
+      <c r="BD168" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12314,7 +12824,8 @@
       <c r="AZ169" s="1"/>
       <c r="BA169" s="1"/>
       <c r="BB169" s="1"/>
-      <c r="BC169" s="1" t="str">
+      <c r="BC169" s="1"/>
+      <c r="BD169" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12377,7 +12888,8 @@
       <c r="AZ170" s="1"/>
       <c r="BA170" s="1"/>
       <c r="BB170" s="1"/>
-      <c r="BC170" s="1" t="str">
+      <c r="BC170" s="1"/>
+      <c r="BD170" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12440,7 +12952,8 @@
       <c r="AZ171" s="1"/>
       <c r="BA171" s="1"/>
       <c r="BB171" s="1"/>
-      <c r="BC171" s="1" t="str">
+      <c r="BC171" s="1"/>
+      <c r="BD171" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12503,7 +13016,8 @@
       <c r="AZ172" s="1"/>
       <c r="BA172" s="1"/>
       <c r="BB172" s="1"/>
-      <c r="BC172" s="1" t="str">
+      <c r="BC172" s="1"/>
+      <c r="BD172" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12566,7 +13080,8 @@
       <c r="AZ173" s="1"/>
       <c r="BA173" s="1"/>
       <c r="BB173" s="1"/>
-      <c r="BC173" s="1" t="str">
+      <c r="BC173" s="1"/>
+      <c r="BD173" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12629,7 +13144,8 @@
       <c r="AZ174" s="1"/>
       <c r="BA174" s="1"/>
       <c r="BB174" s="1"/>
-      <c r="BC174" s="1" t="str">
+      <c r="BC174" s="1"/>
+      <c r="BD174" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12692,7 +13208,8 @@
       <c r="AZ175" s="1"/>
       <c r="BA175" s="1"/>
       <c r="BB175" s="1"/>
-      <c r="BC175" s="1" t="str">
+      <c r="BC175" s="1"/>
+      <c r="BD175" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12755,7 +13272,8 @@
       <c r="AZ176" s="1"/>
       <c r="BA176" s="1"/>
       <c r="BB176" s="1"/>
-      <c r="BC176" s="1" t="str">
+      <c r="BC176" s="1"/>
+      <c r="BD176" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12818,7 +13336,8 @@
       <c r="AZ177" s="1"/>
       <c r="BA177" s="1"/>
       <c r="BB177" s="1"/>
-      <c r="BC177" s="1" t="str">
+      <c r="BC177" s="1"/>
+      <c r="BD177" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12881,7 +13400,8 @@
       <c r="AZ178" s="1"/>
       <c r="BA178" s="1"/>
       <c r="BB178" s="1"/>
-      <c r="BC178" s="1" t="str">
+      <c r="BC178" s="1"/>
+      <c r="BD178" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12944,7 +13464,8 @@
       <c r="AZ179" s="1"/>
       <c r="BA179" s="1"/>
       <c r="BB179" s="1"/>
-      <c r="BC179" s="1" t="str">
+      <c r="BC179" s="1"/>
+      <c r="BD179" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13007,7 +13528,8 @@
       <c r="AZ180" s="1"/>
       <c r="BA180" s="1"/>
       <c r="BB180" s="1"/>
-      <c r="BC180" s="1" t="str">
+      <c r="BC180" s="1"/>
+      <c r="BD180" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13070,7 +13592,8 @@
       <c r="AZ181" s="1"/>
       <c r="BA181" s="1"/>
       <c r="BB181" s="1"/>
-      <c r="BC181" s="1" t="str">
+      <c r="BC181" s="1"/>
+      <c r="BD181" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13133,7 +13656,8 @@
       <c r="AZ182" s="1"/>
       <c r="BA182" s="1"/>
       <c r="BB182" s="1"/>
-      <c r="BC182" s="1" t="str">
+      <c r="BC182" s="1"/>
+      <c r="BD182" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13196,7 +13720,8 @@
       <c r="AZ183" s="1"/>
       <c r="BA183" s="1"/>
       <c r="BB183" s="1"/>
-      <c r="BC183" s="1" t="str">
+      <c r="BC183" s="1"/>
+      <c r="BD183" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13259,7 +13784,8 @@
       <c r="AZ184" s="1"/>
       <c r="BA184" s="1"/>
       <c r="BB184" s="1"/>
-      <c r="BC184" s="1" t="str">
+      <c r="BC184" s="1"/>
+      <c r="BD184" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13322,7 +13848,8 @@
       <c r="AZ185" s="1"/>
       <c r="BA185" s="1"/>
       <c r="BB185" s="1"/>
-      <c r="BC185" s="1" t="str">
+      <c r="BC185" s="1"/>
+      <c r="BD185" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13385,7 +13912,8 @@
       <c r="AZ186" s="1"/>
       <c r="BA186" s="1"/>
       <c r="BB186" s="1"/>
-      <c r="BC186" s="1" t="str">
+      <c r="BC186" s="1"/>
+      <c r="BD186" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13448,7 +13976,8 @@
       <c r="AZ187" s="1"/>
       <c r="BA187" s="1"/>
       <c r="BB187" s="1"/>
-      <c r="BC187" s="1" t="str">
+      <c r="BC187" s="1"/>
+      <c r="BD187" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13511,7 +14040,8 @@
       <c r="AZ188" s="1"/>
       <c r="BA188" s="1"/>
       <c r="BB188" s="1"/>
-      <c r="BC188" s="1" t="str">
+      <c r="BC188" s="1"/>
+      <c r="BD188" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13574,7 +14104,8 @@
       <c r="AZ189" s="1"/>
       <c r="BA189" s="1"/>
       <c r="BB189" s="1"/>
-      <c r="BC189" s="1" t="str">
+      <c r="BC189" s="1"/>
+      <c r="BD189" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13637,7 +14168,8 @@
       <c r="AZ190" s="1"/>
       <c r="BA190" s="1"/>
       <c r="BB190" s="1"/>
-      <c r="BC190" s="1" t="str">
+      <c r="BC190" s="1"/>
+      <c r="BD190" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13700,7 +14232,8 @@
       <c r="AZ191" s="1"/>
       <c r="BA191" s="1"/>
       <c r="BB191" s="1"/>
-      <c r="BC191" s="1" t="str">
+      <c r="BC191" s="1"/>
+      <c r="BD191" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13763,7 +14296,8 @@
       <c r="AZ192" s="1"/>
       <c r="BA192" s="1"/>
       <c r="BB192" s="1"/>
-      <c r="BC192" s="1" t="str">
+      <c r="BC192" s="1"/>
+      <c r="BD192" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13826,7 +14360,8 @@
       <c r="AZ193" s="1"/>
       <c r="BA193" s="1"/>
       <c r="BB193" s="1"/>
-      <c r="BC193" s="1" t="str">
+      <c r="BC193" s="1"/>
+      <c r="BD193" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13889,7 +14424,8 @@
       <c r="AZ194" s="1"/>
       <c r="BA194" s="1"/>
       <c r="BB194" s="1"/>
-      <c r="BC194" s="1" t="str">
+      <c r="BC194" s="1"/>
+      <c r="BD194" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13952,7 +14488,8 @@
       <c r="AZ195" s="1"/>
       <c r="BA195" s="1"/>
       <c r="BB195" s="1"/>
-      <c r="BC195" s="1" t="str">
+      <c r="BC195" s="1"/>
+      <c r="BD195" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14015,7 +14552,8 @@
       <c r="AZ196" s="1"/>
       <c r="BA196" s="1"/>
       <c r="BB196" s="1"/>
-      <c r="BC196" s="1" t="str">
+      <c r="BC196" s="1"/>
+      <c r="BD196" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14078,7 +14616,8 @@
       <c r="AZ197" s="1"/>
       <c r="BA197" s="1"/>
       <c r="BB197" s="1"/>
-      <c r="BC197" s="1" t="str">
+      <c r="BC197" s="1"/>
+      <c r="BD197" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14141,7 +14680,8 @@
       <c r="AZ198" s="1"/>
       <c r="BA198" s="1"/>
       <c r="BB198" s="1"/>
-      <c r="BC198" s="1" t="str">
+      <c r="BC198" s="1"/>
+      <c r="BD198" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14204,7 +14744,8 @@
       <c r="AZ199" s="1"/>
       <c r="BA199" s="1"/>
       <c r="BB199" s="1"/>
-      <c r="BC199" s="1" t="str">
+      <c r="BC199" s="1"/>
+      <c r="BD199" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14267,7 +14808,8 @@
       <c r="AZ200" s="1"/>
       <c r="BA200" s="1"/>
       <c r="BB200" s="1"/>
-      <c r="BC200" s="1" t="str">
+      <c r="BC200" s="1"/>
+      <c r="BD200" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14330,7 +14872,8 @@
       <c r="AZ201" s="1"/>
       <c r="BA201" s="1"/>
       <c r="BB201" s="1"/>
-      <c r="BC201" s="1" t="str">
+      <c r="BC201" s="1"/>
+      <c r="BD201" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14393,7 +14936,8 @@
       <c r="AZ202" s="1"/>
       <c r="BA202" s="1"/>
       <c r="BB202" s="1"/>
-      <c r="BC202" s="1" t="str">
+      <c r="BC202" s="1"/>
+      <c r="BD202" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14456,7 +15000,8 @@
       <c r="AZ203" s="1"/>
       <c r="BA203" s="1"/>
       <c r="BB203" s="1"/>
-      <c r="BC203" s="1" t="str">
+      <c r="BC203" s="1"/>
+      <c r="BD203" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14519,7 +15064,8 @@
       <c r="AZ204" s="1"/>
       <c r="BA204" s="1"/>
       <c r="BB204" s="1"/>
-      <c r="BC204" s="1" t="str">
+      <c r="BC204" s="1"/>
+      <c r="BD204" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14582,7 +15128,8 @@
       <c r="AZ205" s="1"/>
       <c r="BA205" s="1"/>
       <c r="BB205" s="1"/>
-      <c r="BC205" s="1" t="str">
+      <c r="BC205" s="1"/>
+      <c r="BD205" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14645,7 +15192,8 @@
       <c r="AZ206" s="1"/>
       <c r="BA206" s="1"/>
       <c r="BB206" s="1"/>
-      <c r="BC206" s="1" t="str">
+      <c r="BC206" s="1"/>
+      <c r="BD206" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14708,7 +15256,8 @@
       <c r="AZ207" s="1"/>
       <c r="BA207" s="1"/>
       <c r="BB207" s="1"/>
-      <c r="BC207" s="1" t="str">
+      <c r="BC207" s="1"/>
+      <c r="BD207" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14771,7 +15320,8 @@
       <c r="AZ208" s="1"/>
       <c r="BA208" s="1"/>
       <c r="BB208" s="1"/>
-      <c r="BC208" s="1" t="str">
+      <c r="BC208" s="1"/>
+      <c r="BD208" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14834,7 +15384,8 @@
       <c r="AZ209" s="1"/>
       <c r="BA209" s="1"/>
       <c r="BB209" s="1"/>
-      <c r="BC209" s="1" t="str">
+      <c r="BC209" s="1"/>
+      <c r="BD209" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14897,7 +15448,8 @@
       <c r="AZ210" s="1"/>
       <c r="BA210" s="1"/>
       <c r="BB210" s="1"/>
-      <c r="BC210" s="1" t="str">
+      <c r="BC210" s="1"/>
+      <c r="BD210" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14960,7 +15512,8 @@
       <c r="AZ211" s="1"/>
       <c r="BA211" s="1"/>
       <c r="BB211" s="1"/>
-      <c r="BC211" s="1" t="str">
+      <c r="BC211" s="1"/>
+      <c r="BD211" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15023,7 +15576,8 @@
       <c r="AZ212" s="1"/>
       <c r="BA212" s="1"/>
       <c r="BB212" s="1"/>
-      <c r="BC212" s="1" t="str">
+      <c r="BC212" s="1"/>
+      <c r="BD212" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15086,7 +15640,8 @@
       <c r="AZ213" s="1"/>
       <c r="BA213" s="1"/>
       <c r="BB213" s="1"/>
-      <c r="BC213" s="1" t="str">
+      <c r="BC213" s="1"/>
+      <c r="BD213" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15149,7 +15704,8 @@
       <c r="AZ214" s="1"/>
       <c r="BA214" s="1"/>
       <c r="BB214" s="1"/>
-      <c r="BC214" s="1" t="str">
+      <c r="BC214" s="1"/>
+      <c r="BD214" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15212,7 +15768,8 @@
       <c r="AZ215" s="1"/>
       <c r="BA215" s="1"/>
       <c r="BB215" s="1"/>
-      <c r="BC215" s="1" t="str">
+      <c r="BC215" s="1"/>
+      <c r="BD215" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15275,7 +15832,8 @@
       <c r="AZ216" s="1"/>
       <c r="BA216" s="1"/>
       <c r="BB216" s="1"/>
-      <c r="BC216" s="1" t="str">
+      <c r="BC216" s="1"/>
+      <c r="BD216" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15338,7 +15896,8 @@
       <c r="AZ217" s="1"/>
       <c r="BA217" s="1"/>
       <c r="BB217" s="1"/>
-      <c r="BC217" s="1" t="str">
+      <c r="BC217" s="1"/>
+      <c r="BD217" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15401,7 +15960,8 @@
       <c r="AZ218" s="1"/>
       <c r="BA218" s="1"/>
       <c r="BB218" s="1"/>
-      <c r="BC218" s="1" t="str">
+      <c r="BC218" s="1"/>
+      <c r="BD218" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15464,7 +16024,8 @@
       <c r="AZ219" s="1"/>
       <c r="BA219" s="1"/>
       <c r="BB219" s="1"/>
-      <c r="BC219" s="1" t="str">
+      <c r="BC219" s="1"/>
+      <c r="BD219" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15527,7 +16088,8 @@
       <c r="AZ220" s="1"/>
       <c r="BA220" s="1"/>
       <c r="BB220" s="1"/>
-      <c r="BC220" s="1" t="str">
+      <c r="BC220" s="1"/>
+      <c r="BD220" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15590,7 +16152,8 @@
       <c r="AZ221" s="1"/>
       <c r="BA221" s="1"/>
       <c r="BB221" s="1"/>
-      <c r="BC221" s="1" t="str">
+      <c r="BC221" s="1"/>
+      <c r="BD221" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15653,7 +16216,8 @@
       <c r="AZ222" s="1"/>
       <c r="BA222" s="1"/>
       <c r="BB222" s="1"/>
-      <c r="BC222" s="1" t="str">
+      <c r="BC222" s="1"/>
+      <c r="BD222" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15716,7 +16280,8 @@
       <c r="AZ223" s="1"/>
       <c r="BA223" s="1"/>
       <c r="BB223" s="1"/>
-      <c r="BC223" s="1" t="str">
+      <c r="BC223" s="1"/>
+      <c r="BD223" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15779,7 +16344,8 @@
       <c r="AZ224" s="1"/>
       <c r="BA224" s="1"/>
       <c r="BB224" s="1"/>
-      <c r="BC224" s="1" t="str">
+      <c r="BC224" s="1"/>
+      <c r="BD224" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15842,7 +16408,8 @@
       <c r="AZ225" s="1"/>
       <c r="BA225" s="1"/>
       <c r="BB225" s="1"/>
-      <c r="BC225" s="1" t="str">
+      <c r="BC225" s="1"/>
+      <c r="BD225" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15905,7 +16472,8 @@
       <c r="AZ226" s="1"/>
       <c r="BA226" s="1"/>
       <c r="BB226" s="1"/>
-      <c r="BC226" s="1" t="str">
+      <c r="BC226" s="1"/>
+      <c r="BD226" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15968,7 +16536,8 @@
       <c r="AZ227" s="1"/>
       <c r="BA227" s="1"/>
       <c r="BB227" s="1"/>
-      <c r="BC227" s="1" t="str">
+      <c r="BC227" s="1"/>
+      <c r="BD227" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16031,7 +16600,8 @@
       <c r="AZ228" s="1"/>
       <c r="BA228" s="1"/>
       <c r="BB228" s="1"/>
-      <c r="BC228" s="1" t="str">
+      <c r="BC228" s="1"/>
+      <c r="BD228" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16094,7 +16664,8 @@
       <c r="AZ229" s="1"/>
       <c r="BA229" s="1"/>
       <c r="BB229" s="1"/>
-      <c r="BC229" s="1" t="str">
+      <c r="BC229" s="1"/>
+      <c r="BD229" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16157,7 +16728,8 @@
       <c r="AZ230" s="1"/>
       <c r="BA230" s="1"/>
       <c r="BB230" s="1"/>
-      <c r="BC230" s="1" t="str">
+      <c r="BC230" s="1"/>
+      <c r="BD230" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16220,7 +16792,8 @@
       <c r="AZ231" s="1"/>
       <c r="BA231" s="1"/>
       <c r="BB231" s="1"/>
-      <c r="BC231" s="1" t="str">
+      <c r="BC231" s="1"/>
+      <c r="BD231" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16283,7 +16856,8 @@
       <c r="AZ232" s="1"/>
       <c r="BA232" s="1"/>
       <c r="BB232" s="1"/>
-      <c r="BC232" s="1" t="str">
+      <c r="BC232" s="1"/>
+      <c r="BD232" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16346,7 +16920,8 @@
       <c r="AZ233" s="1"/>
       <c r="BA233" s="1"/>
       <c r="BB233" s="1"/>
-      <c r="BC233" s="1" t="str">
+      <c r="BC233" s="1"/>
+      <c r="BD233" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16409,7 +16984,8 @@
       <c r="AZ234" s="1"/>
       <c r="BA234" s="1"/>
       <c r="BB234" s="1"/>
-      <c r="BC234" s="1" t="str">
+      <c r="BC234" s="1"/>
+      <c r="BD234" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16472,7 +17048,8 @@
       <c r="AZ235" s="1"/>
       <c r="BA235" s="1"/>
       <c r="BB235" s="1"/>
-      <c r="BC235" s="1" t="str">
+      <c r="BC235" s="1"/>
+      <c r="BD235" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16535,7 +17112,8 @@
       <c r="AZ236" s="1"/>
       <c r="BA236" s="1"/>
       <c r="BB236" s="1"/>
-      <c r="BC236" s="1" t="str">
+      <c r="BC236" s="1"/>
+      <c r="BD236" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16598,7 +17176,8 @@
       <c r="AZ237" s="1"/>
       <c r="BA237" s="1"/>
       <c r="BB237" s="1"/>
-      <c r="BC237" s="1" t="str">
+      <c r="BC237" s="1"/>
+      <c r="BD237" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16661,7 +17240,8 @@
       <c r="AZ238" s="1"/>
       <c r="BA238" s="1"/>
       <c r="BB238" s="1"/>
-      <c r="BC238" s="1" t="str">
+      <c r="BC238" s="1"/>
+      <c r="BD238" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16724,7 +17304,8 @@
       <c r="AZ239" s="1"/>
       <c r="BA239" s="1"/>
       <c r="BB239" s="1"/>
-      <c r="BC239" s="1" t="str">
+      <c r="BC239" s="1"/>
+      <c r="BD239" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16787,7 +17368,8 @@
       <c r="AZ240" s="1"/>
       <c r="BA240" s="1"/>
       <c r="BB240" s="1"/>
-      <c r="BC240" s="1" t="str">
+      <c r="BC240" s="1"/>
+      <c r="BD240" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16850,7 +17432,8 @@
       <c r="AZ241" s="1"/>
       <c r="BA241" s="1"/>
       <c r="BB241" s="1"/>
-      <c r="BC241" s="1" t="str">
+      <c r="BC241" s="1"/>
+      <c r="BD241" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16913,7 +17496,8 @@
       <c r="AZ242" s="1"/>
       <c r="BA242" s="1"/>
       <c r="BB242" s="1"/>
-      <c r="BC242" s="1" t="str">
+      <c r="BC242" s="1"/>
+      <c r="BD242" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16976,7 +17560,8 @@
       <c r="AZ243" s="1"/>
       <c r="BA243" s="1"/>
       <c r="BB243" s="1"/>
-      <c r="BC243" s="1" t="str">
+      <c r="BC243" s="1"/>
+      <c r="BD243" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17039,7 +17624,8 @@
       <c r="AZ244" s="1"/>
       <c r="BA244" s="1"/>
       <c r="BB244" s="1"/>
-      <c r="BC244" s="1" t="str">
+      <c r="BC244" s="1"/>
+      <c r="BD244" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17102,7 +17688,8 @@
       <c r="AZ245" s="1"/>
       <c r="BA245" s="1"/>
       <c r="BB245" s="1"/>
-      <c r="BC245" s="1" t="str">
+      <c r="BC245" s="1"/>
+      <c r="BD245" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17165,7 +17752,8 @@
       <c r="AZ246" s="1"/>
       <c r="BA246" s="1"/>
       <c r="BB246" s="1"/>
-      <c r="BC246" s="1" t="str">
+      <c r="BC246" s="1"/>
+      <c r="BD246" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17228,7 +17816,8 @@
       <c r="AZ247" s="1"/>
       <c r="BA247" s="1"/>
       <c r="BB247" s="1"/>
-      <c r="BC247" s="1" t="str">
+      <c r="BC247" s="1"/>
+      <c r="BD247" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17291,7 +17880,8 @@
       <c r="AZ248" s="1"/>
       <c r="BA248" s="1"/>
       <c r="BB248" s="1"/>
-      <c r="BC248" s="1" t="str">
+      <c r="BC248" s="1"/>
+      <c r="BD248" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17354,7 +17944,8 @@
       <c r="AZ249" s="1"/>
       <c r="BA249" s="1"/>
       <c r="BB249" s="1"/>
-      <c r="BC249" s="1" t="str">
+      <c r="BC249" s="1"/>
+      <c r="BD249" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17417,7 +18008,8 @@
       <c r="AZ250" s="1"/>
       <c r="BA250" s="1"/>
       <c r="BB250" s="1"/>
-      <c r="BC250" s="1" t="str">
+      <c r="BC250" s="1"/>
+      <c r="BD250" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17480,7 +18072,8 @@
       <c r="AZ251" s="1"/>
       <c r="BA251" s="1"/>
       <c r="BB251" s="1"/>
-      <c r="BC251" s="1" t="str">
+      <c r="BC251" s="1"/>
+      <c r="BD251" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17543,7 +18136,8 @@
       <c r="AZ252" s="1"/>
       <c r="BA252" s="1"/>
       <c r="BB252" s="1"/>
-      <c r="BC252" s="1" t="str">
+      <c r="BC252" s="1"/>
+      <c r="BD252" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17606,7 +18200,8 @@
       <c r="AZ253" s="1"/>
       <c r="BA253" s="1"/>
       <c r="BB253" s="1"/>
-      <c r="BC253" s="1" t="str">
+      <c r="BC253" s="1"/>
+      <c r="BD253" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17669,7 +18264,8 @@
       <c r="AZ254" s="1"/>
       <c r="BA254" s="1"/>
       <c r="BB254" s="1"/>
-      <c r="BC254" s="1" t="str">
+      <c r="BC254" s="1"/>
+      <c r="BD254" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17732,7 +18328,8 @@
       <c r="AZ255" s="1"/>
       <c r="BA255" s="1"/>
       <c r="BB255" s="1"/>
-      <c r="BC255" s="1" t="str">
+      <c r="BC255" s="1"/>
+      <c r="BD255" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17795,7 +18392,8 @@
       <c r="AZ256" s="1"/>
       <c r="BA256" s="1"/>
       <c r="BB256" s="1"/>
-      <c r="BC256" s="1" t="str">
+      <c r="BC256" s="1"/>
+      <c r="BD256" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17858,7 +18456,8 @@
       <c r="AZ257" s="1"/>
       <c r="BA257" s="1"/>
       <c r="BB257" s="1"/>
-      <c r="BC257" s="1" t="str">
+      <c r="BC257" s="1"/>
+      <c r="BD257" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17921,7 +18520,8 @@
       <c r="AZ258" s="1"/>
       <c r="BA258" s="1"/>
       <c r="BB258" s="1"/>
-      <c r="BC258" s="1" t="str">
+      <c r="BC258" s="1"/>
+      <c r="BD258" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17984,7 +18584,8 @@
       <c r="AZ259" s="1"/>
       <c r="BA259" s="1"/>
       <c r="BB259" s="1"/>
-      <c r="BC259" s="1" t="str">
+      <c r="BC259" s="1"/>
+      <c r="BD259" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18047,7 +18648,8 @@
       <c r="AZ260" s="1"/>
       <c r="BA260" s="1"/>
       <c r="BB260" s="1"/>
-      <c r="BC260" s="1" t="str">
+      <c r="BC260" s="1"/>
+      <c r="BD260" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18110,7 +18712,8 @@
       <c r="AZ261" s="1"/>
       <c r="BA261" s="1"/>
       <c r="BB261" s="1"/>
-      <c r="BC261" s="1" t="str">
+      <c r="BC261" s="1"/>
+      <c r="BD261" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18173,7 +18776,8 @@
       <c r="AZ262" s="1"/>
       <c r="BA262" s="1"/>
       <c r="BB262" s="1"/>
-      <c r="BC262" s="1" t="str">
+      <c r="BC262" s="1"/>
+      <c r="BD262" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18236,7 +18840,8 @@
       <c r="AZ263" s="1"/>
       <c r="BA263" s="1"/>
       <c r="BB263" s="1"/>
-      <c r="BC263" s="1" t="str">
+      <c r="BC263" s="1"/>
+      <c r="BD263" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18299,7 +18904,8 @@
       <c r="AZ264" s="1"/>
       <c r="BA264" s="1"/>
       <c r="BB264" s="1"/>
-      <c r="BC264" s="1" t="str">
+      <c r="BC264" s="1"/>
+      <c r="BD264" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18362,7 +18968,8 @@
       <c r="AZ265" s="1"/>
       <c r="BA265" s="1"/>
       <c r="BB265" s="1"/>
-      <c r="BC265" s="1" t="str">
+      <c r="BC265" s="1"/>
+      <c r="BD265" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18425,7 +19032,8 @@
       <c r="AZ266" s="1"/>
       <c r="BA266" s="1"/>
       <c r="BB266" s="1"/>
-      <c r="BC266" s="1" t="str">
+      <c r="BC266" s="1"/>
+      <c r="BD266" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18488,7 +19096,8 @@
       <c r="AZ267" s="1"/>
       <c r="BA267" s="1"/>
       <c r="BB267" s="1"/>
-      <c r="BC267" s="1" t="str">
+      <c r="BC267" s="1"/>
+      <c r="BD267" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18551,7 +19160,8 @@
       <c r="AZ268" s="1"/>
       <c r="BA268" s="1"/>
       <c r="BB268" s="1"/>
-      <c r="BC268" s="1" t="str">
+      <c r="BC268" s="1"/>
+      <c r="BD268" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18614,7 +19224,8 @@
       <c r="AZ269" s="1"/>
       <c r="BA269" s="1"/>
       <c r="BB269" s="1"/>
-      <c r="BC269" s="1" t="str">
+      <c r="BC269" s="1"/>
+      <c r="BD269" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18677,7 +19288,8 @@
       <c r="AZ270" s="1"/>
       <c r="BA270" s="1"/>
       <c r="BB270" s="1"/>
-      <c r="BC270" s="1" t="str">
+      <c r="BC270" s="1"/>
+      <c r="BD270" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18740,7 +19352,8 @@
       <c r="AZ271" s="1"/>
       <c r="BA271" s="1"/>
       <c r="BB271" s="1"/>
-      <c r="BC271" s="1" t="str">
+      <c r="BC271" s="1"/>
+      <c r="BD271" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18803,7 +19416,8 @@
       <c r="AZ272" s="1"/>
       <c r="BA272" s="1"/>
       <c r="BB272" s="1"/>
-      <c r="BC272" s="1" t="str">
+      <c r="BC272" s="1"/>
+      <c r="BD272" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18866,7 +19480,8 @@
       <c r="AZ273" s="1"/>
       <c r="BA273" s="1"/>
       <c r="BB273" s="1"/>
-      <c r="BC273" s="1" t="str">
+      <c r="BC273" s="1"/>
+      <c r="BD273" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18929,7 +19544,8 @@
       <c r="AZ274" s="1"/>
       <c r="BA274" s="1"/>
       <c r="BB274" s="1"/>
-      <c r="BC274" s="1" t="str">
+      <c r="BC274" s="1"/>
+      <c r="BD274" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18992,7 +19608,8 @@
       <c r="AZ275" s="1"/>
       <c r="BA275" s="1"/>
       <c r="BB275" s="1"/>
-      <c r="BC275" s="1" t="str">
+      <c r="BC275" s="1"/>
+      <c r="BD275" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19055,7 +19672,8 @@
       <c r="AZ276" s="1"/>
       <c r="BA276" s="1"/>
       <c r="BB276" s="1"/>
-      <c r="BC276" s="1" t="str">
+      <c r="BC276" s="1"/>
+      <c r="BD276" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19118,7 +19736,8 @@
       <c r="AZ277" s="1"/>
       <c r="BA277" s="1"/>
       <c r="BB277" s="1"/>
-      <c r="BC277" s="1" t="str">
+      <c r="BC277" s="1"/>
+      <c r="BD277" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19181,7 +19800,8 @@
       <c r="AZ278" s="1"/>
       <c r="BA278" s="1"/>
       <c r="BB278" s="1"/>
-      <c r="BC278" s="1" t="str">
+      <c r="BC278" s="1"/>
+      <c r="BD278" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19244,7 +19864,8 @@
       <c r="AZ279" s="1"/>
       <c r="BA279" s="1"/>
       <c r="BB279" s="1"/>
-      <c r="BC279" s="1" t="str">
+      <c r="BC279" s="1"/>
+      <c r="BD279" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19307,7 +19928,8 @@
       <c r="AZ280" s="1"/>
       <c r="BA280" s="1"/>
       <c r="BB280" s="1"/>
-      <c r="BC280" s="1" t="str">
+      <c r="BC280" s="1"/>
+      <c r="BD280" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19370,7 +19992,8 @@
       <c r="AZ281" s="1"/>
       <c r="BA281" s="1"/>
       <c r="BB281" s="1"/>
-      <c r="BC281" s="1" t="str">
+      <c r="BC281" s="1"/>
+      <c r="BD281" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19433,7 +20056,8 @@
       <c r="AZ282" s="1"/>
       <c r="BA282" s="1"/>
       <c r="BB282" s="1"/>
-      <c r="BC282" s="1" t="str">
+      <c r="BC282" s="1"/>
+      <c r="BD282" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19496,7 +20120,8 @@
       <c r="AZ283" s="1"/>
       <c r="BA283" s="1"/>
       <c r="BB283" s="1"/>
-      <c r="BC283" s="1" t="str">
+      <c r="BC283" s="1"/>
+      <c r="BD283" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19559,7 +20184,8 @@
       <c r="AZ284" s="1"/>
       <c r="BA284" s="1"/>
       <c r="BB284" s="1"/>
-      <c r="BC284" s="1" t="str">
+      <c r="BC284" s="1"/>
+      <c r="BD284" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19622,7 +20248,8 @@
       <c r="AZ285" s="1"/>
       <c r="BA285" s="1"/>
       <c r="BB285" s="1"/>
-      <c r="BC285" s="1" t="str">
+      <c r="BC285" s="1"/>
+      <c r="BD285" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19685,7 +20312,8 @@
       <c r="AZ286" s="1"/>
       <c r="BA286" s="1"/>
       <c r="BB286" s="1"/>
-      <c r="BC286" s="1" t="str">
+      <c r="BC286" s="1"/>
+      <c r="BD286" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19748,7 +20376,8 @@
       <c r="AZ287" s="1"/>
       <c r="BA287" s="1"/>
       <c r="BB287" s="1"/>
-      <c r="BC287" s="1" t="str">
+      <c r="BC287" s="1"/>
+      <c r="BD287" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19811,7 +20440,8 @@
       <c r="AZ288" s="1"/>
       <c r="BA288" s="1"/>
       <c r="BB288" s="1"/>
-      <c r="BC288" s="1" t="str">
+      <c r="BC288" s="1"/>
+      <c r="BD288" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19874,7 +20504,8 @@
       <c r="AZ289" s="1"/>
       <c r="BA289" s="1"/>
       <c r="BB289" s="1"/>
-      <c r="BC289" s="1" t="str">
+      <c r="BC289" s="1"/>
+      <c r="BD289" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19937,7 +20568,8 @@
       <c r="AZ290" s="1"/>
       <c r="BA290" s="1"/>
       <c r="BB290" s="1"/>
-      <c r="BC290" s="1" t="str">
+      <c r="BC290" s="1"/>
+      <c r="BD290" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20000,7 +20632,8 @@
       <c r="AZ291" s="1"/>
       <c r="BA291" s="1"/>
       <c r="BB291" s="1"/>
-      <c r="BC291" s="1" t="str">
+      <c r="BC291" s="1"/>
+      <c r="BD291" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20063,7 +20696,8 @@
       <c r="AZ292" s="1"/>
       <c r="BA292" s="1"/>
       <c r="BB292" s="1"/>
-      <c r="BC292" s="1" t="str">
+      <c r="BC292" s="1"/>
+      <c r="BD292" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20126,7 +20760,8 @@
       <c r="AZ293" s="1"/>
       <c r="BA293" s="1"/>
       <c r="BB293" s="1"/>
-      <c r="BC293" s="1" t="str">
+      <c r="BC293" s="1"/>
+      <c r="BD293" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20189,7 +20824,8 @@
       <c r="AZ294" s="1"/>
       <c r="BA294" s="1"/>
       <c r="BB294" s="1"/>
-      <c r="BC294" s="1" t="str">
+      <c r="BC294" s="1"/>
+      <c r="BD294" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20252,7 +20888,8 @@
       <c r="AZ295" s="1"/>
       <c r="BA295" s="1"/>
       <c r="BB295" s="1"/>
-      <c r="BC295" s="1" t="str">
+      <c r="BC295" s="1"/>
+      <c r="BD295" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20315,7 +20952,8 @@
       <c r="AZ296" s="1"/>
       <c r="BA296" s="1"/>
       <c r="BB296" s="1"/>
-      <c r="BC296" s="1" t="str">
+      <c r="BC296" s="1"/>
+      <c r="BD296" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20378,7 +21016,8 @@
       <c r="AZ297" s="1"/>
       <c r="BA297" s="1"/>
       <c r="BB297" s="1"/>
-      <c r="BC297" s="1" t="str">
+      <c r="BC297" s="1"/>
+      <c r="BD297" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20441,7 +21080,8 @@
       <c r="AZ298" s="1"/>
       <c r="BA298" s="1"/>
       <c r="BB298" s="1"/>
-      <c r="BC298" s="1" t="str">
+      <c r="BC298" s="1"/>
+      <c r="BD298" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20504,7 +21144,8 @@
       <c r="AZ299" s="1"/>
       <c r="BA299" s="1"/>
       <c r="BB299" s="1"/>
-      <c r="BC299" s="1" t="str">
+      <c r="BC299" s="1"/>
+      <c r="BD299" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20567,7 +21208,8 @@
       <c r="AZ300" s="1"/>
       <c r="BA300" s="1"/>
       <c r="BB300" s="1"/>
-      <c r="BC300" s="1" t="str">
+      <c r="BC300" s="1"/>
+      <c r="BD300" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20630,7 +21272,8 @@
       <c r="AZ301" s="1"/>
       <c r="BA301" s="1"/>
       <c r="BB301" s="1"/>
-      <c r="BC301" s="1" t="str">
+      <c r="BC301" s="1"/>
+      <c r="BD301" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20693,7 +21336,8 @@
       <c r="AZ302" s="1"/>
       <c r="BA302" s="1"/>
       <c r="BB302" s="1"/>
-      <c r="BC302" s="1" t="str">
+      <c r="BC302" s="1"/>
+      <c r="BD302" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20756,7 +21400,8 @@
       <c r="AZ303" s="1"/>
       <c r="BA303" s="1"/>
       <c r="BB303" s="1"/>
-      <c r="BC303" s="1" t="str">
+      <c r="BC303" s="1"/>
+      <c r="BD303" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20819,7 +21464,8 @@
       <c r="AZ304" s="1"/>
       <c r="BA304" s="1"/>
       <c r="BB304" s="1"/>
-      <c r="BC304" s="1" t="str">
+      <c r="BC304" s="1"/>
+      <c r="BD304" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20882,7 +21528,8 @@
       <c r="AZ305" s="1"/>
       <c r="BA305" s="1"/>
       <c r="BB305" s="1"/>
-      <c r="BC305" s="1" t="str">
+      <c r="BC305" s="1"/>
+      <c r="BD305" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20945,7 +21592,8 @@
       <c r="AZ306" s="1"/>
       <c r="BA306" s="1"/>
       <c r="BB306" s="1"/>
-      <c r="BC306" s="1" t="str">
+      <c r="BC306" s="1"/>
+      <c r="BD306" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21008,7 +21656,8 @@
       <c r="AZ307" s="1"/>
       <c r="BA307" s="1"/>
       <c r="BB307" s="1"/>
-      <c r="BC307" s="1" t="str">
+      <c r="BC307" s="1"/>
+      <c r="BD307" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21071,7 +21720,8 @@
       <c r="AZ308" s="1"/>
       <c r="BA308" s="1"/>
       <c r="BB308" s="1"/>
-      <c r="BC308" s="1" t="str">
+      <c r="BC308" s="1"/>
+      <c r="BD308" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21134,7 +21784,8 @@
       <c r="AZ309" s="1"/>
       <c r="BA309" s="1"/>
       <c r="BB309" s="1"/>
-      <c r="BC309" s="1" t="str">
+      <c r="BC309" s="1"/>
+      <c r="BD309" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21197,7 +21848,8 @@
       <c r="AZ310" s="1"/>
       <c r="BA310" s="1"/>
       <c r="BB310" s="1"/>
-      <c r="BC310" s="1" t="str">
+      <c r="BC310" s="1"/>
+      <c r="BD310" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21260,7 +21912,8 @@
       <c r="AZ311" s="1"/>
       <c r="BA311" s="1"/>
       <c r="BB311" s="1"/>
-      <c r="BC311" s="1" t="str">
+      <c r="BC311" s="1"/>
+      <c r="BD311" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21323,7 +21976,8 @@
       <c r="AZ312" s="1"/>
       <c r="BA312" s="1"/>
       <c r="BB312" s="1"/>
-      <c r="BC312" s="1" t="str">
+      <c r="BC312" s="1"/>
+      <c r="BD312" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21386,7 +22040,8 @@
       <c r="AZ313" s="1"/>
       <c r="BA313" s="1"/>
       <c r="BB313" s="1"/>
-      <c r="BC313" s="1" t="str">
+      <c r="BC313" s="1"/>
+      <c r="BD313" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21449,7 +22104,8 @@
       <c r="AZ314" s="1"/>
       <c r="BA314" s="1"/>
       <c r="BB314" s="1"/>
-      <c r="BC314" s="1" t="str">
+      <c r="BC314" s="1"/>
+      <c r="BD314" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21512,7 +22168,8 @@
       <c r="AZ315" s="1"/>
       <c r="BA315" s="1"/>
       <c r="BB315" s="1"/>
-      <c r="BC315" s="1" t="str">
+      <c r="BC315" s="1"/>
+      <c r="BD315" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21575,7 +22232,8 @@
       <c r="AZ316" s="1"/>
       <c r="BA316" s="1"/>
       <c r="BB316" s="1"/>
-      <c r="BC316" s="1" t="str">
+      <c r="BC316" s="1"/>
+      <c r="BD316" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21638,7 +22296,8 @@
       <c r="AZ317" s="1"/>
       <c r="BA317" s="1"/>
       <c r="BB317" s="1"/>
-      <c r="BC317" s="1" t="str">
+      <c r="BC317" s="1"/>
+      <c r="BD317" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21701,7 +22360,8 @@
       <c r="AZ318" s="1"/>
       <c r="BA318" s="1"/>
       <c r="BB318" s="1"/>
-      <c r="BC318" s="1" t="str">
+      <c r="BC318" s="1"/>
+      <c r="BD318" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21764,7 +22424,8 @@
       <c r="AZ319" s="1"/>
       <c r="BA319" s="1"/>
       <c r="BB319" s="1"/>
-      <c r="BC319" s="1" t="str">
+      <c r="BC319" s="1"/>
+      <c r="BD319" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21827,7 +22488,8 @@
       <c r="AZ320" s="1"/>
       <c r="BA320" s="1"/>
       <c r="BB320" s="1"/>
-      <c r="BC320" s="1" t="str">
+      <c r="BC320" s="1"/>
+      <c r="BD320" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21890,7 +22552,8 @@
       <c r="AZ321" s="1"/>
       <c r="BA321" s="1"/>
       <c r="BB321" s="1"/>
-      <c r="BC321" s="1" t="str">
+      <c r="BC321" s="1"/>
+      <c r="BD321" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21953,7 +22616,8 @@
       <c r="AZ322" s="1"/>
       <c r="BA322" s="1"/>
       <c r="BB322" s="1"/>
-      <c r="BC322" s="1" t="str">
+      <c r="BC322" s="1"/>
+      <c r="BD322" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22016,7 +22680,8 @@
       <c r="AZ323" s="1"/>
       <c r="BA323" s="1"/>
       <c r="BB323" s="1"/>
-      <c r="BC323" s="1" t="str">
+      <c r="BC323" s="1"/>
+      <c r="BD323" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22079,7 +22744,8 @@
       <c r="AZ324" s="1"/>
       <c r="BA324" s="1"/>
       <c r="BB324" s="1"/>
-      <c r="BC324" s="1" t="str">
+      <c r="BC324" s="1"/>
+      <c r="BD324" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22142,7 +22808,8 @@
       <c r="AZ325" s="1"/>
       <c r="BA325" s="1"/>
       <c r="BB325" s="1"/>
-      <c r="BC325" s="1" t="str">
+      <c r="BC325" s="1"/>
+      <c r="BD325" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22205,7 +22872,8 @@
       <c r="AZ326" s="1"/>
       <c r="BA326" s="1"/>
       <c r="BB326" s="1"/>
-      <c r="BC326" s="1" t="str">
+      <c r="BC326" s="1"/>
+      <c r="BD326" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22268,7 +22936,8 @@
       <c r="AZ327" s="1"/>
       <c r="BA327" s="1"/>
       <c r="BB327" s="1"/>
-      <c r="BC327" s="1" t="str">
+      <c r="BC327" s="1"/>
+      <c r="BD327" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22331,7 +23000,8 @@
       <c r="AZ328" s="1"/>
       <c r="BA328" s="1"/>
       <c r="BB328" s="1"/>
-      <c r="BC328" s="1" t="str">
+      <c r="BC328" s="1"/>
+      <c r="BD328" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22394,7 +23064,8 @@
       <c r="AZ329" s="1"/>
       <c r="BA329" s="1"/>
       <c r="BB329" s="1"/>
-      <c r="BC329" s="1" t="str">
+      <c r="BC329" s="1"/>
+      <c r="BD329" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22457,7 +23128,8 @@
       <c r="AZ330" s="1"/>
       <c r="BA330" s="1"/>
       <c r="BB330" s="1"/>
-      <c r="BC330" s="1" t="str">
+      <c r="BC330" s="1"/>
+      <c r="BD330" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22520,7 +23192,8 @@
       <c r="AZ331" s="1"/>
       <c r="BA331" s="1"/>
       <c r="BB331" s="1"/>
-      <c r="BC331" s="1" t="str">
+      <c r="BC331" s="1"/>
+      <c r="BD331" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22583,7 +23256,8 @@
       <c r="AZ332" s="1"/>
       <c r="BA332" s="1"/>
       <c r="BB332" s="1"/>
-      <c r="BC332" s="1" t="str">
+      <c r="BC332" s="1"/>
+      <c r="BD332" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22646,7 +23320,8 @@
       <c r="AZ333" s="1"/>
       <c r="BA333" s="1"/>
       <c r="BB333" s="1"/>
-      <c r="BC333" s="1" t="str">
+      <c r="BC333" s="1"/>
+      <c r="BD333" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22709,7 +23384,8 @@
       <c r="AZ334" s="1"/>
       <c r="BA334" s="1"/>
       <c r="BB334" s="1"/>
-      <c r="BC334" s="1" t="str">
+      <c r="BC334" s="1"/>
+      <c r="BD334" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22772,7 +23448,8 @@
       <c r="AZ335" s="1"/>
       <c r="BA335" s="1"/>
       <c r="BB335" s="1"/>
-      <c r="BC335" s="1" t="str">
+      <c r="BC335" s="1"/>
+      <c r="BD335" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22835,7 +23512,8 @@
       <c r="AZ336" s="1"/>
       <c r="BA336" s="1"/>
       <c r="BB336" s="1"/>
-      <c r="BC336" s="1" t="str">
+      <c r="BC336" s="1"/>
+      <c r="BD336" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22898,7 +23576,8 @@
       <c r="AZ337" s="1"/>
       <c r="BA337" s="1"/>
       <c r="BB337" s="1"/>
-      <c r="BC337" s="1" t="str">
+      <c r="BC337" s="1"/>
+      <c r="BD337" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22961,7 +23640,8 @@
       <c r="AZ338" s="1"/>
       <c r="BA338" s="1"/>
       <c r="BB338" s="1"/>
-      <c r="BC338" s="1" t="str">
+      <c r="BC338" s="1"/>
+      <c r="BD338" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23024,7 +23704,8 @@
       <c r="AZ339" s="1"/>
       <c r="BA339" s="1"/>
       <c r="BB339" s="1"/>
-      <c r="BC339" s="1" t="str">
+      <c r="BC339" s="1"/>
+      <c r="BD339" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23087,7 +23768,8 @@
       <c r="AZ340" s="1"/>
       <c r="BA340" s="1"/>
       <c r="BB340" s="1"/>
-      <c r="BC340" s="1" t="str">
+      <c r="BC340" s="1"/>
+      <c r="BD340" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23150,7 +23832,8 @@
       <c r="AZ341" s="1"/>
       <c r="BA341" s="1"/>
       <c r="BB341" s="1"/>
-      <c r="BC341" s="1" t="str">
+      <c r="BC341" s="1"/>
+      <c r="BD341" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23213,7 +23896,8 @@
       <c r="AZ342" s="1"/>
       <c r="BA342" s="1"/>
       <c r="BB342" s="1"/>
-      <c r="BC342" s="1" t="str">
+      <c r="BC342" s="1"/>
+      <c r="BD342" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23276,7 +23960,8 @@
       <c r="AZ343" s="1"/>
       <c r="BA343" s="1"/>
       <c r="BB343" s="1"/>
-      <c r="BC343" s="1" t="str">
+      <c r="BC343" s="1"/>
+      <c r="BD343" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23339,7 +24024,8 @@
       <c r="AZ344" s="1"/>
       <c r="BA344" s="1"/>
       <c r="BB344" s="1"/>
-      <c r="BC344" s="1" t="str">
+      <c r="BC344" s="1"/>
+      <c r="BD344" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23402,7 +24088,8 @@
       <c r="AZ345" s="1"/>
       <c r="BA345" s="1"/>
       <c r="BB345" s="1"/>
-      <c r="BC345" s="1" t="str">
+      <c r="BC345" s="1"/>
+      <c r="BD345" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23465,7 +24152,8 @@
       <c r="AZ346" s="1"/>
       <c r="BA346" s="1"/>
       <c r="BB346" s="1"/>
-      <c r="BC346" s="1" t="str">
+      <c r="BC346" s="1"/>
+      <c r="BD346" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23528,7 +24216,8 @@
       <c r="AZ347" s="1"/>
       <c r="BA347" s="1"/>
       <c r="BB347" s="1"/>
-      <c r="BC347" s="1" t="str">
+      <c r="BC347" s="1"/>
+      <c r="BD347" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23591,7 +24280,8 @@
       <c r="AZ348" s="1"/>
       <c r="BA348" s="1"/>
       <c r="BB348" s="1"/>
-      <c r="BC348" s="1" t="str">
+      <c r="BC348" s="1"/>
+      <c r="BD348" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23654,7 +24344,8 @@
       <c r="AZ349" s="1"/>
       <c r="BA349" s="1"/>
       <c r="BB349" s="1"/>
-      <c r="BC349" s="1" t="str">
+      <c r="BC349" s="1"/>
+      <c r="BD349" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23717,7 +24408,8 @@
       <c r="AZ350" s="1"/>
       <c r="BA350" s="1"/>
       <c r="BB350" s="1"/>
-      <c r="BC350" s="1" t="str">
+      <c r="BC350" s="1"/>
+      <c r="BD350" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23780,7 +24472,8 @@
       <c r="AZ351" s="1"/>
       <c r="BA351" s="1"/>
       <c r="BB351" s="1"/>
-      <c r="BC351" s="1" t="str">
+      <c r="BC351" s="1"/>
+      <c r="BD351" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23843,7 +24536,8 @@
       <c r="AZ352" s="1"/>
       <c r="BA352" s="1"/>
       <c r="BB352" s="1"/>
-      <c r="BC352" s="1" t="str">
+      <c r="BC352" s="1"/>
+      <c r="BD352" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23906,7 +24600,8 @@
       <c r="AZ353" s="1"/>
       <c r="BA353" s="1"/>
       <c r="BB353" s="1"/>
-      <c r="BC353" s="1" t="str">
+      <c r="BC353" s="1"/>
+      <c r="BD353" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23969,7 +24664,8 @@
       <c r="AZ354" s="1"/>
       <c r="BA354" s="1"/>
       <c r="BB354" s="1"/>
-      <c r="BC354" s="1" t="str">
+      <c r="BC354" s="1"/>
+      <c r="BD354" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24032,7 +24728,8 @@
       <c r="AZ355" s="1"/>
       <c r="BA355" s="1"/>
       <c r="BB355" s="1"/>
-      <c r="BC355" s="1" t="str">
+      <c r="BC355" s="1"/>
+      <c r="BD355" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24095,7 +24792,8 @@
       <c r="AZ356" s="1"/>
       <c r="BA356" s="1"/>
       <c r="BB356" s="1"/>
-      <c r="BC356" s="1" t="str">
+      <c r="BC356" s="1"/>
+      <c r="BD356" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24158,7 +24856,8 @@
       <c r="AZ357" s="1"/>
       <c r="BA357" s="1"/>
       <c r="BB357" s="1"/>
-      <c r="BC357" s="1" t="str">
+      <c r="BC357" s="1"/>
+      <c r="BD357" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24221,7 +24920,8 @@
       <c r="AZ358" s="1"/>
       <c r="BA358" s="1"/>
       <c r="BB358" s="1"/>
-      <c r="BC358" s="1" t="str">
+      <c r="BC358" s="1"/>
+      <c r="BD358" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24284,7 +24984,8 @@
       <c r="AZ359" s="1"/>
       <c r="BA359" s="1"/>
       <c r="BB359" s="1"/>
-      <c r="BC359" s="1" t="str">
+      <c r="BC359" s="1"/>
+      <c r="BD359" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24347,7 +25048,8 @@
       <c r="AZ360" s="1"/>
       <c r="BA360" s="1"/>
       <c r="BB360" s="1"/>
-      <c r="BC360" s="1" t="str">
+      <c r="BC360" s="1"/>
+      <c r="BD360" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24410,7 +25112,8 @@
       <c r="AZ361" s="1"/>
       <c r="BA361" s="1"/>
       <c r="BB361" s="1"/>
-      <c r="BC361" s="1" t="str">
+      <c r="BC361" s="1"/>
+      <c r="BD361" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24473,7 +25176,8 @@
       <c r="AZ362" s="1"/>
       <c r="BA362" s="1"/>
       <c r="BB362" s="1"/>
-      <c r="BC362" s="1" t="str">
+      <c r="BC362" s="1"/>
+      <c r="BD362" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24536,7 +25240,8 @@
       <c r="AZ363" s="1"/>
       <c r="BA363" s="1"/>
       <c r="BB363" s="1"/>
-      <c r="BC363" s="1" t="str">
+      <c r="BC363" s="1"/>
+      <c r="BD363" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24599,7 +25304,8 @@
       <c r="AZ364" s="1"/>
       <c r="BA364" s="1"/>
       <c r="BB364" s="1"/>
-      <c r="BC364" s="1" t="str">
+      <c r="BC364" s="1"/>
+      <c r="BD364" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24662,7 +25368,8 @@
       <c r="AZ365" s="1"/>
       <c r="BA365" s="1"/>
       <c r="BB365" s="1"/>
-      <c r="BC365" s="1" t="str">
+      <c r="BC365" s="1"/>
+      <c r="BD365" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24725,7 +25432,8 @@
       <c r="AZ366" s="1"/>
       <c r="BA366" s="1"/>
       <c r="BB366" s="1"/>
-      <c r="BC366" s="1" t="str">
+      <c r="BC366" s="1"/>
+      <c r="BD366" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24788,7 +25496,8 @@
       <c r="AZ367" s="1"/>
       <c r="BA367" s="1"/>
       <c r="BB367" s="1"/>
-      <c r="BC367" s="1" t="str">
+      <c r="BC367" s="1"/>
+      <c r="BD367" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24851,7 +25560,8 @@
       <c r="AZ368" s="1"/>
       <c r="BA368" s="1"/>
       <c r="BB368" s="1"/>
-      <c r="BC368" s="1" t="str">
+      <c r="BC368" s="1"/>
+      <c r="BD368" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24914,7 +25624,8 @@
       <c r="AZ369" s="1"/>
       <c r="BA369" s="1"/>
       <c r="BB369" s="1"/>
-      <c r="BC369" s="1" t="str">
+      <c r="BC369" s="1"/>
+      <c r="BD369" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24977,7 +25688,8 @@
       <c r="AZ370" s="1"/>
       <c r="BA370" s="1"/>
       <c r="BB370" s="1"/>
-      <c r="BC370" s="1" t="str">
+      <c r="BC370" s="1"/>
+      <c r="BD370" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25040,7 +25752,8 @@
       <c r="AZ371" s="1"/>
       <c r="BA371" s="1"/>
       <c r="BB371" s="1"/>
-      <c r="BC371" s="1" t="str">
+      <c r="BC371" s="1"/>
+      <c r="BD371" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25103,7 +25816,8 @@
       <c r="AZ372" s="1"/>
       <c r="BA372" s="1"/>
       <c r="BB372" s="1"/>
-      <c r="BC372" s="1" t="str">
+      <c r="BC372" s="1"/>
+      <c r="BD372" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25166,7 +25880,8 @@
       <c r="AZ373" s="1"/>
       <c r="BA373" s="1"/>
       <c r="BB373" s="1"/>
-      <c r="BC373" s="1" t="str">
+      <c r="BC373" s="1"/>
+      <c r="BD373" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25229,7 +25944,8 @@
       <c r="AZ374" s="1"/>
       <c r="BA374" s="1"/>
       <c r="BB374" s="1"/>
-      <c r="BC374" s="1" t="str">
+      <c r="BC374" s="1"/>
+      <c r="BD374" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25292,7 +26008,8 @@
       <c r="AZ375" s="1"/>
       <c r="BA375" s="1"/>
       <c r="BB375" s="1"/>
-      <c r="BC375" s="1" t="str">
+      <c r="BC375" s="1"/>
+      <c r="BD375" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25355,7 +26072,8 @@
       <c r="AZ376" s="1"/>
       <c r="BA376" s="1"/>
       <c r="BB376" s="1"/>
-      <c r="BC376" s="1" t="str">
+      <c r="BC376" s="1"/>
+      <c r="BD376" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25418,7 +26136,8 @@
       <c r="AZ377" s="1"/>
       <c r="BA377" s="1"/>
       <c r="BB377" s="1"/>
-      <c r="BC377" s="1" t="str">
+      <c r="BC377" s="1"/>
+      <c r="BD377" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25481,7 +26200,8 @@
       <c r="AZ378" s="1"/>
       <c r="BA378" s="1"/>
       <c r="BB378" s="1"/>
-      <c r="BC378" s="1" t="str">
+      <c r="BC378" s="1"/>
+      <c r="BD378" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25544,7 +26264,8 @@
       <c r="AZ379" s="1"/>
       <c r="BA379" s="1"/>
       <c r="BB379" s="1"/>
-      <c r="BC379" s="1" t="str">
+      <c r="BC379" s="1"/>
+      <c r="BD379" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25607,7 +26328,8 @@
       <c r="AZ380" s="1"/>
       <c r="BA380" s="1"/>
       <c r="BB380" s="1"/>
-      <c r="BC380" s="1" t="str">
+      <c r="BC380" s="1"/>
+      <c r="BD380" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25670,7 +26392,8 @@
       <c r="AZ381" s="1"/>
       <c r="BA381" s="1"/>
       <c r="BB381" s="1"/>
-      <c r="BC381" s="1" t="str">
+      <c r="BC381" s="1"/>
+      <c r="BD381" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25733,7 +26456,8 @@
       <c r="AZ382" s="1"/>
       <c r="BA382" s="1"/>
       <c r="BB382" s="1"/>
-      <c r="BC382" s="1" t="str">
+      <c r="BC382" s="1"/>
+      <c r="BD382" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25796,7 +26520,8 @@
       <c r="AZ383" s="1"/>
       <c r="BA383" s="1"/>
       <c r="BB383" s="1"/>
-      <c r="BC383" s="1" t="str">
+      <c r="BC383" s="1"/>
+      <c r="BD383" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25859,7 +26584,8 @@
       <c r="AZ384" s="1"/>
       <c r="BA384" s="1"/>
       <c r="BB384" s="1"/>
-      <c r="BC384" s="1" t="str">
+      <c r="BC384" s="1"/>
+      <c r="BD384" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25922,7 +26648,8 @@
       <c r="AZ385" s="1"/>
       <c r="BA385" s="1"/>
       <c r="BB385" s="1"/>
-      <c r="BC385" s="1" t="str">
+      <c r="BC385" s="1"/>
+      <c r="BD385" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25985,7 +26712,8 @@
       <c r="AZ386" s="1"/>
       <c r="BA386" s="1"/>
       <c r="BB386" s="1"/>
-      <c r="BC386" s="1" t="str">
+      <c r="BC386" s="1"/>
+      <c r="BD386" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26048,7 +26776,8 @@
       <c r="AZ387" s="1"/>
       <c r="BA387" s="1"/>
       <c r="BB387" s="1"/>
-      <c r="BC387" s="1" t="str">
+      <c r="BC387" s="1"/>
+      <c r="BD387" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26111,7 +26840,8 @@
       <c r="AZ388" s="1"/>
       <c r="BA388" s="1"/>
       <c r="BB388" s="1"/>
-      <c r="BC388" s="1" t="str">
+      <c r="BC388" s="1"/>
+      <c r="BD388" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26174,7 +26904,8 @@
       <c r="AZ389" s="1"/>
       <c r="BA389" s="1"/>
       <c r="BB389" s="1"/>
-      <c r="BC389" s="1" t="str">
+      <c r="BC389" s="1"/>
+      <c r="BD389" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26237,7 +26968,8 @@
       <c r="AZ390" s="1"/>
       <c r="BA390" s="1"/>
       <c r="BB390" s="1"/>
-      <c r="BC390" s="1" t="str">
+      <c r="BC390" s="1"/>
+      <c r="BD390" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26300,7 +27032,8 @@
       <c r="AZ391" s="1"/>
       <c r="BA391" s="1"/>
       <c r="BB391" s="1"/>
-      <c r="BC391" s="1" t="str">
+      <c r="BC391" s="1"/>
+      <c r="BD391" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26363,7 +27096,8 @@
       <c r="AZ392" s="1"/>
       <c r="BA392" s="1"/>
       <c r="BB392" s="1"/>
-      <c r="BC392" s="1" t="str">
+      <c r="BC392" s="1"/>
+      <c r="BD392" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26426,7 +27160,8 @@
       <c r="AZ393" s="1"/>
       <c r="BA393" s="1"/>
       <c r="BB393" s="1"/>
-      <c r="BC393" s="1" t="str">
+      <c r="BC393" s="1"/>
+      <c r="BD393" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26489,7 +27224,8 @@
       <c r="AZ394" s="1"/>
       <c r="BA394" s="1"/>
       <c r="BB394" s="1"/>
-      <c r="BC394" s="1" t="str">
+      <c r="BC394" s="1"/>
+      <c r="BD394" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26552,7 +27288,8 @@
       <c r="AZ395" s="1"/>
       <c r="BA395" s="1"/>
       <c r="BB395" s="1"/>
-      <c r="BC395" s="1" t="str">
+      <c r="BC395" s="1"/>
+      <c r="BD395" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26615,7 +27352,8 @@
       <c r="AZ396" s="1"/>
       <c r="BA396" s="1"/>
       <c r="BB396" s="1"/>
-      <c r="BC396" s="1" t="str">
+      <c r="BC396" s="1"/>
+      <c r="BD396" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26678,7 +27416,8 @@
       <c r="AZ397" s="1"/>
       <c r="BA397" s="1"/>
       <c r="BB397" s="1"/>
-      <c r="BC397" s="1" t="str">
+      <c r="BC397" s="1"/>
+      <c r="BD397" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26741,7 +27480,8 @@
       <c r="AZ398" s="1"/>
       <c r="BA398" s="1"/>
       <c r="BB398" s="1"/>
-      <c r="BC398" s="1" t="str">
+      <c r="BC398" s="1"/>
+      <c r="BD398" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26804,7 +27544,8 @@
       <c r="AZ399" s="1"/>
       <c r="BA399" s="1"/>
       <c r="BB399" s="1"/>
-      <c r="BC399" s="1" t="str">
+      <c r="BC399" s="1"/>
+      <c r="BD399" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26867,7 +27608,8 @@
       <c r="AZ400" s="1"/>
       <c r="BA400" s="1"/>
       <c r="BB400" s="1"/>
-      <c r="BC400" s="1" t="str">
+      <c r="BC400" s="1"/>
+      <c r="BD400" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26930,7 +27672,8 @@
       <c r="AZ401" s="1"/>
       <c r="BA401" s="1"/>
       <c r="BB401" s="1"/>
-      <c r="BC401" s="1" t="str">
+      <c r="BC401" s="1"/>
+      <c r="BD401" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26993,7 +27736,8 @@
       <c r="AZ402" s="1"/>
       <c r="BA402" s="1"/>
       <c r="BB402" s="1"/>
-      <c r="BC402" s="1" t="str">
+      <c r="BC402" s="1"/>
+      <c r="BD402" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27056,7 +27800,8 @@
       <c r="AZ403" s="1"/>
       <c r="BA403" s="1"/>
       <c r="BB403" s="1"/>
-      <c r="BC403" s="1" t="str">
+      <c r="BC403" s="1"/>
+      <c r="BD403" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27119,7 +27864,8 @@
       <c r="AZ404" s="1"/>
       <c r="BA404" s="1"/>
       <c r="BB404" s="1"/>
-      <c r="BC404" s="1" t="str">
+      <c r="BC404" s="1"/>
+      <c r="BD404" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27182,7 +27928,8 @@
       <c r="AZ405" s="1"/>
       <c r="BA405" s="1"/>
       <c r="BB405" s="1"/>
-      <c r="BC405" s="1" t="str">
+      <c r="BC405" s="1"/>
+      <c r="BD405" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27245,7 +27992,8 @@
       <c r="AZ406" s="1"/>
       <c r="BA406" s="1"/>
       <c r="BB406" s="1"/>
-      <c r="BC406" s="1" t="str">
+      <c r="BC406" s="1"/>
+      <c r="BD406" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27308,7 +28056,8 @@
       <c r="AZ407" s="1"/>
       <c r="BA407" s="1"/>
       <c r="BB407" s="1"/>
-      <c r="BC407" s="1" t="str">
+      <c r="BC407" s="1"/>
+      <c r="BD407" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27371,7 +28120,8 @@
       <c r="AZ408" s="1"/>
       <c r="BA408" s="1"/>
       <c r="BB408" s="1"/>
-      <c r="BC408" s="1" t="str">
+      <c r="BC408" s="1"/>
+      <c r="BD408" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27434,7 +28184,8 @@
       <c r="AZ409" s="1"/>
       <c r="BA409" s="1"/>
       <c r="BB409" s="1"/>
-      <c r="BC409" s="1" t="str">
+      <c r="BC409" s="1"/>
+      <c r="BD409" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27497,7 +28248,8 @@
       <c r="AZ410" s="1"/>
       <c r="BA410" s="1"/>
       <c r="BB410" s="1"/>
-      <c r="BC410" s="1" t="str">
+      <c r="BC410" s="1"/>
+      <c r="BD410" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27560,7 +28312,8 @@
       <c r="AZ411" s="1"/>
       <c r="BA411" s="1"/>
       <c r="BB411" s="1"/>
-      <c r="BC411" s="1" t="str">
+      <c r="BC411" s="1"/>
+      <c r="BD411" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27623,7 +28376,8 @@
       <c r="AZ412" s="1"/>
       <c r="BA412" s="1"/>
       <c r="BB412" s="1"/>
-      <c r="BC412" s="1" t="str">
+      <c r="BC412" s="1"/>
+      <c r="BD412" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27686,7 +28440,8 @@
       <c r="AZ413" s="1"/>
       <c r="BA413" s="1"/>
       <c r="BB413" s="1"/>
-      <c r="BC413" s="1" t="str">
+      <c r="BC413" s="1"/>
+      <c r="BD413" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27749,7 +28504,8 @@
       <c r="AZ414" s="1"/>
       <c r="BA414" s="1"/>
       <c r="BB414" s="1"/>
-      <c r="BC414" s="1" t="str">
+      <c r="BC414" s="1"/>
+      <c r="BD414" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27812,7 +28568,8 @@
       <c r="AZ415" s="1"/>
       <c r="BA415" s="1"/>
       <c r="BB415" s="1"/>
-      <c r="BC415" s="1" t="str">
+      <c r="BC415" s="1"/>
+      <c r="BD415" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27875,7 +28632,8 @@
       <c r="AZ416" s="1"/>
       <c r="BA416" s="1"/>
       <c r="BB416" s="1"/>
-      <c r="BC416" s="1" t="str">
+      <c r="BC416" s="1"/>
+      <c r="BD416" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27938,7 +28696,8 @@
       <c r="AZ417" s="1"/>
       <c r="BA417" s="1"/>
       <c r="BB417" s="1"/>
-      <c r="BC417" s="1" t="str">
+      <c r="BC417" s="1"/>
+      <c r="BD417" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28001,7 +28760,8 @@
       <c r="AZ418" s="1"/>
       <c r="BA418" s="1"/>
       <c r="BB418" s="1"/>
-      <c r="BC418" s="1" t="str">
+      <c r="BC418" s="1"/>
+      <c r="BD418" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28064,7 +28824,8 @@
       <c r="AZ419" s="1"/>
       <c r="BA419" s="1"/>
       <c r="BB419" s="1"/>
-      <c r="BC419" s="1" t="str">
+      <c r="BC419" s="1"/>
+      <c r="BD419" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28127,7 +28888,8 @@
       <c r="AZ420" s="1"/>
       <c r="BA420" s="1"/>
       <c r="BB420" s="1"/>
-      <c r="BC420" s="1" t="str">
+      <c r="BC420" s="1"/>
+      <c r="BD420" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28190,7 +28952,8 @@
       <c r="AZ421" s="1"/>
       <c r="BA421" s="1"/>
       <c r="BB421" s="1"/>
-      <c r="BC421" s="1" t="str">
+      <c r="BC421" s="1"/>
+      <c r="BD421" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28253,7 +29016,8 @@
       <c r="AZ422" s="1"/>
       <c r="BA422" s="1"/>
       <c r="BB422" s="1"/>
-      <c r="BC422" s="1" t="str">
+      <c r="BC422" s="1"/>
+      <c r="BD422" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28316,7 +29080,8 @@
       <c r="AZ423" s="1"/>
       <c r="BA423" s="1"/>
       <c r="BB423" s="1"/>
-      <c r="BC423" s="1" t="str">
+      <c r="BC423" s="1"/>
+      <c r="BD423" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28379,7 +29144,8 @@
       <c r="AZ424" s="1"/>
       <c r="BA424" s="1"/>
       <c r="BB424" s="1"/>
-      <c r="BC424" s="1" t="str">
+      <c r="BC424" s="1"/>
+      <c r="BD424" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28442,7 +29208,8 @@
       <c r="AZ425" s="1"/>
       <c r="BA425" s="1"/>
       <c r="BB425" s="1"/>
-      <c r="BC425" s="1" t="str">
+      <c r="BC425" s="1"/>
+      <c r="BD425" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28505,7 +29272,8 @@
       <c r="AZ426" s="1"/>
       <c r="BA426" s="1"/>
       <c r="BB426" s="1"/>
-      <c r="BC426" s="1" t="str">
+      <c r="BC426" s="1"/>
+      <c r="BD426" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28568,7 +29336,8 @@
       <c r="AZ427" s="1"/>
       <c r="BA427" s="1"/>
       <c r="BB427" s="1"/>
-      <c r="BC427" s="1" t="str">
+      <c r="BC427" s="1"/>
+      <c r="BD427" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28631,7 +29400,8 @@
       <c r="AZ428" s="1"/>
       <c r="BA428" s="1"/>
       <c r="BB428" s="1"/>
-      <c r="BC428" s="1" t="str">
+      <c r="BC428" s="1"/>
+      <c r="BD428" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28694,7 +29464,8 @@
       <c r="AZ429" s="1"/>
       <c r="BA429" s="1"/>
       <c r="BB429" s="1"/>
-      <c r="BC429" s="1" t="str">
+      <c r="BC429" s="1"/>
+      <c r="BD429" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28757,7 +29528,8 @@
       <c r="AZ430" s="1"/>
       <c r="BA430" s="1"/>
       <c r="BB430" s="1"/>
-      <c r="BC430" s="1" t="str">
+      <c r="BC430" s="1"/>
+      <c r="BD430" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28820,7 +29592,8 @@
       <c r="AZ431" s="1"/>
       <c r="BA431" s="1"/>
       <c r="BB431" s="1"/>
-      <c r="BC431" s="1" t="str">
+      <c r="BC431" s="1"/>
+      <c r="BD431" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28883,7 +29656,8 @@
       <c r="AZ432" s="1"/>
       <c r="BA432" s="1"/>
       <c r="BB432" s="1"/>
-      <c r="BC432" s="1" t="str">
+      <c r="BC432" s="1"/>
+      <c r="BD432" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28946,7 +29720,8 @@
       <c r="AZ433" s="1"/>
       <c r="BA433" s="1"/>
       <c r="BB433" s="1"/>
-      <c r="BC433" s="1" t="str">
+      <c r="BC433" s="1"/>
+      <c r="BD433" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29009,7 +29784,8 @@
       <c r="AZ434" s="1"/>
       <c r="BA434" s="1"/>
       <c r="BB434" s="1"/>
-      <c r="BC434" s="1" t="str">
+      <c r="BC434" s="1"/>
+      <c r="BD434" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29072,7 +29848,8 @@
       <c r="AZ435" s="1"/>
       <c r="BA435" s="1"/>
       <c r="BB435" s="1"/>
-      <c r="BC435" s="1" t="str">
+      <c r="BC435" s="1"/>
+      <c r="BD435" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29135,7 +29912,8 @@
       <c r="AZ436" s="1"/>
       <c r="BA436" s="1"/>
       <c r="BB436" s="1"/>
-      <c r="BC436" s="1" t="str">
+      <c r="BC436" s="1"/>
+      <c r="BD436" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29198,7 +29976,8 @@
       <c r="AZ437" s="1"/>
       <c r="BA437" s="1"/>
       <c r="BB437" s="1"/>
-      <c r="BC437" s="1" t="str">
+      <c r="BC437" s="1"/>
+      <c r="BD437" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29261,7 +30040,8 @@
       <c r="AZ438" s="1"/>
       <c r="BA438" s="1"/>
       <c r="BB438" s="1"/>
-      <c r="BC438" s="1" t="str">
+      <c r="BC438" s="1"/>
+      <c r="BD438" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29324,7 +30104,8 @@
       <c r="AZ439" s="1"/>
       <c r="BA439" s="1"/>
       <c r="BB439" s="1"/>
-      <c r="BC439" s="1" t="str">
+      <c r="BC439" s="1"/>
+      <c r="BD439" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29387,7 +30168,8 @@
       <c r="AZ440" s="1"/>
       <c r="BA440" s="1"/>
       <c r="BB440" s="1"/>
-      <c r="BC440" s="1" t="str">
+      <c r="BC440" s="1"/>
+      <c r="BD440" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29450,7 +30232,8 @@
       <c r="AZ441" s="1"/>
       <c r="BA441" s="1"/>
       <c r="BB441" s="1"/>
-      <c r="BC441" s="1" t="str">
+      <c r="BC441" s="1"/>
+      <c r="BD441" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29513,7 +30296,8 @@
       <c r="AZ442" s="1"/>
       <c r="BA442" s="1"/>
       <c r="BB442" s="1"/>
-      <c r="BC442" s="1" t="str">
+      <c r="BC442" s="1"/>
+      <c r="BD442" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29576,7 +30360,8 @@
       <c r="AZ443" s="1"/>
       <c r="BA443" s="1"/>
       <c r="BB443" s="1"/>
-      <c r="BC443" s="1" t="str">
+      <c r="BC443" s="1"/>
+      <c r="BD443" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29639,7 +30424,8 @@
       <c r="AZ444" s="1"/>
       <c r="BA444" s="1"/>
       <c r="BB444" s="1"/>
-      <c r="BC444" s="1" t="str">
+      <c r="BC444" s="1"/>
+      <c r="BD444" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29702,7 +30488,8 @@
       <c r="AZ445" s="1"/>
       <c r="BA445" s="1"/>
       <c r="BB445" s="1"/>
-      <c r="BC445" s="1" t="str">
+      <c r="BC445" s="1"/>
+      <c r="BD445" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29765,7 +30552,8 @@
       <c r="AZ446" s="1"/>
       <c r="BA446" s="1"/>
       <c r="BB446" s="1"/>
-      <c r="BC446" s="1" t="str">
+      <c r="BC446" s="1"/>
+      <c r="BD446" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29828,7 +30616,8 @@
       <c r="AZ447" s="1"/>
       <c r="BA447" s="1"/>
       <c r="BB447" s="1"/>
-      <c r="BC447" s="1" t="str">
+      <c r="BC447" s="1"/>
+      <c r="BD447" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29891,7 +30680,8 @@
       <c r="AZ448" s="1"/>
       <c r="BA448" s="1"/>
       <c r="BB448" s="1"/>
-      <c r="BC448" s="1" t="str">
+      <c r="BC448" s="1"/>
+      <c r="BD448" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29954,7 +30744,8 @@
       <c r="AZ449" s="1"/>
       <c r="BA449" s="1"/>
       <c r="BB449" s="1"/>
-      <c r="BC449" s="1" t="str">
+      <c r="BC449" s="1"/>
+      <c r="BD449" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30017,7 +30808,8 @@
       <c r="AZ450" s="1"/>
       <c r="BA450" s="1"/>
       <c r="BB450" s="1"/>
-      <c r="BC450" s="1" t="str">
+      <c r="BC450" s="1"/>
+      <c r="BD450" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30080,7 +30872,8 @@
       <c r="AZ451" s="1"/>
       <c r="BA451" s="1"/>
       <c r="BB451" s="1"/>
-      <c r="BC451" s="1" t="str">
+      <c r="BC451" s="1"/>
+      <c r="BD451" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30143,7 +30936,8 @@
       <c r="AZ452" s="1"/>
       <c r="BA452" s="1"/>
       <c r="BB452" s="1"/>
-      <c r="BC452" s="1" t="str">
+      <c r="BC452" s="1"/>
+      <c r="BD452" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30206,7 +31000,8 @@
       <c r="AZ453" s="1"/>
       <c r="BA453" s="1"/>
       <c r="BB453" s="1"/>
-      <c r="BC453" s="1" t="str">
+      <c r="BC453" s="1"/>
+      <c r="BD453" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30269,7 +31064,8 @@
       <c r="AZ454" s="1"/>
       <c r="BA454" s="1"/>
       <c r="BB454" s="1"/>
-      <c r="BC454" s="1" t="str">
+      <c r="BC454" s="1"/>
+      <c r="BD454" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30332,7 +31128,8 @@
       <c r="AZ455" s="1"/>
       <c r="BA455" s="1"/>
       <c r="BB455" s="1"/>
-      <c r="BC455" s="1" t="str">
+      <c r="BC455" s="1"/>
+      <c r="BD455" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30395,7 +31192,8 @@
       <c r="AZ456" s="1"/>
       <c r="BA456" s="1"/>
       <c r="BB456" s="1"/>
-      <c r="BC456" s="1" t="str">
+      <c r="BC456" s="1"/>
+      <c r="BD456" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30458,7 +31256,8 @@
       <c r="AZ457" s="1"/>
       <c r="BA457" s="1"/>
       <c r="BB457" s="1"/>
-      <c r="BC457" s="1" t="str">
+      <c r="BC457" s="1"/>
+      <c r="BD457" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30521,7 +31320,8 @@
       <c r="AZ458" s="1"/>
       <c r="BA458" s="1"/>
       <c r="BB458" s="1"/>
-      <c r="BC458" s="1" t="str">
+      <c r="BC458" s="1"/>
+      <c r="BD458" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30584,7 +31384,8 @@
       <c r="AZ459" s="1"/>
       <c r="BA459" s="1"/>
       <c r="BB459" s="1"/>
-      <c r="BC459" s="1" t="str">
+      <c r="BC459" s="1"/>
+      <c r="BD459" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30647,7 +31448,8 @@
       <c r="AZ460" s="1"/>
       <c r="BA460" s="1"/>
       <c r="BB460" s="1"/>
-      <c r="BC460" s="1" t="str">
+      <c r="BC460" s="1"/>
+      <c r="BD460" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30710,7 +31512,8 @@
       <c r="AZ461" s="1"/>
       <c r="BA461" s="1"/>
       <c r="BB461" s="1"/>
-      <c r="BC461" s="1" t="str">
+      <c r="BC461" s="1"/>
+      <c r="BD461" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30773,7 +31576,8 @@
       <c r="AZ462" s="1"/>
       <c r="BA462" s="1"/>
       <c r="BB462" s="1"/>
-      <c r="BC462" s="1" t="str">
+      <c r="BC462" s="1"/>
+      <c r="BD462" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30836,7 +31640,8 @@
       <c r="AZ463" s="1"/>
       <c r="BA463" s="1"/>
       <c r="BB463" s="1"/>
-      <c r="BC463" s="1" t="str">
+      <c r="BC463" s="1"/>
+      <c r="BD463" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30899,7 +31704,8 @@
       <c r="AZ464" s="1"/>
       <c r="BA464" s="1"/>
       <c r="BB464" s="1"/>
-      <c r="BC464" s="1" t="str">
+      <c r="BC464" s="1"/>
+      <c r="BD464" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30962,7 +31768,8 @@
       <c r="AZ465" s="1"/>
       <c r="BA465" s="1"/>
       <c r="BB465" s="1"/>
-      <c r="BC465" s="1" t="str">
+      <c r="BC465" s="1"/>
+      <c r="BD465" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31025,7 +31832,8 @@
       <c r="AZ466" s="1"/>
       <c r="BA466" s="1"/>
       <c r="BB466" s="1"/>
-      <c r="BC466" s="1" t="str">
+      <c r="BC466" s="1"/>
+      <c r="BD466" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31088,7 +31896,8 @@
       <c r="AZ467" s="1"/>
       <c r="BA467" s="1"/>
       <c r="BB467" s="1"/>
-      <c r="BC467" s="1" t="str">
+      <c r="BC467" s="1"/>
+      <c r="BD467" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31151,7 +31960,8 @@
       <c r="AZ468" s="1"/>
       <c r="BA468" s="1"/>
       <c r="BB468" s="1"/>
-      <c r="BC468" s="1" t="str">
+      <c r="BC468" s="1"/>
+      <c r="BD468" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31214,7 +32024,8 @@
       <c r="AZ469" s="1"/>
       <c r="BA469" s="1"/>
       <c r="BB469" s="1"/>
-      <c r="BC469" s="1" t="str">
+      <c r="BC469" s="1"/>
+      <c r="BD469" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31277,7 +32088,8 @@
       <c r="AZ470" s="1"/>
       <c r="BA470" s="1"/>
       <c r="BB470" s="1"/>
-      <c r="BC470" s="1" t="str">
+      <c r="BC470" s="1"/>
+      <c r="BD470" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31340,7 +32152,8 @@
       <c r="AZ471" s="1"/>
       <c r="BA471" s="1"/>
       <c r="BB471" s="1"/>
-      <c r="BC471" s="1" t="str">
+      <c r="BC471" s="1"/>
+      <c r="BD471" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31403,7 +32216,8 @@
       <c r="AZ472" s="1"/>
       <c r="BA472" s="1"/>
       <c r="BB472" s="1"/>
-      <c r="BC472" s="1" t="str">
+      <c r="BC472" s="1"/>
+      <c r="BD472" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31466,7 +32280,8 @@
       <c r="AZ473" s="1"/>
       <c r="BA473" s="1"/>
       <c r="BB473" s="1"/>
-      <c r="BC473" s="1" t="str">
+      <c r="BC473" s="1"/>
+      <c r="BD473" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31529,7 +32344,8 @@
       <c r="AZ474" s="1"/>
       <c r="BA474" s="1"/>
       <c r="BB474" s="1"/>
-      <c r="BC474" s="1" t="str">
+      <c r="BC474" s="1"/>
+      <c r="BD474" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31592,7 +32408,8 @@
       <c r="AZ475" s="1"/>
       <c r="BA475" s="1"/>
       <c r="BB475" s="1"/>
-      <c r="BC475" s="1" t="str">
+      <c r="BC475" s="1"/>
+      <c r="BD475" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31655,7 +32472,8 @@
       <c r="AZ476" s="1"/>
       <c r="BA476" s="1"/>
       <c r="BB476" s="1"/>
-      <c r="BC476" s="1" t="str">
+      <c r="BC476" s="1"/>
+      <c r="BD476" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31718,7 +32536,8 @@
       <c r="AZ477" s="1"/>
       <c r="BA477" s="1"/>
       <c r="BB477" s="1"/>
-      <c r="BC477" s="1" t="str">
+      <c r="BC477" s="1"/>
+      <c r="BD477" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31781,7 +32600,8 @@
       <c r="AZ478" s="1"/>
       <c r="BA478" s="1"/>
       <c r="BB478" s="1"/>
-      <c r="BC478" s="1" t="str">
+      <c r="BC478" s="1"/>
+      <c r="BD478" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31844,7 +32664,8 @@
       <c r="AZ479" s="1"/>
       <c r="BA479" s="1"/>
       <c r="BB479" s="1"/>
-      <c r="BC479" s="1" t="str">
+      <c r="BC479" s="1"/>
+      <c r="BD479" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31907,7 +32728,8 @@
       <c r="AZ480" s="1"/>
       <c r="BA480" s="1"/>
       <c r="BB480" s="1"/>
-      <c r="BC480" s="1" t="str">
+      <c r="BC480" s="1"/>
+      <c r="BD480" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31970,7 +32792,8 @@
       <c r="AZ481" s="1"/>
       <c r="BA481" s="1"/>
       <c r="BB481" s="1"/>
-      <c r="BC481" s="1" t="str">
+      <c r="BC481" s="1"/>
+      <c r="BD481" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32033,7 +32856,8 @@
       <c r="AZ482" s="1"/>
       <c r="BA482" s="1"/>
       <c r="BB482" s="1"/>
-      <c r="BC482" s="1" t="str">
+      <c r="BC482" s="1"/>
+      <c r="BD482" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32096,7 +32920,8 @@
       <c r="AZ483" s="1"/>
       <c r="BA483" s="1"/>
       <c r="BB483" s="1"/>
-      <c r="BC483" s="1" t="str">
+      <c r="BC483" s="1"/>
+      <c r="BD483" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32159,7 +32984,8 @@
       <c r="AZ484" s="1"/>
       <c r="BA484" s="1"/>
       <c r="BB484" s="1"/>
-      <c r="BC484" s="1" t="str">
+      <c r="BC484" s="1"/>
+      <c r="BD484" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32222,7 +33048,8 @@
       <c r="AZ485" s="1"/>
       <c r="BA485" s="1"/>
       <c r="BB485" s="1"/>
-      <c r="BC485" s="1" t="str">
+      <c r="BC485" s="1"/>
+      <c r="BD485" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32285,7 +33112,8 @@
       <c r="AZ486" s="1"/>
       <c r="BA486" s="1"/>
       <c r="BB486" s="1"/>
-      <c r="BC486" s="1" t="str">
+      <c r="BC486" s="1"/>
+      <c r="BD486" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32348,7 +33176,8 @@
       <c r="AZ487" s="1"/>
       <c r="BA487" s="1"/>
       <c r="BB487" s="1"/>
-      <c r="BC487" s="1" t="str">
+      <c r="BC487" s="1"/>
+      <c r="BD487" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32411,7 +33240,8 @@
       <c r="AZ488" s="1"/>
       <c r="BA488" s="1"/>
       <c r="BB488" s="1"/>
-      <c r="BC488" s="1" t="str">
+      <c r="BC488" s="1"/>
+      <c r="BD488" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32474,7 +33304,8 @@
       <c r="AZ489" s="1"/>
       <c r="BA489" s="1"/>
       <c r="BB489" s="1"/>
-      <c r="BC489" s="1" t="str">
+      <c r="BC489" s="1"/>
+      <c r="BD489" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32537,7 +33368,8 @@
       <c r="AZ490" s="1"/>
       <c r="BA490" s="1"/>
       <c r="BB490" s="1"/>
-      <c r="BC490" s="1" t="str">
+      <c r="BC490" s="1"/>
+      <c r="BD490" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32600,7 +33432,8 @@
       <c r="AZ491" s="1"/>
       <c r="BA491" s="1"/>
       <c r="BB491" s="1"/>
-      <c r="BC491" s="1" t="str">
+      <c r="BC491" s="1"/>
+      <c r="BD491" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32663,7 +33496,8 @@
       <c r="AZ492" s="1"/>
       <c r="BA492" s="1"/>
       <c r="BB492" s="1"/>
-      <c r="BC492" s="1" t="str">
+      <c r="BC492" s="1"/>
+      <c r="BD492" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32726,7 +33560,8 @@
       <c r="AZ493" s="1"/>
       <c r="BA493" s="1"/>
       <c r="BB493" s="1"/>
-      <c r="BC493" s="1" t="str">
+      <c r="BC493" s="1"/>
+      <c r="BD493" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32789,7 +33624,8 @@
       <c r="AZ494" s="1"/>
       <c r="BA494" s="1"/>
       <c r="BB494" s="1"/>
-      <c r="BC494" s="1" t="str">
+      <c r="BC494" s="1"/>
+      <c r="BD494" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32852,7 +33688,8 @@
       <c r="AZ495" s="1"/>
       <c r="BA495" s="1"/>
       <c r="BB495" s="1"/>
-      <c r="BC495" s="1" t="str">
+      <c r="BC495" s="1"/>
+      <c r="BD495" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32915,7 +33752,8 @@
       <c r="AZ496" s="1"/>
       <c r="BA496" s="1"/>
       <c r="BB496" s="1"/>
-      <c r="BC496" s="1" t="str">
+      <c r="BC496" s="1"/>
+      <c r="BD496" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32978,7 +33816,8 @@
       <c r="AZ497" s="1"/>
       <c r="BA497" s="1"/>
       <c r="BB497" s="1"/>
-      <c r="BC497" s="1" t="str">
+      <c r="BC497" s="1"/>
+      <c r="BD497" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33041,7 +33880,8 @@
       <c r="AZ498" s="1"/>
       <c r="BA498" s="1"/>
       <c r="BB498" s="1"/>
-      <c r="BC498" s="1" t="str">
+      <c r="BC498" s="1"/>
+      <c r="BD498" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33104,7 +33944,8 @@
       <c r="AZ499" s="1"/>
       <c r="BA499" s="1"/>
       <c r="BB499" s="1"/>
-      <c r="BC499" s="1" t="str">
+      <c r="BC499" s="1"/>
+      <c r="BD499" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33167,7 +34008,8 @@
       <c r="AZ500" s="1"/>
       <c r="BA500" s="1"/>
       <c r="BB500" s="1"/>
-      <c r="BC500" s="1" t="str">
+      <c r="BC500" s="1"/>
+      <c r="BD500" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33230,7 +34072,8 @@
       <c r="AZ501" s="1"/>
       <c r="BA501" s="1"/>
       <c r="BB501" s="1"/>
-      <c r="BC501" s="1" t="str">
+      <c r="BC501" s="1"/>
+      <c r="BD501" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33293,7 +34136,8 @@
       <c r="AZ502" s="1"/>
       <c r="BA502" s="1"/>
       <c r="BB502" s="1"/>
-      <c r="BC502" s="1" t="str">
+      <c r="BC502" s="1"/>
+      <c r="BD502" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33356,7 +34200,8 @@
       <c r="AZ503" s="1"/>
       <c r="BA503" s="1"/>
       <c r="BB503" s="1"/>
-      <c r="BC503" s="1" t="str">
+      <c r="BC503" s="1"/>
+      <c r="BD503" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33419,7 +34264,8 @@
       <c r="AZ504" s="1"/>
       <c r="BA504" s="1"/>
       <c r="BB504" s="1"/>
-      <c r="BC504" s="1" t="str">
+      <c r="BC504" s="1"/>
+      <c r="BD504" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33482,7 +34328,8 @@
       <c r="AZ505" s="1"/>
       <c r="BA505" s="1"/>
       <c r="BB505" s="1"/>
-      <c r="BC505" s="1" t="str">
+      <c r="BC505" s="1"/>
+      <c r="BD505" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33545,7 +34392,8 @@
       <c r="AZ506" s="1"/>
       <c r="BA506" s="1"/>
       <c r="BB506" s="1"/>
-      <c r="BC506" s="1" t="str">
+      <c r="BC506" s="1"/>
+      <c r="BD506" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33608,7 +34456,8 @@
       <c r="AZ507" s="1"/>
       <c r="BA507" s="1"/>
       <c r="BB507" s="1"/>
-      <c r="BC507" s="1" t="str">
+      <c r="BC507" s="1"/>
+      <c r="BD507" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33671,7 +34520,8 @@
       <c r="AZ508" s="1"/>
       <c r="BA508" s="1"/>
       <c r="BB508" s="1"/>
-      <c r="BC508" s="1" t="str">
+      <c r="BC508" s="1"/>
+      <c r="BD508" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33734,7 +34584,8 @@
       <c r="AZ509" s="1"/>
       <c r="BA509" s="1"/>
       <c r="BB509" s="1"/>
-      <c r="BC509" s="1" t="str">
+      <c r="BC509" s="1"/>
+      <c r="BD509" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33797,7 +34648,8 @@
       <c r="AZ510" s="1"/>
       <c r="BA510" s="1"/>
       <c r="BB510" s="1"/>
-      <c r="BC510" s="1" t="str">
+      <c r="BC510" s="1"/>
+      <c r="BD510" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33860,7 +34712,8 @@
       <c r="AZ511" s="1"/>
       <c r="BA511" s="1"/>
       <c r="BB511" s="1"/>
-      <c r="BC511" s="1" t="str">
+      <c r="BC511" s="1"/>
+      <c r="BD511" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33923,7 +34776,8 @@
       <c r="AZ512" s="1"/>
       <c r="BA512" s="1"/>
       <c r="BB512" s="1"/>
-      <c r="BC512" s="1" t="str">
+      <c r="BC512" s="1"/>
+      <c r="BD512" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33986,7 +34840,8 @@
       <c r="AZ513" s="1"/>
       <c r="BA513" s="1"/>
       <c r="BB513" s="1"/>
-      <c r="BC513" s="1" t="str">
+      <c r="BC513" s="1"/>
+      <c r="BD513" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34049,7 +34904,8 @@
       <c r="AZ514" s="1"/>
       <c r="BA514" s="1"/>
       <c r="BB514" s="1"/>
-      <c r="BC514" s="1" t="str">
+      <c r="BC514" s="1"/>
+      <c r="BD514" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34112,7 +34968,8 @@
       <c r="AZ515" s="1"/>
       <c r="BA515" s="1"/>
       <c r="BB515" s="1"/>
-      <c r="BC515" s="1" t="str">
+      <c r="BC515" s="1"/>
+      <c r="BD515" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34175,7 +35032,8 @@
       <c r="AZ516" s="1"/>
       <c r="BA516" s="1"/>
       <c r="BB516" s="1"/>
-      <c r="BC516" s="1" t="str">
+      <c r="BC516" s="1"/>
+      <c r="BD516" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34238,7 +35096,8 @@
       <c r="AZ517" s="1"/>
       <c r="BA517" s="1"/>
       <c r="BB517" s="1"/>
-      <c r="BC517" s="1" t="str">
+      <c r="BC517" s="1"/>
+      <c r="BD517" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34301,7 +35160,8 @@
       <c r="AZ518" s="1"/>
       <c r="BA518" s="1"/>
       <c r="BB518" s="1"/>
-      <c r="BC518" s="1" t="str">
+      <c r="BC518" s="1"/>
+      <c r="BD518" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34364,7 +35224,8 @@
       <c r="AZ519" s="1"/>
       <c r="BA519" s="1"/>
       <c r="BB519" s="1"/>
-      <c r="BC519" s="1" t="str">
+      <c r="BC519" s="1"/>
+      <c r="BD519" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34427,7 +35288,8 @@
       <c r="AZ520" s="1"/>
       <c r="BA520" s="1"/>
       <c r="BB520" s="1"/>
-      <c r="BC520" s="1" t="str">
+      <c r="BC520" s="1"/>
+      <c r="BD520" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34490,7 +35352,8 @@
       <c r="AZ521" s="1"/>
       <c r="BA521" s="1"/>
       <c r="BB521" s="1"/>
-      <c r="BC521" s="1" t="str">
+      <c r="BC521" s="1"/>
+      <c r="BD521" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34553,7 +35416,8 @@
       <c r="AZ522" s="1"/>
       <c r="BA522" s="1"/>
       <c r="BB522" s="1"/>
-      <c r="BC522" s="1" t="str">
+      <c r="BC522" s="1"/>
+      <c r="BD522" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34616,7 +35480,8 @@
       <c r="AZ523" s="1"/>
       <c r="BA523" s="1"/>
       <c r="BB523" s="1"/>
-      <c r="BC523" s="1" t="str">
+      <c r="BC523" s="1"/>
+      <c r="BD523" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34679,7 +35544,8 @@
       <c r="AZ524" s="1"/>
       <c r="BA524" s="1"/>
       <c r="BB524" s="1"/>
-      <c r="BC524" s="1" t="str">
+      <c r="BC524" s="1"/>
+      <c r="BD524" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34742,7 +35608,8 @@
       <c r="AZ525" s="1"/>
       <c r="BA525" s="1"/>
       <c r="BB525" s="1"/>
-      <c r="BC525" s="1" t="str">
+      <c r="BC525" s="1"/>
+      <c r="BD525" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34805,7 +35672,8 @@
       <c r="AZ526" s="1"/>
       <c r="BA526" s="1"/>
       <c r="BB526" s="1"/>
-      <c r="BC526" s="1" t="str">
+      <c r="BC526" s="1"/>
+      <c r="BD526" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34868,7 +35736,8 @@
       <c r="AZ527" s="1"/>
       <c r="BA527" s="1"/>
       <c r="BB527" s="1"/>
-      <c r="BC527" s="1" t="str">
+      <c r="BC527" s="1"/>
+      <c r="BD527" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34931,7 +35800,8 @@
       <c r="AZ528" s="1"/>
       <c r="BA528" s="1"/>
       <c r="BB528" s="1"/>
-      <c r="BC528" s="1" t="str">
+      <c r="BC528" s="1"/>
+      <c r="BD528" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34994,7 +35864,8 @@
       <c r="AZ529" s="1"/>
       <c r="BA529" s="1"/>
       <c r="BB529" s="1"/>
-      <c r="BC529" s="1" t="str">
+      <c r="BC529" s="1"/>
+      <c r="BD529" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35057,7 +35928,8 @@
       <c r="AZ530" s="1"/>
       <c r="BA530" s="1"/>
       <c r="BB530" s="1"/>
-      <c r="BC530" s="1" t="str">
+      <c r="BC530" s="1"/>
+      <c r="BD530" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35120,7 +35992,8 @@
       <c r="AZ531" s="1"/>
       <c r="BA531" s="1"/>
       <c r="BB531" s="1"/>
-      <c r="BC531" s="1" t="str">
+      <c r="BC531" s="1"/>
+      <c r="BD531" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35183,7 +36056,8 @@
       <c r="AZ532" s="1"/>
       <c r="BA532" s="1"/>
       <c r="BB532" s="1"/>
-      <c r="BC532" s="1" t="str">
+      <c r="BC532" s="1"/>
+      <c r="BD532" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35246,7 +36120,8 @@
       <c r="AZ533" s="1"/>
       <c r="BA533" s="1"/>
       <c r="BB533" s="1"/>
-      <c r="BC533" s="1" t="str">
+      <c r="BC533" s="1"/>
+      <c r="BD533" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35309,7 +36184,8 @@
       <c r="AZ534" s="1"/>
       <c r="BA534" s="1"/>
       <c r="BB534" s="1"/>
-      <c r="BC534" s="1" t="str">
+      <c r="BC534" s="1"/>
+      <c r="BD534" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35372,7 +36248,8 @@
       <c r="AZ535" s="1"/>
       <c r="BA535" s="1"/>
       <c r="BB535" s="1"/>
-      <c r="BC535" s="1" t="str">
+      <c r="BC535" s="1"/>
+      <c r="BD535" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35435,7 +36312,8 @@
       <c r="AZ536" s="1"/>
       <c r="BA536" s="1"/>
       <c r="BB536" s="1"/>
-      <c r="BC536" s="1" t="str">
+      <c r="BC536" s="1"/>
+      <c r="BD536" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35498,7 +36376,8 @@
       <c r="AZ537" s="1"/>
       <c r="BA537" s="1"/>
       <c r="BB537" s="1"/>
-      <c r="BC537" s="1" t="str">
+      <c r="BC537" s="1"/>
+      <c r="BD537" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35561,7 +36440,8 @@
       <c r="AZ538" s="1"/>
       <c r="BA538" s="1"/>
       <c r="BB538" s="1"/>
-      <c r="BC538" s="1" t="str">
+      <c r="BC538" s="1"/>
+      <c r="BD538" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35624,7 +36504,8 @@
       <c r="AZ539" s="1"/>
       <c r="BA539" s="1"/>
       <c r="BB539" s="1"/>
-      <c r="BC539" s="1" t="str">
+      <c r="BC539" s="1"/>
+      <c r="BD539" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35687,7 +36568,8 @@
       <c r="AZ540" s="1"/>
       <c r="BA540" s="1"/>
       <c r="BB540" s="1"/>
-      <c r="BC540" s="1" t="str">
+      <c r="BC540" s="1"/>
+      <c r="BD540" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35750,7 +36632,8 @@
       <c r="AZ541" s="1"/>
       <c r="BA541" s="1"/>
       <c r="BB541" s="1"/>
-      <c r="BC541" s="1" t="str">
+      <c r="BC541" s="1"/>
+      <c r="BD541" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35813,7 +36696,8 @@
       <c r="AZ542" s="1"/>
       <c r="BA542" s="1"/>
       <c r="BB542" s="1"/>
-      <c r="BC542" s="1" t="str">
+      <c r="BC542" s="1"/>
+      <c r="BD542" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35876,7 +36760,8 @@
       <c r="AZ543" s="1"/>
       <c r="BA543" s="1"/>
       <c r="BB543" s="1"/>
-      <c r="BC543" s="1" t="str">
+      <c r="BC543" s="1"/>
+      <c r="BD543" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35939,7 +36824,8 @@
       <c r="AZ544" s="1"/>
       <c r="BA544" s="1"/>
       <c r="BB544" s="1"/>
-      <c r="BC544" s="1" t="str">
+      <c r="BC544" s="1"/>
+      <c r="BD544" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36002,7 +36888,8 @@
       <c r="AZ545" s="1"/>
       <c r="BA545" s="1"/>
       <c r="BB545" s="1"/>
-      <c r="BC545" s="1" t="str">
+      <c r="BC545" s="1"/>
+      <c r="BD545" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36065,7 +36952,8 @@
       <c r="AZ546" s="1"/>
       <c r="BA546" s="1"/>
       <c r="BB546" s="1"/>
-      <c r="BC546" s="1" t="str">
+      <c r="BC546" s="1"/>
+      <c r="BD546" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36128,7 +37016,8 @@
       <c r="AZ547" s="1"/>
       <c r="BA547" s="1"/>
       <c r="BB547" s="1"/>
-      <c r="BC547" s="1" t="str">
+      <c r="BC547" s="1"/>
+      <c r="BD547" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36191,7 +37080,8 @@
       <c r="AZ548" s="1"/>
       <c r="BA548" s="1"/>
       <c r="BB548" s="1"/>
-      <c r="BC548" s="1" t="str">
+      <c r="BC548" s="1"/>
+      <c r="BD548" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36254,7 +37144,8 @@
       <c r="AZ549" s="1"/>
       <c r="BA549" s="1"/>
       <c r="BB549" s="1"/>
-      <c r="BC549" s="1" t="str">
+      <c r="BC549" s="1"/>
+      <c r="BD549" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36317,7 +37208,8 @@
       <c r="AZ550" s="1"/>
       <c r="BA550" s="1"/>
       <c r="BB550" s="1"/>
-      <c r="BC550" s="1" t="str">
+      <c r="BC550" s="1"/>
+      <c r="BD550" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36380,7 +37272,8 @@
       <c r="AZ551" s="1"/>
       <c r="BA551" s="1"/>
       <c r="BB551" s="1"/>
-      <c r="BC551" s="1" t="str">
+      <c r="BC551" s="1"/>
+      <c r="BD551" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36443,7 +37336,8 @@
       <c r="AZ552" s="1"/>
       <c r="BA552" s="1"/>
       <c r="BB552" s="1"/>
-      <c r="BC552" s="1" t="str">
+      <c r="BC552" s="1"/>
+      <c r="BD552" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36506,7 +37400,8 @@
       <c r="AZ553" s="1"/>
       <c r="BA553" s="1"/>
       <c r="BB553" s="1"/>
-      <c r="BC553" s="1" t="str">
+      <c r="BC553" s="1"/>
+      <c r="BD553" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36569,7 +37464,8 @@
       <c r="AZ554" s="1"/>
       <c r="BA554" s="1"/>
       <c r="BB554" s="1"/>
-      <c r="BC554" s="1" t="str">
+      <c r="BC554" s="1"/>
+      <c r="BD554" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36632,7 +37528,8 @@
       <c r="AZ555" s="1"/>
       <c r="BA555" s="1"/>
       <c r="BB555" s="1"/>
-      <c r="BC555" s="1" t="str">
+      <c r="BC555" s="1"/>
+      <c r="BD555" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36695,7 +37592,8 @@
       <c r="AZ556" s="1"/>
       <c r="BA556" s="1"/>
       <c r="BB556" s="1"/>
-      <c r="BC556" s="1" t="str">
+      <c r="BC556" s="1"/>
+      <c r="BD556" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36758,7 +37656,8 @@
       <c r="AZ557" s="1"/>
       <c r="BA557" s="1"/>
       <c r="BB557" s="1"/>
-      <c r="BC557" s="1" t="str">
+      <c r="BC557" s="1"/>
+      <c r="BD557" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36821,7 +37720,8 @@
       <c r="AZ558" s="1"/>
       <c r="BA558" s="1"/>
       <c r="BB558" s="1"/>
-      <c r="BC558" s="1" t="str">
+      <c r="BC558" s="1"/>
+      <c r="BD558" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36884,7 +37784,8 @@
       <c r="AZ559" s="1"/>
       <c r="BA559" s="1"/>
       <c r="BB559" s="1"/>
-      <c r="BC559" s="1" t="str">
+      <c r="BC559" s="1"/>
+      <c r="BD559" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36947,7 +37848,8 @@
       <c r="AZ560" s="1"/>
       <c r="BA560" s="1"/>
       <c r="BB560" s="1"/>
-      <c r="BC560" s="1" t="str">
+      <c r="BC560" s="1"/>
+      <c r="BD560" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37010,7 +37912,8 @@
       <c r="AZ561" s="1"/>
       <c r="BA561" s="1"/>
       <c r="BB561" s="1"/>
-      <c r="BC561" s="1" t="str">
+      <c r="BC561" s="1"/>
+      <c r="BD561" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37073,7 +37976,8 @@
       <c r="AZ562" s="1"/>
       <c r="BA562" s="1"/>
       <c r="BB562" s="1"/>
-      <c r="BC562" s="1" t="str">
+      <c r="BC562" s="1"/>
+      <c r="BD562" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37136,7 +38040,8 @@
       <c r="AZ563" s="1"/>
       <c r="BA563" s="1"/>
       <c r="BB563" s="1"/>
-      <c r="BC563" s="1" t="str">
+      <c r="BC563" s="1"/>
+      <c r="BD563" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37199,7 +38104,8 @@
       <c r="AZ564" s="1"/>
       <c r="BA564" s="1"/>
       <c r="BB564" s="1"/>
-      <c r="BC564" s="1" t="str">
+      <c r="BC564" s="1"/>
+      <c r="BD564" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37262,7 +38168,8 @@
       <c r="AZ565" s="1"/>
       <c r="BA565" s="1"/>
       <c r="BB565" s="1"/>
-      <c r="BC565" s="1" t="str">
+      <c r="BC565" s="1"/>
+      <c r="BD565" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37325,7 +38232,8 @@
       <c r="AZ566" s="1"/>
       <c r="BA566" s="1"/>
       <c r="BB566" s="1"/>
-      <c r="BC566" s="1" t="str">
+      <c r="BC566" s="1"/>
+      <c r="BD566" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37388,7 +38296,8 @@
       <c r="AZ567" s="1"/>
       <c r="BA567" s="1"/>
       <c r="BB567" s="1"/>
-      <c r="BC567" s="1" t="str">
+      <c r="BC567" s="1"/>
+      <c r="BD567" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37451,7 +38360,8 @@
       <c r="AZ568" s="1"/>
       <c r="BA568" s="1"/>
       <c r="BB568" s="1"/>
-      <c r="BC568" s="1" t="str">
+      <c r="BC568" s="1"/>
+      <c r="BD568" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37514,7 +38424,8 @@
       <c r="AZ569" s="1"/>
       <c r="BA569" s="1"/>
       <c r="BB569" s="1"/>
-      <c r="BC569" s="1" t="str">
+      <c r="BC569" s="1"/>
+      <c r="BD569" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37577,7 +38488,8 @@
       <c r="AZ570" s="1"/>
       <c r="BA570" s="1"/>
       <c r="BB570" s="1"/>
-      <c r="BC570" s="1" t="str">
+      <c r="BC570" s="1"/>
+      <c r="BD570" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37640,7 +38552,8 @@
       <c r="AZ571" s="1"/>
       <c r="BA571" s="1"/>
       <c r="BB571" s="1"/>
-      <c r="BC571" s="1" t="str">
+      <c r="BC571" s="1"/>
+      <c r="BD571" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37703,7 +38616,8 @@
       <c r="AZ572" s="1"/>
       <c r="BA572" s="1"/>
       <c r="BB572" s="1"/>
-      <c r="BC572" s="1" t="str">
+      <c r="BC572" s="1"/>
+      <c r="BD572" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37766,7 +38680,8 @@
       <c r="AZ573" s="1"/>
       <c r="BA573" s="1"/>
       <c r="BB573" s="1"/>
-      <c r="BC573" s="1" t="str">
+      <c r="BC573" s="1"/>
+      <c r="BD573" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37829,7 +38744,8 @@
       <c r="AZ574" s="1"/>
       <c r="BA574" s="1"/>
       <c r="BB574" s="1"/>
-      <c r="BC574" s="1" t="str">
+      <c r="BC574" s="1"/>
+      <c r="BD574" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37892,7 +38808,8 @@
       <c r="AZ575" s="1"/>
       <c r="BA575" s="1"/>
       <c r="BB575" s="1"/>
-      <c r="BC575" s="1" t="str">
+      <c r="BC575" s="1"/>
+      <c r="BD575" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37955,7 +38872,8 @@
       <c r="AZ576" s="1"/>
       <c r="BA576" s="1"/>
       <c r="BB576" s="1"/>
-      <c r="BC576" s="1" t="str">
+      <c r="BC576" s="1"/>
+      <c r="BD576" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38018,7 +38936,8 @@
       <c r="AZ577" s="1"/>
       <c r="BA577" s="1"/>
       <c r="BB577" s="1"/>
-      <c r="BC577" s="1" t="str">
+      <c r="BC577" s="1"/>
+      <c r="BD577" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38081,7 +39000,8 @@
       <c r="AZ578" s="1"/>
       <c r="BA578" s="1"/>
       <c r="BB578" s="1"/>
-      <c r="BC578" s="1" t="str">
+      <c r="BC578" s="1"/>
+      <c r="BD578" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38144,7 +39064,8 @@
       <c r="AZ579" s="1"/>
       <c r="BA579" s="1"/>
       <c r="BB579" s="1"/>
-      <c r="BC579" s="1" t="str">
+      <c r="BC579" s="1"/>
+      <c r="BD579" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38207,7 +39128,8 @@
       <c r="AZ580" s="1"/>
       <c r="BA580" s="1"/>
       <c r="BB580" s="1"/>
-      <c r="BC580" s="1" t="str">
+      <c r="BC580" s="1"/>
+      <c r="BD580" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38270,7 +39192,8 @@
       <c r="AZ581" s="1"/>
       <c r="BA581" s="1"/>
       <c r="BB581" s="1"/>
-      <c r="BC581" s="1" t="str">
+      <c r="BC581" s="1"/>
+      <c r="BD581" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38333,7 +39256,8 @@
       <c r="AZ582" s="1"/>
       <c r="BA582" s="1"/>
       <c r="BB582" s="1"/>
-      <c r="BC582" s="1" t="str">
+      <c r="BC582" s="1"/>
+      <c r="BD582" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38396,7 +39320,8 @@
       <c r="AZ583" s="1"/>
       <c r="BA583" s="1"/>
       <c r="BB583" s="1"/>
-      <c r="BC583" s="1" t="str">
+      <c r="BC583" s="1"/>
+      <c r="BD583" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38459,7 +39384,8 @@
       <c r="AZ584" s="1"/>
       <c r="BA584" s="1"/>
       <c r="BB584" s="1"/>
-      <c r="BC584" s="1" t="str">
+      <c r="BC584" s="1"/>
+      <c r="BD584" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38522,7 +39448,8 @@
       <c r="AZ585" s="1"/>
       <c r="BA585" s="1"/>
       <c r="BB585" s="1"/>
-      <c r="BC585" s="1" t="str">
+      <c r="BC585" s="1"/>
+      <c r="BD585" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38585,7 +39512,8 @@
       <c r="AZ586" s="1"/>
       <c r="BA586" s="1"/>
       <c r="BB586" s="1"/>
-      <c r="BC586" s="1" t="str">
+      <c r="BC586" s="1"/>
+      <c r="BD586" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38648,7 +39576,8 @@
       <c r="AZ587" s="1"/>
       <c r="BA587" s="1"/>
       <c r="BB587" s="1"/>
-      <c r="BC587" s="1" t="str">
+      <c r="BC587" s="1"/>
+      <c r="BD587" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38711,7 +39640,8 @@
       <c r="AZ588" s="1"/>
       <c r="BA588" s="1"/>
       <c r="BB588" s="1"/>
-      <c r="BC588" s="1" t="str">
+      <c r="BC588" s="1"/>
+      <c r="BD588" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38774,7 +39704,8 @@
       <c r="AZ589" s="1"/>
       <c r="BA589" s="1"/>
       <c r="BB589" s="1"/>
-      <c r="BC589" s="1" t="str">
+      <c r="BC589" s="1"/>
+      <c r="BD589" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38837,7 +39768,8 @@
       <c r="AZ590" s="1"/>
       <c r="BA590" s="1"/>
       <c r="BB590" s="1"/>
-      <c r="BC590" s="1" t="str">
+      <c r="BC590" s="1"/>
+      <c r="BD590" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38900,7 +39832,8 @@
       <c r="AZ591" s="1"/>
       <c r="BA591" s="1"/>
       <c r="BB591" s="1"/>
-      <c r="BC591" s="1" t="str">
+      <c r="BC591" s="1"/>
+      <c r="BD591" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38963,7 +39896,8 @@
       <c r="AZ592" s="1"/>
       <c r="BA592" s="1"/>
       <c r="BB592" s="1"/>
-      <c r="BC592" s="1" t="str">
+      <c r="BC592" s="1"/>
+      <c r="BD592" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39026,7 +39960,8 @@
       <c r="AZ593" s="1"/>
       <c r="BA593" s="1"/>
       <c r="BB593" s="1"/>
-      <c r="BC593" s="1" t="str">
+      <c r="BC593" s="1"/>
+      <c r="BD593" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39089,7 +40024,8 @@
       <c r="AZ594" s="1"/>
       <c r="BA594" s="1"/>
       <c r="BB594" s="1"/>
-      <c r="BC594" s="1" t="str">
+      <c r="BC594" s="1"/>
+      <c r="BD594" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39152,7 +40088,8 @@
       <c r="AZ595" s="1"/>
       <c r="BA595" s="1"/>
       <c r="BB595" s="1"/>
-      <c r="BC595" s="1" t="str">
+      <c r="BC595" s="1"/>
+      <c r="BD595" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39215,7 +40152,8 @@
       <c r="AZ596" s="1"/>
       <c r="BA596" s="1"/>
       <c r="BB596" s="1"/>
-      <c r="BC596" s="1" t="str">
+      <c r="BC596" s="1"/>
+      <c r="BD596" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39278,7 +40216,8 @@
       <c r="AZ597" s="1"/>
       <c r="BA597" s="1"/>
       <c r="BB597" s="1"/>
-      <c r="BC597" s="1" t="str">
+      <c r="BC597" s="1"/>
+      <c r="BD597" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39341,7 +40280,8 @@
       <c r="AZ598" s="1"/>
       <c r="BA598" s="1"/>
       <c r="BB598" s="1"/>
-      <c r="BC598" s="1" t="str">
+      <c r="BC598" s="1"/>
+      <c r="BD598" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39404,7 +40344,8 @@
       <c r="AZ599" s="1"/>
       <c r="BA599" s="1"/>
       <c r="BB599" s="1"/>
-      <c r="BC599" s="1" t="str">
+      <c r="BC599" s="1"/>
+      <c r="BD599" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39467,7 +40408,8 @@
       <c r="AZ600" s="1"/>
       <c r="BA600" s="1"/>
       <c r="BB600" s="1"/>
-      <c r="BC600" s="1" t="str">
+      <c r="BC600" s="1"/>
+      <c r="BD600" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39530,7 +40472,8 @@
       <c r="AZ601" s="1"/>
       <c r="BA601" s="1"/>
       <c r="BB601" s="1"/>
-      <c r="BC601" s="1" t="str">
+      <c r="BC601" s="1"/>
+      <c r="BD601" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39593,7 +40536,8 @@
       <c r="AZ602" s="1"/>
       <c r="BA602" s="1"/>
       <c r="BB602" s="1"/>
-      <c r="BC602" s="1" t="str">
+      <c r="BC602" s="1"/>
+      <c r="BD602" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39656,7 +40600,8 @@
       <c r="AZ603" s="1"/>
       <c r="BA603" s="1"/>
       <c r="BB603" s="1"/>
-      <c r="BC603" s="1" t="str">
+      <c r="BC603" s="1"/>
+      <c r="BD603" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39719,7 +40664,8 @@
       <c r="AZ604" s="1"/>
       <c r="BA604" s="1"/>
       <c r="BB604" s="1"/>
-      <c r="BC604" s="1" t="str">
+      <c r="BC604" s="1"/>
+      <c r="BD604" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39782,7 +40728,8 @@
       <c r="AZ605" s="1"/>
       <c r="BA605" s="1"/>
       <c r="BB605" s="1"/>
-      <c r="BC605" s="1" t="str">
+      <c r="BC605" s="1"/>
+      <c r="BD605" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39845,7 +40792,8 @@
       <c r="AZ606" s="1"/>
       <c r="BA606" s="1"/>
       <c r="BB606" s="1"/>
-      <c r="BC606" s="1" t="str">
+      <c r="BC606" s="1"/>
+      <c r="BD606" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39908,7 +40856,8 @@
       <c r="AZ607" s="1"/>
       <c r="BA607" s="1"/>
       <c r="BB607" s="1"/>
-      <c r="BC607" s="1" t="str">
+      <c r="BC607" s="1"/>
+      <c r="BD607" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39971,7 +40920,8 @@
       <c r="AZ608" s="1"/>
       <c r="BA608" s="1"/>
       <c r="BB608" s="1"/>
-      <c r="BC608" s="1" t="str">
+      <c r="BC608" s="1"/>
+      <c r="BD608" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40034,7 +40984,8 @@
       <c r="AZ609" s="1"/>
       <c r="BA609" s="1"/>
       <c r="BB609" s="1"/>
-      <c r="BC609" s="1" t="str">
+      <c r="BC609" s="1"/>
+      <c r="BD609" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40097,7 +41048,8 @@
       <c r="AZ610" s="1"/>
       <c r="BA610" s="1"/>
       <c r="BB610" s="1"/>
-      <c r="BC610" s="1" t="str">
+      <c r="BC610" s="1"/>
+      <c r="BD610" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40160,7 +41112,8 @@
       <c r="AZ611" s="1"/>
       <c r="BA611" s="1"/>
       <c r="BB611" s="1"/>
-      <c r="BC611" s="1" t="str">
+      <c r="BC611" s="1"/>
+      <c r="BD611" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40223,7 +41176,8 @@
       <c r="AZ612" s="1"/>
       <c r="BA612" s="1"/>
       <c r="BB612" s="1"/>
-      <c r="BC612" s="1" t="str">
+      <c r="BC612" s="1"/>
+      <c r="BD612" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40286,7 +41240,8 @@
       <c r="AZ613" s="1"/>
       <c r="BA613" s="1"/>
       <c r="BB613" s="1"/>
-      <c r="BC613" s="1" t="str">
+      <c r="BC613" s="1"/>
+      <c r="BD613" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40349,7 +41304,8 @@
       <c r="AZ614" s="1"/>
       <c r="BA614" s="1"/>
       <c r="BB614" s="1"/>
-      <c r="BC614" s="1" t="str">
+      <c r="BC614" s="1"/>
+      <c r="BD614" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40412,7 +41368,8 @@
       <c r="AZ615" s="1"/>
       <c r="BA615" s="1"/>
       <c r="BB615" s="1"/>
-      <c r="BC615" s="1" t="str">
+      <c r="BC615" s="1"/>
+      <c r="BD615" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40475,7 +41432,8 @@
       <c r="AZ616" s="1"/>
       <c r="BA616" s="1"/>
       <c r="BB616" s="1"/>
-      <c r="BC616" s="1" t="str">
+      <c r="BC616" s="1"/>
+      <c r="BD616" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40538,7 +41496,8 @@
       <c r="AZ617" s="1"/>
       <c r="BA617" s="1"/>
       <c r="BB617" s="1"/>
-      <c r="BC617" s="1" t="str">
+      <c r="BC617" s="1"/>
+      <c r="BD617" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40601,7 +41560,8 @@
       <c r="AZ618" s="1"/>
       <c r="BA618" s="1"/>
       <c r="BB618" s="1"/>
-      <c r="BC618" s="1" t="str">
+      <c r="BC618" s="1"/>
+      <c r="BD618" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40664,7 +41624,8 @@
       <c r="AZ619" s="1"/>
       <c r="BA619" s="1"/>
       <c r="BB619" s="1"/>
-      <c r="BC619" s="1" t="str">
+      <c r="BC619" s="1"/>
+      <c r="BD619" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40727,7 +41688,8 @@
       <c r="AZ620" s="1"/>
       <c r="BA620" s="1"/>
       <c r="BB620" s="1"/>
-      <c r="BC620" s="1" t="str">
+      <c r="BC620" s="1"/>
+      <c r="BD620" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40790,7 +41752,8 @@
       <c r="AZ621" s="1"/>
       <c r="BA621" s="1"/>
       <c r="BB621" s="1"/>
-      <c r="BC621" s="1" t="str">
+      <c r="BC621" s="1"/>
+      <c r="BD621" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40853,7 +41816,8 @@
       <c r="AZ622" s="1"/>
       <c r="BA622" s="1"/>
       <c r="BB622" s="1"/>
-      <c r="BC622" s="1" t="str">
+      <c r="BC622" s="1"/>
+      <c r="BD622" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40916,7 +41880,8 @@
       <c r="AZ623" s="1"/>
       <c r="BA623" s="1"/>
       <c r="BB623" s="1"/>
-      <c r="BC623" s="1" t="str">
+      <c r="BC623" s="1"/>
+      <c r="BD623" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40979,7 +41944,8 @@
       <c r="AZ624" s="1"/>
       <c r="BA624" s="1"/>
       <c r="BB624" s="1"/>
-      <c r="BC624" s="1" t="str">
+      <c r="BC624" s="1"/>
+      <c r="BD624" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41042,7 +42008,8 @@
       <c r="AZ625" s="1"/>
       <c r="BA625" s="1"/>
       <c r="BB625" s="1"/>
-      <c r="BC625" s="1" t="str">
+      <c r="BC625" s="1"/>
+      <c r="BD625" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41105,7 +42072,8 @@
       <c r="AZ626" s="1"/>
       <c r="BA626" s="1"/>
       <c r="BB626" s="1"/>
-      <c r="BC626" s="1" t="str">
+      <c r="BC626" s="1"/>
+      <c r="BD626" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41168,7 +42136,8 @@
       <c r="AZ627" s="1"/>
       <c r="BA627" s="1"/>
       <c r="BB627" s="1"/>
-      <c r="BC627" s="1" t="str">
+      <c r="BC627" s="1"/>
+      <c r="BD627" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41231,7 +42200,8 @@
       <c r="AZ628" s="1"/>
       <c r="BA628" s="1"/>
       <c r="BB628" s="1"/>
-      <c r="BC628" s="1" t="str">
+      <c r="BC628" s="1"/>
+      <c r="BD628" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41294,7 +42264,8 @@
       <c r="AZ629" s="1"/>
       <c r="BA629" s="1"/>
       <c r="BB629" s="1"/>
-      <c r="BC629" s="1" t="str">
+      <c r="BC629" s="1"/>
+      <c r="BD629" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41357,7 +42328,8 @@
       <c r="AZ630" s="1"/>
       <c r="BA630" s="1"/>
       <c r="BB630" s="1"/>
-      <c r="BC630" s="1" t="str">
+      <c r="BC630" s="1"/>
+      <c r="BD630" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41420,7 +42392,8 @@
       <c r="AZ631" s="1"/>
       <c r="BA631" s="1"/>
       <c r="BB631" s="1"/>
-      <c r="BC631" s="1" t="str">
+      <c r="BC631" s="1"/>
+      <c r="BD631" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41483,7 +42456,8 @@
       <c r="AZ632" s="1"/>
       <c r="BA632" s="1"/>
       <c r="BB632" s="1"/>
-      <c r="BC632" s="1" t="str">
+      <c r="BC632" s="1"/>
+      <c r="BD632" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41546,7 +42520,8 @@
       <c r="AZ633" s="1"/>
       <c r="BA633" s="1"/>
       <c r="BB633" s="1"/>
-      <c r="BC633" s="1" t="str">
+      <c r="BC633" s="1"/>
+      <c r="BD633" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41609,7 +42584,8 @@
       <c r="AZ634" s="1"/>
       <c r="BA634" s="1"/>
       <c r="BB634" s="1"/>
-      <c r="BC634" s="1" t="str">
+      <c r="BC634" s="1"/>
+      <c r="BD634" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41672,7 +42648,8 @@
       <c r="AZ635" s="1"/>
       <c r="BA635" s="1"/>
       <c r="BB635" s="1"/>
-      <c r="BC635" s="1" t="str">
+      <c r="BC635" s="1"/>
+      <c r="BD635" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41735,7 +42712,8 @@
       <c r="AZ636" s="1"/>
       <c r="BA636" s="1"/>
       <c r="BB636" s="1"/>
-      <c r="BC636" s="1" t="str">
+      <c r="BC636" s="1"/>
+      <c r="BD636" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41798,7 +42776,8 @@
       <c r="AZ637" s="1"/>
       <c r="BA637" s="1"/>
       <c r="BB637" s="1"/>
-      <c r="BC637" s="1" t="str">
+      <c r="BC637" s="1"/>
+      <c r="BD637" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41861,7 +42840,8 @@
       <c r="AZ638" s="1"/>
       <c r="BA638" s="1"/>
       <c r="BB638" s="1"/>
-      <c r="BC638" s="1" t="str">
+      <c r="BC638" s="1"/>
+      <c r="BD638" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41924,7 +42904,8 @@
       <c r="AZ639" s="1"/>
       <c r="BA639" s="1"/>
       <c r="BB639" s="1"/>
-      <c r="BC639" s="1" t="str">
+      <c r="BC639" s="1"/>
+      <c r="BD639" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41987,7 +42968,8 @@
       <c r="AZ640" s="1"/>
       <c r="BA640" s="1"/>
       <c r="BB640" s="1"/>
-      <c r="BC640" s="1" t="str">
+      <c r="BC640" s="1"/>
+      <c r="BD640" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42050,7 +43032,8 @@
       <c r="AZ641" s="1"/>
       <c r="BA641" s="1"/>
       <c r="BB641" s="1"/>
-      <c r="BC641" s="1" t="str">
+      <c r="BC641" s="1"/>
+      <c r="BD641" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42113,7 +43096,8 @@
       <c r="AZ642" s="1"/>
       <c r="BA642" s="1"/>
       <c r="BB642" s="1"/>
-      <c r="BC642" s="1" t="str">
+      <c r="BC642" s="1"/>
+      <c r="BD642" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42176,7 +43160,8 @@
       <c r="AZ643" s="1"/>
       <c r="BA643" s="1"/>
       <c r="BB643" s="1"/>
-      <c r="BC643" s="1" t="str">
+      <c r="BC643" s="1"/>
+      <c r="BD643" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42239,7 +43224,8 @@
       <c r="AZ644" s="1"/>
       <c r="BA644" s="1"/>
       <c r="BB644" s="1"/>
-      <c r="BC644" s="1" t="str">
+      <c r="BC644" s="1"/>
+      <c r="BD644" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42302,7 +43288,8 @@
       <c r="AZ645" s="1"/>
       <c r="BA645" s="1"/>
       <c r="BB645" s="1"/>
-      <c r="BC645" s="1" t="str">
+      <c r="BC645" s="1"/>
+      <c r="BD645" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42365,7 +43352,8 @@
       <c r="AZ646" s="1"/>
       <c r="BA646" s="1"/>
       <c r="BB646" s="1"/>
-      <c r="BC646" s="1" t="str">
+      <c r="BC646" s="1"/>
+      <c r="BD646" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42428,7 +43416,8 @@
       <c r="AZ647" s="1"/>
       <c r="BA647" s="1"/>
       <c r="BB647" s="1"/>
-      <c r="BC647" s="1" t="str">
+      <c r="BC647" s="1"/>
+      <c r="BD647" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42491,7 +43480,8 @@
       <c r="AZ648" s="1"/>
       <c r="BA648" s="1"/>
       <c r="BB648" s="1"/>
-      <c r="BC648" s="1" t="str">
+      <c r="BC648" s="1"/>
+      <c r="BD648" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42554,7 +43544,8 @@
       <c r="AZ649" s="1"/>
       <c r="BA649" s="1"/>
       <c r="BB649" s="1"/>
-      <c r="BC649" s="1" t="str">
+      <c r="BC649" s="1"/>
+      <c r="BD649" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42617,7 +43608,8 @@
       <c r="AZ650" s="1"/>
       <c r="BA650" s="1"/>
       <c r="BB650" s="1"/>
-      <c r="BC650" s="1" t="str">
+      <c r="BC650" s="1"/>
+      <c r="BD650" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42680,7 +43672,8 @@
       <c r="AZ651" s="1"/>
       <c r="BA651" s="1"/>
       <c r="BB651" s="1"/>
-      <c r="BC651" s="1" t="str">
+      <c r="BC651" s="1"/>
+      <c r="BD651" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42743,7 +43736,8 @@
       <c r="AZ652" s="1"/>
       <c r="BA652" s="1"/>
       <c r="BB652" s="1"/>
-      <c r="BC652" s="1" t="str">
+      <c r="BC652" s="1"/>
+      <c r="BD652" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42806,7 +43800,8 @@
       <c r="AZ653" s="1"/>
       <c r="BA653" s="1"/>
       <c r="BB653" s="1"/>
-      <c r="BC653" s="1" t="str">
+      <c r="BC653" s="1"/>
+      <c r="BD653" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42869,7 +43864,8 @@
       <c r="AZ654" s="1"/>
       <c r="BA654" s="1"/>
       <c r="BB654" s="1"/>
-      <c r="BC654" s="1" t="str">
+      <c r="BC654" s="1"/>
+      <c r="BD654" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42932,7 +43928,8 @@
       <c r="AZ655" s="1"/>
       <c r="BA655" s="1"/>
       <c r="BB655" s="1"/>
-      <c r="BC655" s="1" t="str">
+      <c r="BC655" s="1"/>
+      <c r="BD655" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42995,7 +43992,8 @@
       <c r="AZ656" s="1"/>
       <c r="BA656" s="1"/>
       <c r="BB656" s="1"/>
-      <c r="BC656" s="1" t="str">
+      <c r="BC656" s="1"/>
+      <c r="BD656" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43058,7 +44056,8 @@
       <c r="AZ657" s="1"/>
       <c r="BA657" s="1"/>
       <c r="BB657" s="1"/>
-      <c r="BC657" s="1" t="str">
+      <c r="BC657" s="1"/>
+      <c r="BD657" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43121,7 +44120,8 @@
       <c r="AZ658" s="1"/>
       <c r="BA658" s="1"/>
       <c r="BB658" s="1"/>
-      <c r="BC658" s="1" t="str">
+      <c r="BC658" s="1"/>
+      <c r="BD658" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43184,7 +44184,8 @@
       <c r="AZ659" s="1"/>
       <c r="BA659" s="1"/>
       <c r="BB659" s="1"/>
-      <c r="BC659" s="1" t="str">
+      <c r="BC659" s="1"/>
+      <c r="BD659" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43247,7 +44248,8 @@
       <c r="AZ660" s="1"/>
       <c r="BA660" s="1"/>
       <c r="BB660" s="1"/>
-      <c r="BC660" s="1" t="str">
+      <c r="BC660" s="1"/>
+      <c r="BD660" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43310,7 +44312,8 @@
       <c r="AZ661" s="1"/>
       <c r="BA661" s="1"/>
       <c r="BB661" s="1"/>
-      <c r="BC661" s="1" t="str">
+      <c r="BC661" s="1"/>
+      <c r="BD661" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43373,7 +44376,8 @@
       <c r="AZ662" s="1"/>
       <c r="BA662" s="1"/>
       <c r="BB662" s="1"/>
-      <c r="BC662" s="1" t="str">
+      <c r="BC662" s="1"/>
+      <c r="BD662" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43436,7 +44440,8 @@
       <c r="AZ663" s="1"/>
       <c r="BA663" s="1"/>
       <c r="BB663" s="1"/>
-      <c r="BC663" s="1" t="str">
+      <c r="BC663" s="1"/>
+      <c r="BD663" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43499,7 +44504,8 @@
       <c r="AZ664" s="1"/>
       <c r="BA664" s="1"/>
       <c r="BB664" s="1"/>
-      <c r="BC664" s="1" t="str">
+      <c r="BC664" s="1"/>
+      <c r="BD664" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43562,7 +44568,8 @@
       <c r="AZ665" s="1"/>
       <c r="BA665" s="1"/>
       <c r="BB665" s="1"/>
-      <c r="BC665" s="1" t="str">
+      <c r="BC665" s="1"/>
+      <c r="BD665" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43625,7 +44632,8 @@
       <c r="AZ666" s="1"/>
       <c r="BA666" s="1"/>
       <c r="BB666" s="1"/>
-      <c r="BC666" s="1" t="str">
+      <c r="BC666" s="1"/>
+      <c r="BD666" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43688,7 +44696,8 @@
       <c r="AZ667" s="1"/>
       <c r="BA667" s="1"/>
       <c r="BB667" s="1"/>
-      <c r="BC667" s="1" t="str">
+      <c r="BC667" s="1"/>
+      <c r="BD667" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43751,7 +44760,8 @@
       <c r="AZ668" s="1"/>
       <c r="BA668" s="1"/>
       <c r="BB668" s="1"/>
-      <c r="BC668" s="1" t="str">
+      <c r="BC668" s="1"/>
+      <c r="BD668" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43814,7 +44824,8 @@
       <c r="AZ669" s="1"/>
       <c r="BA669" s="1"/>
       <c r="BB669" s="1"/>
-      <c r="BC669" s="1" t="str">
+      <c r="BC669" s="1"/>
+      <c r="BD669" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43877,7 +44888,8 @@
       <c r="AZ670" s="1"/>
       <c r="BA670" s="1"/>
       <c r="BB670" s="1"/>
-      <c r="BC670" s="1" t="str">
+      <c r="BC670" s="1"/>
+      <c r="BD670" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43940,7 +44952,8 @@
       <c r="AZ671" s="1"/>
       <c r="BA671" s="1"/>
       <c r="BB671" s="1"/>
-      <c r="BC671" s="1" t="str">
+      <c r="BC671" s="1"/>
+      <c r="BD671" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44003,7 +45016,8 @@
       <c r="AZ672" s="1"/>
       <c r="BA672" s="1"/>
       <c r="BB672" s="1"/>
-      <c r="BC672" s="1" t="str">
+      <c r="BC672" s="1"/>
+      <c r="BD672" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44066,7 +45080,8 @@
       <c r="AZ673" s="1"/>
       <c r="BA673" s="1"/>
       <c r="BB673" s="1"/>
-      <c r="BC673" s="1" t="str">
+      <c r="BC673" s="1"/>
+      <c r="BD673" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44129,7 +45144,8 @@
       <c r="AZ674" s="1"/>
       <c r="BA674" s="1"/>
       <c r="BB674" s="1"/>
-      <c r="BC674" s="1" t="str">
+      <c r="BC674" s="1"/>
+      <c r="BD674" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44192,7 +45208,8 @@
       <c r="AZ675" s="1"/>
       <c r="BA675" s="1"/>
       <c r="BB675" s="1"/>
-      <c r="BC675" s="1" t="str">
+      <c r="BC675" s="1"/>
+      <c r="BD675" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44255,7 +45272,8 @@
       <c r="AZ676" s="1"/>
       <c r="BA676" s="1"/>
       <c r="BB676" s="1"/>
-      <c r="BC676" s="1" t="str">
+      <c r="BC676" s="1"/>
+      <c r="BD676" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44318,7 +45336,8 @@
       <c r="AZ677" s="1"/>
       <c r="BA677" s="1"/>
       <c r="BB677" s="1"/>
-      <c r="BC677" s="1" t="str">
+      <c r="BC677" s="1"/>
+      <c r="BD677" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44381,7 +45400,8 @@
       <c r="AZ678" s="1"/>
       <c r="BA678" s="1"/>
       <c r="BB678" s="1"/>
-      <c r="BC678" s="1" t="str">
+      <c r="BC678" s="1"/>
+      <c r="BD678" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44444,7 +45464,8 @@
       <c r="AZ679" s="1"/>
       <c r="BA679" s="1"/>
       <c r="BB679" s="1"/>
-      <c r="BC679" s="1" t="str">
+      <c r="BC679" s="1"/>
+      <c r="BD679" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44507,7 +45528,8 @@
       <c r="AZ680" s="1"/>
       <c r="BA680" s="1"/>
       <c r="BB680" s="1"/>
-      <c r="BC680" s="1" t="str">
+      <c r="BC680" s="1"/>
+      <c r="BD680" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44570,7 +45592,8 @@
       <c r="AZ681" s="1"/>
       <c r="BA681" s="1"/>
       <c r="BB681" s="1"/>
-      <c r="BC681" s="1" t="str">
+      <c r="BC681" s="1"/>
+      <c r="BD681" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44633,7 +45656,8 @@
       <c r="AZ682" s="1"/>
       <c r="BA682" s="1"/>
       <c r="BB682" s="1"/>
-      <c r="BC682" s="1" t="str">
+      <c r="BC682" s="1"/>
+      <c r="BD682" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44696,7 +45720,8 @@
       <c r="AZ683" s="1"/>
       <c r="BA683" s="1"/>
       <c r="BB683" s="1"/>
-      <c r="BC683" s="1" t="str">
+      <c r="BC683" s="1"/>
+      <c r="BD683" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44759,7 +45784,8 @@
       <c r="AZ684" s="1"/>
       <c r="BA684" s="1"/>
       <c r="BB684" s="1"/>
-      <c r="BC684" s="1" t="str">
+      <c r="BC684" s="1"/>
+      <c r="BD684" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44822,7 +45848,8 @@
       <c r="AZ685" s="1"/>
       <c r="BA685" s="1"/>
       <c r="BB685" s="1"/>
-      <c r="BC685" s="1" t="str">
+      <c r="BC685" s="1"/>
+      <c r="BD685" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44885,7 +45912,8 @@
       <c r="AZ686" s="1"/>
       <c r="BA686" s="1"/>
       <c r="BB686" s="1"/>
-      <c r="BC686" s="1" t="str">
+      <c r="BC686" s="1"/>
+      <c r="BD686" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44948,7 +45976,8 @@
       <c r="AZ687" s="1"/>
       <c r="BA687" s="1"/>
       <c r="BB687" s="1"/>
-      <c r="BC687" s="1" t="str">
+      <c r="BC687" s="1"/>
+      <c r="BD687" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45011,7 +46040,8 @@
       <c r="AZ688" s="1"/>
       <c r="BA688" s="1"/>
       <c r="BB688" s="1"/>
-      <c r="BC688" s="1" t="str">
+      <c r="BC688" s="1"/>
+      <c r="BD688" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45074,7 +46104,8 @@
       <c r="AZ689" s="1"/>
       <c r="BA689" s="1"/>
       <c r="BB689" s="1"/>
-      <c r="BC689" s="1" t="str">
+      <c r="BC689" s="1"/>
+      <c r="BD689" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45137,7 +46168,8 @@
       <c r="AZ690" s="1"/>
       <c r="BA690" s="1"/>
       <c r="BB690" s="1"/>
-      <c r="BC690" s="1" t="str">
+      <c r="BC690" s="1"/>
+      <c r="BD690" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45200,7 +46232,8 @@
       <c r="AZ691" s="1"/>
       <c r="BA691" s="1"/>
       <c r="BB691" s="1"/>
-      <c r="BC691" s="1" t="str">
+      <c r="BC691" s="1"/>
+      <c r="BD691" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45263,7 +46296,8 @@
       <c r="AZ692" s="1"/>
       <c r="BA692" s="1"/>
       <c r="BB692" s="1"/>
-      <c r="BC692" s="1" t="str">
+      <c r="BC692" s="1"/>
+      <c r="BD692" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45326,7 +46360,8 @@
       <c r="AZ693" s="1"/>
       <c r="BA693" s="1"/>
       <c r="BB693" s="1"/>
-      <c r="BC693" s="1" t="str">
+      <c r="BC693" s="1"/>
+      <c r="BD693" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45389,7 +46424,8 @@
       <c r="AZ694" s="1"/>
       <c r="BA694" s="1"/>
       <c r="BB694" s="1"/>
-      <c r="BC694" s="1" t="str">
+      <c r="BC694" s="1"/>
+      <c r="BD694" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45452,7 +46488,8 @@
       <c r="AZ695" s="1"/>
       <c r="BA695" s="1"/>
       <c r="BB695" s="1"/>
-      <c r="BC695" s="1" t="str">
+      <c r="BC695" s="1"/>
+      <c r="BD695" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45515,7 +46552,8 @@
       <c r="AZ696" s="1"/>
       <c r="BA696" s="1"/>
       <c r="BB696" s="1"/>
-      <c r="BC696" s="1" t="str">
+      <c r="BC696" s="1"/>
+      <c r="BD696" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45578,7 +46616,8 @@
       <c r="AZ697" s="1"/>
       <c r="BA697" s="1"/>
       <c r="BB697" s="1"/>
-      <c r="BC697" s="1" t="str">
+      <c r="BC697" s="1"/>
+      <c r="BD697" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45641,7 +46680,8 @@
       <c r="AZ698" s="1"/>
       <c r="BA698" s="1"/>
       <c r="BB698" s="1"/>
-      <c r="BC698" s="1" t="str">
+      <c r="BC698" s="1"/>
+      <c r="BD698" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45704,7 +46744,8 @@
       <c r="AZ699" s="1"/>
       <c r="BA699" s="1"/>
       <c r="BB699" s="1"/>
-      <c r="BC699" s="1" t="str">
+      <c r="BC699" s="1"/>
+      <c r="BD699" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45767,7 +46808,8 @@
       <c r="AZ700" s="1"/>
       <c r="BA700" s="1"/>
       <c r="BB700" s="1"/>
-      <c r="BC700" s="1" t="str">
+      <c r="BC700" s="1"/>
+      <c r="BD700" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>

--- a/DATA_VENTA26.1.xlsx
+++ b/DATA_VENTA26.1.xlsx
@@ -2386,12 +2386,12 @@
       </c>
       <c r="AB10" s="1"/>
       <c r="AC10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
+        <v>50</v>
+      </c>
+      <c r="AD10" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),95.0)</f>
         <v>95</v>
-      </c>
-      <c r="AD10" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
-        <v>50</v>
       </c>
       <c r="AE10" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1600.0)</f>
@@ -2606,12 +2606,12 @@
       </c>
       <c r="AB11" s="1"/>
       <c r="AC11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
+        <v>50</v>
+      </c>
+      <c r="AD11" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),95.0)</f>
         <v>95</v>
-      </c>
-      <c r="AD11" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
-        <v>50</v>
       </c>
       <c r="AE11" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1400.0)</f>
@@ -2719,128 +2719,431 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-      <c r="Q12" s="1"/>
-      <c r="R12" s="1"/>
-      <c r="S12" s="1"/>
-      <c r="T12" s="1"/>
-      <c r="U12" s="1"/>
-      <c r="V12" s="1"/>
-      <c r="W12" s="1"/>
-      <c r="X12" s="1"/>
+      <c r="A12" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
+        <v>11</v>
+      </c>
+      <c r="B12" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5223837.0)</f>
+        <v>5223837</v>
+      </c>
+      <c r="C12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0000427094")</f>
+        <v>0000427094</v>
+      </c>
+      <c r="D12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LEONELA SMITH ")</f>
+        <v>LEONELA SMITH </v>
+      </c>
+      <c r="E12" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SONCCO BALDEON")</f>
+        <v>SONCCO BALDEON</v>
+      </c>
+      <c r="F12" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0630529E7)</f>
+        <v>60630529</v>
+      </c>
+      <c r="G12" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.7019605E8)</f>
+        <v>970196050</v>
+      </c>
+      <c r="H12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"rinelabaldeon1@gmail.com")</f>
+        <v>rinelabaldeon1@gmail.com</v>
+      </c>
+      <c r="I12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Comunicación Audiovisual y Cine")</f>
+        <v>Comunicación Audiovisual y Cine</v>
+      </c>
+      <c r="J12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Comunicaciones")</f>
+        <v>Comunicaciones</v>
+      </c>
+      <c r="K12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Antigua")</f>
+        <v>Antigua</v>
+      </c>
+      <c r="L12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Admisión Ordinaria")</f>
+        <v>Admisión Ordinaria</v>
+      </c>
+      <c r="M12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Semi-presencial")</f>
+        <v>Semi-presencial</v>
+      </c>
+      <c r="N12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Diurno")</f>
+        <v>Diurno</v>
+      </c>
+      <c r="O12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NUEVO")</f>
+        <v>NUEVO</v>
+      </c>
+      <c r="P12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCALA REGULAR")</f>
+        <v>ESCALA REGULAR</v>
+      </c>
+      <c r="Q12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="R12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="S12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FABIOLA")</f>
+        <v>FABIOLA</v>
+      </c>
+      <c r="T12" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45806.0)</f>
+        <v>45806</v>
+      </c>
+      <c r="U12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO LINK")</f>
+        <v>PAGO LINK</v>
+      </c>
+      <c r="V12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO FRACCIONADO")</f>
+        <v>PAGO FRACCIONADO</v>
+      </c>
+      <c r="W12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1125.0)</f>
+        <v>1125</v>
+      </c>
+      <c r="X12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"20/06/2025")</f>
+        <v>20/06/2025</v>
+      </c>
       <c r="Y12" s="1"/>
-      <c r="Z12" s="1"/>
-      <c r="AA12" s="1"/>
+      <c r="Z12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO FRACCIONADO")</f>
+        <v>PAGO FRACCIONADO</v>
+      </c>
+      <c r="AA12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
+        <v>#N/A</v>
+      </c>
       <c r="AB12" s="1"/>
-      <c r="AC12" s="1"/>
-      <c r="AD12" s="1"/>
-      <c r="AE12" s="1"/>
-      <c r="AF12" s="1"/>
-      <c r="AG12" s="1"/>
-      <c r="AH12" s="1"/>
-      <c r="AI12" s="1"/>
-      <c r="AJ12" s="1"/>
-      <c r="AK12" s="1"/>
-      <c r="AL12" s="1"/>
-      <c r="AM12" s="1"/>
-      <c r="AN12" s="1"/>
-      <c r="AO12" s="1"/>
-      <c r="AP12" s="1"/>
-      <c r="AQ12" s="1"/>
-      <c r="AR12" s="1"/>
-      <c r="AS12" s="1"/>
-      <c r="AT12" s="1"/>
-      <c r="AU12" s="1"/>
-      <c r="AV12" s="1"/>
-      <c r="AW12" s="1"/>
-      <c r="AX12" s="1"/>
-      <c r="AY12" s="1"/>
-      <c r="AZ12" s="1"/>
-      <c r="BA12" s="1"/>
-      <c r="BB12" s="1"/>
-      <c r="BC12" s="1"/>
+      <c r="AC12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
+        <v>50</v>
+      </c>
+      <c r="AD12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),95.0)</f>
+        <v>95</v>
+      </c>
+      <c r="AE12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1500.0)</f>
+        <v>1500</v>
+      </c>
+      <c r="AF12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1500.0)</f>
+        <v>1500</v>
+      </c>
+      <c r="AG12" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH12" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI12" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),696963.0)</f>
+        <v>696963</v>
+      </c>
+      <c r="AK12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Más de 15 kms")</f>
+        <v>Más de 15 kms</v>
+      </c>
+      <c r="AL12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"05 301 a 550")</f>
+        <v>05 301 a 550</v>
+      </c>
+      <c r="AM12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0")</f>
+        <v>0</v>
+      </c>
+      <c r="AN12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="AO12" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2025.0)</f>
+        <v>2025</v>
+      </c>
+      <c r="AP12" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
+        <v>45778</v>
+      </c>
+      <c r="AQ12" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45775.0)</f>
+        <v>45775</v>
+      </c>
+      <c r="AR12" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45803.0)</f>
+        <v>45803</v>
+      </c>
+      <c r="AS12" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
+        <v>45778</v>
+      </c>
+      <c r="AT12" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45775.0)</f>
+        <v>45775</v>
+      </c>
+      <c r="AU12" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
+      <c r="AV12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIGITAL")</f>
+        <v>DIGITAL</v>
+      </c>
+      <c r="AW12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FORMULARIO")</f>
+        <v>FORMULARIO</v>
+      </c>
+      <c r="AX12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEARCH MARCA")</f>
+        <v>SEARCH MARCA</v>
+      </c>
+      <c r="AY12" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cinthia Mariella Orosco")</f>
+        <v>Cinthia Mariella Orosco</v>
+      </c>
+      <c r="BA12" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.3161094224924012)</f>
+        <v>0.3161094225</v>
+      </c>
+      <c r="BB12" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1500.0)</f>
+        <v>1500</v>
+      </c>
+      <c r="BC12" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="BD12" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
-      <c r="Q13" s="1"/>
-      <c r="R13" s="1"/>
-      <c r="S13" s="1"/>
-      <c r="T13" s="1"/>
-      <c r="U13" s="1"/>
-      <c r="V13" s="1"/>
-      <c r="W13" s="1"/>
+      <c r="A13" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
+        <v>12</v>
+      </c>
+      <c r="B13" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3309142.0)</f>
+        <v>3309142</v>
+      </c>
+      <c r="C13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0000427318")</f>
+        <v>0000427318</v>
+      </c>
+      <c r="D13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MARIA CLAUDIA")</f>
+        <v>MARIA CLAUDIA</v>
+      </c>
+      <c r="E13" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BEJARANO DAVILA")</f>
+        <v>BEJARANO DAVILA</v>
+      </c>
+      <c r="F13" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.1516154E7)</f>
+        <v>61516154</v>
+      </c>
+      <c r="G13" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.93655979E8)</f>
+        <v>993655979</v>
+      </c>
+      <c r="H13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"maclauwu@gmail.com")</f>
+        <v>maclauwu@gmail.com</v>
+      </c>
+      <c r="I13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Arquitectura de Interiores")</f>
+        <v>Arquitectura de Interiores</v>
+      </c>
+      <c r="J13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Arquitecturas")</f>
+        <v>Arquitecturas</v>
+      </c>
+      <c r="K13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Antigua")</f>
+        <v>Antigua</v>
+      </c>
+      <c r="L13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Admisión Ordinaria")</f>
+        <v>Admisión Ordinaria</v>
+      </c>
+      <c r="M13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Semi-presencial")</f>
+        <v>Semi-presencial</v>
+      </c>
+      <c r="N13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Diurno")</f>
+        <v>Diurno</v>
+      </c>
+      <c r="O13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NUEVO")</f>
+        <v>NUEVO</v>
+      </c>
+      <c r="P13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCALA REGULAR")</f>
+        <v>ESCALA REGULAR</v>
+      </c>
+      <c r="Q13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="R13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="S13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="T13" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45806.0)</f>
+        <v>45806</v>
+      </c>
+      <c r="U13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO LINK")</f>
+        <v>PAGO LINK</v>
+      </c>
+      <c r="V13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO FRACCIONADO")</f>
+        <v>PAGO FRACCIONADO</v>
+      </c>
+      <c r="W13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1595.0)</f>
+        <v>1595</v>
+      </c>
       <c r="X13" s="1"/>
       <c r="Y13" s="1"/>
-      <c r="Z13" s="1"/>
-      <c r="AA13" s="1"/>
+      <c r="Z13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO FRACCIONADO")</f>
+        <v>PAGO FRACCIONADO</v>
+      </c>
+      <c r="AA13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
+        <v>#N/A</v>
+      </c>
       <c r="AB13" s="1"/>
-      <c r="AC13" s="1"/>
-      <c r="AD13" s="1"/>
-      <c r="AE13" s="1"/>
-      <c r="AF13" s="1"/>
-      <c r="AG13" s="1"/>
-      <c r="AH13" s="1"/>
-      <c r="AI13" s="1"/>
-      <c r="AJ13" s="1"/>
+      <c r="AC13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
+        <v>50</v>
+      </c>
+      <c r="AD13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),95.0)</f>
+        <v>95</v>
+      </c>
+      <c r="AE13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1500.0)</f>
+        <v>1500</v>
+      </c>
+      <c r="AF13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1500.0)</f>
+        <v>1500</v>
+      </c>
+      <c r="AG13" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH13" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI13" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),693614.0)</f>
+        <v>693614</v>
+      </c>
       <c r="AK13" s="1"/>
       <c r="AL13" s="1"/>
-      <c r="AM13" s="1"/>
-      <c r="AN13" s="1"/>
-      <c r="AO13" s="1"/>
-      <c r="AP13" s="1"/>
-      <c r="AQ13" s="1"/>
-      <c r="AR13" s="1"/>
-      <c r="AS13" s="1"/>
-      <c r="AT13" s="1"/>
-      <c r="AU13" s="1"/>
-      <c r="AV13" s="1"/>
-      <c r="AW13" s="1"/>
-      <c r="AX13" s="1"/>
-      <c r="AY13" s="1"/>
-      <c r="AZ13" s="1"/>
-      <c r="BA13" s="1"/>
-      <c r="BB13" s="1"/>
-      <c r="BC13" s="1"/>
+      <c r="AM13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0")</f>
+        <v>0</v>
+      </c>
+      <c r="AN13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="AO13" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2025.0)</f>
+        <v>2025</v>
+      </c>
+      <c r="AP13" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
+        <v>45778</v>
+      </c>
+      <c r="AQ13" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45775.0)</f>
+        <v>45775</v>
+      </c>
+      <c r="AR13" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45804.0)</f>
+        <v>45804</v>
+      </c>
+      <c r="AS13" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
+        <v>45778</v>
+      </c>
+      <c r="AT13" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45775.0)</f>
+        <v>45775</v>
+      </c>
+      <c r="AU13" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+      <c r="AV13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TRADICIONAL")</f>
+        <v>TRADICIONAL</v>
+      </c>
+      <c r="AW13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COLEGIOS")</f>
+        <v>COLEGIOS</v>
+      </c>
+      <c r="AX13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COLEGIOS")</f>
+        <v>COLEGIOS</v>
+      </c>
+      <c r="AY13" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cinthia Mariella Orosco")</f>
+        <v>Cinthia Mariella Orosco</v>
+      </c>
+      <c r="BA13" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.030395136778115502)</f>
+        <v>0.03039513678</v>
+      </c>
+      <c r="BB13" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1500.0)</f>
+        <v>1500</v>
+      </c>
+      <c r="BC13" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="BD13" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>

--- a/DATA_VENTA26.1.xlsx
+++ b/DATA_VENTA26.1.xlsx
@@ -3031,7 +3031,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1595.0)</f>
         <v>1595</v>
       </c>
-      <c r="X13" s="1"/>
+      <c r="X13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
       <c r="Y13" s="1"/>
       <c r="Z13" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO FRACCIONADO")</f>
@@ -3155,59 +3158,209 @@
         <v/>
       </c>
       <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
-      <c r="R14" s="1"/>
-      <c r="S14" s="1"/>
-      <c r="T14" s="1"/>
-      <c r="U14" s="1"/>
-      <c r="V14" s="1"/>
-      <c r="W14" s="1"/>
-      <c r="X14" s="1"/>
-      <c r="Y14" s="1"/>
-      <c r="Z14" s="1"/>
-      <c r="AA14" s="1"/>
+      <c r="C14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0000427368")</f>
+        <v>0000427368</v>
+      </c>
+      <c r="D14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DOMÉNICA PAOLA ")</f>
+        <v>DOMÉNICA PAOLA </v>
+      </c>
+      <c r="E14" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GÓMEZ ORÉ")</f>
+        <v>GÓMEZ ORÉ</v>
+      </c>
+      <c r="F14" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.1684165E7)</f>
+        <v>71684165</v>
+      </c>
+      <c r="G14" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.08559699E8)</f>
+        <v>908559699</v>
+      </c>
+      <c r="H14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Domenicapaolagomezore@gmail.com")</f>
+        <v>Domenicapaolagomezore@gmail.com</v>
+      </c>
+      <c r="I14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Comunicación Audiovisual y Cine")</f>
+        <v>Comunicación Audiovisual y Cine</v>
+      </c>
+      <c r="J14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Comunicaciones")</f>
+        <v>Comunicaciones</v>
+      </c>
+      <c r="K14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Antigua")</f>
+        <v>Antigua</v>
+      </c>
+      <c r="L14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Admisión Ordinaria")</f>
+        <v>Admisión Ordinaria</v>
+      </c>
+      <c r="M14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Semi-presencial")</f>
+        <v>Semi-presencial</v>
+      </c>
+      <c r="N14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Diurno")</f>
+        <v>Diurno</v>
+      </c>
+      <c r="O14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NUEVO")</f>
+        <v>NUEVO</v>
+      </c>
+      <c r="P14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCALA REGULAR")</f>
+        <v>ESCALA REGULAR</v>
+      </c>
+      <c r="Q14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="R14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Pago BBVA")</f>
+        <v>Pago BBVA</v>
+      </c>
+      <c r="S14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FABIOLA")</f>
+        <v>FABIOLA</v>
+      </c>
+      <c r="T14" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45807.0)</f>
+        <v>45807</v>
+      </c>
+      <c r="U14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Pago Link")</f>
+        <v>Pago Link</v>
+      </c>
+      <c r="V14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="W14" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="X14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="Y14" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45807.0)</f>
+        <v>45807</v>
+      </c>
+      <c r="Z14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="AA14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
+        <v>#N/A</v>
+      </c>
       <c r="AB14" s="1"/>
-      <c r="AC14" s="1"/>
-      <c r="AD14" s="1"/>
-      <c r="AE14" s="1"/>
-      <c r="AF14" s="1"/>
-      <c r="AG14" s="1"/>
-      <c r="AH14" s="1"/>
-      <c r="AI14" s="1"/>
-      <c r="AJ14" s="1"/>
+      <c r="AC14" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
+        <v>50</v>
+      </c>
+      <c r="AD14" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),95.0)</f>
+        <v>95</v>
+      </c>
+      <c r="AE14" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1500.0)</f>
+        <v>1500</v>
+      </c>
+      <c r="AF14" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1500.0)</f>
+        <v>1500</v>
+      </c>
+      <c r="AG14" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH14" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI14" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),500249.0)</f>
+        <v>500249</v>
+      </c>
       <c r="AK14" s="1"/>
       <c r="AL14" s="1"/>
-      <c r="AM14" s="1"/>
-      <c r="AN14" s="1"/>
-      <c r="AO14" s="1"/>
-      <c r="AP14" s="1"/>
-      <c r="AQ14" s="1"/>
-      <c r="AR14" s="1"/>
-      <c r="AS14" s="1"/>
-      <c r="AT14" s="1"/>
-      <c r="AU14" s="1"/>
-      <c r="AV14" s="1"/>
-      <c r="AW14" s="1"/>
-      <c r="AX14" s="1"/>
-      <c r="AY14" s="1"/>
-      <c r="AZ14" s="1"/>
-      <c r="BA14" s="1"/>
-      <c r="BB14" s="1"/>
-      <c r="BC14" s="1"/>
+      <c r="AM14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0")</f>
+        <v>0</v>
+      </c>
+      <c r="AN14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="AO14" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2025.0)</f>
+        <v>2025</v>
+      </c>
+      <c r="AP14" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
+        <v>45778</v>
+      </c>
+      <c r="AQ14" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45775.0)</f>
+        <v>45775</v>
+      </c>
+      <c r="AR14" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45801.0)</f>
+        <v>45801</v>
+      </c>
+      <c r="AS14" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
+        <v>45778</v>
+      </c>
+      <c r="AT14" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45775.0)</f>
+        <v>45775</v>
+      </c>
+      <c r="AU14" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
+        <v>6</v>
+      </c>
+      <c r="AV14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIGITAL")</f>
+        <v>DIGITAL</v>
+      </c>
+      <c r="AW14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BIDIRECCIONAL")</f>
+        <v>BIDIRECCIONAL</v>
+      </c>
+      <c r="AX14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ORGANICO")</f>
+        <v>ORGANICO</v>
+      </c>
+      <c r="AY14" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cinthia Mariella Orosco")</f>
+        <v>Cinthia Mariella Orosco</v>
+      </c>
+      <c r="BA14" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BB14" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1500.0)</f>
+        <v>1500</v>
+      </c>
+      <c r="BC14" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="BD14" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
@@ -3219,123 +3372,432 @@
         <v/>
       </c>
       <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
-      <c r="Q15" s="1"/>
-      <c r="R15" s="1"/>
-      <c r="S15" s="1"/>
-      <c r="T15" s="1"/>
-      <c r="U15" s="1"/>
-      <c r="V15" s="1"/>
-      <c r="W15" s="1"/>
-      <c r="X15" s="1"/>
-      <c r="Y15" s="1"/>
-      <c r="Z15" s="1"/>
-      <c r="AA15" s="1"/>
+      <c r="C15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0000427439")</f>
+        <v>0000427439</v>
+      </c>
+      <c r="D15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIS ANGEL")</f>
+        <v>LUIS ANGEL</v>
+      </c>
+      <c r="E15" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"OSVEN ARANDA")</f>
+        <v>OSVEN ARANDA</v>
+      </c>
+      <c r="F15" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1259267E7)</f>
+        <v>41259267</v>
+      </c>
+      <c r="G15" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.18851982E8)</f>
+        <v>918851982</v>
+      </c>
+      <c r="H15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"osven.sac@gmail.com")</f>
+        <v>osven.sac@gmail.com</v>
+      </c>
+      <c r="I15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Arquitectura")</f>
+        <v>Arquitectura</v>
+      </c>
+      <c r="J15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Arquitecturas")</f>
+        <v>Arquitecturas</v>
+      </c>
+      <c r="K15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Antigua")</f>
+        <v>Antigua</v>
+      </c>
+      <c r="L15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Admisión Ordinaria")</f>
+        <v>Admisión Ordinaria</v>
+      </c>
+      <c r="M15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Semi-presencial")</f>
+        <v>Semi-presencial</v>
+      </c>
+      <c r="N15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Diurno")</f>
+        <v>Diurno</v>
+      </c>
+      <c r="O15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NUEVO")</f>
+        <v>NUEVO</v>
+      </c>
+      <c r="P15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCALA REGULAR")</f>
+        <v>ESCALA REGULAR</v>
+      </c>
+      <c r="Q15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="R15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="S15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="T15" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45807.0)</f>
+        <v>45807</v>
+      </c>
+      <c r="U15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"POS")</f>
+        <v>POS</v>
+      </c>
+      <c r="V15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="W15" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="X15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="Y15" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45807.0)</f>
+        <v>45807</v>
+      </c>
+      <c r="Z15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="AA15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
+        <v>#N/A</v>
+      </c>
       <c r="AB15" s="1"/>
-      <c r="AC15" s="1"/>
-      <c r="AD15" s="1"/>
-      <c r="AE15" s="1"/>
-      <c r="AF15" s="1"/>
-      <c r="AG15" s="1"/>
-      <c r="AH15" s="1"/>
-      <c r="AI15" s="1"/>
-      <c r="AJ15" s="1"/>
+      <c r="AC15" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),850.0)</f>
+        <v>850</v>
+      </c>
+      <c r="AD15" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE15" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),850.0)</f>
+        <v>850</v>
+      </c>
+      <c r="AF15" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),850.0)</f>
+        <v>850</v>
+      </c>
+      <c r="AG15" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH15" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI15" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="AK15" s="1"/>
       <c r="AL15" s="1"/>
-      <c r="AM15" s="1"/>
-      <c r="AN15" s="1"/>
-      <c r="AO15" s="1"/>
-      <c r="AP15" s="1"/>
-      <c r="AQ15" s="1"/>
-      <c r="AR15" s="1"/>
-      <c r="AS15" s="1"/>
-      <c r="AT15" s="1"/>
-      <c r="AU15" s="1"/>
-      <c r="AV15" s="1"/>
-      <c r="AW15" s="1"/>
-      <c r="AX15" s="1"/>
-      <c r="AY15" s="1"/>
-      <c r="AZ15" s="1"/>
-      <c r="BA15" s="1"/>
-      <c r="BB15" s="1"/>
-      <c r="BC15" s="1"/>
+      <c r="AM15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0")</f>
+        <v>0</v>
+      </c>
+      <c r="AN15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="AO15" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1998.0)</f>
+        <v>1998</v>
+      </c>
+      <c r="AP15" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
+        <v>45778</v>
+      </c>
+      <c r="AQ15" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45775.0)</f>
+        <v>45775</v>
+      </c>
+      <c r="AR15" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45801.0)</f>
+        <v>45801</v>
+      </c>
+      <c r="AS15" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
+        <v>45778</v>
+      </c>
+      <c r="AT15" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45775.0)</f>
+        <v>45775</v>
+      </c>
+      <c r="AU15" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
+        <v>6</v>
+      </c>
+      <c r="AV15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIGITAL")</f>
+        <v>DIGITAL</v>
+      </c>
+      <c r="AW15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BIDIRECCIONAL")</f>
+        <v>BIDIRECCIONAL</v>
+      </c>
+      <c r="AX15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ORGANICO")</f>
+        <v>ORGANICO</v>
+      </c>
+      <c r="AY15" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Meri Ricalde")</f>
+        <v>Meri Ricalde</v>
+      </c>
+      <c r="BA15" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BB15" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),850.0)</f>
+        <v>850</v>
+      </c>
+      <c r="BC15" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="BD15" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1"/>
-      <c r="S16" s="1"/>
-      <c r="T16" s="1"/>
-      <c r="U16" s="1"/>
-      <c r="V16" s="1"/>
-      <c r="W16" s="1"/>
-      <c r="X16" s="1"/>
-      <c r="Y16" s="1"/>
-      <c r="Z16" s="1"/>
-      <c r="AA16" s="1"/>
+      <c r="A16" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="B16" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1478516.0)</f>
+        <v>1478516</v>
+      </c>
+      <c r="C16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0000427548")</f>
+        <v>0000427548</v>
+      </c>
+      <c r="D16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"JADE ALESSANDRA ")</f>
+        <v>JADE ALESSANDRA </v>
+      </c>
+      <c r="E16" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," HUAMANI CALDERON")</f>
+        <v> HUAMANI CALDERON</v>
+      </c>
+      <c r="F16" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.2064162E7)</f>
+        <v>72064162</v>
+      </c>
+      <c r="G16" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.84124408E8)</f>
+        <v>984124408</v>
+      </c>
+      <c r="H16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"jade.iiriss@gmail.com")</f>
+        <v>jade.iiriss@gmail.com</v>
+      </c>
+      <c r="I16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Comunicación Audiovisual y Cine")</f>
+        <v>Comunicación Audiovisual y Cine</v>
+      </c>
+      <c r="J16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Comunicaciones")</f>
+        <v>Comunicaciones</v>
+      </c>
+      <c r="K16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Antigua")</f>
+        <v>Antigua</v>
+      </c>
+      <c r="L16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Admisión de Alto Rendimiento")</f>
+        <v>Admisión de Alto Rendimiento</v>
+      </c>
+      <c r="M16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Semi-presencial")</f>
+        <v>Semi-presencial</v>
+      </c>
+      <c r="N16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Diurno")</f>
+        <v>Diurno</v>
+      </c>
+      <c r="O16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NUEVO")</f>
+        <v>NUEVO</v>
+      </c>
+      <c r="P16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCALA REGULAR")</f>
+        <v>ESCALA REGULAR</v>
+      </c>
+      <c r="Q16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="R16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="S16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="T16" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45808.0)</f>
+        <v>45808</v>
+      </c>
+      <c r="U16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARGO")</f>
+        <v>CARGO</v>
+      </c>
+      <c r="V16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="W16" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="X16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="Y16" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45808.0)</f>
+        <v>45808</v>
+      </c>
+      <c r="Z16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="AA16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
+        <v>#N/A</v>
+      </c>
       <c r="AB16" s="1"/>
-      <c r="AC16" s="1"/>
-      <c r="AD16" s="1"/>
-      <c r="AE16" s="1"/>
-      <c r="AF16" s="1"/>
-      <c r="AG16" s="1"/>
-      <c r="AH16" s="1"/>
-      <c r="AI16" s="1"/>
-      <c r="AJ16" s="1"/>
-      <c r="AK16" s="1"/>
-      <c r="AL16" s="1"/>
-      <c r="AM16" s="1"/>
-      <c r="AN16" s="1"/>
-      <c r="AO16" s="1"/>
-      <c r="AP16" s="1"/>
-      <c r="AQ16" s="1"/>
-      <c r="AR16" s="1"/>
-      <c r="AS16" s="1"/>
-      <c r="AT16" s="1"/>
-      <c r="AU16" s="1"/>
-      <c r="AV16" s="1"/>
-      <c r="AW16" s="1"/>
-      <c r="AX16" s="1"/>
-      <c r="AY16" s="1"/>
-      <c r="AZ16" s="1"/>
-      <c r="BA16" s="1"/>
-      <c r="BB16" s="1"/>
-      <c r="BC16" s="1"/>
+      <c r="AC16" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
+        <v>50</v>
+      </c>
+      <c r="AD16" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),95.0)</f>
+        <v>95</v>
+      </c>
+      <c r="AE16" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1500.0)</f>
+        <v>1500</v>
+      </c>
+      <c r="AF16" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1500.0)</f>
+        <v>1500</v>
+      </c>
+      <c r="AG16" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH16" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI16" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1640671.0)</f>
+        <v>1640671</v>
+      </c>
+      <c r="AK16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"5kms a 10 kms")</f>
+        <v>5kms a 10 kms</v>
+      </c>
+      <c r="AL16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"06 551 a 800")</f>
+        <v>06 551 a 800</v>
+      </c>
+      <c r="AM16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0")</f>
+        <v>0</v>
+      </c>
+      <c r="AN16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="AO16" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2025.0)</f>
+        <v>2025</v>
+      </c>
+      <c r="AP16" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
+        <v>45778</v>
+      </c>
+      <c r="AQ16" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45775.0)</f>
+        <v>45775</v>
+      </c>
+      <c r="AR16" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45762.0)</f>
+        <v>45762</v>
+      </c>
+      <c r="AS16" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45748.0)</f>
+        <v>45748</v>
+      </c>
+      <c r="AT16" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45747.0)</f>
+        <v>45747</v>
+      </c>
+      <c r="AU16" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.0)</f>
+        <v>46</v>
+      </c>
+      <c r="AV16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TRADICIONAL")</f>
+        <v>TRADICIONAL</v>
+      </c>
+      <c r="AW16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VISITA")</f>
+        <v>VISITA</v>
+      </c>
+      <c r="AX16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VISITA")</f>
+        <v>VISITA</v>
+      </c>
+      <c r="AY16" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Daniel Zapata")</f>
+        <v>Daniel Zapata</v>
+      </c>
+      <c r="BA16" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BB16" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1500.0)</f>
+        <v>1500</v>
+      </c>
+      <c r="BC16" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="BD16" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
@@ -3347,59 +3809,209 @@
         <v/>
       </c>
       <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-      <c r="Q17" s="1"/>
-      <c r="R17" s="1"/>
-      <c r="S17" s="1"/>
-      <c r="T17" s="1"/>
-      <c r="U17" s="1"/>
-      <c r="V17" s="1"/>
-      <c r="W17" s="1"/>
-      <c r="X17" s="1"/>
-      <c r="Y17" s="1"/>
-      <c r="Z17" s="1"/>
-      <c r="AA17" s="1"/>
+      <c r="C17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0000427599")</f>
+        <v>0000427599</v>
+      </c>
+      <c r="D17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIS MIGUEL ANTHONY ")</f>
+        <v>LUIS MIGUEL ANTHONY </v>
+      </c>
+      <c r="E17" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TARRILLO BARBOZA")</f>
+        <v>TARRILLO BARBOZA</v>
+      </c>
+      <c r="F17" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.3162077E7)</f>
+        <v>73162077</v>
+      </c>
+      <c r="G17" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.16083982E8)</f>
+        <v>916083982</v>
+      </c>
+      <c r="H17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"anthonytb335@gmail.com")</f>
+        <v>anthonytb335@gmail.com</v>
+      </c>
+      <c r="I17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Administración y Negocios Internacionales")</f>
+        <v>Administración y Negocios Internacionales</v>
+      </c>
+      <c r="J17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Negocios")</f>
+        <v>Negocios</v>
+      </c>
+      <c r="K17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Nueva")</f>
+        <v>Nueva</v>
+      </c>
+      <c r="L17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Admisión de Alto Rendimiento")</f>
+        <v>Admisión de Alto Rendimiento</v>
+      </c>
+      <c r="M17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Semi-presencial")</f>
+        <v>Semi-presencial</v>
+      </c>
+      <c r="N17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Diurno")</f>
+        <v>Diurno</v>
+      </c>
+      <c r="O17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NUEVO")</f>
+        <v>NUEVO</v>
+      </c>
+      <c r="P17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCALA REGULAR")</f>
+        <v>ESCALA REGULAR</v>
+      </c>
+      <c r="Q17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="R17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="S17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="T17" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45809.0)</f>
+        <v>45809</v>
+      </c>
+      <c r="U17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARGO")</f>
+        <v>CARGO</v>
+      </c>
+      <c r="V17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="W17" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="X17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="Y17" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45809.0)</f>
+        <v>45809</v>
+      </c>
+      <c r="Z17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="AA17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
+        <v>#N/A</v>
+      </c>
       <c r="AB17" s="1"/>
-      <c r="AC17" s="1"/>
-      <c r="AD17" s="1"/>
-      <c r="AE17" s="1"/>
-      <c r="AF17" s="1"/>
-      <c r="AG17" s="1"/>
-      <c r="AH17" s="1"/>
-      <c r="AI17" s="1"/>
-      <c r="AJ17" s="1"/>
+      <c r="AC17" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
+        <v>50</v>
+      </c>
+      <c r="AD17" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),95.0)</f>
+        <v>95</v>
+      </c>
+      <c r="AE17" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1350.0)</f>
+        <v>1350</v>
+      </c>
+      <c r="AF17" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1350.0)</f>
+        <v>1350</v>
+      </c>
+      <c r="AG17" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH17" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI17" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1507789.0)</f>
+        <v>1507789</v>
+      </c>
       <c r="AK17" s="1"/>
       <c r="AL17" s="1"/>
-      <c r="AM17" s="1"/>
-      <c r="AN17" s="1"/>
-      <c r="AO17" s="1"/>
-      <c r="AP17" s="1"/>
-      <c r="AQ17" s="1"/>
-      <c r="AR17" s="1"/>
-      <c r="AS17" s="1"/>
-      <c r="AT17" s="1"/>
-      <c r="AU17" s="1"/>
-      <c r="AV17" s="1"/>
-      <c r="AW17" s="1"/>
-      <c r="AX17" s="1"/>
-      <c r="AY17" s="1"/>
-      <c r="AZ17" s="1"/>
-      <c r="BA17" s="1"/>
-      <c r="BB17" s="1"/>
-      <c r="BC17" s="1"/>
+      <c r="AM17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0")</f>
+        <v>0</v>
+      </c>
+      <c r="AN17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="AO17" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2025.0)</f>
+        <v>2025</v>
+      </c>
+      <c r="AP17" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45809.0)</f>
+        <v>45809</v>
+      </c>
+      <c r="AQ17" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45803.0)</f>
+        <v>45803</v>
+      </c>
+      <c r="AR17" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45806.0)</f>
+        <v>45806</v>
+      </c>
+      <c r="AS17" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
+        <v>45778</v>
+      </c>
+      <c r="AT17" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45775.0)</f>
+        <v>45775</v>
+      </c>
+      <c r="AU17" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
+      <c r="AV17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TRADICIONAL")</f>
+        <v>TRADICIONAL</v>
+      </c>
+      <c r="AW17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COLEGIOS")</f>
+        <v>COLEGIOS</v>
+      </c>
+      <c r="AX17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COLEGIOS")</f>
+        <v>COLEGIOS</v>
+      </c>
+      <c r="AY17" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Daniel Zapata")</f>
+        <v>Daniel Zapata</v>
+      </c>
+      <c r="BA17" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BB17" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1350.0)</f>
+        <v>1350</v>
+      </c>
+      <c r="BC17" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="BD17" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>

--- a/DATA_VENTA26.1.xlsx
+++ b/DATA_VENTA26.1.xlsx
@@ -285,8 +285,8 @@
         <v>ID CAMPUS</v>
       </c>
       <c r="D1" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NOMBRES")</f>
-        <v>NOMBRES</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NOMBRE")</f>
+        <v>NOMBRE</v>
       </c>
       <c r="E1" s="2" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"APELLIDOS")</f>
@@ -606,7 +606,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
         <v>#N/A</v>
       </c>
-      <c r="AB2" s="1"/>
+      <c r="AB2" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
       <c r="AC2" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -829,7 +832,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
         <v>#N/A</v>
       </c>
-      <c r="AB3" s="1"/>
+      <c r="AB3" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
       <c r="AC3" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.0)</f>
         <v>40</v>
@@ -1052,7 +1058,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
         <v>#N/A</v>
       </c>
-      <c r="AB4" s="1"/>
+      <c r="AB4" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
       <c r="AC4" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.0)</f>
         <v>40</v>
@@ -1275,7 +1284,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
         <v>#N/A</v>
       </c>
-      <c r="AB5" s="1"/>
+      <c r="AB5" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
       <c r="AC5" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -1492,7 +1504,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
         <v>#N/A</v>
       </c>
-      <c r="AB6" s="1"/>
+      <c r="AB6" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
       <c r="AC6" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -1715,7 +1730,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
         <v>#N/A</v>
       </c>
-      <c r="AB7" s="1"/>
+      <c r="AB7" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
       <c r="AC7" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.0)</f>
         <v>40</v>
@@ -1938,7 +1956,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
         <v>#N/A</v>
       </c>
-      <c r="AB8" s="1"/>
+      <c r="AB8" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
       <c r="AC8" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.0)</f>
         <v>40</v>
@@ -2161,7 +2182,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
         <v>#N/A</v>
       </c>
-      <c r="AB9" s="1"/>
+      <c r="AB9" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
       <c r="AC9" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.0)</f>
         <v>40</v>
@@ -2384,7 +2408,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
         <v>#N/A</v>
       </c>
-      <c r="AB10" s="1"/>
+      <c r="AB10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
       <c r="AC10" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
         <v>50</v>
@@ -2604,7 +2631,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
         <v>#N/A</v>
       </c>
-      <c r="AB11" s="1"/>
+      <c r="AB11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
       <c r="AC11" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
         <v>50</v>
@@ -2824,7 +2854,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
         <v>#N/A</v>
       </c>
-      <c r="AB12" s="1"/>
+      <c r="AB12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
       <c r="AC12" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
         <v>50</v>
@@ -3032,8 +3065,8 @@
         <v>1595</v>
       </c>
       <c r="X13" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
-        <v>-</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"04/06/2025")</f>
+        <v>04/06/2025</v>
       </c>
       <c r="Y13" s="1"/>
       <c r="Z13" s="1" t="str">
@@ -3044,7 +3077,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
         <v>#N/A</v>
       </c>
-      <c r="AB13" s="1"/>
+      <c r="AB13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
       <c r="AC13" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
         <v>50</v>
@@ -3153,11 +3189,14 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="B14" s="1"/>
+      <c r="A14" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.0)</f>
+        <v>13</v>
+      </c>
+      <c r="B14" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5220457.0)</f>
+        <v>5220457</v>
+      </c>
       <c r="C14" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0000427368")</f>
         <v>0000427368</v>
@@ -3258,7 +3297,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
         <v>#N/A</v>
       </c>
-      <c r="AB14" s="1"/>
+      <c r="AB14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
       <c r="AC14" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
         <v>50</v>
@@ -3291,8 +3333,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),500249.0)</f>
         <v>500249</v>
       </c>
-      <c r="AK14" s="1"/>
-      <c r="AL14" s="1"/>
+      <c r="AK14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"10 kms a 15 kms")</f>
+        <v>10 kms a 15 kms</v>
+      </c>
+      <c r="AL14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"06 551 a 800")</f>
+        <v>06 551 a 800</v>
+      </c>
       <c r="AM14" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0")</f>
         <v>0</v>
@@ -3367,11 +3415,14 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="B15" s="1"/>
+      <c r="A15" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.0)</f>
+        <v>14</v>
+      </c>
+      <c r="B15" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4534883.0)</f>
+        <v>4534883</v>
+      </c>
       <c r="C15" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0000427439")</f>
         <v>0000427439</v>
@@ -3472,7 +3523,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
         <v>#N/A</v>
       </c>
-      <c r="AB15" s="1"/>
+      <c r="AB15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
       <c r="AC15" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),850.0)</f>
         <v>850</v>
@@ -3582,8 +3636,8 @@
     </row>
     <row r="16">
       <c r="A16" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.0)</f>
+        <v>15</v>
       </c>
       <c r="B16" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1478516.0)</f>
@@ -3598,8 +3652,8 @@
         <v>JADE ALESSANDRA </v>
       </c>
       <c r="E16" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," HUAMANI CALDERON")</f>
-        <v> HUAMANI CALDERON</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HUAMANI CALDERON")</f>
+        <v>HUAMANI CALDERON</v>
       </c>
       <c r="F16" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.2064162E7)</f>
@@ -3689,7 +3743,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
         <v>#N/A</v>
       </c>
-      <c r="AB16" s="1"/>
+      <c r="AB16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
       <c r="AC16" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
         <v>50</v>
@@ -3804,11 +3861,14 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="B17" s="1"/>
+      <c r="A17" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.0)</f>
+        <v>16</v>
+      </c>
+      <c r="B17" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5228770.0)</f>
+        <v>5228770</v>
+      </c>
       <c r="C17" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0000427599")</f>
         <v>0000427599</v>
@@ -3909,7 +3969,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
         <v>#N/A</v>
       </c>
-      <c r="AB17" s="1"/>
+      <c r="AB17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
       <c r="AC17" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
         <v>50</v>
@@ -3942,8 +4005,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1507789.0)</f>
         <v>1507789</v>
       </c>
-      <c r="AK17" s="1"/>
-      <c r="AL17" s="1"/>
+      <c r="AK17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"5kms a 10 kms")</f>
+        <v>5kms a 10 kms</v>
+      </c>
+      <c r="AL17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"05 301 a 550")</f>
+        <v>05 301 a 550</v>
+      </c>
       <c r="AM17" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0")</f>
         <v>0</v>

--- a/DATA_VENTA26.1.xlsx
+++ b/DATA_VENTA26.1.xlsx
@@ -493,6 +493,18 @@
         <v>RINDIO EXAMEN</v>
       </c>
       <c r="BD1" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CURSO A NIVELAR")</f>
+        <v>CURSO A NIVELAR</v>
+      </c>
+      <c r="BE1" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TIENE CREDENCIALES")</f>
+        <v>TIENE CREDENCIALES</v>
+      </c>
+      <c r="BF1" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CONFIRMADO INICIA UCAL")</f>
+        <v>CONFIRMADO INICIA UCAL</v>
+      </c>
+      <c r="BG1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Respuestas NEE")</f>
         <v>Respuestas NEE</v>
       </c>
@@ -719,6 +731,18 @@
         <v>0</v>
       </c>
       <c r="BD2" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="BE2" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF2" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="BG2" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -945,6 +969,18 @@
         <v>1</v>
       </c>
       <c r="BD3" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Matemáticas")</f>
+        <v>Matemáticas</v>
+      </c>
+      <c r="BE3" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF3" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="BG3" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -1171,6 +1207,18 @@
         <v>0</v>
       </c>
       <c r="BD4" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="BE4" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF4" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="BG4" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -1391,6 +1439,18 @@
         <v>0</v>
       </c>
       <c r="BD5" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="BE5" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF5" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="BG5" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -1617,6 +1677,18 @@
         <v>0</v>
       </c>
       <c r="BD6" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="BE6" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF6" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="BG6" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -1843,6 +1915,18 @@
         <v>0</v>
       </c>
       <c r="BD7" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="BE7" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF7" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="BG7" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -2069,6 +2153,18 @@
         <v>0</v>
       </c>
       <c r="BD8" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="BE8" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF8" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="BG8" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -2295,6 +2391,18 @@
         <v>0</v>
       </c>
       <c r="BD9" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="BE9" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF9" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="BG9" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -2521,6 +2629,18 @@
         <v>0</v>
       </c>
       <c r="BD10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="BE10" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF10" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="BG10" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -2744,6 +2864,18 @@
         <v>0</v>
       </c>
       <c r="BD11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="BE11" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF11" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="BG11" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -2967,6 +3099,18 @@
         <v>0</v>
       </c>
       <c r="BD12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="BE12" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF12" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="BG12" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -3184,6 +3328,18 @@
         <v>0</v>
       </c>
       <c r="BD13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="BE13" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF13" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="BG13" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -3410,6 +3566,18 @@
         <v>0</v>
       </c>
       <c r="BD14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="BE14" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF14" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="BG14" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -3630,6 +3798,18 @@
         <v>0</v>
       </c>
       <c r="BD15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="BE15" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF15" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="BG15" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -3856,6 +4036,18 @@
         <v>0</v>
       </c>
       <c r="BD16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="BE16" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF16" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="BG16" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4082,70 +4274,250 @@
         <v>0</v>
       </c>
       <c r="BD17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="BE17" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF17" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="BG17" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-      <c r="Q18" s="1"/>
-      <c r="R18" s="1"/>
-      <c r="S18" s="1"/>
-      <c r="T18" s="1"/>
-      <c r="U18" s="1"/>
-      <c r="V18" s="1"/>
-      <c r="W18" s="1"/>
-      <c r="X18" s="1"/>
-      <c r="Y18" s="1"/>
-      <c r="Z18" s="1"/>
-      <c r="AA18" s="1"/>
-      <c r="AB18" s="1"/>
-      <c r="AC18" s="1"/>
-      <c r="AD18" s="1"/>
-      <c r="AE18" s="1"/>
-      <c r="AF18" s="1"/>
-      <c r="AG18" s="1"/>
-      <c r="AH18" s="1"/>
-      <c r="AI18" s="1"/>
-      <c r="AJ18" s="1"/>
+      <c r="A18" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.0)</f>
+        <v>17</v>
+      </c>
+      <c r="B18" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4560562.0)</f>
+        <v>4560562</v>
+      </c>
+      <c r="C18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0000427857")</f>
+        <v>0000427857</v>
+      </c>
+      <c r="D18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TAMARA MONSERAT")</f>
+        <v>TAMARA MONSERAT</v>
+      </c>
+      <c r="E18" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARRASCO HORNA")</f>
+        <v>CARRASCO HORNA</v>
+      </c>
+      <c r="F18" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.1933923E7)</f>
+        <v>61933923</v>
+      </c>
+      <c r="G18" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.46577974E8)</f>
+        <v>946577974</v>
+      </c>
+      <c r="H18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"tamaracarrascohorna@gmail.com")</f>
+        <v>tamaracarrascohorna@gmail.com</v>
+      </c>
+      <c r="I18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Arquitectura de Interiores")</f>
+        <v>Arquitectura de Interiores</v>
+      </c>
+      <c r="J18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Arquitecturas")</f>
+        <v>Arquitecturas</v>
+      </c>
+      <c r="K18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Antigua")</f>
+        <v>Antigua</v>
+      </c>
+      <c r="L18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Admisión de Alto Rendimiento")</f>
+        <v>Admisión de Alto Rendimiento</v>
+      </c>
+      <c r="M18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Semi-presencial")</f>
+        <v>Semi-presencial</v>
+      </c>
+      <c r="N18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Diurno")</f>
+        <v>Diurno</v>
+      </c>
+      <c r="O18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NUEVO")</f>
+        <v>NUEVO</v>
+      </c>
+      <c r="P18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCALA REGULAR")</f>
+        <v>ESCALA REGULAR</v>
+      </c>
+      <c r="Q18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="R18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="S18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="T18" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45812.0)</f>
+        <v>45812</v>
+      </c>
+      <c r="U18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"POS")</f>
+        <v>POS</v>
+      </c>
+      <c r="V18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="W18" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="X18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="Y18" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45812.0)</f>
+        <v>45812</v>
+      </c>
+      <c r="Z18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="AA18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AB18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="AC18" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
+        <v>50</v>
+      </c>
+      <c r="AD18" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),95.0)</f>
+        <v>95</v>
+      </c>
+      <c r="AE18" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1500.0)</f>
+        <v>1500</v>
+      </c>
+      <c r="AF18" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1500.0)</f>
+        <v>1500</v>
+      </c>
+      <c r="AG18" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH18" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI18" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1509751.0)</f>
+        <v>1509751</v>
+      </c>
       <c r="AK18" s="1"/>
       <c r="AL18" s="1"/>
-      <c r="AM18" s="1"/>
-      <c r="AN18" s="1"/>
-      <c r="AO18" s="1"/>
-      <c r="AP18" s="1"/>
-      <c r="AQ18" s="1"/>
-      <c r="AR18" s="1"/>
-      <c r="AS18" s="1"/>
-      <c r="AT18" s="1"/>
-      <c r="AU18" s="1"/>
-      <c r="AV18" s="1"/>
-      <c r="AW18" s="1"/>
-      <c r="AX18" s="1"/>
-      <c r="AY18" s="1"/>
-      <c r="AZ18" s="1"/>
-      <c r="BA18" s="1"/>
-      <c r="BB18" s="1"/>
-      <c r="BC18" s="1"/>
+      <c r="AM18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0")</f>
+        <v>0</v>
+      </c>
+      <c r="AN18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="AO18" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2025.0)</f>
+        <v>2025</v>
+      </c>
+      <c r="AP18" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45809.0)</f>
+        <v>45809</v>
+      </c>
+      <c r="AQ18" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45803.0)</f>
+        <v>45803</v>
+      </c>
+      <c r="AR18" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45802.0)</f>
+        <v>45802</v>
+      </c>
+      <c r="AS18" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
+        <v>45778</v>
+      </c>
+      <c r="AT18" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45775.0)</f>
+        <v>45775</v>
+      </c>
+      <c r="AU18" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
+      </c>
+      <c r="AV18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIGITAL")</f>
+        <v>DIGITAL</v>
+      </c>
+      <c r="AW18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BIDIRECCIONAL")</f>
+        <v>BIDIRECCIONAL</v>
+      </c>
+      <c r="AX18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ORGANICO")</f>
+        <v>ORGANICO</v>
+      </c>
+      <c r="AY18" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Daniel Zapata")</f>
+        <v>Daniel Zapata</v>
+      </c>
+      <c r="BA18" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BB18" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1500.0)</f>
+        <v>1500</v>
+      </c>
+      <c r="BC18" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="BD18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="BE18" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF18" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="BG18" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4209,7 +4581,10 @@
       <c r="BA19" s="1"/>
       <c r="BB19" s="1"/>
       <c r="BC19" s="1"/>
-      <c r="BD19" s="1" t="str">
+      <c r="BD19" s="1"/>
+      <c r="BE19" s="1"/>
+      <c r="BF19" s="1"/>
+      <c r="BG19" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4273,7 +4648,10 @@
       <c r="BA20" s="1"/>
       <c r="BB20" s="1"/>
       <c r="BC20" s="1"/>
-      <c r="BD20" s="1" t="str">
+      <c r="BD20" s="1"/>
+      <c r="BE20" s="1"/>
+      <c r="BF20" s="1"/>
+      <c r="BG20" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4337,7 +4715,10 @@
       <c r="BA21" s="1"/>
       <c r="BB21" s="1"/>
       <c r="BC21" s="1"/>
-      <c r="BD21" s="1" t="str">
+      <c r="BD21" s="1"/>
+      <c r="BE21" s="1"/>
+      <c r="BF21" s="1"/>
+      <c r="BG21" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4401,7 +4782,10 @@
       <c r="BA22" s="1"/>
       <c r="BB22" s="1"/>
       <c r="BC22" s="1"/>
-      <c r="BD22" s="1" t="str">
+      <c r="BD22" s="1"/>
+      <c r="BE22" s="1"/>
+      <c r="BF22" s="1"/>
+      <c r="BG22" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4465,7 +4849,10 @@
       <c r="BA23" s="1"/>
       <c r="BB23" s="1"/>
       <c r="BC23" s="1"/>
-      <c r="BD23" s="1" t="str">
+      <c r="BD23" s="1"/>
+      <c r="BE23" s="1"/>
+      <c r="BF23" s="1"/>
+      <c r="BG23" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4529,7 +4916,10 @@
       <c r="BA24" s="1"/>
       <c r="BB24" s="1"/>
       <c r="BC24" s="1"/>
-      <c r="BD24" s="1" t="str">
+      <c r="BD24" s="1"/>
+      <c r="BE24" s="1"/>
+      <c r="BF24" s="1"/>
+      <c r="BG24" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4593,7 +4983,10 @@
       <c r="BA25" s="1"/>
       <c r="BB25" s="1"/>
       <c r="BC25" s="1"/>
-      <c r="BD25" s="1" t="str">
+      <c r="BD25" s="1"/>
+      <c r="BE25" s="1"/>
+      <c r="BF25" s="1"/>
+      <c r="BG25" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4657,7 +5050,10 @@
       <c r="BA26" s="1"/>
       <c r="BB26" s="1"/>
       <c r="BC26" s="1"/>
-      <c r="BD26" s="1" t="str">
+      <c r="BD26" s="1"/>
+      <c r="BE26" s="1"/>
+      <c r="BF26" s="1"/>
+      <c r="BG26" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4721,7 +5117,10 @@
       <c r="BA27" s="1"/>
       <c r="BB27" s="1"/>
       <c r="BC27" s="1"/>
-      <c r="BD27" s="1" t="str">
+      <c r="BD27" s="1"/>
+      <c r="BE27" s="1"/>
+      <c r="BF27" s="1"/>
+      <c r="BG27" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4785,7 +5184,10 @@
       <c r="BA28" s="1"/>
       <c r="BB28" s="1"/>
       <c r="BC28" s="1"/>
-      <c r="BD28" s="1" t="str">
+      <c r="BD28" s="1"/>
+      <c r="BE28" s="1"/>
+      <c r="BF28" s="1"/>
+      <c r="BG28" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4849,7 +5251,10 @@
       <c r="BA29" s="1"/>
       <c r="BB29" s="1"/>
       <c r="BC29" s="1"/>
-      <c r="BD29" s="1" t="str">
+      <c r="BD29" s="1"/>
+      <c r="BE29" s="1"/>
+      <c r="BF29" s="1"/>
+      <c r="BG29" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4913,7 +5318,10 @@
       <c r="BA30" s="1"/>
       <c r="BB30" s="1"/>
       <c r="BC30" s="1"/>
-      <c r="BD30" s="1" t="str">
+      <c r="BD30" s="1"/>
+      <c r="BE30" s="1"/>
+      <c r="BF30" s="1"/>
+      <c r="BG30" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4977,7 +5385,10 @@
       <c r="BA31" s="1"/>
       <c r="BB31" s="1"/>
       <c r="BC31" s="1"/>
-      <c r="BD31" s="1" t="str">
+      <c r="BD31" s="1"/>
+      <c r="BE31" s="1"/>
+      <c r="BF31" s="1"/>
+      <c r="BG31" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5041,7 +5452,10 @@
       <c r="BA32" s="1"/>
       <c r="BB32" s="1"/>
       <c r="BC32" s="1"/>
-      <c r="BD32" s="1" t="str">
+      <c r="BD32" s="1"/>
+      <c r="BE32" s="1"/>
+      <c r="BF32" s="1"/>
+      <c r="BG32" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5105,7 +5519,10 @@
       <c r="BA33" s="1"/>
       <c r="BB33" s="1"/>
       <c r="BC33" s="1"/>
-      <c r="BD33" s="1" t="str">
+      <c r="BD33" s="1"/>
+      <c r="BE33" s="1"/>
+      <c r="BF33" s="1"/>
+      <c r="BG33" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5169,7 +5586,10 @@
       <c r="BA34" s="1"/>
       <c r="BB34" s="1"/>
       <c r="BC34" s="1"/>
-      <c r="BD34" s="1" t="str">
+      <c r="BD34" s="1"/>
+      <c r="BE34" s="1"/>
+      <c r="BF34" s="1"/>
+      <c r="BG34" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5233,7 +5653,10 @@
       <c r="BA35" s="1"/>
       <c r="BB35" s="1"/>
       <c r="BC35" s="1"/>
-      <c r="BD35" s="1" t="str">
+      <c r="BD35" s="1"/>
+      <c r="BE35" s="1"/>
+      <c r="BF35" s="1"/>
+      <c r="BG35" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5297,7 +5720,10 @@
       <c r="BA36" s="1"/>
       <c r="BB36" s="1"/>
       <c r="BC36" s="1"/>
-      <c r="BD36" s="1" t="str">
+      <c r="BD36" s="1"/>
+      <c r="BE36" s="1"/>
+      <c r="BF36" s="1"/>
+      <c r="BG36" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5361,7 +5787,10 @@
       <c r="BA37" s="1"/>
       <c r="BB37" s="1"/>
       <c r="BC37" s="1"/>
-      <c r="BD37" s="1" t="str">
+      <c r="BD37" s="1"/>
+      <c r="BE37" s="1"/>
+      <c r="BF37" s="1"/>
+      <c r="BG37" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5425,7 +5854,10 @@
       <c r="BA38" s="1"/>
       <c r="BB38" s="1"/>
       <c r="BC38" s="1"/>
-      <c r="BD38" s="1" t="str">
+      <c r="BD38" s="1"/>
+      <c r="BE38" s="1"/>
+      <c r="BF38" s="1"/>
+      <c r="BG38" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5489,7 +5921,10 @@
       <c r="BA39" s="1"/>
       <c r="BB39" s="1"/>
       <c r="BC39" s="1"/>
-      <c r="BD39" s="1" t="str">
+      <c r="BD39" s="1"/>
+      <c r="BE39" s="1"/>
+      <c r="BF39" s="1"/>
+      <c r="BG39" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5553,7 +5988,10 @@
       <c r="BA40" s="1"/>
       <c r="BB40" s="1"/>
       <c r="BC40" s="1"/>
-      <c r="BD40" s="1" t="str">
+      <c r="BD40" s="1"/>
+      <c r="BE40" s="1"/>
+      <c r="BF40" s="1"/>
+      <c r="BG40" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5617,7 +6055,10 @@
       <c r="BA41" s="1"/>
       <c r="BB41" s="1"/>
       <c r="BC41" s="1"/>
-      <c r="BD41" s="1" t="str">
+      <c r="BD41" s="1"/>
+      <c r="BE41" s="1"/>
+      <c r="BF41" s="1"/>
+      <c r="BG41" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5681,7 +6122,10 @@
       <c r="BA42" s="1"/>
       <c r="BB42" s="1"/>
       <c r="BC42" s="1"/>
-      <c r="BD42" s="1" t="str">
+      <c r="BD42" s="1"/>
+      <c r="BE42" s="1"/>
+      <c r="BF42" s="1"/>
+      <c r="BG42" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5745,7 +6189,10 @@
       <c r="BA43" s="1"/>
       <c r="BB43" s="1"/>
       <c r="BC43" s="1"/>
-      <c r="BD43" s="1" t="str">
+      <c r="BD43" s="1"/>
+      <c r="BE43" s="1"/>
+      <c r="BF43" s="1"/>
+      <c r="BG43" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5809,7 +6256,10 @@
       <c r="BA44" s="1"/>
       <c r="BB44" s="1"/>
       <c r="BC44" s="1"/>
-      <c r="BD44" s="1" t="str">
+      <c r="BD44" s="1"/>
+      <c r="BE44" s="1"/>
+      <c r="BF44" s="1"/>
+      <c r="BG44" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5873,7 +6323,10 @@
       <c r="BA45" s="1"/>
       <c r="BB45" s="1"/>
       <c r="BC45" s="1"/>
-      <c r="BD45" s="1" t="str">
+      <c r="BD45" s="1"/>
+      <c r="BE45" s="1"/>
+      <c r="BF45" s="1"/>
+      <c r="BG45" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5937,7 +6390,10 @@
       <c r="BA46" s="1"/>
       <c r="BB46" s="1"/>
       <c r="BC46" s="1"/>
-      <c r="BD46" s="1" t="str">
+      <c r="BD46" s="1"/>
+      <c r="BE46" s="1"/>
+      <c r="BF46" s="1"/>
+      <c r="BG46" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6001,7 +6457,10 @@
       <c r="BA47" s="1"/>
       <c r="BB47" s="1"/>
       <c r="BC47" s="1"/>
-      <c r="BD47" s="1" t="str">
+      <c r="BD47" s="1"/>
+      <c r="BE47" s="1"/>
+      <c r="BF47" s="1"/>
+      <c r="BG47" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6065,7 +6524,10 @@
       <c r="BA48" s="1"/>
       <c r="BB48" s="1"/>
       <c r="BC48" s="1"/>
-      <c r="BD48" s="1" t="str">
+      <c r="BD48" s="1"/>
+      <c r="BE48" s="1"/>
+      <c r="BF48" s="1"/>
+      <c r="BG48" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6129,7 +6591,10 @@
       <c r="BA49" s="1"/>
       <c r="BB49" s="1"/>
       <c r="BC49" s="1"/>
-      <c r="BD49" s="1" t="str">
+      <c r="BD49" s="1"/>
+      <c r="BE49" s="1"/>
+      <c r="BF49" s="1"/>
+      <c r="BG49" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6193,7 +6658,10 @@
       <c r="BA50" s="1"/>
       <c r="BB50" s="1"/>
       <c r="BC50" s="1"/>
-      <c r="BD50" s="1" t="str">
+      <c r="BD50" s="1"/>
+      <c r="BE50" s="1"/>
+      <c r="BF50" s="1"/>
+      <c r="BG50" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6257,7 +6725,10 @@
       <c r="BA51" s="1"/>
       <c r="BB51" s="1"/>
       <c r="BC51" s="1"/>
-      <c r="BD51" s="1" t="str">
+      <c r="BD51" s="1"/>
+      <c r="BE51" s="1"/>
+      <c r="BF51" s="1"/>
+      <c r="BG51" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6321,7 +6792,10 @@
       <c r="BA52" s="1"/>
       <c r="BB52" s="1"/>
       <c r="BC52" s="1"/>
-      <c r="BD52" s="1" t="str">
+      <c r="BD52" s="1"/>
+      <c r="BE52" s="1"/>
+      <c r="BF52" s="1"/>
+      <c r="BG52" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6385,7 +6859,10 @@
       <c r="BA53" s="1"/>
       <c r="BB53" s="1"/>
       <c r="BC53" s="1"/>
-      <c r="BD53" s="1" t="str">
+      <c r="BD53" s="1"/>
+      <c r="BE53" s="1"/>
+      <c r="BF53" s="1"/>
+      <c r="BG53" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6449,7 +6926,10 @@
       <c r="BA54" s="1"/>
       <c r="BB54" s="1"/>
       <c r="BC54" s="1"/>
-      <c r="BD54" s="1" t="str">
+      <c r="BD54" s="1"/>
+      <c r="BE54" s="1"/>
+      <c r="BF54" s="1"/>
+      <c r="BG54" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6513,7 +6993,10 @@
       <c r="BA55" s="1"/>
       <c r="BB55" s="1"/>
       <c r="BC55" s="1"/>
-      <c r="BD55" s="1" t="str">
+      <c r="BD55" s="1"/>
+      <c r="BE55" s="1"/>
+      <c r="BF55" s="1"/>
+      <c r="BG55" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6577,7 +7060,10 @@
       <c r="BA56" s="1"/>
       <c r="BB56" s="1"/>
       <c r="BC56" s="1"/>
-      <c r="BD56" s="1" t="str">
+      <c r="BD56" s="1"/>
+      <c r="BE56" s="1"/>
+      <c r="BF56" s="1"/>
+      <c r="BG56" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6641,7 +7127,10 @@
       <c r="BA57" s="1"/>
       <c r="BB57" s="1"/>
       <c r="BC57" s="1"/>
-      <c r="BD57" s="1" t="str">
+      <c r="BD57" s="1"/>
+      <c r="BE57" s="1"/>
+      <c r="BF57" s="1"/>
+      <c r="BG57" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6705,7 +7194,10 @@
       <c r="BA58" s="1"/>
       <c r="BB58" s="1"/>
       <c r="BC58" s="1"/>
-      <c r="BD58" s="1" t="str">
+      <c r="BD58" s="1"/>
+      <c r="BE58" s="1"/>
+      <c r="BF58" s="1"/>
+      <c r="BG58" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6769,7 +7261,10 @@
       <c r="BA59" s="1"/>
       <c r="BB59" s="1"/>
       <c r="BC59" s="1"/>
-      <c r="BD59" s="1" t="str">
+      <c r="BD59" s="1"/>
+      <c r="BE59" s="1"/>
+      <c r="BF59" s="1"/>
+      <c r="BG59" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6833,7 +7328,10 @@
       <c r="BA60" s="1"/>
       <c r="BB60" s="1"/>
       <c r="BC60" s="1"/>
-      <c r="BD60" s="1" t="str">
+      <c r="BD60" s="1"/>
+      <c r="BE60" s="1"/>
+      <c r="BF60" s="1"/>
+      <c r="BG60" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6897,7 +7395,10 @@
       <c r="BA61" s="1"/>
       <c r="BB61" s="1"/>
       <c r="BC61" s="1"/>
-      <c r="BD61" s="1" t="str">
+      <c r="BD61" s="1"/>
+      <c r="BE61" s="1"/>
+      <c r="BF61" s="1"/>
+      <c r="BG61" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6961,7 +7462,10 @@
       <c r="BA62" s="1"/>
       <c r="BB62" s="1"/>
       <c r="BC62" s="1"/>
-      <c r="BD62" s="1" t="str">
+      <c r="BD62" s="1"/>
+      <c r="BE62" s="1"/>
+      <c r="BF62" s="1"/>
+      <c r="BG62" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7025,7 +7529,10 @@
       <c r="BA63" s="1"/>
       <c r="BB63" s="1"/>
       <c r="BC63" s="1"/>
-      <c r="BD63" s="1" t="str">
+      <c r="BD63" s="1"/>
+      <c r="BE63" s="1"/>
+      <c r="BF63" s="1"/>
+      <c r="BG63" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7089,7 +7596,10 @@
       <c r="BA64" s="1"/>
       <c r="BB64" s="1"/>
       <c r="BC64" s="1"/>
-      <c r="BD64" s="1" t="str">
+      <c r="BD64" s="1"/>
+      <c r="BE64" s="1"/>
+      <c r="BF64" s="1"/>
+      <c r="BG64" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7153,7 +7663,10 @@
       <c r="BA65" s="1"/>
       <c r="BB65" s="1"/>
       <c r="BC65" s="1"/>
-      <c r="BD65" s="1" t="str">
+      <c r="BD65" s="1"/>
+      <c r="BE65" s="1"/>
+      <c r="BF65" s="1"/>
+      <c r="BG65" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7217,7 +7730,10 @@
       <c r="BA66" s="1"/>
       <c r="BB66" s="1"/>
       <c r="BC66" s="1"/>
-      <c r="BD66" s="1" t="str">
+      <c r="BD66" s="1"/>
+      <c r="BE66" s="1"/>
+      <c r="BF66" s="1"/>
+      <c r="BG66" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7281,7 +7797,10 @@
       <c r="BA67" s="1"/>
       <c r="BB67" s="1"/>
       <c r="BC67" s="1"/>
-      <c r="BD67" s="1" t="str">
+      <c r="BD67" s="1"/>
+      <c r="BE67" s="1"/>
+      <c r="BF67" s="1"/>
+      <c r="BG67" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7345,7 +7864,10 @@
       <c r="BA68" s="1"/>
       <c r="BB68" s="1"/>
       <c r="BC68" s="1"/>
-      <c r="BD68" s="1" t="str">
+      <c r="BD68" s="1"/>
+      <c r="BE68" s="1"/>
+      <c r="BF68" s="1"/>
+      <c r="BG68" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7409,7 +7931,10 @@
       <c r="BA69" s="1"/>
       <c r="BB69" s="1"/>
       <c r="BC69" s="1"/>
-      <c r="BD69" s="1" t="str">
+      <c r="BD69" s="1"/>
+      <c r="BE69" s="1"/>
+      <c r="BF69" s="1"/>
+      <c r="BG69" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7473,7 +7998,10 @@
       <c r="BA70" s="1"/>
       <c r="BB70" s="1"/>
       <c r="BC70" s="1"/>
-      <c r="BD70" s="1" t="str">
+      <c r="BD70" s="1"/>
+      <c r="BE70" s="1"/>
+      <c r="BF70" s="1"/>
+      <c r="BG70" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7537,7 +8065,10 @@
       <c r="BA71" s="1"/>
       <c r="BB71" s="1"/>
       <c r="BC71" s="1"/>
-      <c r="BD71" s="1" t="str">
+      <c r="BD71" s="1"/>
+      <c r="BE71" s="1"/>
+      <c r="BF71" s="1"/>
+      <c r="BG71" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7601,7 +8132,10 @@
       <c r="BA72" s="1"/>
       <c r="BB72" s="1"/>
       <c r="BC72" s="1"/>
-      <c r="BD72" s="1" t="str">
+      <c r="BD72" s="1"/>
+      <c r="BE72" s="1"/>
+      <c r="BF72" s="1"/>
+      <c r="BG72" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7665,7 +8199,10 @@
       <c r="BA73" s="1"/>
       <c r="BB73" s="1"/>
       <c r="BC73" s="1"/>
-      <c r="BD73" s="1" t="str">
+      <c r="BD73" s="1"/>
+      <c r="BE73" s="1"/>
+      <c r="BF73" s="1"/>
+      <c r="BG73" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7729,7 +8266,10 @@
       <c r="BA74" s="1"/>
       <c r="BB74" s="1"/>
       <c r="BC74" s="1"/>
-      <c r="BD74" s="1" t="str">
+      <c r="BD74" s="1"/>
+      <c r="BE74" s="1"/>
+      <c r="BF74" s="1"/>
+      <c r="BG74" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7793,7 +8333,10 @@
       <c r="BA75" s="1"/>
       <c r="BB75" s="1"/>
       <c r="BC75" s="1"/>
-      <c r="BD75" s="1" t="str">
+      <c r="BD75" s="1"/>
+      <c r="BE75" s="1"/>
+      <c r="BF75" s="1"/>
+      <c r="BG75" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7857,7 +8400,10 @@
       <c r="BA76" s="1"/>
       <c r="BB76" s="1"/>
       <c r="BC76" s="1"/>
-      <c r="BD76" s="1" t="str">
+      <c r="BD76" s="1"/>
+      <c r="BE76" s="1"/>
+      <c r="BF76" s="1"/>
+      <c r="BG76" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7921,7 +8467,10 @@
       <c r="BA77" s="1"/>
       <c r="BB77" s="1"/>
       <c r="BC77" s="1"/>
-      <c r="BD77" s="1" t="str">
+      <c r="BD77" s="1"/>
+      <c r="BE77" s="1"/>
+      <c r="BF77" s="1"/>
+      <c r="BG77" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7985,7 +8534,10 @@
       <c r="BA78" s="1"/>
       <c r="BB78" s="1"/>
       <c r="BC78" s="1"/>
-      <c r="BD78" s="1" t="str">
+      <c r="BD78" s="1"/>
+      <c r="BE78" s="1"/>
+      <c r="BF78" s="1"/>
+      <c r="BG78" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8049,7 +8601,10 @@
       <c r="BA79" s="1"/>
       <c r="BB79" s="1"/>
       <c r="BC79" s="1"/>
-      <c r="BD79" s="1" t="str">
+      <c r="BD79" s="1"/>
+      <c r="BE79" s="1"/>
+      <c r="BF79" s="1"/>
+      <c r="BG79" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8113,7 +8668,10 @@
       <c r="BA80" s="1"/>
       <c r="BB80" s="1"/>
       <c r="BC80" s="1"/>
-      <c r="BD80" s="1" t="str">
+      <c r="BD80" s="1"/>
+      <c r="BE80" s="1"/>
+      <c r="BF80" s="1"/>
+      <c r="BG80" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8177,7 +8735,10 @@
       <c r="BA81" s="1"/>
       <c r="BB81" s="1"/>
       <c r="BC81" s="1"/>
-      <c r="BD81" s="1" t="str">
+      <c r="BD81" s="1"/>
+      <c r="BE81" s="1"/>
+      <c r="BF81" s="1"/>
+      <c r="BG81" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8241,7 +8802,10 @@
       <c r="BA82" s="1"/>
       <c r="BB82" s="1"/>
       <c r="BC82" s="1"/>
-      <c r="BD82" s="1" t="str">
+      <c r="BD82" s="1"/>
+      <c r="BE82" s="1"/>
+      <c r="BF82" s="1"/>
+      <c r="BG82" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8305,7 +8869,10 @@
       <c r="BA83" s="1"/>
       <c r="BB83" s="1"/>
       <c r="BC83" s="1"/>
-      <c r="BD83" s="1" t="str">
+      <c r="BD83" s="1"/>
+      <c r="BE83" s="1"/>
+      <c r="BF83" s="1"/>
+      <c r="BG83" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8369,7 +8936,10 @@
       <c r="BA84" s="1"/>
       <c r="BB84" s="1"/>
       <c r="BC84" s="1"/>
-      <c r="BD84" s="1" t="str">
+      <c r="BD84" s="1"/>
+      <c r="BE84" s="1"/>
+      <c r="BF84" s="1"/>
+      <c r="BG84" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8433,7 +9003,10 @@
       <c r="BA85" s="1"/>
       <c r="BB85" s="1"/>
       <c r="BC85" s="1"/>
-      <c r="BD85" s="1" t="str">
+      <c r="BD85" s="1"/>
+      <c r="BE85" s="1"/>
+      <c r="BF85" s="1"/>
+      <c r="BG85" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8497,7 +9070,10 @@
       <c r="BA86" s="1"/>
       <c r="BB86" s="1"/>
       <c r="BC86" s="1"/>
-      <c r="BD86" s="1" t="str">
+      <c r="BD86" s="1"/>
+      <c r="BE86" s="1"/>
+      <c r="BF86" s="1"/>
+      <c r="BG86" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8561,7 +9137,10 @@
       <c r="BA87" s="1"/>
       <c r="BB87" s="1"/>
       <c r="BC87" s="1"/>
-      <c r="BD87" s="1" t="str">
+      <c r="BD87" s="1"/>
+      <c r="BE87" s="1"/>
+      <c r="BF87" s="1"/>
+      <c r="BG87" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8625,7 +9204,10 @@
       <c r="BA88" s="1"/>
       <c r="BB88" s="1"/>
       <c r="BC88" s="1"/>
-      <c r="BD88" s="1" t="str">
+      <c r="BD88" s="1"/>
+      <c r="BE88" s="1"/>
+      <c r="BF88" s="1"/>
+      <c r="BG88" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8689,7 +9271,10 @@
       <c r="BA89" s="1"/>
       <c r="BB89" s="1"/>
       <c r="BC89" s="1"/>
-      <c r="BD89" s="1" t="str">
+      <c r="BD89" s="1"/>
+      <c r="BE89" s="1"/>
+      <c r="BF89" s="1"/>
+      <c r="BG89" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8753,7 +9338,10 @@
       <c r="BA90" s="1"/>
       <c r="BB90" s="1"/>
       <c r="BC90" s="1"/>
-      <c r="BD90" s="1" t="str">
+      <c r="BD90" s="1"/>
+      <c r="BE90" s="1"/>
+      <c r="BF90" s="1"/>
+      <c r="BG90" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8817,7 +9405,10 @@
       <c r="BA91" s="1"/>
       <c r="BB91" s="1"/>
       <c r="BC91" s="1"/>
-      <c r="BD91" s="1" t="str">
+      <c r="BD91" s="1"/>
+      <c r="BE91" s="1"/>
+      <c r="BF91" s="1"/>
+      <c r="BG91" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8881,7 +9472,10 @@
       <c r="BA92" s="1"/>
       <c r="BB92" s="1"/>
       <c r="BC92" s="1"/>
-      <c r="BD92" s="1" t="str">
+      <c r="BD92" s="1"/>
+      <c r="BE92" s="1"/>
+      <c r="BF92" s="1"/>
+      <c r="BG92" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8945,7 +9539,10 @@
       <c r="BA93" s="1"/>
       <c r="BB93" s="1"/>
       <c r="BC93" s="1"/>
-      <c r="BD93" s="1" t="str">
+      <c r="BD93" s="1"/>
+      <c r="BE93" s="1"/>
+      <c r="BF93" s="1"/>
+      <c r="BG93" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9009,7 +9606,10 @@
       <c r="BA94" s="1"/>
       <c r="BB94" s="1"/>
       <c r="BC94" s="1"/>
-      <c r="BD94" s="1" t="str">
+      <c r="BD94" s="1"/>
+      <c r="BE94" s="1"/>
+      <c r="BF94" s="1"/>
+      <c r="BG94" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9073,7 +9673,10 @@
       <c r="BA95" s="1"/>
       <c r="BB95" s="1"/>
       <c r="BC95" s="1"/>
-      <c r="BD95" s="1" t="str">
+      <c r="BD95" s="1"/>
+      <c r="BE95" s="1"/>
+      <c r="BF95" s="1"/>
+      <c r="BG95" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9137,7 +9740,10 @@
       <c r="BA96" s="1"/>
       <c r="BB96" s="1"/>
       <c r="BC96" s="1"/>
-      <c r="BD96" s="1" t="str">
+      <c r="BD96" s="1"/>
+      <c r="BE96" s="1"/>
+      <c r="BF96" s="1"/>
+      <c r="BG96" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9201,7 +9807,10 @@
       <c r="BA97" s="1"/>
       <c r="BB97" s="1"/>
       <c r="BC97" s="1"/>
-      <c r="BD97" s="1" t="str">
+      <c r="BD97" s="1"/>
+      <c r="BE97" s="1"/>
+      <c r="BF97" s="1"/>
+      <c r="BG97" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9265,7 +9874,10 @@
       <c r="BA98" s="1"/>
       <c r="BB98" s="1"/>
       <c r="BC98" s="1"/>
-      <c r="BD98" s="1" t="str">
+      <c r="BD98" s="1"/>
+      <c r="BE98" s="1"/>
+      <c r="BF98" s="1"/>
+      <c r="BG98" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9329,7 +9941,10 @@
       <c r="BA99" s="1"/>
       <c r="BB99" s="1"/>
       <c r="BC99" s="1"/>
-      <c r="BD99" s="1" t="str">
+      <c r="BD99" s="1"/>
+      <c r="BE99" s="1"/>
+      <c r="BF99" s="1"/>
+      <c r="BG99" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9393,7 +10008,10 @@
       <c r="BA100" s="1"/>
       <c r="BB100" s="1"/>
       <c r="BC100" s="1"/>
-      <c r="BD100" s="1" t="str">
+      <c r="BD100" s="1"/>
+      <c r="BE100" s="1"/>
+      <c r="BF100" s="1"/>
+      <c r="BG100" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9457,7 +10075,10 @@
       <c r="BA101" s="1"/>
       <c r="BB101" s="1"/>
       <c r="BC101" s="1"/>
-      <c r="BD101" s="1" t="str">
+      <c r="BD101" s="1"/>
+      <c r="BE101" s="1"/>
+      <c r="BF101" s="1"/>
+      <c r="BG101" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9521,7 +10142,10 @@
       <c r="BA102" s="1"/>
       <c r="BB102" s="1"/>
       <c r="BC102" s="1"/>
-      <c r="BD102" s="1" t="str">
+      <c r="BD102" s="1"/>
+      <c r="BE102" s="1"/>
+      <c r="BF102" s="1"/>
+      <c r="BG102" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9585,7 +10209,10 @@
       <c r="BA103" s="1"/>
       <c r="BB103" s="1"/>
       <c r="BC103" s="1"/>
-      <c r="BD103" s="1" t="str">
+      <c r="BD103" s="1"/>
+      <c r="BE103" s="1"/>
+      <c r="BF103" s="1"/>
+      <c r="BG103" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9649,7 +10276,10 @@
       <c r="BA104" s="1"/>
       <c r="BB104" s="1"/>
       <c r="BC104" s="1"/>
-      <c r="BD104" s="1" t="str">
+      <c r="BD104" s="1"/>
+      <c r="BE104" s="1"/>
+      <c r="BF104" s="1"/>
+      <c r="BG104" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9713,7 +10343,10 @@
       <c r="BA105" s="1"/>
       <c r="BB105" s="1"/>
       <c r="BC105" s="1"/>
-      <c r="BD105" s="1" t="str">
+      <c r="BD105" s="1"/>
+      <c r="BE105" s="1"/>
+      <c r="BF105" s="1"/>
+      <c r="BG105" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9777,7 +10410,10 @@
       <c r="BA106" s="1"/>
       <c r="BB106" s="1"/>
       <c r="BC106" s="1"/>
-      <c r="BD106" s="1" t="str">
+      <c r="BD106" s="1"/>
+      <c r="BE106" s="1"/>
+      <c r="BF106" s="1"/>
+      <c r="BG106" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9841,7 +10477,10 @@
       <c r="BA107" s="1"/>
       <c r="BB107" s="1"/>
       <c r="BC107" s="1"/>
-      <c r="BD107" s="1" t="str">
+      <c r="BD107" s="1"/>
+      <c r="BE107" s="1"/>
+      <c r="BF107" s="1"/>
+      <c r="BG107" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9905,7 +10544,10 @@
       <c r="BA108" s="1"/>
       <c r="BB108" s="1"/>
       <c r="BC108" s="1"/>
-      <c r="BD108" s="1" t="str">
+      <c r="BD108" s="1"/>
+      <c r="BE108" s="1"/>
+      <c r="BF108" s="1"/>
+      <c r="BG108" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9969,7 +10611,10 @@
       <c r="BA109" s="1"/>
       <c r="BB109" s="1"/>
       <c r="BC109" s="1"/>
-      <c r="BD109" s="1" t="str">
+      <c r="BD109" s="1"/>
+      <c r="BE109" s="1"/>
+      <c r="BF109" s="1"/>
+      <c r="BG109" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10033,7 +10678,10 @@
       <c r="BA110" s="1"/>
       <c r="BB110" s="1"/>
       <c r="BC110" s="1"/>
-      <c r="BD110" s="1" t="str">
+      <c r="BD110" s="1"/>
+      <c r="BE110" s="1"/>
+      <c r="BF110" s="1"/>
+      <c r="BG110" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10097,7 +10745,10 @@
       <c r="BA111" s="1"/>
       <c r="BB111" s="1"/>
       <c r="BC111" s="1"/>
-      <c r="BD111" s="1" t="str">
+      <c r="BD111" s="1"/>
+      <c r="BE111" s="1"/>
+      <c r="BF111" s="1"/>
+      <c r="BG111" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10161,7 +10812,10 @@
       <c r="BA112" s="1"/>
       <c r="BB112" s="1"/>
       <c r="BC112" s="1"/>
-      <c r="BD112" s="1" t="str">
+      <c r="BD112" s="1"/>
+      <c r="BE112" s="1"/>
+      <c r="BF112" s="1"/>
+      <c r="BG112" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10225,7 +10879,10 @@
       <c r="BA113" s="1"/>
       <c r="BB113" s="1"/>
       <c r="BC113" s="1"/>
-      <c r="BD113" s="1" t="str">
+      <c r="BD113" s="1"/>
+      <c r="BE113" s="1"/>
+      <c r="BF113" s="1"/>
+      <c r="BG113" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10289,7 +10946,10 @@
       <c r="BA114" s="1"/>
       <c r="BB114" s="1"/>
       <c r="BC114" s="1"/>
-      <c r="BD114" s="1" t="str">
+      <c r="BD114" s="1"/>
+      <c r="BE114" s="1"/>
+      <c r="BF114" s="1"/>
+      <c r="BG114" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10353,7 +11013,10 @@
       <c r="BA115" s="1"/>
       <c r="BB115" s="1"/>
       <c r="BC115" s="1"/>
-      <c r="BD115" s="1" t="str">
+      <c r="BD115" s="1"/>
+      <c r="BE115" s="1"/>
+      <c r="BF115" s="1"/>
+      <c r="BG115" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10417,7 +11080,10 @@
       <c r="BA116" s="1"/>
       <c r="BB116" s="1"/>
       <c r="BC116" s="1"/>
-      <c r="BD116" s="1" t="str">
+      <c r="BD116" s="1"/>
+      <c r="BE116" s="1"/>
+      <c r="BF116" s="1"/>
+      <c r="BG116" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10481,7 +11147,10 @@
       <c r="BA117" s="1"/>
       <c r="BB117" s="1"/>
       <c r="BC117" s="1"/>
-      <c r="BD117" s="1" t="str">
+      <c r="BD117" s="1"/>
+      <c r="BE117" s="1"/>
+      <c r="BF117" s="1"/>
+      <c r="BG117" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10545,7 +11214,10 @@
       <c r="BA118" s="1"/>
       <c r="BB118" s="1"/>
       <c r="BC118" s="1"/>
-      <c r="BD118" s="1" t="str">
+      <c r="BD118" s="1"/>
+      <c r="BE118" s="1"/>
+      <c r="BF118" s="1"/>
+      <c r="BG118" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10609,7 +11281,10 @@
       <c r="BA119" s="1"/>
       <c r="BB119" s="1"/>
       <c r="BC119" s="1"/>
-      <c r="BD119" s="1" t="str">
+      <c r="BD119" s="1"/>
+      <c r="BE119" s="1"/>
+      <c r="BF119" s="1"/>
+      <c r="BG119" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10673,7 +11348,10 @@
       <c r="BA120" s="1"/>
       <c r="BB120" s="1"/>
       <c r="BC120" s="1"/>
-      <c r="BD120" s="1" t="str">
+      <c r="BD120" s="1"/>
+      <c r="BE120" s="1"/>
+      <c r="BF120" s="1"/>
+      <c r="BG120" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10737,7 +11415,10 @@
       <c r="BA121" s="1"/>
       <c r="BB121" s="1"/>
       <c r="BC121" s="1"/>
-      <c r="BD121" s="1" t="str">
+      <c r="BD121" s="1"/>
+      <c r="BE121" s="1"/>
+      <c r="BF121" s="1"/>
+      <c r="BG121" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10801,7 +11482,10 @@
       <c r="BA122" s="1"/>
       <c r="BB122" s="1"/>
       <c r="BC122" s="1"/>
-      <c r="BD122" s="1" t="str">
+      <c r="BD122" s="1"/>
+      <c r="BE122" s="1"/>
+      <c r="BF122" s="1"/>
+      <c r="BG122" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10865,7 +11549,10 @@
       <c r="BA123" s="1"/>
       <c r="BB123" s="1"/>
       <c r="BC123" s="1"/>
-      <c r="BD123" s="1" t="str">
+      <c r="BD123" s="1"/>
+      <c r="BE123" s="1"/>
+      <c r="BF123" s="1"/>
+      <c r="BG123" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10929,7 +11616,10 @@
       <c r="BA124" s="1"/>
       <c r="BB124" s="1"/>
       <c r="BC124" s="1"/>
-      <c r="BD124" s="1" t="str">
+      <c r="BD124" s="1"/>
+      <c r="BE124" s="1"/>
+      <c r="BF124" s="1"/>
+      <c r="BG124" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10993,7 +11683,10 @@
       <c r="BA125" s="1"/>
       <c r="BB125" s="1"/>
       <c r="BC125" s="1"/>
-      <c r="BD125" s="1" t="str">
+      <c r="BD125" s="1"/>
+      <c r="BE125" s="1"/>
+      <c r="BF125" s="1"/>
+      <c r="BG125" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11057,7 +11750,10 @@
       <c r="BA126" s="1"/>
       <c r="BB126" s="1"/>
       <c r="BC126" s="1"/>
-      <c r="BD126" s="1" t="str">
+      <c r="BD126" s="1"/>
+      <c r="BE126" s="1"/>
+      <c r="BF126" s="1"/>
+      <c r="BG126" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11121,7 +11817,10 @@
       <c r="BA127" s="1"/>
       <c r="BB127" s="1"/>
       <c r="BC127" s="1"/>
-      <c r="BD127" s="1" t="str">
+      <c r="BD127" s="1"/>
+      <c r="BE127" s="1"/>
+      <c r="BF127" s="1"/>
+      <c r="BG127" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11185,7 +11884,10 @@
       <c r="BA128" s="1"/>
       <c r="BB128" s="1"/>
       <c r="BC128" s="1"/>
-      <c r="BD128" s="1" t="str">
+      <c r="BD128" s="1"/>
+      <c r="BE128" s="1"/>
+      <c r="BF128" s="1"/>
+      <c r="BG128" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11249,7 +11951,10 @@
       <c r="BA129" s="1"/>
       <c r="BB129" s="1"/>
       <c r="BC129" s="1"/>
-      <c r="BD129" s="1" t="str">
+      <c r="BD129" s="1"/>
+      <c r="BE129" s="1"/>
+      <c r="BF129" s="1"/>
+      <c r="BG129" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11313,7 +12018,10 @@
       <c r="BA130" s="1"/>
       <c r="BB130" s="1"/>
       <c r="BC130" s="1"/>
-      <c r="BD130" s="1" t="str">
+      <c r="BD130" s="1"/>
+      <c r="BE130" s="1"/>
+      <c r="BF130" s="1"/>
+      <c r="BG130" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11377,7 +12085,10 @@
       <c r="BA131" s="1"/>
       <c r="BB131" s="1"/>
       <c r="BC131" s="1"/>
-      <c r="BD131" s="1" t="str">
+      <c r="BD131" s="1"/>
+      <c r="BE131" s="1"/>
+      <c r="BF131" s="1"/>
+      <c r="BG131" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11441,7 +12152,10 @@
       <c r="BA132" s="1"/>
       <c r="BB132" s="1"/>
       <c r="BC132" s="1"/>
-      <c r="BD132" s="1" t="str">
+      <c r="BD132" s="1"/>
+      <c r="BE132" s="1"/>
+      <c r="BF132" s="1"/>
+      <c r="BG132" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11505,7 +12219,10 @@
       <c r="BA133" s="1"/>
       <c r="BB133" s="1"/>
       <c r="BC133" s="1"/>
-      <c r="BD133" s="1" t="str">
+      <c r="BD133" s="1"/>
+      <c r="BE133" s="1"/>
+      <c r="BF133" s="1"/>
+      <c r="BG133" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11569,7 +12286,10 @@
       <c r="BA134" s="1"/>
       <c r="BB134" s="1"/>
       <c r="BC134" s="1"/>
-      <c r="BD134" s="1" t="str">
+      <c r="BD134" s="1"/>
+      <c r="BE134" s="1"/>
+      <c r="BF134" s="1"/>
+      <c r="BG134" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11633,7 +12353,10 @@
       <c r="BA135" s="1"/>
       <c r="BB135" s="1"/>
       <c r="BC135" s="1"/>
-      <c r="BD135" s="1" t="str">
+      <c r="BD135" s="1"/>
+      <c r="BE135" s="1"/>
+      <c r="BF135" s="1"/>
+      <c r="BG135" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11697,7 +12420,10 @@
       <c r="BA136" s="1"/>
       <c r="BB136" s="1"/>
       <c r="BC136" s="1"/>
-      <c r="BD136" s="1" t="str">
+      <c r="BD136" s="1"/>
+      <c r="BE136" s="1"/>
+      <c r="BF136" s="1"/>
+      <c r="BG136" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11761,7 +12487,10 @@
       <c r="BA137" s="1"/>
       <c r="BB137" s="1"/>
       <c r="BC137" s="1"/>
-      <c r="BD137" s="1" t="str">
+      <c r="BD137" s="1"/>
+      <c r="BE137" s="1"/>
+      <c r="BF137" s="1"/>
+      <c r="BG137" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11825,7 +12554,10 @@
       <c r="BA138" s="1"/>
       <c r="BB138" s="1"/>
       <c r="BC138" s="1"/>
-      <c r="BD138" s="1" t="str">
+      <c r="BD138" s="1"/>
+      <c r="BE138" s="1"/>
+      <c r="BF138" s="1"/>
+      <c r="BG138" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11889,7 +12621,10 @@
       <c r="BA139" s="1"/>
       <c r="BB139" s="1"/>
       <c r="BC139" s="1"/>
-      <c r="BD139" s="1" t="str">
+      <c r="BD139" s="1"/>
+      <c r="BE139" s="1"/>
+      <c r="BF139" s="1"/>
+      <c r="BG139" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11953,7 +12688,10 @@
       <c r="BA140" s="1"/>
       <c r="BB140" s="1"/>
       <c r="BC140" s="1"/>
-      <c r="BD140" s="1" t="str">
+      <c r="BD140" s="1"/>
+      <c r="BE140" s="1"/>
+      <c r="BF140" s="1"/>
+      <c r="BG140" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12017,7 +12755,10 @@
       <c r="BA141" s="1"/>
       <c r="BB141" s="1"/>
       <c r="BC141" s="1"/>
-      <c r="BD141" s="1" t="str">
+      <c r="BD141" s="1"/>
+      <c r="BE141" s="1"/>
+      <c r="BF141" s="1"/>
+      <c r="BG141" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12081,7 +12822,10 @@
       <c r="BA142" s="1"/>
       <c r="BB142" s="1"/>
       <c r="BC142" s="1"/>
-      <c r="BD142" s="1" t="str">
+      <c r="BD142" s="1"/>
+      <c r="BE142" s="1"/>
+      <c r="BF142" s="1"/>
+      <c r="BG142" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12145,7 +12889,10 @@
       <c r="BA143" s="1"/>
       <c r="BB143" s="1"/>
       <c r="BC143" s="1"/>
-      <c r="BD143" s="1" t="str">
+      <c r="BD143" s="1"/>
+      <c r="BE143" s="1"/>
+      <c r="BF143" s="1"/>
+      <c r="BG143" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12209,7 +12956,10 @@
       <c r="BA144" s="1"/>
       <c r="BB144" s="1"/>
       <c r="BC144" s="1"/>
-      <c r="BD144" s="1" t="str">
+      <c r="BD144" s="1"/>
+      <c r="BE144" s="1"/>
+      <c r="BF144" s="1"/>
+      <c r="BG144" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12273,7 +13023,10 @@
       <c r="BA145" s="1"/>
       <c r="BB145" s="1"/>
       <c r="BC145" s="1"/>
-      <c r="BD145" s="1" t="str">
+      <c r="BD145" s="1"/>
+      <c r="BE145" s="1"/>
+      <c r="BF145" s="1"/>
+      <c r="BG145" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12337,7 +13090,10 @@
       <c r="BA146" s="1"/>
       <c r="BB146" s="1"/>
       <c r="BC146" s="1"/>
-      <c r="BD146" s="1" t="str">
+      <c r="BD146" s="1"/>
+      <c r="BE146" s="1"/>
+      <c r="BF146" s="1"/>
+      <c r="BG146" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12401,7 +13157,10 @@
       <c r="BA147" s="1"/>
       <c r="BB147" s="1"/>
       <c r="BC147" s="1"/>
-      <c r="BD147" s="1" t="str">
+      <c r="BD147" s="1"/>
+      <c r="BE147" s="1"/>
+      <c r="BF147" s="1"/>
+      <c r="BG147" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12465,7 +13224,10 @@
       <c r="BA148" s="1"/>
       <c r="BB148" s="1"/>
       <c r="BC148" s="1"/>
-      <c r="BD148" s="1" t="str">
+      <c r="BD148" s="1"/>
+      <c r="BE148" s="1"/>
+      <c r="BF148" s="1"/>
+      <c r="BG148" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12529,7 +13291,10 @@
       <c r="BA149" s="1"/>
       <c r="BB149" s="1"/>
       <c r="BC149" s="1"/>
-      <c r="BD149" s="1" t="str">
+      <c r="BD149" s="1"/>
+      <c r="BE149" s="1"/>
+      <c r="BF149" s="1"/>
+      <c r="BG149" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12593,7 +13358,10 @@
       <c r="BA150" s="1"/>
       <c r="BB150" s="1"/>
       <c r="BC150" s="1"/>
-      <c r="BD150" s="1" t="str">
+      <c r="BD150" s="1"/>
+      <c r="BE150" s="1"/>
+      <c r="BF150" s="1"/>
+      <c r="BG150" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12657,7 +13425,10 @@
       <c r="BA151" s="1"/>
       <c r="BB151" s="1"/>
       <c r="BC151" s="1"/>
-      <c r="BD151" s="1" t="str">
+      <c r="BD151" s="1"/>
+      <c r="BE151" s="1"/>
+      <c r="BF151" s="1"/>
+      <c r="BG151" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12721,7 +13492,10 @@
       <c r="BA152" s="1"/>
       <c r="BB152" s="1"/>
       <c r="BC152" s="1"/>
-      <c r="BD152" s="1" t="str">
+      <c r="BD152" s="1"/>
+      <c r="BE152" s="1"/>
+      <c r="BF152" s="1"/>
+      <c r="BG152" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12785,7 +13559,10 @@
       <c r="BA153" s="1"/>
       <c r="BB153" s="1"/>
       <c r="BC153" s="1"/>
-      <c r="BD153" s="1" t="str">
+      <c r="BD153" s="1"/>
+      <c r="BE153" s="1"/>
+      <c r="BF153" s="1"/>
+      <c r="BG153" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12849,7 +13626,10 @@
       <c r="BA154" s="1"/>
       <c r="BB154" s="1"/>
       <c r="BC154" s="1"/>
-      <c r="BD154" s="1" t="str">
+      <c r="BD154" s="1"/>
+      <c r="BE154" s="1"/>
+      <c r="BF154" s="1"/>
+      <c r="BG154" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12913,7 +13693,10 @@
       <c r="BA155" s="1"/>
       <c r="BB155" s="1"/>
       <c r="BC155" s="1"/>
-      <c r="BD155" s="1" t="str">
+      <c r="BD155" s="1"/>
+      <c r="BE155" s="1"/>
+      <c r="BF155" s="1"/>
+      <c r="BG155" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12977,7 +13760,10 @@
       <c r="BA156" s="1"/>
       <c r="BB156" s="1"/>
       <c r="BC156" s="1"/>
-      <c r="BD156" s="1" t="str">
+      <c r="BD156" s="1"/>
+      <c r="BE156" s="1"/>
+      <c r="BF156" s="1"/>
+      <c r="BG156" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13041,7 +13827,10 @@
       <c r="BA157" s="1"/>
       <c r="BB157" s="1"/>
       <c r="BC157" s="1"/>
-      <c r="BD157" s="1" t="str">
+      <c r="BD157" s="1"/>
+      <c r="BE157" s="1"/>
+      <c r="BF157" s="1"/>
+      <c r="BG157" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13105,7 +13894,10 @@
       <c r="BA158" s="1"/>
       <c r="BB158" s="1"/>
       <c r="BC158" s="1"/>
-      <c r="BD158" s="1" t="str">
+      <c r="BD158" s="1"/>
+      <c r="BE158" s="1"/>
+      <c r="BF158" s="1"/>
+      <c r="BG158" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13169,7 +13961,10 @@
       <c r="BA159" s="1"/>
       <c r="BB159" s="1"/>
       <c r="BC159" s="1"/>
-      <c r="BD159" s="1" t="str">
+      <c r="BD159" s="1"/>
+      <c r="BE159" s="1"/>
+      <c r="BF159" s="1"/>
+      <c r="BG159" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13233,7 +14028,10 @@
       <c r="BA160" s="1"/>
       <c r="BB160" s="1"/>
       <c r="BC160" s="1"/>
-      <c r="BD160" s="1" t="str">
+      <c r="BD160" s="1"/>
+      <c r="BE160" s="1"/>
+      <c r="BF160" s="1"/>
+      <c r="BG160" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13297,7 +14095,10 @@
       <c r="BA161" s="1"/>
       <c r="BB161" s="1"/>
       <c r="BC161" s="1"/>
-      <c r="BD161" s="1" t="str">
+      <c r="BD161" s="1"/>
+      <c r="BE161" s="1"/>
+      <c r="BF161" s="1"/>
+      <c r="BG161" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13361,7 +14162,10 @@
       <c r="BA162" s="1"/>
       <c r="BB162" s="1"/>
       <c r="BC162" s="1"/>
-      <c r="BD162" s="1" t="str">
+      <c r="BD162" s="1"/>
+      <c r="BE162" s="1"/>
+      <c r="BF162" s="1"/>
+      <c r="BG162" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13425,7 +14229,10 @@
       <c r="BA163" s="1"/>
       <c r="BB163" s="1"/>
       <c r="BC163" s="1"/>
-      <c r="BD163" s="1" t="str">
+      <c r="BD163" s="1"/>
+      <c r="BE163" s="1"/>
+      <c r="BF163" s="1"/>
+      <c r="BG163" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13489,7 +14296,10 @@
       <c r="BA164" s="1"/>
       <c r="BB164" s="1"/>
       <c r="BC164" s="1"/>
-      <c r="BD164" s="1" t="str">
+      <c r="BD164" s="1"/>
+      <c r="BE164" s="1"/>
+      <c r="BF164" s="1"/>
+      <c r="BG164" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13553,7 +14363,10 @@
       <c r="BA165" s="1"/>
       <c r="BB165" s="1"/>
       <c r="BC165" s="1"/>
-      <c r="BD165" s="1" t="str">
+      <c r="BD165" s="1"/>
+      <c r="BE165" s="1"/>
+      <c r="BF165" s="1"/>
+      <c r="BG165" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13617,7 +14430,10 @@
       <c r="BA166" s="1"/>
       <c r="BB166" s="1"/>
       <c r="BC166" s="1"/>
-      <c r="BD166" s="1" t="str">
+      <c r="BD166" s="1"/>
+      <c r="BE166" s="1"/>
+      <c r="BF166" s="1"/>
+      <c r="BG166" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13681,7 +14497,10 @@
       <c r="BA167" s="1"/>
       <c r="BB167" s="1"/>
       <c r="BC167" s="1"/>
-      <c r="BD167" s="1" t="str">
+      <c r="BD167" s="1"/>
+      <c r="BE167" s="1"/>
+      <c r="BF167" s="1"/>
+      <c r="BG167" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13745,7 +14564,10 @@
       <c r="BA168" s="1"/>
       <c r="BB168" s="1"/>
       <c r="BC168" s="1"/>
-      <c r="BD168" s="1" t="str">
+      <c r="BD168" s="1"/>
+      <c r="BE168" s="1"/>
+      <c r="BF168" s="1"/>
+      <c r="BG168" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13809,7 +14631,10 @@
       <c r="BA169" s="1"/>
       <c r="BB169" s="1"/>
       <c r="BC169" s="1"/>
-      <c r="BD169" s="1" t="str">
+      <c r="BD169" s="1"/>
+      <c r="BE169" s="1"/>
+      <c r="BF169" s="1"/>
+      <c r="BG169" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13873,7 +14698,10 @@
       <c r="BA170" s="1"/>
       <c r="BB170" s="1"/>
       <c r="BC170" s="1"/>
-      <c r="BD170" s="1" t="str">
+      <c r="BD170" s="1"/>
+      <c r="BE170" s="1"/>
+      <c r="BF170" s="1"/>
+      <c r="BG170" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13937,7 +14765,10 @@
       <c r="BA171" s="1"/>
       <c r="BB171" s="1"/>
       <c r="BC171" s="1"/>
-      <c r="BD171" s="1" t="str">
+      <c r="BD171" s="1"/>
+      <c r="BE171" s="1"/>
+      <c r="BF171" s="1"/>
+      <c r="BG171" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14001,7 +14832,10 @@
       <c r="BA172" s="1"/>
       <c r="BB172" s="1"/>
       <c r="BC172" s="1"/>
-      <c r="BD172" s="1" t="str">
+      <c r="BD172" s="1"/>
+      <c r="BE172" s="1"/>
+      <c r="BF172" s="1"/>
+      <c r="BG172" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14065,7 +14899,10 @@
       <c r="BA173" s="1"/>
       <c r="BB173" s="1"/>
       <c r="BC173" s="1"/>
-      <c r="BD173" s="1" t="str">
+      <c r="BD173" s="1"/>
+      <c r="BE173" s="1"/>
+      <c r="BF173" s="1"/>
+      <c r="BG173" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14129,7 +14966,10 @@
       <c r="BA174" s="1"/>
       <c r="BB174" s="1"/>
       <c r="BC174" s="1"/>
-      <c r="BD174" s="1" t="str">
+      <c r="BD174" s="1"/>
+      <c r="BE174" s="1"/>
+      <c r="BF174" s="1"/>
+      <c r="BG174" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14193,7 +15033,10 @@
       <c r="BA175" s="1"/>
       <c r="BB175" s="1"/>
       <c r="BC175" s="1"/>
-      <c r="BD175" s="1" t="str">
+      <c r="BD175" s="1"/>
+      <c r="BE175" s="1"/>
+      <c r="BF175" s="1"/>
+      <c r="BG175" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14257,7 +15100,10 @@
       <c r="BA176" s="1"/>
       <c r="BB176" s="1"/>
       <c r="BC176" s="1"/>
-      <c r="BD176" s="1" t="str">
+      <c r="BD176" s="1"/>
+      <c r="BE176" s="1"/>
+      <c r="BF176" s="1"/>
+      <c r="BG176" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14321,7 +15167,10 @@
       <c r="BA177" s="1"/>
       <c r="BB177" s="1"/>
       <c r="BC177" s="1"/>
-      <c r="BD177" s="1" t="str">
+      <c r="BD177" s="1"/>
+      <c r="BE177" s="1"/>
+      <c r="BF177" s="1"/>
+      <c r="BG177" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14385,7 +15234,10 @@
       <c r="BA178" s="1"/>
       <c r="BB178" s="1"/>
       <c r="BC178" s="1"/>
-      <c r="BD178" s="1" t="str">
+      <c r="BD178" s="1"/>
+      <c r="BE178" s="1"/>
+      <c r="BF178" s="1"/>
+      <c r="BG178" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14449,7 +15301,10 @@
       <c r="BA179" s="1"/>
       <c r="BB179" s="1"/>
       <c r="BC179" s="1"/>
-      <c r="BD179" s="1" t="str">
+      <c r="BD179" s="1"/>
+      <c r="BE179" s="1"/>
+      <c r="BF179" s="1"/>
+      <c r="BG179" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14513,7 +15368,10 @@
       <c r="BA180" s="1"/>
       <c r="BB180" s="1"/>
       <c r="BC180" s="1"/>
-      <c r="BD180" s="1" t="str">
+      <c r="BD180" s="1"/>
+      <c r="BE180" s="1"/>
+      <c r="BF180" s="1"/>
+      <c r="BG180" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14577,7 +15435,10 @@
       <c r="BA181" s="1"/>
       <c r="BB181" s="1"/>
       <c r="BC181" s="1"/>
-      <c r="BD181" s="1" t="str">
+      <c r="BD181" s="1"/>
+      <c r="BE181" s="1"/>
+      <c r="BF181" s="1"/>
+      <c r="BG181" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14641,7 +15502,10 @@
       <c r="BA182" s="1"/>
       <c r="BB182" s="1"/>
       <c r="BC182" s="1"/>
-      <c r="BD182" s="1" t="str">
+      <c r="BD182" s="1"/>
+      <c r="BE182" s="1"/>
+      <c r="BF182" s="1"/>
+      <c r="BG182" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14705,7 +15569,10 @@
       <c r="BA183" s="1"/>
       <c r="BB183" s="1"/>
       <c r="BC183" s="1"/>
-      <c r="BD183" s="1" t="str">
+      <c r="BD183" s="1"/>
+      <c r="BE183" s="1"/>
+      <c r="BF183" s="1"/>
+      <c r="BG183" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14769,7 +15636,10 @@
       <c r="BA184" s="1"/>
       <c r="BB184" s="1"/>
       <c r="BC184" s="1"/>
-      <c r="BD184" s="1" t="str">
+      <c r="BD184" s="1"/>
+      <c r="BE184" s="1"/>
+      <c r="BF184" s="1"/>
+      <c r="BG184" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14833,7 +15703,10 @@
       <c r="BA185" s="1"/>
       <c r="BB185" s="1"/>
       <c r="BC185" s="1"/>
-      <c r="BD185" s="1" t="str">
+      <c r="BD185" s="1"/>
+      <c r="BE185" s="1"/>
+      <c r="BF185" s="1"/>
+      <c r="BG185" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14897,7 +15770,10 @@
       <c r="BA186" s="1"/>
       <c r="BB186" s="1"/>
       <c r="BC186" s="1"/>
-      <c r="BD186" s="1" t="str">
+      <c r="BD186" s="1"/>
+      <c r="BE186" s="1"/>
+      <c r="BF186" s="1"/>
+      <c r="BG186" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14961,7 +15837,10 @@
       <c r="BA187" s="1"/>
       <c r="BB187" s="1"/>
       <c r="BC187" s="1"/>
-      <c r="BD187" s="1" t="str">
+      <c r="BD187" s="1"/>
+      <c r="BE187" s="1"/>
+      <c r="BF187" s="1"/>
+      <c r="BG187" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15025,7 +15904,10 @@
       <c r="BA188" s="1"/>
       <c r="BB188" s="1"/>
       <c r="BC188" s="1"/>
-      <c r="BD188" s="1" t="str">
+      <c r="BD188" s="1"/>
+      <c r="BE188" s="1"/>
+      <c r="BF188" s="1"/>
+      <c r="BG188" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15089,7 +15971,10 @@
       <c r="BA189" s="1"/>
       <c r="BB189" s="1"/>
       <c r="BC189" s="1"/>
-      <c r="BD189" s="1" t="str">
+      <c r="BD189" s="1"/>
+      <c r="BE189" s="1"/>
+      <c r="BF189" s="1"/>
+      <c r="BG189" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15153,7 +16038,10 @@
       <c r="BA190" s="1"/>
       <c r="BB190" s="1"/>
       <c r="BC190" s="1"/>
-      <c r="BD190" s="1" t="str">
+      <c r="BD190" s="1"/>
+      <c r="BE190" s="1"/>
+      <c r="BF190" s="1"/>
+      <c r="BG190" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15217,7 +16105,10 @@
       <c r="BA191" s="1"/>
       <c r="BB191" s="1"/>
       <c r="BC191" s="1"/>
-      <c r="BD191" s="1" t="str">
+      <c r="BD191" s="1"/>
+      <c r="BE191" s="1"/>
+      <c r="BF191" s="1"/>
+      <c r="BG191" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15281,7 +16172,10 @@
       <c r="BA192" s="1"/>
       <c r="BB192" s="1"/>
       <c r="BC192" s="1"/>
-      <c r="BD192" s="1" t="str">
+      <c r="BD192" s="1"/>
+      <c r="BE192" s="1"/>
+      <c r="BF192" s="1"/>
+      <c r="BG192" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15345,7 +16239,10 @@
       <c r="BA193" s="1"/>
       <c r="BB193" s="1"/>
       <c r="BC193" s="1"/>
-      <c r="BD193" s="1" t="str">
+      <c r="BD193" s="1"/>
+      <c r="BE193" s="1"/>
+      <c r="BF193" s="1"/>
+      <c r="BG193" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15409,7 +16306,10 @@
       <c r="BA194" s="1"/>
       <c r="BB194" s="1"/>
       <c r="BC194" s="1"/>
-      <c r="BD194" s="1" t="str">
+      <c r="BD194" s="1"/>
+      <c r="BE194" s="1"/>
+      <c r="BF194" s="1"/>
+      <c r="BG194" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15473,7 +16373,10 @@
       <c r="BA195" s="1"/>
       <c r="BB195" s="1"/>
       <c r="BC195" s="1"/>
-      <c r="BD195" s="1" t="str">
+      <c r="BD195" s="1"/>
+      <c r="BE195" s="1"/>
+      <c r="BF195" s="1"/>
+      <c r="BG195" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15537,7 +16440,10 @@
       <c r="BA196" s="1"/>
       <c r="BB196" s="1"/>
       <c r="BC196" s="1"/>
-      <c r="BD196" s="1" t="str">
+      <c r="BD196" s="1"/>
+      <c r="BE196" s="1"/>
+      <c r="BF196" s="1"/>
+      <c r="BG196" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15601,7 +16507,10 @@
       <c r="BA197" s="1"/>
       <c r="BB197" s="1"/>
       <c r="BC197" s="1"/>
-      <c r="BD197" s="1" t="str">
+      <c r="BD197" s="1"/>
+      <c r="BE197" s="1"/>
+      <c r="BF197" s="1"/>
+      <c r="BG197" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15665,7 +16574,10 @@
       <c r="BA198" s="1"/>
       <c r="BB198" s="1"/>
       <c r="BC198" s="1"/>
-      <c r="BD198" s="1" t="str">
+      <c r="BD198" s="1"/>
+      <c r="BE198" s="1"/>
+      <c r="BF198" s="1"/>
+      <c r="BG198" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15729,7 +16641,10 @@
       <c r="BA199" s="1"/>
       <c r="BB199" s="1"/>
       <c r="BC199" s="1"/>
-      <c r="BD199" s="1" t="str">
+      <c r="BD199" s="1"/>
+      <c r="BE199" s="1"/>
+      <c r="BF199" s="1"/>
+      <c r="BG199" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15793,7 +16708,10 @@
       <c r="BA200" s="1"/>
       <c r="BB200" s="1"/>
       <c r="BC200" s="1"/>
-      <c r="BD200" s="1" t="str">
+      <c r="BD200" s="1"/>
+      <c r="BE200" s="1"/>
+      <c r="BF200" s="1"/>
+      <c r="BG200" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15857,7 +16775,10 @@
       <c r="BA201" s="1"/>
       <c r="BB201" s="1"/>
       <c r="BC201" s="1"/>
-      <c r="BD201" s="1" t="str">
+      <c r="BD201" s="1"/>
+      <c r="BE201" s="1"/>
+      <c r="BF201" s="1"/>
+      <c r="BG201" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15921,7 +16842,10 @@
       <c r="BA202" s="1"/>
       <c r="BB202" s="1"/>
       <c r="BC202" s="1"/>
-      <c r="BD202" s="1" t="str">
+      <c r="BD202" s="1"/>
+      <c r="BE202" s="1"/>
+      <c r="BF202" s="1"/>
+      <c r="BG202" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15985,7 +16909,10 @@
       <c r="BA203" s="1"/>
       <c r="BB203" s="1"/>
       <c r="BC203" s="1"/>
-      <c r="BD203" s="1" t="str">
+      <c r="BD203" s="1"/>
+      <c r="BE203" s="1"/>
+      <c r="BF203" s="1"/>
+      <c r="BG203" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16049,7 +16976,10 @@
       <c r="BA204" s="1"/>
       <c r="BB204" s="1"/>
       <c r="BC204" s="1"/>
-      <c r="BD204" s="1" t="str">
+      <c r="BD204" s="1"/>
+      <c r="BE204" s="1"/>
+      <c r="BF204" s="1"/>
+      <c r="BG204" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16113,7 +17043,10 @@
       <c r="BA205" s="1"/>
       <c r="BB205" s="1"/>
       <c r="BC205" s="1"/>
-      <c r="BD205" s="1" t="str">
+      <c r="BD205" s="1"/>
+      <c r="BE205" s="1"/>
+      <c r="BF205" s="1"/>
+      <c r="BG205" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16177,7 +17110,10 @@
       <c r="BA206" s="1"/>
       <c r="BB206" s="1"/>
       <c r="BC206" s="1"/>
-      <c r="BD206" s="1" t="str">
+      <c r="BD206" s="1"/>
+      <c r="BE206" s="1"/>
+      <c r="BF206" s="1"/>
+      <c r="BG206" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16241,7 +17177,10 @@
       <c r="BA207" s="1"/>
       <c r="BB207" s="1"/>
       <c r="BC207" s="1"/>
-      <c r="BD207" s="1" t="str">
+      <c r="BD207" s="1"/>
+      <c r="BE207" s="1"/>
+      <c r="BF207" s="1"/>
+      <c r="BG207" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16305,7 +17244,10 @@
       <c r="BA208" s="1"/>
       <c r="BB208" s="1"/>
       <c r="BC208" s="1"/>
-      <c r="BD208" s="1" t="str">
+      <c r="BD208" s="1"/>
+      <c r="BE208" s="1"/>
+      <c r="BF208" s="1"/>
+      <c r="BG208" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16369,7 +17311,10 @@
       <c r="BA209" s="1"/>
       <c r="BB209" s="1"/>
       <c r="BC209" s="1"/>
-      <c r="BD209" s="1" t="str">
+      <c r="BD209" s="1"/>
+      <c r="BE209" s="1"/>
+      <c r="BF209" s="1"/>
+      <c r="BG209" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16433,7 +17378,10 @@
       <c r="BA210" s="1"/>
       <c r="BB210" s="1"/>
       <c r="BC210" s="1"/>
-      <c r="BD210" s="1" t="str">
+      <c r="BD210" s="1"/>
+      <c r="BE210" s="1"/>
+      <c r="BF210" s="1"/>
+      <c r="BG210" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16497,7 +17445,10 @@
       <c r="BA211" s="1"/>
       <c r="BB211" s="1"/>
       <c r="BC211" s="1"/>
-      <c r="BD211" s="1" t="str">
+      <c r="BD211" s="1"/>
+      <c r="BE211" s="1"/>
+      <c r="BF211" s="1"/>
+      <c r="BG211" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16561,7 +17512,10 @@
       <c r="BA212" s="1"/>
       <c r="BB212" s="1"/>
       <c r="BC212" s="1"/>
-      <c r="BD212" s="1" t="str">
+      <c r="BD212" s="1"/>
+      <c r="BE212" s="1"/>
+      <c r="BF212" s="1"/>
+      <c r="BG212" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16625,7 +17579,10 @@
       <c r="BA213" s="1"/>
       <c r="BB213" s="1"/>
       <c r="BC213" s="1"/>
-      <c r="BD213" s="1" t="str">
+      <c r="BD213" s="1"/>
+      <c r="BE213" s="1"/>
+      <c r="BF213" s="1"/>
+      <c r="BG213" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16689,7 +17646,10 @@
       <c r="BA214" s="1"/>
       <c r="BB214" s="1"/>
       <c r="BC214" s="1"/>
-      <c r="BD214" s="1" t="str">
+      <c r="BD214" s="1"/>
+      <c r="BE214" s="1"/>
+      <c r="BF214" s="1"/>
+      <c r="BG214" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16753,7 +17713,10 @@
       <c r="BA215" s="1"/>
       <c r="BB215" s="1"/>
       <c r="BC215" s="1"/>
-      <c r="BD215" s="1" t="str">
+      <c r="BD215" s="1"/>
+      <c r="BE215" s="1"/>
+      <c r="BF215" s="1"/>
+      <c r="BG215" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16817,7 +17780,10 @@
       <c r="BA216" s="1"/>
       <c r="BB216" s="1"/>
       <c r="BC216" s="1"/>
-      <c r="BD216" s="1" t="str">
+      <c r="BD216" s="1"/>
+      <c r="BE216" s="1"/>
+      <c r="BF216" s="1"/>
+      <c r="BG216" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16881,7 +17847,10 @@
       <c r="BA217" s="1"/>
       <c r="BB217" s="1"/>
       <c r="BC217" s="1"/>
-      <c r="BD217" s="1" t="str">
+      <c r="BD217" s="1"/>
+      <c r="BE217" s="1"/>
+      <c r="BF217" s="1"/>
+      <c r="BG217" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16945,7 +17914,10 @@
       <c r="BA218" s="1"/>
       <c r="BB218" s="1"/>
       <c r="BC218" s="1"/>
-      <c r="BD218" s="1" t="str">
+      <c r="BD218" s="1"/>
+      <c r="BE218" s="1"/>
+      <c r="BF218" s="1"/>
+      <c r="BG218" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17009,7 +17981,10 @@
       <c r="BA219" s="1"/>
       <c r="BB219" s="1"/>
       <c r="BC219" s="1"/>
-      <c r="BD219" s="1" t="str">
+      <c r="BD219" s="1"/>
+      <c r="BE219" s="1"/>
+      <c r="BF219" s="1"/>
+      <c r="BG219" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17073,7 +18048,10 @@
       <c r="BA220" s="1"/>
       <c r="BB220" s="1"/>
       <c r="BC220" s="1"/>
-      <c r="BD220" s="1" t="str">
+      <c r="BD220" s="1"/>
+      <c r="BE220" s="1"/>
+      <c r="BF220" s="1"/>
+      <c r="BG220" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17137,7 +18115,10 @@
       <c r="BA221" s="1"/>
       <c r="BB221" s="1"/>
       <c r="BC221" s="1"/>
-      <c r="BD221" s="1" t="str">
+      <c r="BD221" s="1"/>
+      <c r="BE221" s="1"/>
+      <c r="BF221" s="1"/>
+      <c r="BG221" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17201,7 +18182,10 @@
       <c r="BA222" s="1"/>
       <c r="BB222" s="1"/>
       <c r="BC222" s="1"/>
-      <c r="BD222" s="1" t="str">
+      <c r="BD222" s="1"/>
+      <c r="BE222" s="1"/>
+      <c r="BF222" s="1"/>
+      <c r="BG222" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17265,7 +18249,10 @@
       <c r="BA223" s="1"/>
       <c r="BB223" s="1"/>
       <c r="BC223" s="1"/>
-      <c r="BD223" s="1" t="str">
+      <c r="BD223" s="1"/>
+      <c r="BE223" s="1"/>
+      <c r="BF223" s="1"/>
+      <c r="BG223" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17329,7 +18316,10 @@
       <c r="BA224" s="1"/>
       <c r="BB224" s="1"/>
       <c r="BC224" s="1"/>
-      <c r="BD224" s="1" t="str">
+      <c r="BD224" s="1"/>
+      <c r="BE224" s="1"/>
+      <c r="BF224" s="1"/>
+      <c r="BG224" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17393,7 +18383,10 @@
       <c r="BA225" s="1"/>
       <c r="BB225" s="1"/>
       <c r="BC225" s="1"/>
-      <c r="BD225" s="1" t="str">
+      <c r="BD225" s="1"/>
+      <c r="BE225" s="1"/>
+      <c r="BF225" s="1"/>
+      <c r="BG225" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17457,7 +18450,10 @@
       <c r="BA226" s="1"/>
       <c r="BB226" s="1"/>
       <c r="BC226" s="1"/>
-      <c r="BD226" s="1" t="str">
+      <c r="BD226" s="1"/>
+      <c r="BE226" s="1"/>
+      <c r="BF226" s="1"/>
+      <c r="BG226" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17521,7 +18517,10 @@
       <c r="BA227" s="1"/>
       <c r="BB227" s="1"/>
       <c r="BC227" s="1"/>
-      <c r="BD227" s="1" t="str">
+      <c r="BD227" s="1"/>
+      <c r="BE227" s="1"/>
+      <c r="BF227" s="1"/>
+      <c r="BG227" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17585,7 +18584,10 @@
       <c r="BA228" s="1"/>
       <c r="BB228" s="1"/>
       <c r="BC228" s="1"/>
-      <c r="BD228" s="1" t="str">
+      <c r="BD228" s="1"/>
+      <c r="BE228" s="1"/>
+      <c r="BF228" s="1"/>
+      <c r="BG228" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17649,7 +18651,10 @@
       <c r="BA229" s="1"/>
       <c r="BB229" s="1"/>
       <c r="BC229" s="1"/>
-      <c r="BD229" s="1" t="str">
+      <c r="BD229" s="1"/>
+      <c r="BE229" s="1"/>
+      <c r="BF229" s="1"/>
+      <c r="BG229" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17713,7 +18718,10 @@
       <c r="BA230" s="1"/>
       <c r="BB230" s="1"/>
       <c r="BC230" s="1"/>
-      <c r="BD230" s="1" t="str">
+      <c r="BD230" s="1"/>
+      <c r="BE230" s="1"/>
+      <c r="BF230" s="1"/>
+      <c r="BG230" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17777,7 +18785,10 @@
       <c r="BA231" s="1"/>
       <c r="BB231" s="1"/>
       <c r="BC231" s="1"/>
-      <c r="BD231" s="1" t="str">
+      <c r="BD231" s="1"/>
+      <c r="BE231" s="1"/>
+      <c r="BF231" s="1"/>
+      <c r="BG231" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17841,7 +18852,10 @@
       <c r="BA232" s="1"/>
       <c r="BB232" s="1"/>
       <c r="BC232" s="1"/>
-      <c r="BD232" s="1" t="str">
+      <c r="BD232" s="1"/>
+      <c r="BE232" s="1"/>
+      <c r="BF232" s="1"/>
+      <c r="BG232" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17905,7 +18919,10 @@
       <c r="BA233" s="1"/>
       <c r="BB233" s="1"/>
       <c r="BC233" s="1"/>
-      <c r="BD233" s="1" t="str">
+      <c r="BD233" s="1"/>
+      <c r="BE233" s="1"/>
+      <c r="BF233" s="1"/>
+      <c r="BG233" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17969,7 +18986,10 @@
       <c r="BA234" s="1"/>
       <c r="BB234" s="1"/>
       <c r="BC234" s="1"/>
-      <c r="BD234" s="1" t="str">
+      <c r="BD234" s="1"/>
+      <c r="BE234" s="1"/>
+      <c r="BF234" s="1"/>
+      <c r="BG234" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18033,7 +19053,10 @@
       <c r="BA235" s="1"/>
       <c r="BB235" s="1"/>
       <c r="BC235" s="1"/>
-      <c r="BD235" s="1" t="str">
+      <c r="BD235" s="1"/>
+      <c r="BE235" s="1"/>
+      <c r="BF235" s="1"/>
+      <c r="BG235" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18097,7 +19120,10 @@
       <c r="BA236" s="1"/>
       <c r="BB236" s="1"/>
       <c r="BC236" s="1"/>
-      <c r="BD236" s="1" t="str">
+      <c r="BD236" s="1"/>
+      <c r="BE236" s="1"/>
+      <c r="BF236" s="1"/>
+      <c r="BG236" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18161,7 +19187,10 @@
       <c r="BA237" s="1"/>
       <c r="BB237" s="1"/>
       <c r="BC237" s="1"/>
-      <c r="BD237" s="1" t="str">
+      <c r="BD237" s="1"/>
+      <c r="BE237" s="1"/>
+      <c r="BF237" s="1"/>
+      <c r="BG237" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18225,7 +19254,10 @@
       <c r="BA238" s="1"/>
       <c r="BB238" s="1"/>
       <c r="BC238" s="1"/>
-      <c r="BD238" s="1" t="str">
+      <c r="BD238" s="1"/>
+      <c r="BE238" s="1"/>
+      <c r="BF238" s="1"/>
+      <c r="BG238" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18289,7 +19321,10 @@
       <c r="BA239" s="1"/>
       <c r="BB239" s="1"/>
       <c r="BC239" s="1"/>
-      <c r="BD239" s="1" t="str">
+      <c r="BD239" s="1"/>
+      <c r="BE239" s="1"/>
+      <c r="BF239" s="1"/>
+      <c r="BG239" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18353,7 +19388,10 @@
       <c r="BA240" s="1"/>
       <c r="BB240" s="1"/>
       <c r="BC240" s="1"/>
-      <c r="BD240" s="1" t="str">
+      <c r="BD240" s="1"/>
+      <c r="BE240" s="1"/>
+      <c r="BF240" s="1"/>
+      <c r="BG240" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18417,7 +19455,10 @@
       <c r="BA241" s="1"/>
       <c r="BB241" s="1"/>
       <c r="BC241" s="1"/>
-      <c r="BD241" s="1" t="str">
+      <c r="BD241" s="1"/>
+      <c r="BE241" s="1"/>
+      <c r="BF241" s="1"/>
+      <c r="BG241" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18481,7 +19522,10 @@
       <c r="BA242" s="1"/>
       <c r="BB242" s="1"/>
       <c r="BC242" s="1"/>
-      <c r="BD242" s="1" t="str">
+      <c r="BD242" s="1"/>
+      <c r="BE242" s="1"/>
+      <c r="BF242" s="1"/>
+      <c r="BG242" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18545,7 +19589,10 @@
       <c r="BA243" s="1"/>
       <c r="BB243" s="1"/>
       <c r="BC243" s="1"/>
-      <c r="BD243" s="1" t="str">
+      <c r="BD243" s="1"/>
+      <c r="BE243" s="1"/>
+      <c r="BF243" s="1"/>
+      <c r="BG243" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18609,7 +19656,10 @@
       <c r="BA244" s="1"/>
       <c r="BB244" s="1"/>
       <c r="BC244" s="1"/>
-      <c r="BD244" s="1" t="str">
+      <c r="BD244" s="1"/>
+      <c r="BE244" s="1"/>
+      <c r="BF244" s="1"/>
+      <c r="BG244" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18673,7 +19723,10 @@
       <c r="BA245" s="1"/>
       <c r="BB245" s="1"/>
       <c r="BC245" s="1"/>
-      <c r="BD245" s="1" t="str">
+      <c r="BD245" s="1"/>
+      <c r="BE245" s="1"/>
+      <c r="BF245" s="1"/>
+      <c r="BG245" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18737,7 +19790,10 @@
       <c r="BA246" s="1"/>
       <c r="BB246" s="1"/>
       <c r="BC246" s="1"/>
-      <c r="BD246" s="1" t="str">
+      <c r="BD246" s="1"/>
+      <c r="BE246" s="1"/>
+      <c r="BF246" s="1"/>
+      <c r="BG246" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18801,7 +19857,10 @@
       <c r="BA247" s="1"/>
       <c r="BB247" s="1"/>
       <c r="BC247" s="1"/>
-      <c r="BD247" s="1" t="str">
+      <c r="BD247" s="1"/>
+      <c r="BE247" s="1"/>
+      <c r="BF247" s="1"/>
+      <c r="BG247" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18865,7 +19924,10 @@
       <c r="BA248" s="1"/>
       <c r="BB248" s="1"/>
       <c r="BC248" s="1"/>
-      <c r="BD248" s="1" t="str">
+      <c r="BD248" s="1"/>
+      <c r="BE248" s="1"/>
+      <c r="BF248" s="1"/>
+      <c r="BG248" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18929,7 +19991,10 @@
       <c r="BA249" s="1"/>
       <c r="BB249" s="1"/>
       <c r="BC249" s="1"/>
-      <c r="BD249" s="1" t="str">
+      <c r="BD249" s="1"/>
+      <c r="BE249" s="1"/>
+      <c r="BF249" s="1"/>
+      <c r="BG249" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18993,7 +20058,10 @@
       <c r="BA250" s="1"/>
       <c r="BB250" s="1"/>
       <c r="BC250" s="1"/>
-      <c r="BD250" s="1" t="str">
+      <c r="BD250" s="1"/>
+      <c r="BE250" s="1"/>
+      <c r="BF250" s="1"/>
+      <c r="BG250" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19057,7 +20125,10 @@
       <c r="BA251" s="1"/>
       <c r="BB251" s="1"/>
       <c r="BC251" s="1"/>
-      <c r="BD251" s="1" t="str">
+      <c r="BD251" s="1"/>
+      <c r="BE251" s="1"/>
+      <c r="BF251" s="1"/>
+      <c r="BG251" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19121,7 +20192,10 @@
       <c r="BA252" s="1"/>
       <c r="BB252" s="1"/>
       <c r="BC252" s="1"/>
-      <c r="BD252" s="1" t="str">
+      <c r="BD252" s="1"/>
+      <c r="BE252" s="1"/>
+      <c r="BF252" s="1"/>
+      <c r="BG252" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19185,7 +20259,10 @@
       <c r="BA253" s="1"/>
       <c r="BB253" s="1"/>
       <c r="BC253" s="1"/>
-      <c r="BD253" s="1" t="str">
+      <c r="BD253" s="1"/>
+      <c r="BE253" s="1"/>
+      <c r="BF253" s="1"/>
+      <c r="BG253" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19249,7 +20326,10 @@
       <c r="BA254" s="1"/>
       <c r="BB254" s="1"/>
       <c r="BC254" s="1"/>
-      <c r="BD254" s="1" t="str">
+      <c r="BD254" s="1"/>
+      <c r="BE254" s="1"/>
+      <c r="BF254" s="1"/>
+      <c r="BG254" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19313,7 +20393,10 @@
       <c r="BA255" s="1"/>
       <c r="BB255" s="1"/>
       <c r="BC255" s="1"/>
-      <c r="BD255" s="1" t="str">
+      <c r="BD255" s="1"/>
+      <c r="BE255" s="1"/>
+      <c r="BF255" s="1"/>
+      <c r="BG255" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19377,7 +20460,10 @@
       <c r="BA256" s="1"/>
       <c r="BB256" s="1"/>
       <c r="BC256" s="1"/>
-      <c r="BD256" s="1" t="str">
+      <c r="BD256" s="1"/>
+      <c r="BE256" s="1"/>
+      <c r="BF256" s="1"/>
+      <c r="BG256" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19441,7 +20527,10 @@
       <c r="BA257" s="1"/>
       <c r="BB257" s="1"/>
       <c r="BC257" s="1"/>
-      <c r="BD257" s="1" t="str">
+      <c r="BD257" s="1"/>
+      <c r="BE257" s="1"/>
+      <c r="BF257" s="1"/>
+      <c r="BG257" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19505,7 +20594,10 @@
       <c r="BA258" s="1"/>
       <c r="BB258" s="1"/>
       <c r="BC258" s="1"/>
-      <c r="BD258" s="1" t="str">
+      <c r="BD258" s="1"/>
+      <c r="BE258" s="1"/>
+      <c r="BF258" s="1"/>
+      <c r="BG258" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19569,7 +20661,10 @@
       <c r="BA259" s="1"/>
       <c r="BB259" s="1"/>
       <c r="BC259" s="1"/>
-      <c r="BD259" s="1" t="str">
+      <c r="BD259" s="1"/>
+      <c r="BE259" s="1"/>
+      <c r="BF259" s="1"/>
+      <c r="BG259" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19633,7 +20728,10 @@
       <c r="BA260" s="1"/>
       <c r="BB260" s="1"/>
       <c r="BC260" s="1"/>
-      <c r="BD260" s="1" t="str">
+      <c r="BD260" s="1"/>
+      <c r="BE260" s="1"/>
+      <c r="BF260" s="1"/>
+      <c r="BG260" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19697,7 +20795,10 @@
       <c r="BA261" s="1"/>
       <c r="BB261" s="1"/>
       <c r="BC261" s="1"/>
-      <c r="BD261" s="1" t="str">
+      <c r="BD261" s="1"/>
+      <c r="BE261" s="1"/>
+      <c r="BF261" s="1"/>
+      <c r="BG261" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19761,7 +20862,10 @@
       <c r="BA262" s="1"/>
       <c r="BB262" s="1"/>
       <c r="BC262" s="1"/>
-      <c r="BD262" s="1" t="str">
+      <c r="BD262" s="1"/>
+      <c r="BE262" s="1"/>
+      <c r="BF262" s="1"/>
+      <c r="BG262" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19825,7 +20929,10 @@
       <c r="BA263" s="1"/>
       <c r="BB263" s="1"/>
       <c r="BC263" s="1"/>
-      <c r="BD263" s="1" t="str">
+      <c r="BD263" s="1"/>
+      <c r="BE263" s="1"/>
+      <c r="BF263" s="1"/>
+      <c r="BG263" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19889,7 +20996,10 @@
       <c r="BA264" s="1"/>
       <c r="BB264" s="1"/>
       <c r="BC264" s="1"/>
-      <c r="BD264" s="1" t="str">
+      <c r="BD264" s="1"/>
+      <c r="BE264" s="1"/>
+      <c r="BF264" s="1"/>
+      <c r="BG264" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19953,7 +21063,10 @@
       <c r="BA265" s="1"/>
       <c r="BB265" s="1"/>
       <c r="BC265" s="1"/>
-      <c r="BD265" s="1" t="str">
+      <c r="BD265" s="1"/>
+      <c r="BE265" s="1"/>
+      <c r="BF265" s="1"/>
+      <c r="BG265" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20017,7 +21130,10 @@
       <c r="BA266" s="1"/>
       <c r="BB266" s="1"/>
       <c r="BC266" s="1"/>
-      <c r="BD266" s="1" t="str">
+      <c r="BD266" s="1"/>
+      <c r="BE266" s="1"/>
+      <c r="BF266" s="1"/>
+      <c r="BG266" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20081,7 +21197,10 @@
       <c r="BA267" s="1"/>
       <c r="BB267" s="1"/>
       <c r="BC267" s="1"/>
-      <c r="BD267" s="1" t="str">
+      <c r="BD267" s="1"/>
+      <c r="BE267" s="1"/>
+      <c r="BF267" s="1"/>
+      <c r="BG267" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20145,7 +21264,10 @@
       <c r="BA268" s="1"/>
       <c r="BB268" s="1"/>
       <c r="BC268" s="1"/>
-      <c r="BD268" s="1" t="str">
+      <c r="BD268" s="1"/>
+      <c r="BE268" s="1"/>
+      <c r="BF268" s="1"/>
+      <c r="BG268" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20209,7 +21331,10 @@
       <c r="BA269" s="1"/>
       <c r="BB269" s="1"/>
       <c r="BC269" s="1"/>
-      <c r="BD269" s="1" t="str">
+      <c r="BD269" s="1"/>
+      <c r="BE269" s="1"/>
+      <c r="BF269" s="1"/>
+      <c r="BG269" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20273,7 +21398,10 @@
       <c r="BA270" s="1"/>
       <c r="BB270" s="1"/>
       <c r="BC270" s="1"/>
-      <c r="BD270" s="1" t="str">
+      <c r="BD270" s="1"/>
+      <c r="BE270" s="1"/>
+      <c r="BF270" s="1"/>
+      <c r="BG270" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20337,7 +21465,10 @@
       <c r="BA271" s="1"/>
       <c r="BB271" s="1"/>
       <c r="BC271" s="1"/>
-      <c r="BD271" s="1" t="str">
+      <c r="BD271" s="1"/>
+      <c r="BE271" s="1"/>
+      <c r="BF271" s="1"/>
+      <c r="BG271" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20401,7 +21532,10 @@
       <c r="BA272" s="1"/>
       <c r="BB272" s="1"/>
       <c r="BC272" s="1"/>
-      <c r="BD272" s="1" t="str">
+      <c r="BD272" s="1"/>
+      <c r="BE272" s="1"/>
+      <c r="BF272" s="1"/>
+      <c r="BG272" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20465,7 +21599,10 @@
       <c r="BA273" s="1"/>
       <c r="BB273" s="1"/>
       <c r="BC273" s="1"/>
-      <c r="BD273" s="1" t="str">
+      <c r="BD273" s="1"/>
+      <c r="BE273" s="1"/>
+      <c r="BF273" s="1"/>
+      <c r="BG273" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20529,7 +21666,10 @@
       <c r="BA274" s="1"/>
       <c r="BB274" s="1"/>
       <c r="BC274" s="1"/>
-      <c r="BD274" s="1" t="str">
+      <c r="BD274" s="1"/>
+      <c r="BE274" s="1"/>
+      <c r="BF274" s="1"/>
+      <c r="BG274" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20593,7 +21733,10 @@
       <c r="BA275" s="1"/>
       <c r="BB275" s="1"/>
       <c r="BC275" s="1"/>
-      <c r="BD275" s="1" t="str">
+      <c r="BD275" s="1"/>
+      <c r="BE275" s="1"/>
+      <c r="BF275" s="1"/>
+      <c r="BG275" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20657,7 +21800,10 @@
       <c r="BA276" s="1"/>
       <c r="BB276" s="1"/>
       <c r="BC276" s="1"/>
-      <c r="BD276" s="1" t="str">
+      <c r="BD276" s="1"/>
+      <c r="BE276" s="1"/>
+      <c r="BF276" s="1"/>
+      <c r="BG276" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20721,7 +21867,10 @@
       <c r="BA277" s="1"/>
       <c r="BB277" s="1"/>
       <c r="BC277" s="1"/>
-      <c r="BD277" s="1" t="str">
+      <c r="BD277" s="1"/>
+      <c r="BE277" s="1"/>
+      <c r="BF277" s="1"/>
+      <c r="BG277" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20785,7 +21934,10 @@
       <c r="BA278" s="1"/>
       <c r="BB278" s="1"/>
       <c r="BC278" s="1"/>
-      <c r="BD278" s="1" t="str">
+      <c r="BD278" s="1"/>
+      <c r="BE278" s="1"/>
+      <c r="BF278" s="1"/>
+      <c r="BG278" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20849,7 +22001,10 @@
       <c r="BA279" s="1"/>
       <c r="BB279" s="1"/>
       <c r="BC279" s="1"/>
-      <c r="BD279" s="1" t="str">
+      <c r="BD279" s="1"/>
+      <c r="BE279" s="1"/>
+      <c r="BF279" s="1"/>
+      <c r="BG279" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20913,7 +22068,10 @@
       <c r="BA280" s="1"/>
       <c r="BB280" s="1"/>
       <c r="BC280" s="1"/>
-      <c r="BD280" s="1" t="str">
+      <c r="BD280" s="1"/>
+      <c r="BE280" s="1"/>
+      <c r="BF280" s="1"/>
+      <c r="BG280" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20977,7 +22135,10 @@
       <c r="BA281" s="1"/>
       <c r="BB281" s="1"/>
       <c r="BC281" s="1"/>
-      <c r="BD281" s="1" t="str">
+      <c r="BD281" s="1"/>
+      <c r="BE281" s="1"/>
+      <c r="BF281" s="1"/>
+      <c r="BG281" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21041,7 +22202,10 @@
       <c r="BA282" s="1"/>
       <c r="BB282" s="1"/>
       <c r="BC282" s="1"/>
-      <c r="BD282" s="1" t="str">
+      <c r="BD282" s="1"/>
+      <c r="BE282" s="1"/>
+      <c r="BF282" s="1"/>
+      <c r="BG282" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21105,7 +22269,10 @@
       <c r="BA283" s="1"/>
       <c r="BB283" s="1"/>
       <c r="BC283" s="1"/>
-      <c r="BD283" s="1" t="str">
+      <c r="BD283" s="1"/>
+      <c r="BE283" s="1"/>
+      <c r="BF283" s="1"/>
+      <c r="BG283" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21169,7 +22336,10 @@
       <c r="BA284" s="1"/>
       <c r="BB284" s="1"/>
       <c r="BC284" s="1"/>
-      <c r="BD284" s="1" t="str">
+      <c r="BD284" s="1"/>
+      <c r="BE284" s="1"/>
+      <c r="BF284" s="1"/>
+      <c r="BG284" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21233,7 +22403,10 @@
       <c r="BA285" s="1"/>
       <c r="BB285" s="1"/>
       <c r="BC285" s="1"/>
-      <c r="BD285" s="1" t="str">
+      <c r="BD285" s="1"/>
+      <c r="BE285" s="1"/>
+      <c r="BF285" s="1"/>
+      <c r="BG285" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21297,7 +22470,10 @@
       <c r="BA286" s="1"/>
       <c r="BB286" s="1"/>
       <c r="BC286" s="1"/>
-      <c r="BD286" s="1" t="str">
+      <c r="BD286" s="1"/>
+      <c r="BE286" s="1"/>
+      <c r="BF286" s="1"/>
+      <c r="BG286" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21361,7 +22537,10 @@
       <c r="BA287" s="1"/>
       <c r="BB287" s="1"/>
       <c r="BC287" s="1"/>
-      <c r="BD287" s="1" t="str">
+      <c r="BD287" s="1"/>
+      <c r="BE287" s="1"/>
+      <c r="BF287" s="1"/>
+      <c r="BG287" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21425,7 +22604,10 @@
       <c r="BA288" s="1"/>
       <c r="BB288" s="1"/>
       <c r="BC288" s="1"/>
-      <c r="BD288" s="1" t="str">
+      <c r="BD288" s="1"/>
+      <c r="BE288" s="1"/>
+      <c r="BF288" s="1"/>
+      <c r="BG288" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21489,7 +22671,10 @@
       <c r="BA289" s="1"/>
       <c r="BB289" s="1"/>
       <c r="BC289" s="1"/>
-      <c r="BD289" s="1" t="str">
+      <c r="BD289" s="1"/>
+      <c r="BE289" s="1"/>
+      <c r="BF289" s="1"/>
+      <c r="BG289" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21553,7 +22738,10 @@
       <c r="BA290" s="1"/>
       <c r="BB290" s="1"/>
       <c r="BC290" s="1"/>
-      <c r="BD290" s="1" t="str">
+      <c r="BD290" s="1"/>
+      <c r="BE290" s="1"/>
+      <c r="BF290" s="1"/>
+      <c r="BG290" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21617,7 +22805,10 @@
       <c r="BA291" s="1"/>
       <c r="BB291" s="1"/>
       <c r="BC291" s="1"/>
-      <c r="BD291" s="1" t="str">
+      <c r="BD291" s="1"/>
+      <c r="BE291" s="1"/>
+      <c r="BF291" s="1"/>
+      <c r="BG291" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21681,7 +22872,10 @@
       <c r="BA292" s="1"/>
       <c r="BB292" s="1"/>
       <c r="BC292" s="1"/>
-      <c r="BD292" s="1" t="str">
+      <c r="BD292" s="1"/>
+      <c r="BE292" s="1"/>
+      <c r="BF292" s="1"/>
+      <c r="BG292" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21745,7 +22939,10 @@
       <c r="BA293" s="1"/>
       <c r="BB293" s="1"/>
       <c r="BC293" s="1"/>
-      <c r="BD293" s="1" t="str">
+      <c r="BD293" s="1"/>
+      <c r="BE293" s="1"/>
+      <c r="BF293" s="1"/>
+      <c r="BG293" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21809,7 +23006,10 @@
       <c r="BA294" s="1"/>
       <c r="BB294" s="1"/>
       <c r="BC294" s="1"/>
-      <c r="BD294" s="1" t="str">
+      <c r="BD294" s="1"/>
+      <c r="BE294" s="1"/>
+      <c r="BF294" s="1"/>
+      <c r="BG294" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21873,7 +23073,10 @@
       <c r="BA295" s="1"/>
       <c r="BB295" s="1"/>
       <c r="BC295" s="1"/>
-      <c r="BD295" s="1" t="str">
+      <c r="BD295" s="1"/>
+      <c r="BE295" s="1"/>
+      <c r="BF295" s="1"/>
+      <c r="BG295" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21937,7 +23140,10 @@
       <c r="BA296" s="1"/>
       <c r="BB296" s="1"/>
       <c r="BC296" s="1"/>
-      <c r="BD296" s="1" t="str">
+      <c r="BD296" s="1"/>
+      <c r="BE296" s="1"/>
+      <c r="BF296" s="1"/>
+      <c r="BG296" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22001,7 +23207,10 @@
       <c r="BA297" s="1"/>
       <c r="BB297" s="1"/>
       <c r="BC297" s="1"/>
-      <c r="BD297" s="1" t="str">
+      <c r="BD297" s="1"/>
+      <c r="BE297" s="1"/>
+      <c r="BF297" s="1"/>
+      <c r="BG297" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22065,7 +23274,10 @@
       <c r="BA298" s="1"/>
       <c r="BB298" s="1"/>
       <c r="BC298" s="1"/>
-      <c r="BD298" s="1" t="str">
+      <c r="BD298" s="1"/>
+      <c r="BE298" s="1"/>
+      <c r="BF298" s="1"/>
+      <c r="BG298" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22129,7 +23341,10 @@
       <c r="BA299" s="1"/>
       <c r="BB299" s="1"/>
       <c r="BC299" s="1"/>
-      <c r="BD299" s="1" t="str">
+      <c r="BD299" s="1"/>
+      <c r="BE299" s="1"/>
+      <c r="BF299" s="1"/>
+      <c r="BG299" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22193,7 +23408,10 @@
       <c r="BA300" s="1"/>
       <c r="BB300" s="1"/>
       <c r="BC300" s="1"/>
-      <c r="BD300" s="1" t="str">
+      <c r="BD300" s="1"/>
+      <c r="BE300" s="1"/>
+      <c r="BF300" s="1"/>
+      <c r="BG300" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22257,7 +23475,10 @@
       <c r="BA301" s="1"/>
       <c r="BB301" s="1"/>
       <c r="BC301" s="1"/>
-      <c r="BD301" s="1" t="str">
+      <c r="BD301" s="1"/>
+      <c r="BE301" s="1"/>
+      <c r="BF301" s="1"/>
+      <c r="BG301" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22321,7 +23542,10 @@
       <c r="BA302" s="1"/>
       <c r="BB302" s="1"/>
       <c r="BC302" s="1"/>
-      <c r="BD302" s="1" t="str">
+      <c r="BD302" s="1"/>
+      <c r="BE302" s="1"/>
+      <c r="BF302" s="1"/>
+      <c r="BG302" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22385,7 +23609,10 @@
       <c r="BA303" s="1"/>
       <c r="BB303" s="1"/>
       <c r="BC303" s="1"/>
-      <c r="BD303" s="1" t="str">
+      <c r="BD303" s="1"/>
+      <c r="BE303" s="1"/>
+      <c r="BF303" s="1"/>
+      <c r="BG303" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22449,7 +23676,10 @@
       <c r="BA304" s="1"/>
       <c r="BB304" s="1"/>
       <c r="BC304" s="1"/>
-      <c r="BD304" s="1" t="str">
+      <c r="BD304" s="1"/>
+      <c r="BE304" s="1"/>
+      <c r="BF304" s="1"/>
+      <c r="BG304" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22513,7 +23743,10 @@
       <c r="BA305" s="1"/>
       <c r="BB305" s="1"/>
       <c r="BC305" s="1"/>
-      <c r="BD305" s="1" t="str">
+      <c r="BD305" s="1"/>
+      <c r="BE305" s="1"/>
+      <c r="BF305" s="1"/>
+      <c r="BG305" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22577,7 +23810,10 @@
       <c r="BA306" s="1"/>
       <c r="BB306" s="1"/>
       <c r="BC306" s="1"/>
-      <c r="BD306" s="1" t="str">
+      <c r="BD306" s="1"/>
+      <c r="BE306" s="1"/>
+      <c r="BF306" s="1"/>
+      <c r="BG306" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22641,7 +23877,10 @@
       <c r="BA307" s="1"/>
       <c r="BB307" s="1"/>
       <c r="BC307" s="1"/>
-      <c r="BD307" s="1" t="str">
+      <c r="BD307" s="1"/>
+      <c r="BE307" s="1"/>
+      <c r="BF307" s="1"/>
+      <c r="BG307" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22705,7 +23944,10 @@
       <c r="BA308" s="1"/>
       <c r="BB308" s="1"/>
       <c r="BC308" s="1"/>
-      <c r="BD308" s="1" t="str">
+      <c r="BD308" s="1"/>
+      <c r="BE308" s="1"/>
+      <c r="BF308" s="1"/>
+      <c r="BG308" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22769,7 +24011,10 @@
       <c r="BA309" s="1"/>
       <c r="BB309" s="1"/>
       <c r="BC309" s="1"/>
-      <c r="BD309" s="1" t="str">
+      <c r="BD309" s="1"/>
+      <c r="BE309" s="1"/>
+      <c r="BF309" s="1"/>
+      <c r="BG309" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22833,7 +24078,10 @@
       <c r="BA310" s="1"/>
       <c r="BB310" s="1"/>
       <c r="BC310" s="1"/>
-      <c r="BD310" s="1" t="str">
+      <c r="BD310" s="1"/>
+      <c r="BE310" s="1"/>
+      <c r="BF310" s="1"/>
+      <c r="BG310" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22897,7 +24145,10 @@
       <c r="BA311" s="1"/>
       <c r="BB311" s="1"/>
       <c r="BC311" s="1"/>
-      <c r="BD311" s="1" t="str">
+      <c r="BD311" s="1"/>
+      <c r="BE311" s="1"/>
+      <c r="BF311" s="1"/>
+      <c r="BG311" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22961,7 +24212,10 @@
       <c r="BA312" s="1"/>
       <c r="BB312" s="1"/>
       <c r="BC312" s="1"/>
-      <c r="BD312" s="1" t="str">
+      <c r="BD312" s="1"/>
+      <c r="BE312" s="1"/>
+      <c r="BF312" s="1"/>
+      <c r="BG312" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23025,7 +24279,10 @@
       <c r="BA313" s="1"/>
       <c r="BB313" s="1"/>
       <c r="BC313" s="1"/>
-      <c r="BD313" s="1" t="str">
+      <c r="BD313" s="1"/>
+      <c r="BE313" s="1"/>
+      <c r="BF313" s="1"/>
+      <c r="BG313" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23089,7 +24346,10 @@
       <c r="BA314" s="1"/>
       <c r="BB314" s="1"/>
       <c r="BC314" s="1"/>
-      <c r="BD314" s="1" t="str">
+      <c r="BD314" s="1"/>
+      <c r="BE314" s="1"/>
+      <c r="BF314" s="1"/>
+      <c r="BG314" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23153,7 +24413,10 @@
       <c r="BA315" s="1"/>
       <c r="BB315" s="1"/>
       <c r="BC315" s="1"/>
-      <c r="BD315" s="1" t="str">
+      <c r="BD315" s="1"/>
+      <c r="BE315" s="1"/>
+      <c r="BF315" s="1"/>
+      <c r="BG315" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23217,7 +24480,10 @@
       <c r="BA316" s="1"/>
       <c r="BB316" s="1"/>
       <c r="BC316" s="1"/>
-      <c r="BD316" s="1" t="str">
+      <c r="BD316" s="1"/>
+      <c r="BE316" s="1"/>
+      <c r="BF316" s="1"/>
+      <c r="BG316" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23281,7 +24547,10 @@
       <c r="BA317" s="1"/>
       <c r="BB317" s="1"/>
       <c r="BC317" s="1"/>
-      <c r="BD317" s="1" t="str">
+      <c r="BD317" s="1"/>
+      <c r="BE317" s="1"/>
+      <c r="BF317" s="1"/>
+      <c r="BG317" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23345,7 +24614,10 @@
       <c r="BA318" s="1"/>
       <c r="BB318" s="1"/>
       <c r="BC318" s="1"/>
-      <c r="BD318" s="1" t="str">
+      <c r="BD318" s="1"/>
+      <c r="BE318" s="1"/>
+      <c r="BF318" s="1"/>
+      <c r="BG318" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23409,7 +24681,10 @@
       <c r="BA319" s="1"/>
       <c r="BB319" s="1"/>
       <c r="BC319" s="1"/>
-      <c r="BD319" s="1" t="str">
+      <c r="BD319" s="1"/>
+      <c r="BE319" s="1"/>
+      <c r="BF319" s="1"/>
+      <c r="BG319" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23473,7 +24748,10 @@
       <c r="BA320" s="1"/>
       <c r="BB320" s="1"/>
       <c r="BC320" s="1"/>
-      <c r="BD320" s="1" t="str">
+      <c r="BD320" s="1"/>
+      <c r="BE320" s="1"/>
+      <c r="BF320" s="1"/>
+      <c r="BG320" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23537,7 +24815,10 @@
       <c r="BA321" s="1"/>
       <c r="BB321" s="1"/>
       <c r="BC321" s="1"/>
-      <c r="BD321" s="1" t="str">
+      <c r="BD321" s="1"/>
+      <c r="BE321" s="1"/>
+      <c r="BF321" s="1"/>
+      <c r="BG321" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23601,7 +24882,10 @@
       <c r="BA322" s="1"/>
       <c r="BB322" s="1"/>
       <c r="BC322" s="1"/>
-      <c r="BD322" s="1" t="str">
+      <c r="BD322" s="1"/>
+      <c r="BE322" s="1"/>
+      <c r="BF322" s="1"/>
+      <c r="BG322" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23665,7 +24949,10 @@
       <c r="BA323" s="1"/>
       <c r="BB323" s="1"/>
       <c r="BC323" s="1"/>
-      <c r="BD323" s="1" t="str">
+      <c r="BD323" s="1"/>
+      <c r="BE323" s="1"/>
+      <c r="BF323" s="1"/>
+      <c r="BG323" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23729,7 +25016,10 @@
       <c r="BA324" s="1"/>
       <c r="BB324" s="1"/>
       <c r="BC324" s="1"/>
-      <c r="BD324" s="1" t="str">
+      <c r="BD324" s="1"/>
+      <c r="BE324" s="1"/>
+      <c r="BF324" s="1"/>
+      <c r="BG324" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23793,7 +25083,10 @@
       <c r="BA325" s="1"/>
       <c r="BB325" s="1"/>
       <c r="BC325" s="1"/>
-      <c r="BD325" s="1" t="str">
+      <c r="BD325" s="1"/>
+      <c r="BE325" s="1"/>
+      <c r="BF325" s="1"/>
+      <c r="BG325" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23857,7 +25150,10 @@
       <c r="BA326" s="1"/>
       <c r="BB326" s="1"/>
       <c r="BC326" s="1"/>
-      <c r="BD326" s="1" t="str">
+      <c r="BD326" s="1"/>
+      <c r="BE326" s="1"/>
+      <c r="BF326" s="1"/>
+      <c r="BG326" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23921,7 +25217,10 @@
       <c r="BA327" s="1"/>
       <c r="BB327" s="1"/>
       <c r="BC327" s="1"/>
-      <c r="BD327" s="1" t="str">
+      <c r="BD327" s="1"/>
+      <c r="BE327" s="1"/>
+      <c r="BF327" s="1"/>
+      <c r="BG327" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23985,7 +25284,10 @@
       <c r="BA328" s="1"/>
       <c r="BB328" s="1"/>
       <c r="BC328" s="1"/>
-      <c r="BD328" s="1" t="str">
+      <c r="BD328" s="1"/>
+      <c r="BE328" s="1"/>
+      <c r="BF328" s="1"/>
+      <c r="BG328" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24049,7 +25351,10 @@
       <c r="BA329" s="1"/>
       <c r="BB329" s="1"/>
       <c r="BC329" s="1"/>
-      <c r="BD329" s="1" t="str">
+      <c r="BD329" s="1"/>
+      <c r="BE329" s="1"/>
+      <c r="BF329" s="1"/>
+      <c r="BG329" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24113,7 +25418,10 @@
       <c r="BA330" s="1"/>
       <c r="BB330" s="1"/>
       <c r="BC330" s="1"/>
-      <c r="BD330" s="1" t="str">
+      <c r="BD330" s="1"/>
+      <c r="BE330" s="1"/>
+      <c r="BF330" s="1"/>
+      <c r="BG330" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24177,7 +25485,10 @@
       <c r="BA331" s="1"/>
       <c r="BB331" s="1"/>
       <c r="BC331" s="1"/>
-      <c r="BD331" s="1" t="str">
+      <c r="BD331" s="1"/>
+      <c r="BE331" s="1"/>
+      <c r="BF331" s="1"/>
+      <c r="BG331" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24241,7 +25552,10 @@
       <c r="BA332" s="1"/>
       <c r="BB332" s="1"/>
       <c r="BC332" s="1"/>
-      <c r="BD332" s="1" t="str">
+      <c r="BD332" s="1"/>
+      <c r="BE332" s="1"/>
+      <c r="BF332" s="1"/>
+      <c r="BG332" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24305,7 +25619,10 @@
       <c r="BA333" s="1"/>
       <c r="BB333" s="1"/>
       <c r="BC333" s="1"/>
-      <c r="BD333" s="1" t="str">
+      <c r="BD333" s="1"/>
+      <c r="BE333" s="1"/>
+      <c r="BF333" s="1"/>
+      <c r="BG333" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24369,7 +25686,10 @@
       <c r="BA334" s="1"/>
       <c r="BB334" s="1"/>
       <c r="BC334" s="1"/>
-      <c r="BD334" s="1" t="str">
+      <c r="BD334" s="1"/>
+      <c r="BE334" s="1"/>
+      <c r="BF334" s="1"/>
+      <c r="BG334" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24433,7 +25753,10 @@
       <c r="BA335" s="1"/>
       <c r="BB335" s="1"/>
       <c r="BC335" s="1"/>
-      <c r="BD335" s="1" t="str">
+      <c r="BD335" s="1"/>
+      <c r="BE335" s="1"/>
+      <c r="BF335" s="1"/>
+      <c r="BG335" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24497,7 +25820,10 @@
       <c r="BA336" s="1"/>
       <c r="BB336" s="1"/>
       <c r="BC336" s="1"/>
-      <c r="BD336" s="1" t="str">
+      <c r="BD336" s="1"/>
+      <c r="BE336" s="1"/>
+      <c r="BF336" s="1"/>
+      <c r="BG336" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24561,7 +25887,10 @@
       <c r="BA337" s="1"/>
       <c r="BB337" s="1"/>
       <c r="BC337" s="1"/>
-      <c r="BD337" s="1" t="str">
+      <c r="BD337" s="1"/>
+      <c r="BE337" s="1"/>
+      <c r="BF337" s="1"/>
+      <c r="BG337" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24625,7 +25954,10 @@
       <c r="BA338" s="1"/>
       <c r="BB338" s="1"/>
       <c r="BC338" s="1"/>
-      <c r="BD338" s="1" t="str">
+      <c r="BD338" s="1"/>
+      <c r="BE338" s="1"/>
+      <c r="BF338" s="1"/>
+      <c r="BG338" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24689,7 +26021,10 @@
       <c r="BA339" s="1"/>
       <c r="BB339" s="1"/>
       <c r="BC339" s="1"/>
-      <c r="BD339" s="1" t="str">
+      <c r="BD339" s="1"/>
+      <c r="BE339" s="1"/>
+      <c r="BF339" s="1"/>
+      <c r="BG339" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24753,7 +26088,10 @@
       <c r="BA340" s="1"/>
       <c r="BB340" s="1"/>
       <c r="BC340" s="1"/>
-      <c r="BD340" s="1" t="str">
+      <c r="BD340" s="1"/>
+      <c r="BE340" s="1"/>
+      <c r="BF340" s="1"/>
+      <c r="BG340" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24817,7 +26155,10 @@
       <c r="BA341" s="1"/>
       <c r="BB341" s="1"/>
       <c r="BC341" s="1"/>
-      <c r="BD341" s="1" t="str">
+      <c r="BD341" s="1"/>
+      <c r="BE341" s="1"/>
+      <c r="BF341" s="1"/>
+      <c r="BG341" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24881,7 +26222,10 @@
       <c r="BA342" s="1"/>
       <c r="BB342" s="1"/>
       <c r="BC342" s="1"/>
-      <c r="BD342" s="1" t="str">
+      <c r="BD342" s="1"/>
+      <c r="BE342" s="1"/>
+      <c r="BF342" s="1"/>
+      <c r="BG342" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24945,7 +26289,10 @@
       <c r="BA343" s="1"/>
       <c r="BB343" s="1"/>
       <c r="BC343" s="1"/>
-      <c r="BD343" s="1" t="str">
+      <c r="BD343" s="1"/>
+      <c r="BE343" s="1"/>
+      <c r="BF343" s="1"/>
+      <c r="BG343" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25009,7 +26356,10 @@
       <c r="BA344" s="1"/>
       <c r="BB344" s="1"/>
       <c r="BC344" s="1"/>
-      <c r="BD344" s="1" t="str">
+      <c r="BD344" s="1"/>
+      <c r="BE344" s="1"/>
+      <c r="BF344" s="1"/>
+      <c r="BG344" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25073,7 +26423,10 @@
       <c r="BA345" s="1"/>
       <c r="BB345" s="1"/>
       <c r="BC345" s="1"/>
-      <c r="BD345" s="1" t="str">
+      <c r="BD345" s="1"/>
+      <c r="BE345" s="1"/>
+      <c r="BF345" s="1"/>
+      <c r="BG345" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25137,7 +26490,10 @@
       <c r="BA346" s="1"/>
       <c r="BB346" s="1"/>
       <c r="BC346" s="1"/>
-      <c r="BD346" s="1" t="str">
+      <c r="BD346" s="1"/>
+      <c r="BE346" s="1"/>
+      <c r="BF346" s="1"/>
+      <c r="BG346" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25201,7 +26557,10 @@
       <c r="BA347" s="1"/>
       <c r="BB347" s="1"/>
       <c r="BC347" s="1"/>
-      <c r="BD347" s="1" t="str">
+      <c r="BD347" s="1"/>
+      <c r="BE347" s="1"/>
+      <c r="BF347" s="1"/>
+      <c r="BG347" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25265,7 +26624,10 @@
       <c r="BA348" s="1"/>
       <c r="BB348" s="1"/>
       <c r="BC348" s="1"/>
-      <c r="BD348" s="1" t="str">
+      <c r="BD348" s="1"/>
+      <c r="BE348" s="1"/>
+      <c r="BF348" s="1"/>
+      <c r="BG348" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25329,7 +26691,10 @@
       <c r="BA349" s="1"/>
       <c r="BB349" s="1"/>
       <c r="BC349" s="1"/>
-      <c r="BD349" s="1" t="str">
+      <c r="BD349" s="1"/>
+      <c r="BE349" s="1"/>
+      <c r="BF349" s="1"/>
+      <c r="BG349" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25393,7 +26758,10 @@
       <c r="BA350" s="1"/>
       <c r="BB350" s="1"/>
       <c r="BC350" s="1"/>
-      <c r="BD350" s="1" t="str">
+      <c r="BD350" s="1"/>
+      <c r="BE350" s="1"/>
+      <c r="BF350" s="1"/>
+      <c r="BG350" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25457,7 +26825,10 @@
       <c r="BA351" s="1"/>
       <c r="BB351" s="1"/>
       <c r="BC351" s="1"/>
-      <c r="BD351" s="1" t="str">
+      <c r="BD351" s="1"/>
+      <c r="BE351" s="1"/>
+      <c r="BF351" s="1"/>
+      <c r="BG351" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25521,7 +26892,10 @@
       <c r="BA352" s="1"/>
       <c r="BB352" s="1"/>
       <c r="BC352" s="1"/>
-      <c r="BD352" s="1" t="str">
+      <c r="BD352" s="1"/>
+      <c r="BE352" s="1"/>
+      <c r="BF352" s="1"/>
+      <c r="BG352" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25585,7 +26959,10 @@
       <c r="BA353" s="1"/>
       <c r="BB353" s="1"/>
       <c r="BC353" s="1"/>
-      <c r="BD353" s="1" t="str">
+      <c r="BD353" s="1"/>
+      <c r="BE353" s="1"/>
+      <c r="BF353" s="1"/>
+      <c r="BG353" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25649,7 +27026,10 @@
       <c r="BA354" s="1"/>
       <c r="BB354" s="1"/>
       <c r="BC354" s="1"/>
-      <c r="BD354" s="1" t="str">
+      <c r="BD354" s="1"/>
+      <c r="BE354" s="1"/>
+      <c r="BF354" s="1"/>
+      <c r="BG354" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25713,7 +27093,10 @@
       <c r="BA355" s="1"/>
       <c r="BB355" s="1"/>
       <c r="BC355" s="1"/>
-      <c r="BD355" s="1" t="str">
+      <c r="BD355" s="1"/>
+      <c r="BE355" s="1"/>
+      <c r="BF355" s="1"/>
+      <c r="BG355" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25777,7 +27160,10 @@
       <c r="BA356" s="1"/>
       <c r="BB356" s="1"/>
       <c r="BC356" s="1"/>
-      <c r="BD356" s="1" t="str">
+      <c r="BD356" s="1"/>
+      <c r="BE356" s="1"/>
+      <c r="BF356" s="1"/>
+      <c r="BG356" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25841,7 +27227,10 @@
       <c r="BA357" s="1"/>
       <c r="BB357" s="1"/>
       <c r="BC357" s="1"/>
-      <c r="BD357" s="1" t="str">
+      <c r="BD357" s="1"/>
+      <c r="BE357" s="1"/>
+      <c r="BF357" s="1"/>
+      <c r="BG357" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25905,7 +27294,10 @@
       <c r="BA358" s="1"/>
       <c r="BB358" s="1"/>
       <c r="BC358" s="1"/>
-      <c r="BD358" s="1" t="str">
+      <c r="BD358" s="1"/>
+      <c r="BE358" s="1"/>
+      <c r="BF358" s="1"/>
+      <c r="BG358" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25969,7 +27361,10 @@
       <c r="BA359" s="1"/>
       <c r="BB359" s="1"/>
       <c r="BC359" s="1"/>
-      <c r="BD359" s="1" t="str">
+      <c r="BD359" s="1"/>
+      <c r="BE359" s="1"/>
+      <c r="BF359" s="1"/>
+      <c r="BG359" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26033,7 +27428,10 @@
       <c r="BA360" s="1"/>
       <c r="BB360" s="1"/>
       <c r="BC360" s="1"/>
-      <c r="BD360" s="1" t="str">
+      <c r="BD360" s="1"/>
+      <c r="BE360" s="1"/>
+      <c r="BF360" s="1"/>
+      <c r="BG360" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26097,7 +27495,10 @@
       <c r="BA361" s="1"/>
       <c r="BB361" s="1"/>
       <c r="BC361" s="1"/>
-      <c r="BD361" s="1" t="str">
+      <c r="BD361" s="1"/>
+      <c r="BE361" s="1"/>
+      <c r="BF361" s="1"/>
+      <c r="BG361" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26161,7 +27562,10 @@
       <c r="BA362" s="1"/>
       <c r="BB362" s="1"/>
       <c r="BC362" s="1"/>
-      <c r="BD362" s="1" t="str">
+      <c r="BD362" s="1"/>
+      <c r="BE362" s="1"/>
+      <c r="BF362" s="1"/>
+      <c r="BG362" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26225,7 +27629,10 @@
       <c r="BA363" s="1"/>
       <c r="BB363" s="1"/>
       <c r="BC363" s="1"/>
-      <c r="BD363" s="1" t="str">
+      <c r="BD363" s="1"/>
+      <c r="BE363" s="1"/>
+      <c r="BF363" s="1"/>
+      <c r="BG363" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26289,7 +27696,10 @@
       <c r="BA364" s="1"/>
       <c r="BB364" s="1"/>
       <c r="BC364" s="1"/>
-      <c r="BD364" s="1" t="str">
+      <c r="BD364" s="1"/>
+      <c r="BE364" s="1"/>
+      <c r="BF364" s="1"/>
+      <c r="BG364" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26353,7 +27763,10 @@
       <c r="BA365" s="1"/>
       <c r="BB365" s="1"/>
       <c r="BC365" s="1"/>
-      <c r="BD365" s="1" t="str">
+      <c r="BD365" s="1"/>
+      <c r="BE365" s="1"/>
+      <c r="BF365" s="1"/>
+      <c r="BG365" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26417,7 +27830,10 @@
       <c r="BA366" s="1"/>
       <c r="BB366" s="1"/>
       <c r="BC366" s="1"/>
-      <c r="BD366" s="1" t="str">
+      <c r="BD366" s="1"/>
+      <c r="BE366" s="1"/>
+      <c r="BF366" s="1"/>
+      <c r="BG366" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26481,7 +27897,10 @@
       <c r="BA367" s="1"/>
       <c r="BB367" s="1"/>
       <c r="BC367" s="1"/>
-      <c r="BD367" s="1" t="str">
+      <c r="BD367" s="1"/>
+      <c r="BE367" s="1"/>
+      <c r="BF367" s="1"/>
+      <c r="BG367" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26545,7 +27964,10 @@
       <c r="BA368" s="1"/>
       <c r="BB368" s="1"/>
       <c r="BC368" s="1"/>
-      <c r="BD368" s="1" t="str">
+      <c r="BD368" s="1"/>
+      <c r="BE368" s="1"/>
+      <c r="BF368" s="1"/>
+      <c r="BG368" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26609,7 +28031,10 @@
       <c r="BA369" s="1"/>
       <c r="BB369" s="1"/>
       <c r="BC369" s="1"/>
-      <c r="BD369" s="1" t="str">
+      <c r="BD369" s="1"/>
+      <c r="BE369" s="1"/>
+      <c r="BF369" s="1"/>
+      <c r="BG369" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26673,7 +28098,10 @@
       <c r="BA370" s="1"/>
       <c r="BB370" s="1"/>
       <c r="BC370" s="1"/>
-      <c r="BD370" s="1" t="str">
+      <c r="BD370" s="1"/>
+      <c r="BE370" s="1"/>
+      <c r="BF370" s="1"/>
+      <c r="BG370" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26737,7 +28165,10 @@
       <c r="BA371" s="1"/>
       <c r="BB371" s="1"/>
       <c r="BC371" s="1"/>
-      <c r="BD371" s="1" t="str">
+      <c r="BD371" s="1"/>
+      <c r="BE371" s="1"/>
+      <c r="BF371" s="1"/>
+      <c r="BG371" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26801,7 +28232,10 @@
       <c r="BA372" s="1"/>
       <c r="BB372" s="1"/>
       <c r="BC372" s="1"/>
-      <c r="BD372" s="1" t="str">
+      <c r="BD372" s="1"/>
+      <c r="BE372" s="1"/>
+      <c r="BF372" s="1"/>
+      <c r="BG372" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26865,7 +28299,10 @@
       <c r="BA373" s="1"/>
       <c r="BB373" s="1"/>
       <c r="BC373" s="1"/>
-      <c r="BD373" s="1" t="str">
+      <c r="BD373" s="1"/>
+      <c r="BE373" s="1"/>
+      <c r="BF373" s="1"/>
+      <c r="BG373" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26929,7 +28366,10 @@
       <c r="BA374" s="1"/>
       <c r="BB374" s="1"/>
       <c r="BC374" s="1"/>
-      <c r="BD374" s="1" t="str">
+      <c r="BD374" s="1"/>
+      <c r="BE374" s="1"/>
+      <c r="BF374" s="1"/>
+      <c r="BG374" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26993,7 +28433,10 @@
       <c r="BA375" s="1"/>
       <c r="BB375" s="1"/>
       <c r="BC375" s="1"/>
-      <c r="BD375" s="1" t="str">
+      <c r="BD375" s="1"/>
+      <c r="BE375" s="1"/>
+      <c r="BF375" s="1"/>
+      <c r="BG375" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27057,7 +28500,10 @@
       <c r="BA376" s="1"/>
       <c r="BB376" s="1"/>
       <c r="BC376" s="1"/>
-      <c r="BD376" s="1" t="str">
+      <c r="BD376" s="1"/>
+      <c r="BE376" s="1"/>
+      <c r="BF376" s="1"/>
+      <c r="BG376" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27121,7 +28567,10 @@
       <c r="BA377" s="1"/>
       <c r="BB377" s="1"/>
       <c r="BC377" s="1"/>
-      <c r="BD377" s="1" t="str">
+      <c r="BD377" s="1"/>
+      <c r="BE377" s="1"/>
+      <c r="BF377" s="1"/>
+      <c r="BG377" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27185,7 +28634,10 @@
       <c r="BA378" s="1"/>
       <c r="BB378" s="1"/>
       <c r="BC378" s="1"/>
-      <c r="BD378" s="1" t="str">
+      <c r="BD378" s="1"/>
+      <c r="BE378" s="1"/>
+      <c r="BF378" s="1"/>
+      <c r="BG378" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27249,7 +28701,10 @@
       <c r="BA379" s="1"/>
       <c r="BB379" s="1"/>
       <c r="BC379" s="1"/>
-      <c r="BD379" s="1" t="str">
+      <c r="BD379" s="1"/>
+      <c r="BE379" s="1"/>
+      <c r="BF379" s="1"/>
+      <c r="BG379" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27313,7 +28768,10 @@
       <c r="BA380" s="1"/>
       <c r="BB380" s="1"/>
       <c r="BC380" s="1"/>
-      <c r="BD380" s="1" t="str">
+      <c r="BD380" s="1"/>
+      <c r="BE380" s="1"/>
+      <c r="BF380" s="1"/>
+      <c r="BG380" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27377,7 +28835,10 @@
       <c r="BA381" s="1"/>
       <c r="BB381" s="1"/>
       <c r="BC381" s="1"/>
-      <c r="BD381" s="1" t="str">
+      <c r="BD381" s="1"/>
+      <c r="BE381" s="1"/>
+      <c r="BF381" s="1"/>
+      <c r="BG381" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27441,7 +28902,10 @@
       <c r="BA382" s="1"/>
       <c r="BB382" s="1"/>
       <c r="BC382" s="1"/>
-      <c r="BD382" s="1" t="str">
+      <c r="BD382" s="1"/>
+      <c r="BE382" s="1"/>
+      <c r="BF382" s="1"/>
+      <c r="BG382" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27505,7 +28969,10 @@
       <c r="BA383" s="1"/>
       <c r="BB383" s="1"/>
       <c r="BC383" s="1"/>
-      <c r="BD383" s="1" t="str">
+      <c r="BD383" s="1"/>
+      <c r="BE383" s="1"/>
+      <c r="BF383" s="1"/>
+      <c r="BG383" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27569,7 +29036,10 @@
       <c r="BA384" s="1"/>
       <c r="BB384" s="1"/>
       <c r="BC384" s="1"/>
-      <c r="BD384" s="1" t="str">
+      <c r="BD384" s="1"/>
+      <c r="BE384" s="1"/>
+      <c r="BF384" s="1"/>
+      <c r="BG384" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27633,7 +29103,10 @@
       <c r="BA385" s="1"/>
       <c r="BB385" s="1"/>
       <c r="BC385" s="1"/>
-      <c r="BD385" s="1" t="str">
+      <c r="BD385" s="1"/>
+      <c r="BE385" s="1"/>
+      <c r="BF385" s="1"/>
+      <c r="BG385" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27697,7 +29170,10 @@
       <c r="BA386" s="1"/>
       <c r="BB386" s="1"/>
       <c r="BC386" s="1"/>
-      <c r="BD386" s="1" t="str">
+      <c r="BD386" s="1"/>
+      <c r="BE386" s="1"/>
+      <c r="BF386" s="1"/>
+      <c r="BG386" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27761,7 +29237,10 @@
       <c r="BA387" s="1"/>
       <c r="BB387" s="1"/>
       <c r="BC387" s="1"/>
-      <c r="BD387" s="1" t="str">
+      <c r="BD387" s="1"/>
+      <c r="BE387" s="1"/>
+      <c r="BF387" s="1"/>
+      <c r="BG387" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27825,7 +29304,10 @@
       <c r="BA388" s="1"/>
       <c r="BB388" s="1"/>
       <c r="BC388" s="1"/>
-      <c r="BD388" s="1" t="str">
+      <c r="BD388" s="1"/>
+      <c r="BE388" s="1"/>
+      <c r="BF388" s="1"/>
+      <c r="BG388" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27889,7 +29371,10 @@
       <c r="BA389" s="1"/>
       <c r="BB389" s="1"/>
       <c r="BC389" s="1"/>
-      <c r="BD389" s="1" t="str">
+      <c r="BD389" s="1"/>
+      <c r="BE389" s="1"/>
+      <c r="BF389" s="1"/>
+      <c r="BG389" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27953,7 +29438,10 @@
       <c r="BA390" s="1"/>
       <c r="BB390" s="1"/>
       <c r="BC390" s="1"/>
-      <c r="BD390" s="1" t="str">
+      <c r="BD390" s="1"/>
+      <c r="BE390" s="1"/>
+      <c r="BF390" s="1"/>
+      <c r="BG390" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28017,7 +29505,10 @@
       <c r="BA391" s="1"/>
       <c r="BB391" s="1"/>
       <c r="BC391" s="1"/>
-      <c r="BD391" s="1" t="str">
+      <c r="BD391" s="1"/>
+      <c r="BE391" s="1"/>
+      <c r="BF391" s="1"/>
+      <c r="BG391" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28081,7 +29572,10 @@
       <c r="BA392" s="1"/>
       <c r="BB392" s="1"/>
       <c r="BC392" s="1"/>
-      <c r="BD392" s="1" t="str">
+      <c r="BD392" s="1"/>
+      <c r="BE392" s="1"/>
+      <c r="BF392" s="1"/>
+      <c r="BG392" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28145,7 +29639,10 @@
       <c r="BA393" s="1"/>
       <c r="BB393" s="1"/>
       <c r="BC393" s="1"/>
-      <c r="BD393" s="1" t="str">
+      <c r="BD393" s="1"/>
+      <c r="BE393" s="1"/>
+      <c r="BF393" s="1"/>
+      <c r="BG393" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28209,7 +29706,10 @@
       <c r="BA394" s="1"/>
       <c r="BB394" s="1"/>
       <c r="BC394" s="1"/>
-      <c r="BD394" s="1" t="str">
+      <c r="BD394" s="1"/>
+      <c r="BE394" s="1"/>
+      <c r="BF394" s="1"/>
+      <c r="BG394" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28273,7 +29773,10 @@
       <c r="BA395" s="1"/>
       <c r="BB395" s="1"/>
       <c r="BC395" s="1"/>
-      <c r="BD395" s="1" t="str">
+      <c r="BD395" s="1"/>
+      <c r="BE395" s="1"/>
+      <c r="BF395" s="1"/>
+      <c r="BG395" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28337,7 +29840,10 @@
       <c r="BA396" s="1"/>
       <c r="BB396" s="1"/>
       <c r="BC396" s="1"/>
-      <c r="BD396" s="1" t="str">
+      <c r="BD396" s="1"/>
+      <c r="BE396" s="1"/>
+      <c r="BF396" s="1"/>
+      <c r="BG396" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28401,7 +29907,10 @@
       <c r="BA397" s="1"/>
       <c r="BB397" s="1"/>
       <c r="BC397" s="1"/>
-      <c r="BD397" s="1" t="str">
+      <c r="BD397" s="1"/>
+      <c r="BE397" s="1"/>
+      <c r="BF397" s="1"/>
+      <c r="BG397" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28465,7 +29974,10 @@
       <c r="BA398" s="1"/>
       <c r="BB398" s="1"/>
       <c r="BC398" s="1"/>
-      <c r="BD398" s="1" t="str">
+      <c r="BD398" s="1"/>
+      <c r="BE398" s="1"/>
+      <c r="BF398" s="1"/>
+      <c r="BG398" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28529,7 +30041,10 @@
       <c r="BA399" s="1"/>
       <c r="BB399" s="1"/>
       <c r="BC399" s="1"/>
-      <c r="BD399" s="1" t="str">
+      <c r="BD399" s="1"/>
+      <c r="BE399" s="1"/>
+      <c r="BF399" s="1"/>
+      <c r="BG399" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28593,7 +30108,10 @@
       <c r="BA400" s="1"/>
       <c r="BB400" s="1"/>
       <c r="BC400" s="1"/>
-      <c r="BD400" s="1" t="str">
+      <c r="BD400" s="1"/>
+      <c r="BE400" s="1"/>
+      <c r="BF400" s="1"/>
+      <c r="BG400" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28657,7 +30175,10 @@
       <c r="BA401" s="1"/>
       <c r="BB401" s="1"/>
       <c r="BC401" s="1"/>
-      <c r="BD401" s="1" t="str">
+      <c r="BD401" s="1"/>
+      <c r="BE401" s="1"/>
+      <c r="BF401" s="1"/>
+      <c r="BG401" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28721,7 +30242,10 @@
       <c r="BA402" s="1"/>
       <c r="BB402" s="1"/>
       <c r="BC402" s="1"/>
-      <c r="BD402" s="1" t="str">
+      <c r="BD402" s="1"/>
+      <c r="BE402" s="1"/>
+      <c r="BF402" s="1"/>
+      <c r="BG402" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28785,7 +30309,10 @@
       <c r="BA403" s="1"/>
       <c r="BB403" s="1"/>
       <c r="BC403" s="1"/>
-      <c r="BD403" s="1" t="str">
+      <c r="BD403" s="1"/>
+      <c r="BE403" s="1"/>
+      <c r="BF403" s="1"/>
+      <c r="BG403" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28849,7 +30376,10 @@
       <c r="BA404" s="1"/>
       <c r="BB404" s="1"/>
       <c r="BC404" s="1"/>
-      <c r="BD404" s="1" t="str">
+      <c r="BD404" s="1"/>
+      <c r="BE404" s="1"/>
+      <c r="BF404" s="1"/>
+      <c r="BG404" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28913,7 +30443,10 @@
       <c r="BA405" s="1"/>
       <c r="BB405" s="1"/>
       <c r="BC405" s="1"/>
-      <c r="BD405" s="1" t="str">
+      <c r="BD405" s="1"/>
+      <c r="BE405" s="1"/>
+      <c r="BF405" s="1"/>
+      <c r="BG405" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28977,7 +30510,10 @@
       <c r="BA406" s="1"/>
       <c r="BB406" s="1"/>
       <c r="BC406" s="1"/>
-      <c r="BD406" s="1" t="str">
+      <c r="BD406" s="1"/>
+      <c r="BE406" s="1"/>
+      <c r="BF406" s="1"/>
+      <c r="BG406" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29041,7 +30577,10 @@
       <c r="BA407" s="1"/>
       <c r="BB407" s="1"/>
       <c r="BC407" s="1"/>
-      <c r="BD407" s="1" t="str">
+      <c r="BD407" s="1"/>
+      <c r="BE407" s="1"/>
+      <c r="BF407" s="1"/>
+      <c r="BG407" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29105,7 +30644,10 @@
       <c r="BA408" s="1"/>
       <c r="BB408" s="1"/>
       <c r="BC408" s="1"/>
-      <c r="BD408" s="1" t="str">
+      <c r="BD408" s="1"/>
+      <c r="BE408" s="1"/>
+      <c r="BF408" s="1"/>
+      <c r="BG408" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29169,7 +30711,10 @@
       <c r="BA409" s="1"/>
       <c r="BB409" s="1"/>
       <c r="BC409" s="1"/>
-      <c r="BD409" s="1" t="str">
+      <c r="BD409" s="1"/>
+      <c r="BE409" s="1"/>
+      <c r="BF409" s="1"/>
+      <c r="BG409" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29233,7 +30778,10 @@
       <c r="BA410" s="1"/>
       <c r="BB410" s="1"/>
       <c r="BC410" s="1"/>
-      <c r="BD410" s="1" t="str">
+      <c r="BD410" s="1"/>
+      <c r="BE410" s="1"/>
+      <c r="BF410" s="1"/>
+      <c r="BG410" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29297,7 +30845,10 @@
       <c r="BA411" s="1"/>
       <c r="BB411" s="1"/>
       <c r="BC411" s="1"/>
-      <c r="BD411" s="1" t="str">
+      <c r="BD411" s="1"/>
+      <c r="BE411" s="1"/>
+      <c r="BF411" s="1"/>
+      <c r="BG411" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29361,7 +30912,10 @@
       <c r="BA412" s="1"/>
       <c r="BB412" s="1"/>
       <c r="BC412" s="1"/>
-      <c r="BD412" s="1" t="str">
+      <c r="BD412" s="1"/>
+      <c r="BE412" s="1"/>
+      <c r="BF412" s="1"/>
+      <c r="BG412" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29425,7 +30979,10 @@
       <c r="BA413" s="1"/>
       <c r="BB413" s="1"/>
       <c r="BC413" s="1"/>
-      <c r="BD413" s="1" t="str">
+      <c r="BD413" s="1"/>
+      <c r="BE413" s="1"/>
+      <c r="BF413" s="1"/>
+      <c r="BG413" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29489,7 +31046,10 @@
       <c r="BA414" s="1"/>
       <c r="BB414" s="1"/>
       <c r="BC414" s="1"/>
-      <c r="BD414" s="1" t="str">
+      <c r="BD414" s="1"/>
+      <c r="BE414" s="1"/>
+      <c r="BF414" s="1"/>
+      <c r="BG414" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29553,7 +31113,10 @@
       <c r="BA415" s="1"/>
       <c r="BB415" s="1"/>
       <c r="BC415" s="1"/>
-      <c r="BD415" s="1" t="str">
+      <c r="BD415" s="1"/>
+      <c r="BE415" s="1"/>
+      <c r="BF415" s="1"/>
+      <c r="BG415" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29617,7 +31180,10 @@
       <c r="BA416" s="1"/>
       <c r="BB416" s="1"/>
       <c r="BC416" s="1"/>
-      <c r="BD416" s="1" t="str">
+      <c r="BD416" s="1"/>
+      <c r="BE416" s="1"/>
+      <c r="BF416" s="1"/>
+      <c r="BG416" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29681,7 +31247,10 @@
       <c r="BA417" s="1"/>
       <c r="BB417" s="1"/>
       <c r="BC417" s="1"/>
-      <c r="BD417" s="1" t="str">
+      <c r="BD417" s="1"/>
+      <c r="BE417" s="1"/>
+      <c r="BF417" s="1"/>
+      <c r="BG417" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29745,7 +31314,10 @@
       <c r="BA418" s="1"/>
       <c r="BB418" s="1"/>
       <c r="BC418" s="1"/>
-      <c r="BD418" s="1" t="str">
+      <c r="BD418" s="1"/>
+      <c r="BE418" s="1"/>
+      <c r="BF418" s="1"/>
+      <c r="BG418" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29809,7 +31381,10 @@
       <c r="BA419" s="1"/>
       <c r="BB419" s="1"/>
       <c r="BC419" s="1"/>
-      <c r="BD419" s="1" t="str">
+      <c r="BD419" s="1"/>
+      <c r="BE419" s="1"/>
+      <c r="BF419" s="1"/>
+      <c r="BG419" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29873,7 +31448,10 @@
       <c r="BA420" s="1"/>
       <c r="BB420" s="1"/>
       <c r="BC420" s="1"/>
-      <c r="BD420" s="1" t="str">
+      <c r="BD420" s="1"/>
+      <c r="BE420" s="1"/>
+      <c r="BF420" s="1"/>
+      <c r="BG420" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29937,7 +31515,10 @@
       <c r="BA421" s="1"/>
       <c r="BB421" s="1"/>
       <c r="BC421" s="1"/>
-      <c r="BD421" s="1" t="str">
+      <c r="BD421" s="1"/>
+      <c r="BE421" s="1"/>
+      <c r="BF421" s="1"/>
+      <c r="BG421" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30001,7 +31582,10 @@
       <c r="BA422" s="1"/>
       <c r="BB422" s="1"/>
       <c r="BC422" s="1"/>
-      <c r="BD422" s="1" t="str">
+      <c r="BD422" s="1"/>
+      <c r="BE422" s="1"/>
+      <c r="BF422" s="1"/>
+      <c r="BG422" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30065,7 +31649,10 @@
       <c r="BA423" s="1"/>
       <c r="BB423" s="1"/>
       <c r="BC423" s="1"/>
-      <c r="BD423" s="1" t="str">
+      <c r="BD423" s="1"/>
+      <c r="BE423" s="1"/>
+      <c r="BF423" s="1"/>
+      <c r="BG423" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30129,7 +31716,10 @@
       <c r="BA424" s="1"/>
       <c r="BB424" s="1"/>
       <c r="BC424" s="1"/>
-      <c r="BD424" s="1" t="str">
+      <c r="BD424" s="1"/>
+      <c r="BE424" s="1"/>
+      <c r="BF424" s="1"/>
+      <c r="BG424" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30193,7 +31783,10 @@
       <c r="BA425" s="1"/>
       <c r="BB425" s="1"/>
       <c r="BC425" s="1"/>
-      <c r="BD425" s="1" t="str">
+      <c r="BD425" s="1"/>
+      <c r="BE425" s="1"/>
+      <c r="BF425" s="1"/>
+      <c r="BG425" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30257,7 +31850,10 @@
       <c r="BA426" s="1"/>
       <c r="BB426" s="1"/>
       <c r="BC426" s="1"/>
-      <c r="BD426" s="1" t="str">
+      <c r="BD426" s="1"/>
+      <c r="BE426" s="1"/>
+      <c r="BF426" s="1"/>
+      <c r="BG426" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30321,7 +31917,10 @@
       <c r="BA427" s="1"/>
       <c r="BB427" s="1"/>
       <c r="BC427" s="1"/>
-      <c r="BD427" s="1" t="str">
+      <c r="BD427" s="1"/>
+      <c r="BE427" s="1"/>
+      <c r="BF427" s="1"/>
+      <c r="BG427" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30385,7 +31984,10 @@
       <c r="BA428" s="1"/>
       <c r="BB428" s="1"/>
       <c r="BC428" s="1"/>
-      <c r="BD428" s="1" t="str">
+      <c r="BD428" s="1"/>
+      <c r="BE428" s="1"/>
+      <c r="BF428" s="1"/>
+      <c r="BG428" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30449,7 +32051,10 @@
       <c r="BA429" s="1"/>
       <c r="BB429" s="1"/>
       <c r="BC429" s="1"/>
-      <c r="BD429" s="1" t="str">
+      <c r="BD429" s="1"/>
+      <c r="BE429" s="1"/>
+      <c r="BF429" s="1"/>
+      <c r="BG429" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30513,7 +32118,10 @@
       <c r="BA430" s="1"/>
       <c r="BB430" s="1"/>
       <c r="BC430" s="1"/>
-      <c r="BD430" s="1" t="str">
+      <c r="BD430" s="1"/>
+      <c r="BE430" s="1"/>
+      <c r="BF430" s="1"/>
+      <c r="BG430" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30577,7 +32185,10 @@
       <c r="BA431" s="1"/>
       <c r="BB431" s="1"/>
       <c r="BC431" s="1"/>
-      <c r="BD431" s="1" t="str">
+      <c r="BD431" s="1"/>
+      <c r="BE431" s="1"/>
+      <c r="BF431" s="1"/>
+      <c r="BG431" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30641,7 +32252,10 @@
       <c r="BA432" s="1"/>
       <c r="BB432" s="1"/>
       <c r="BC432" s="1"/>
-      <c r="BD432" s="1" t="str">
+      <c r="BD432" s="1"/>
+      <c r="BE432" s="1"/>
+      <c r="BF432" s="1"/>
+      <c r="BG432" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30705,7 +32319,10 @@
       <c r="BA433" s="1"/>
       <c r="BB433" s="1"/>
       <c r="BC433" s="1"/>
-      <c r="BD433" s="1" t="str">
+      <c r="BD433" s="1"/>
+      <c r="BE433" s="1"/>
+      <c r="BF433" s="1"/>
+      <c r="BG433" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30769,7 +32386,10 @@
       <c r="BA434" s="1"/>
       <c r="BB434" s="1"/>
       <c r="BC434" s="1"/>
-      <c r="BD434" s="1" t="str">
+      <c r="BD434" s="1"/>
+      <c r="BE434" s="1"/>
+      <c r="BF434" s="1"/>
+      <c r="BG434" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30833,7 +32453,10 @@
       <c r="BA435" s="1"/>
       <c r="BB435" s="1"/>
       <c r="BC435" s="1"/>
-      <c r="BD435" s="1" t="str">
+      <c r="BD435" s="1"/>
+      <c r="BE435" s="1"/>
+      <c r="BF435" s="1"/>
+      <c r="BG435" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30897,7 +32520,10 @@
       <c r="BA436" s="1"/>
       <c r="BB436" s="1"/>
       <c r="BC436" s="1"/>
-      <c r="BD436" s="1" t="str">
+      <c r="BD436" s="1"/>
+      <c r="BE436" s="1"/>
+      <c r="BF436" s="1"/>
+      <c r="BG436" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30961,7 +32587,10 @@
       <c r="BA437" s="1"/>
       <c r="BB437" s="1"/>
       <c r="BC437" s="1"/>
-      <c r="BD437" s="1" t="str">
+      <c r="BD437" s="1"/>
+      <c r="BE437" s="1"/>
+      <c r="BF437" s="1"/>
+      <c r="BG437" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31025,7 +32654,10 @@
       <c r="BA438" s="1"/>
       <c r="BB438" s="1"/>
       <c r="BC438" s="1"/>
-      <c r="BD438" s="1" t="str">
+      <c r="BD438" s="1"/>
+      <c r="BE438" s="1"/>
+      <c r="BF438" s="1"/>
+      <c r="BG438" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31089,7 +32721,10 @@
       <c r="BA439" s="1"/>
       <c r="BB439" s="1"/>
       <c r="BC439" s="1"/>
-      <c r="BD439" s="1" t="str">
+      <c r="BD439" s="1"/>
+      <c r="BE439" s="1"/>
+      <c r="BF439" s="1"/>
+      <c r="BG439" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31153,7 +32788,10 @@
       <c r="BA440" s="1"/>
       <c r="BB440" s="1"/>
       <c r="BC440" s="1"/>
-      <c r="BD440" s="1" t="str">
+      <c r="BD440" s="1"/>
+      <c r="BE440" s="1"/>
+      <c r="BF440" s="1"/>
+      <c r="BG440" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31217,7 +32855,10 @@
       <c r="BA441" s="1"/>
       <c r="BB441" s="1"/>
       <c r="BC441" s="1"/>
-      <c r="BD441" s="1" t="str">
+      <c r="BD441" s="1"/>
+      <c r="BE441" s="1"/>
+      <c r="BF441" s="1"/>
+      <c r="BG441" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31281,7 +32922,10 @@
       <c r="BA442" s="1"/>
       <c r="BB442" s="1"/>
       <c r="BC442" s="1"/>
-      <c r="BD442" s="1" t="str">
+      <c r="BD442" s="1"/>
+      <c r="BE442" s="1"/>
+      <c r="BF442" s="1"/>
+      <c r="BG442" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31345,7 +32989,10 @@
       <c r="BA443" s="1"/>
       <c r="BB443" s="1"/>
       <c r="BC443" s="1"/>
-      <c r="BD443" s="1" t="str">
+      <c r="BD443" s="1"/>
+      <c r="BE443" s="1"/>
+      <c r="BF443" s="1"/>
+      <c r="BG443" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31409,7 +33056,10 @@
       <c r="BA444" s="1"/>
       <c r="BB444" s="1"/>
       <c r="BC444" s="1"/>
-      <c r="BD444" s="1" t="str">
+      <c r="BD444" s="1"/>
+      <c r="BE444" s="1"/>
+      <c r="BF444" s="1"/>
+      <c r="BG444" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31473,7 +33123,10 @@
       <c r="BA445" s="1"/>
       <c r="BB445" s="1"/>
       <c r="BC445" s="1"/>
-      <c r="BD445" s="1" t="str">
+      <c r="BD445" s="1"/>
+      <c r="BE445" s="1"/>
+      <c r="BF445" s="1"/>
+      <c r="BG445" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31537,7 +33190,10 @@
       <c r="BA446" s="1"/>
       <c r="BB446" s="1"/>
       <c r="BC446" s="1"/>
-      <c r="BD446" s="1" t="str">
+      <c r="BD446" s="1"/>
+      <c r="BE446" s="1"/>
+      <c r="BF446" s="1"/>
+      <c r="BG446" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31601,7 +33257,10 @@
       <c r="BA447" s="1"/>
       <c r="BB447" s="1"/>
       <c r="BC447" s="1"/>
-      <c r="BD447" s="1" t="str">
+      <c r="BD447" s="1"/>
+      <c r="BE447" s="1"/>
+      <c r="BF447" s="1"/>
+      <c r="BG447" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31665,7 +33324,10 @@
       <c r="BA448" s="1"/>
       <c r="BB448" s="1"/>
       <c r="BC448" s="1"/>
-      <c r="BD448" s="1" t="str">
+      <c r="BD448" s="1"/>
+      <c r="BE448" s="1"/>
+      <c r="BF448" s="1"/>
+      <c r="BG448" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31729,7 +33391,10 @@
       <c r="BA449" s="1"/>
       <c r="BB449" s="1"/>
       <c r="BC449" s="1"/>
-      <c r="BD449" s="1" t="str">
+      <c r="BD449" s="1"/>
+      <c r="BE449" s="1"/>
+      <c r="BF449" s="1"/>
+      <c r="BG449" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31793,7 +33458,10 @@
       <c r="BA450" s="1"/>
       <c r="BB450" s="1"/>
       <c r="BC450" s="1"/>
-      <c r="BD450" s="1" t="str">
+      <c r="BD450" s="1"/>
+      <c r="BE450" s="1"/>
+      <c r="BF450" s="1"/>
+      <c r="BG450" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31857,7 +33525,10 @@
       <c r="BA451" s="1"/>
       <c r="BB451" s="1"/>
       <c r="BC451" s="1"/>
-      <c r="BD451" s="1" t="str">
+      <c r="BD451" s="1"/>
+      <c r="BE451" s="1"/>
+      <c r="BF451" s="1"/>
+      <c r="BG451" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31921,7 +33592,10 @@
       <c r="BA452" s="1"/>
       <c r="BB452" s="1"/>
       <c r="BC452" s="1"/>
-      <c r="BD452" s="1" t="str">
+      <c r="BD452" s="1"/>
+      <c r="BE452" s="1"/>
+      <c r="BF452" s="1"/>
+      <c r="BG452" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31985,7 +33659,10 @@
       <c r="BA453" s="1"/>
       <c r="BB453" s="1"/>
       <c r="BC453" s="1"/>
-      <c r="BD453" s="1" t="str">
+      <c r="BD453" s="1"/>
+      <c r="BE453" s="1"/>
+      <c r="BF453" s="1"/>
+      <c r="BG453" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32049,7 +33726,10 @@
       <c r="BA454" s="1"/>
       <c r="BB454" s="1"/>
       <c r="BC454" s="1"/>
-      <c r="BD454" s="1" t="str">
+      <c r="BD454" s="1"/>
+      <c r="BE454" s="1"/>
+      <c r="BF454" s="1"/>
+      <c r="BG454" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32113,7 +33793,10 @@
       <c r="BA455" s="1"/>
       <c r="BB455" s="1"/>
       <c r="BC455" s="1"/>
-      <c r="BD455" s="1" t="str">
+      <c r="BD455" s="1"/>
+      <c r="BE455" s="1"/>
+      <c r="BF455" s="1"/>
+      <c r="BG455" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32177,7 +33860,10 @@
       <c r="BA456" s="1"/>
       <c r="BB456" s="1"/>
       <c r="BC456" s="1"/>
-      <c r="BD456" s="1" t="str">
+      <c r="BD456" s="1"/>
+      <c r="BE456" s="1"/>
+      <c r="BF456" s="1"/>
+      <c r="BG456" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32241,7 +33927,10 @@
       <c r="BA457" s="1"/>
       <c r="BB457" s="1"/>
       <c r="BC457" s="1"/>
-      <c r="BD457" s="1" t="str">
+      <c r="BD457" s="1"/>
+      <c r="BE457" s="1"/>
+      <c r="BF457" s="1"/>
+      <c r="BG457" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32305,7 +33994,10 @@
       <c r="BA458" s="1"/>
       <c r="BB458" s="1"/>
       <c r="BC458" s="1"/>
-      <c r="BD458" s="1" t="str">
+      <c r="BD458" s="1"/>
+      <c r="BE458" s="1"/>
+      <c r="BF458" s="1"/>
+      <c r="BG458" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32369,7 +34061,10 @@
       <c r="BA459" s="1"/>
       <c r="BB459" s="1"/>
       <c r="BC459" s="1"/>
-      <c r="BD459" s="1" t="str">
+      <c r="BD459" s="1"/>
+      <c r="BE459" s="1"/>
+      <c r="BF459" s="1"/>
+      <c r="BG459" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32433,7 +34128,10 @@
       <c r="BA460" s="1"/>
       <c r="BB460" s="1"/>
       <c r="BC460" s="1"/>
-      <c r="BD460" s="1" t="str">
+      <c r="BD460" s="1"/>
+      <c r="BE460" s="1"/>
+      <c r="BF460" s="1"/>
+      <c r="BG460" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32497,7 +34195,10 @@
       <c r="BA461" s="1"/>
       <c r="BB461" s="1"/>
       <c r="BC461" s="1"/>
-      <c r="BD461" s="1" t="str">
+      <c r="BD461" s="1"/>
+      <c r="BE461" s="1"/>
+      <c r="BF461" s="1"/>
+      <c r="BG461" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32561,7 +34262,10 @@
       <c r="BA462" s="1"/>
       <c r="BB462" s="1"/>
       <c r="BC462" s="1"/>
-      <c r="BD462" s="1" t="str">
+      <c r="BD462" s="1"/>
+      <c r="BE462" s="1"/>
+      <c r="BF462" s="1"/>
+      <c r="BG462" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32625,7 +34329,10 @@
       <c r="BA463" s="1"/>
       <c r="BB463" s="1"/>
       <c r="BC463" s="1"/>
-      <c r="BD463" s="1" t="str">
+      <c r="BD463" s="1"/>
+      <c r="BE463" s="1"/>
+      <c r="BF463" s="1"/>
+      <c r="BG463" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32689,7 +34396,10 @@
       <c r="BA464" s="1"/>
       <c r="BB464" s="1"/>
       <c r="BC464" s="1"/>
-      <c r="BD464" s="1" t="str">
+      <c r="BD464" s="1"/>
+      <c r="BE464" s="1"/>
+      <c r="BF464" s="1"/>
+      <c r="BG464" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32753,7 +34463,10 @@
       <c r="BA465" s="1"/>
       <c r="BB465" s="1"/>
       <c r="BC465" s="1"/>
-      <c r="BD465" s="1" t="str">
+      <c r="BD465" s="1"/>
+      <c r="BE465" s="1"/>
+      <c r="BF465" s="1"/>
+      <c r="BG465" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32817,7 +34530,10 @@
       <c r="BA466" s="1"/>
       <c r="BB466" s="1"/>
       <c r="BC466" s="1"/>
-      <c r="BD466" s="1" t="str">
+      <c r="BD466" s="1"/>
+      <c r="BE466" s="1"/>
+      <c r="BF466" s="1"/>
+      <c r="BG466" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32881,7 +34597,10 @@
       <c r="BA467" s="1"/>
       <c r="BB467" s="1"/>
       <c r="BC467" s="1"/>
-      <c r="BD467" s="1" t="str">
+      <c r="BD467" s="1"/>
+      <c r="BE467" s="1"/>
+      <c r="BF467" s="1"/>
+      <c r="BG467" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32945,7 +34664,10 @@
       <c r="BA468" s="1"/>
       <c r="BB468" s="1"/>
       <c r="BC468" s="1"/>
-      <c r="BD468" s="1" t="str">
+      <c r="BD468" s="1"/>
+      <c r="BE468" s="1"/>
+      <c r="BF468" s="1"/>
+      <c r="BG468" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33009,7 +34731,10 @@
       <c r="BA469" s="1"/>
       <c r="BB469" s="1"/>
       <c r="BC469" s="1"/>
-      <c r="BD469" s="1" t="str">
+      <c r="BD469" s="1"/>
+      <c r="BE469" s="1"/>
+      <c r="BF469" s="1"/>
+      <c r="BG469" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33073,7 +34798,10 @@
       <c r="BA470" s="1"/>
       <c r="BB470" s="1"/>
       <c r="BC470" s="1"/>
-      <c r="BD470" s="1" t="str">
+      <c r="BD470" s="1"/>
+      <c r="BE470" s="1"/>
+      <c r="BF470" s="1"/>
+      <c r="BG470" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33137,7 +34865,10 @@
       <c r="BA471" s="1"/>
       <c r="BB471" s="1"/>
       <c r="BC471" s="1"/>
-      <c r="BD471" s="1" t="str">
+      <c r="BD471" s="1"/>
+      <c r="BE471" s="1"/>
+      <c r="BF471" s="1"/>
+      <c r="BG471" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33201,7 +34932,10 @@
       <c r="BA472" s="1"/>
       <c r="BB472" s="1"/>
       <c r="BC472" s="1"/>
-      <c r="BD472" s="1" t="str">
+      <c r="BD472" s="1"/>
+      <c r="BE472" s="1"/>
+      <c r="BF472" s="1"/>
+      <c r="BG472" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33265,7 +34999,10 @@
       <c r="BA473" s="1"/>
       <c r="BB473" s="1"/>
       <c r="BC473" s="1"/>
-      <c r="BD473" s="1" t="str">
+      <c r="BD473" s="1"/>
+      <c r="BE473" s="1"/>
+      <c r="BF473" s="1"/>
+      <c r="BG473" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33329,7 +35066,10 @@
       <c r="BA474" s="1"/>
       <c r="BB474" s="1"/>
       <c r="BC474" s="1"/>
-      <c r="BD474" s="1" t="str">
+      <c r="BD474" s="1"/>
+      <c r="BE474" s="1"/>
+      <c r="BF474" s="1"/>
+      <c r="BG474" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33393,7 +35133,10 @@
       <c r="BA475" s="1"/>
       <c r="BB475" s="1"/>
       <c r="BC475" s="1"/>
-      <c r="BD475" s="1" t="str">
+      <c r="BD475" s="1"/>
+      <c r="BE475" s="1"/>
+      <c r="BF475" s="1"/>
+      <c r="BG475" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33457,7 +35200,10 @@
       <c r="BA476" s="1"/>
       <c r="BB476" s="1"/>
       <c r="BC476" s="1"/>
-      <c r="BD476" s="1" t="str">
+      <c r="BD476" s="1"/>
+      <c r="BE476" s="1"/>
+      <c r="BF476" s="1"/>
+      <c r="BG476" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33521,7 +35267,10 @@
       <c r="BA477" s="1"/>
       <c r="BB477" s="1"/>
       <c r="BC477" s="1"/>
-      <c r="BD477" s="1" t="str">
+      <c r="BD477" s="1"/>
+      <c r="BE477" s="1"/>
+      <c r="BF477" s="1"/>
+      <c r="BG477" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33585,7 +35334,10 @@
       <c r="BA478" s="1"/>
       <c r="BB478" s="1"/>
       <c r="BC478" s="1"/>
-      <c r="BD478" s="1" t="str">
+      <c r="BD478" s="1"/>
+      <c r="BE478" s="1"/>
+      <c r="BF478" s="1"/>
+      <c r="BG478" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33649,7 +35401,10 @@
       <c r="BA479" s="1"/>
       <c r="BB479" s="1"/>
       <c r="BC479" s="1"/>
-      <c r="BD479" s="1" t="str">
+      <c r="BD479" s="1"/>
+      <c r="BE479" s="1"/>
+      <c r="BF479" s="1"/>
+      <c r="BG479" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33713,7 +35468,10 @@
       <c r="BA480" s="1"/>
       <c r="BB480" s="1"/>
       <c r="BC480" s="1"/>
-      <c r="BD480" s="1" t="str">
+      <c r="BD480" s="1"/>
+      <c r="BE480" s="1"/>
+      <c r="BF480" s="1"/>
+      <c r="BG480" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33777,7 +35535,10 @@
       <c r="BA481" s="1"/>
       <c r="BB481" s="1"/>
       <c r="BC481" s="1"/>
-      <c r="BD481" s="1" t="str">
+      <c r="BD481" s="1"/>
+      <c r="BE481" s="1"/>
+      <c r="BF481" s="1"/>
+      <c r="BG481" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33841,7 +35602,10 @@
       <c r="BA482" s="1"/>
       <c r="BB482" s="1"/>
       <c r="BC482" s="1"/>
-      <c r="BD482" s="1" t="str">
+      <c r="BD482" s="1"/>
+      <c r="BE482" s="1"/>
+      <c r="BF482" s="1"/>
+      <c r="BG482" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33905,7 +35669,10 @@
       <c r="BA483" s="1"/>
       <c r="BB483" s="1"/>
       <c r="BC483" s="1"/>
-      <c r="BD483" s="1" t="str">
+      <c r="BD483" s="1"/>
+      <c r="BE483" s="1"/>
+      <c r="BF483" s="1"/>
+      <c r="BG483" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33969,7 +35736,10 @@
       <c r="BA484" s="1"/>
       <c r="BB484" s="1"/>
       <c r="BC484" s="1"/>
-      <c r="BD484" s="1" t="str">
+      <c r="BD484" s="1"/>
+      <c r="BE484" s="1"/>
+      <c r="BF484" s="1"/>
+      <c r="BG484" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34033,7 +35803,10 @@
       <c r="BA485" s="1"/>
       <c r="BB485" s="1"/>
       <c r="BC485" s="1"/>
-      <c r="BD485" s="1" t="str">
+      <c r="BD485" s="1"/>
+      <c r="BE485" s="1"/>
+      <c r="BF485" s="1"/>
+      <c r="BG485" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34097,7 +35870,10 @@
       <c r="BA486" s="1"/>
       <c r="BB486" s="1"/>
       <c r="BC486" s="1"/>
-      <c r="BD486" s="1" t="str">
+      <c r="BD486" s="1"/>
+      <c r="BE486" s="1"/>
+      <c r="BF486" s="1"/>
+      <c r="BG486" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34161,7 +35937,10 @@
       <c r="BA487" s="1"/>
       <c r="BB487" s="1"/>
       <c r="BC487" s="1"/>
-      <c r="BD487" s="1" t="str">
+      <c r="BD487" s="1"/>
+      <c r="BE487" s="1"/>
+      <c r="BF487" s="1"/>
+      <c r="BG487" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34225,7 +36004,10 @@
       <c r="BA488" s="1"/>
       <c r="BB488" s="1"/>
       <c r="BC488" s="1"/>
-      <c r="BD488" s="1" t="str">
+      <c r="BD488" s="1"/>
+      <c r="BE488" s="1"/>
+      <c r="BF488" s="1"/>
+      <c r="BG488" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34289,7 +36071,10 @@
       <c r="BA489" s="1"/>
       <c r="BB489" s="1"/>
       <c r="BC489" s="1"/>
-      <c r="BD489" s="1" t="str">
+      <c r="BD489" s="1"/>
+      <c r="BE489" s="1"/>
+      <c r="BF489" s="1"/>
+      <c r="BG489" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34353,7 +36138,10 @@
       <c r="BA490" s="1"/>
       <c r="BB490" s="1"/>
       <c r="BC490" s="1"/>
-      <c r="BD490" s="1" t="str">
+      <c r="BD490" s="1"/>
+      <c r="BE490" s="1"/>
+      <c r="BF490" s="1"/>
+      <c r="BG490" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34417,7 +36205,10 @@
       <c r="BA491" s="1"/>
       <c r="BB491" s="1"/>
       <c r="BC491" s="1"/>
-      <c r="BD491" s="1" t="str">
+      <c r="BD491" s="1"/>
+      <c r="BE491" s="1"/>
+      <c r="BF491" s="1"/>
+      <c r="BG491" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34481,7 +36272,10 @@
       <c r="BA492" s="1"/>
       <c r="BB492" s="1"/>
       <c r="BC492" s="1"/>
-      <c r="BD492" s="1" t="str">
+      <c r="BD492" s="1"/>
+      <c r="BE492" s="1"/>
+      <c r="BF492" s="1"/>
+      <c r="BG492" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34545,7 +36339,10 @@
       <c r="BA493" s="1"/>
       <c r="BB493" s="1"/>
       <c r="BC493" s="1"/>
-      <c r="BD493" s="1" t="str">
+      <c r="BD493" s="1"/>
+      <c r="BE493" s="1"/>
+      <c r="BF493" s="1"/>
+      <c r="BG493" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34609,7 +36406,10 @@
       <c r="BA494" s="1"/>
       <c r="BB494" s="1"/>
       <c r="BC494" s="1"/>
-      <c r="BD494" s="1" t="str">
+      <c r="BD494" s="1"/>
+      <c r="BE494" s="1"/>
+      <c r="BF494" s="1"/>
+      <c r="BG494" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34673,7 +36473,10 @@
       <c r="BA495" s="1"/>
       <c r="BB495" s="1"/>
       <c r="BC495" s="1"/>
-      <c r="BD495" s="1" t="str">
+      <c r="BD495" s="1"/>
+      <c r="BE495" s="1"/>
+      <c r="BF495" s="1"/>
+      <c r="BG495" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34737,7 +36540,10 @@
       <c r="BA496" s="1"/>
       <c r="BB496" s="1"/>
       <c r="BC496" s="1"/>
-      <c r="BD496" s="1" t="str">
+      <c r="BD496" s="1"/>
+      <c r="BE496" s="1"/>
+      <c r="BF496" s="1"/>
+      <c r="BG496" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34801,7 +36607,10 @@
       <c r="BA497" s="1"/>
       <c r="BB497" s="1"/>
       <c r="BC497" s="1"/>
-      <c r="BD497" s="1" t="str">
+      <c r="BD497" s="1"/>
+      <c r="BE497" s="1"/>
+      <c r="BF497" s="1"/>
+      <c r="BG497" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34865,7 +36674,10 @@
       <c r="BA498" s="1"/>
       <c r="BB498" s="1"/>
       <c r="BC498" s="1"/>
-      <c r="BD498" s="1" t="str">
+      <c r="BD498" s="1"/>
+      <c r="BE498" s="1"/>
+      <c r="BF498" s="1"/>
+      <c r="BG498" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34929,7 +36741,10 @@
       <c r="BA499" s="1"/>
       <c r="BB499" s="1"/>
       <c r="BC499" s="1"/>
-      <c r="BD499" s="1" t="str">
+      <c r="BD499" s="1"/>
+      <c r="BE499" s="1"/>
+      <c r="BF499" s="1"/>
+      <c r="BG499" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34993,7 +36808,10 @@
       <c r="BA500" s="1"/>
       <c r="BB500" s="1"/>
       <c r="BC500" s="1"/>
-      <c r="BD500" s="1" t="str">
+      <c r="BD500" s="1"/>
+      <c r="BE500" s="1"/>
+      <c r="BF500" s="1"/>
+      <c r="BG500" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35057,7 +36875,10 @@
       <c r="BA501" s="1"/>
       <c r="BB501" s="1"/>
       <c r="BC501" s="1"/>
-      <c r="BD501" s="1" t="str">
+      <c r="BD501" s="1"/>
+      <c r="BE501" s="1"/>
+      <c r="BF501" s="1"/>
+      <c r="BG501" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35121,7 +36942,10 @@
       <c r="BA502" s="1"/>
       <c r="BB502" s="1"/>
       <c r="BC502" s="1"/>
-      <c r="BD502" s="1" t="str">
+      <c r="BD502" s="1"/>
+      <c r="BE502" s="1"/>
+      <c r="BF502" s="1"/>
+      <c r="BG502" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35185,7 +37009,10 @@
       <c r="BA503" s="1"/>
       <c r="BB503" s="1"/>
       <c r="BC503" s="1"/>
-      <c r="BD503" s="1" t="str">
+      <c r="BD503" s="1"/>
+      <c r="BE503" s="1"/>
+      <c r="BF503" s="1"/>
+      <c r="BG503" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35249,7 +37076,10 @@
       <c r="BA504" s="1"/>
       <c r="BB504" s="1"/>
       <c r="BC504" s="1"/>
-      <c r="BD504" s="1" t="str">
+      <c r="BD504" s="1"/>
+      <c r="BE504" s="1"/>
+      <c r="BF504" s="1"/>
+      <c r="BG504" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35313,7 +37143,10 @@
       <c r="BA505" s="1"/>
       <c r="BB505" s="1"/>
       <c r="BC505" s="1"/>
-      <c r="BD505" s="1" t="str">
+      <c r="BD505" s="1"/>
+      <c r="BE505" s="1"/>
+      <c r="BF505" s="1"/>
+      <c r="BG505" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35377,7 +37210,10 @@
       <c r="BA506" s="1"/>
       <c r="BB506" s="1"/>
       <c r="BC506" s="1"/>
-      <c r="BD506" s="1" t="str">
+      <c r="BD506" s="1"/>
+      <c r="BE506" s="1"/>
+      <c r="BF506" s="1"/>
+      <c r="BG506" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35441,7 +37277,10 @@
       <c r="BA507" s="1"/>
       <c r="BB507" s="1"/>
       <c r="BC507" s="1"/>
-      <c r="BD507" s="1" t="str">
+      <c r="BD507" s="1"/>
+      <c r="BE507" s="1"/>
+      <c r="BF507" s="1"/>
+      <c r="BG507" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35505,7 +37344,10 @@
       <c r="BA508" s="1"/>
       <c r="BB508" s="1"/>
       <c r="BC508" s="1"/>
-      <c r="BD508" s="1" t="str">
+      <c r="BD508" s="1"/>
+      <c r="BE508" s="1"/>
+      <c r="BF508" s="1"/>
+      <c r="BG508" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35569,7 +37411,10 @@
       <c r="BA509" s="1"/>
       <c r="BB509" s="1"/>
       <c r="BC509" s="1"/>
-      <c r="BD509" s="1" t="str">
+      <c r="BD509" s="1"/>
+      <c r="BE509" s="1"/>
+      <c r="BF509" s="1"/>
+      <c r="BG509" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35633,7 +37478,10 @@
       <c r="BA510" s="1"/>
       <c r="BB510" s="1"/>
       <c r="BC510" s="1"/>
-      <c r="BD510" s="1" t="str">
+      <c r="BD510" s="1"/>
+      <c r="BE510" s="1"/>
+      <c r="BF510" s="1"/>
+      <c r="BG510" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35697,7 +37545,10 @@
       <c r="BA511" s="1"/>
       <c r="BB511" s="1"/>
       <c r="BC511" s="1"/>
-      <c r="BD511" s="1" t="str">
+      <c r="BD511" s="1"/>
+      <c r="BE511" s="1"/>
+      <c r="BF511" s="1"/>
+      <c r="BG511" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35761,7 +37612,10 @@
       <c r="BA512" s="1"/>
       <c r="BB512" s="1"/>
       <c r="BC512" s="1"/>
-      <c r="BD512" s="1" t="str">
+      <c r="BD512" s="1"/>
+      <c r="BE512" s="1"/>
+      <c r="BF512" s="1"/>
+      <c r="BG512" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35825,7 +37679,10 @@
       <c r="BA513" s="1"/>
       <c r="BB513" s="1"/>
       <c r="BC513" s="1"/>
-      <c r="BD513" s="1" t="str">
+      <c r="BD513" s="1"/>
+      <c r="BE513" s="1"/>
+      <c r="BF513" s="1"/>
+      <c r="BG513" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35889,7 +37746,10 @@
       <c r="BA514" s="1"/>
       <c r="BB514" s="1"/>
       <c r="BC514" s="1"/>
-      <c r="BD514" s="1" t="str">
+      <c r="BD514" s="1"/>
+      <c r="BE514" s="1"/>
+      <c r="BF514" s="1"/>
+      <c r="BG514" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35953,7 +37813,10 @@
       <c r="BA515" s="1"/>
       <c r="BB515" s="1"/>
       <c r="BC515" s="1"/>
-      <c r="BD515" s="1" t="str">
+      <c r="BD515" s="1"/>
+      <c r="BE515" s="1"/>
+      <c r="BF515" s="1"/>
+      <c r="BG515" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36017,7 +37880,10 @@
       <c r="BA516" s="1"/>
       <c r="BB516" s="1"/>
       <c r="BC516" s="1"/>
-      <c r="BD516" s="1" t="str">
+      <c r="BD516" s="1"/>
+      <c r="BE516" s="1"/>
+      <c r="BF516" s="1"/>
+      <c r="BG516" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36081,7 +37947,10 @@
       <c r="BA517" s="1"/>
       <c r="BB517" s="1"/>
       <c r="BC517" s="1"/>
-      <c r="BD517" s="1" t="str">
+      <c r="BD517" s="1"/>
+      <c r="BE517" s="1"/>
+      <c r="BF517" s="1"/>
+      <c r="BG517" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36145,7 +38014,10 @@
       <c r="BA518" s="1"/>
       <c r="BB518" s="1"/>
       <c r="BC518" s="1"/>
-      <c r="BD518" s="1" t="str">
+      <c r="BD518" s="1"/>
+      <c r="BE518" s="1"/>
+      <c r="BF518" s="1"/>
+      <c r="BG518" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36209,7 +38081,10 @@
       <c r="BA519" s="1"/>
       <c r="BB519" s="1"/>
       <c r="BC519" s="1"/>
-      <c r="BD519" s="1" t="str">
+      <c r="BD519" s="1"/>
+      <c r="BE519" s="1"/>
+      <c r="BF519" s="1"/>
+      <c r="BG519" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36273,7 +38148,10 @@
       <c r="BA520" s="1"/>
       <c r="BB520" s="1"/>
       <c r="BC520" s="1"/>
-      <c r="BD520" s="1" t="str">
+      <c r="BD520" s="1"/>
+      <c r="BE520" s="1"/>
+      <c r="BF520" s="1"/>
+      <c r="BG520" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36337,7 +38215,10 @@
       <c r="BA521" s="1"/>
       <c r="BB521" s="1"/>
       <c r="BC521" s="1"/>
-      <c r="BD521" s="1" t="str">
+      <c r="BD521" s="1"/>
+      <c r="BE521" s="1"/>
+      <c r="BF521" s="1"/>
+      <c r="BG521" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36401,7 +38282,10 @@
       <c r="BA522" s="1"/>
       <c r="BB522" s="1"/>
       <c r="BC522" s="1"/>
-      <c r="BD522" s="1" t="str">
+      <c r="BD522" s="1"/>
+      <c r="BE522" s="1"/>
+      <c r="BF522" s="1"/>
+      <c r="BG522" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36465,7 +38349,10 @@
       <c r="BA523" s="1"/>
       <c r="BB523" s="1"/>
       <c r="BC523" s="1"/>
-      <c r="BD523" s="1" t="str">
+      <c r="BD523" s="1"/>
+      <c r="BE523" s="1"/>
+      <c r="BF523" s="1"/>
+      <c r="BG523" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36529,7 +38416,10 @@
       <c r="BA524" s="1"/>
       <c r="BB524" s="1"/>
       <c r="BC524" s="1"/>
-      <c r="BD524" s="1" t="str">
+      <c r="BD524" s="1"/>
+      <c r="BE524" s="1"/>
+      <c r="BF524" s="1"/>
+      <c r="BG524" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36593,7 +38483,10 @@
       <c r="BA525" s="1"/>
       <c r="BB525" s="1"/>
       <c r="BC525" s="1"/>
-      <c r="BD525" s="1" t="str">
+      <c r="BD525" s="1"/>
+      <c r="BE525" s="1"/>
+      <c r="BF525" s="1"/>
+      <c r="BG525" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36657,7 +38550,10 @@
       <c r="BA526" s="1"/>
       <c r="BB526" s="1"/>
       <c r="BC526" s="1"/>
-      <c r="BD526" s="1" t="str">
+      <c r="BD526" s="1"/>
+      <c r="BE526" s="1"/>
+      <c r="BF526" s="1"/>
+      <c r="BG526" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36721,7 +38617,10 @@
       <c r="BA527" s="1"/>
       <c r="BB527" s="1"/>
       <c r="BC527" s="1"/>
-      <c r="BD527" s="1" t="str">
+      <c r="BD527" s="1"/>
+      <c r="BE527" s="1"/>
+      <c r="BF527" s="1"/>
+      <c r="BG527" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36785,7 +38684,10 @@
       <c r="BA528" s="1"/>
       <c r="BB528" s="1"/>
       <c r="BC528" s="1"/>
-      <c r="BD528" s="1" t="str">
+      <c r="BD528" s="1"/>
+      <c r="BE528" s="1"/>
+      <c r="BF528" s="1"/>
+      <c r="BG528" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36849,7 +38751,10 @@
       <c r="BA529" s="1"/>
       <c r="BB529" s="1"/>
       <c r="BC529" s="1"/>
-      <c r="BD529" s="1" t="str">
+      <c r="BD529" s="1"/>
+      <c r="BE529" s="1"/>
+      <c r="BF529" s="1"/>
+      <c r="BG529" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36913,7 +38818,10 @@
       <c r="BA530" s="1"/>
       <c r="BB530" s="1"/>
       <c r="BC530" s="1"/>
-      <c r="BD530" s="1" t="str">
+      <c r="BD530" s="1"/>
+      <c r="BE530" s="1"/>
+      <c r="BF530" s="1"/>
+      <c r="BG530" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36977,7 +38885,10 @@
       <c r="BA531" s="1"/>
       <c r="BB531" s="1"/>
       <c r="BC531" s="1"/>
-      <c r="BD531" s="1" t="str">
+      <c r="BD531" s="1"/>
+      <c r="BE531" s="1"/>
+      <c r="BF531" s="1"/>
+      <c r="BG531" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37041,7 +38952,10 @@
       <c r="BA532" s="1"/>
       <c r="BB532" s="1"/>
       <c r="BC532" s="1"/>
-      <c r="BD532" s="1" t="str">
+      <c r="BD532" s="1"/>
+      <c r="BE532" s="1"/>
+      <c r="BF532" s="1"/>
+      <c r="BG532" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37105,7 +39019,10 @@
       <c r="BA533" s="1"/>
       <c r="BB533" s="1"/>
       <c r="BC533" s="1"/>
-      <c r="BD533" s="1" t="str">
+      <c r="BD533" s="1"/>
+      <c r="BE533" s="1"/>
+      <c r="BF533" s="1"/>
+      <c r="BG533" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37169,7 +39086,10 @@
       <c r="BA534" s="1"/>
       <c r="BB534" s="1"/>
       <c r="BC534" s="1"/>
-      <c r="BD534" s="1" t="str">
+      <c r="BD534" s="1"/>
+      <c r="BE534" s="1"/>
+      <c r="BF534" s="1"/>
+      <c r="BG534" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37233,7 +39153,10 @@
       <c r="BA535" s="1"/>
       <c r="BB535" s="1"/>
       <c r="BC535" s="1"/>
-      <c r="BD535" s="1" t="str">
+      <c r="BD535" s="1"/>
+      <c r="BE535" s="1"/>
+      <c r="BF535" s="1"/>
+      <c r="BG535" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37297,7 +39220,10 @@
       <c r="BA536" s="1"/>
       <c r="BB536" s="1"/>
       <c r="BC536" s="1"/>
-      <c r="BD536" s="1" t="str">
+      <c r="BD536" s="1"/>
+      <c r="BE536" s="1"/>
+      <c r="BF536" s="1"/>
+      <c r="BG536" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37361,7 +39287,10 @@
       <c r="BA537" s="1"/>
       <c r="BB537" s="1"/>
       <c r="BC537" s="1"/>
-      <c r="BD537" s="1" t="str">
+      <c r="BD537" s="1"/>
+      <c r="BE537" s="1"/>
+      <c r="BF537" s="1"/>
+      <c r="BG537" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37425,7 +39354,10 @@
       <c r="BA538" s="1"/>
       <c r="BB538" s="1"/>
       <c r="BC538" s="1"/>
-      <c r="BD538" s="1" t="str">
+      <c r="BD538" s="1"/>
+      <c r="BE538" s="1"/>
+      <c r="BF538" s="1"/>
+      <c r="BG538" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37489,7 +39421,10 @@
       <c r="BA539" s="1"/>
       <c r="BB539" s="1"/>
       <c r="BC539" s="1"/>
-      <c r="BD539" s="1" t="str">
+      <c r="BD539" s="1"/>
+      <c r="BE539" s="1"/>
+      <c r="BF539" s="1"/>
+      <c r="BG539" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37553,7 +39488,10 @@
       <c r="BA540" s="1"/>
       <c r="BB540" s="1"/>
       <c r="BC540" s="1"/>
-      <c r="BD540" s="1" t="str">
+      <c r="BD540" s="1"/>
+      <c r="BE540" s="1"/>
+      <c r="BF540" s="1"/>
+      <c r="BG540" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37617,7 +39555,10 @@
       <c r="BA541" s="1"/>
       <c r="BB541" s="1"/>
       <c r="BC541" s="1"/>
-      <c r="BD541" s="1" t="str">
+      <c r="BD541" s="1"/>
+      <c r="BE541" s="1"/>
+      <c r="BF541" s="1"/>
+      <c r="BG541" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37681,7 +39622,10 @@
       <c r="BA542" s="1"/>
       <c r="BB542" s="1"/>
       <c r="BC542" s="1"/>
-      <c r="BD542" s="1" t="str">
+      <c r="BD542" s="1"/>
+      <c r="BE542" s="1"/>
+      <c r="BF542" s="1"/>
+      <c r="BG542" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37745,7 +39689,10 @@
       <c r="BA543" s="1"/>
       <c r="BB543" s="1"/>
       <c r="BC543" s="1"/>
-      <c r="BD543" s="1" t="str">
+      <c r="BD543" s="1"/>
+      <c r="BE543" s="1"/>
+      <c r="BF543" s="1"/>
+      <c r="BG543" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37809,7 +39756,10 @@
       <c r="BA544" s="1"/>
       <c r="BB544" s="1"/>
       <c r="BC544" s="1"/>
-      <c r="BD544" s="1" t="str">
+      <c r="BD544" s="1"/>
+      <c r="BE544" s="1"/>
+      <c r="BF544" s="1"/>
+      <c r="BG544" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37873,7 +39823,10 @@
       <c r="BA545" s="1"/>
       <c r="BB545" s="1"/>
       <c r="BC545" s="1"/>
-      <c r="BD545" s="1" t="str">
+      <c r="BD545" s="1"/>
+      <c r="BE545" s="1"/>
+      <c r="BF545" s="1"/>
+      <c r="BG545" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37937,7 +39890,10 @@
       <c r="BA546" s="1"/>
       <c r="BB546" s="1"/>
       <c r="BC546" s="1"/>
-      <c r="BD546" s="1" t="str">
+      <c r="BD546" s="1"/>
+      <c r="BE546" s="1"/>
+      <c r="BF546" s="1"/>
+      <c r="BG546" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38001,7 +39957,10 @@
       <c r="BA547" s="1"/>
       <c r="BB547" s="1"/>
       <c r="BC547" s="1"/>
-      <c r="BD547" s="1" t="str">
+      <c r="BD547" s="1"/>
+      <c r="BE547" s="1"/>
+      <c r="BF547" s="1"/>
+      <c r="BG547" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38065,7 +40024,10 @@
       <c r="BA548" s="1"/>
       <c r="BB548" s="1"/>
       <c r="BC548" s="1"/>
-      <c r="BD548" s="1" t="str">
+      <c r="BD548" s="1"/>
+      <c r="BE548" s="1"/>
+      <c r="BF548" s="1"/>
+      <c r="BG548" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38129,7 +40091,10 @@
       <c r="BA549" s="1"/>
       <c r="BB549" s="1"/>
       <c r="BC549" s="1"/>
-      <c r="BD549" s="1" t="str">
+      <c r="BD549" s="1"/>
+      <c r="BE549" s="1"/>
+      <c r="BF549" s="1"/>
+      <c r="BG549" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38193,7 +40158,10 @@
       <c r="BA550" s="1"/>
       <c r="BB550" s="1"/>
       <c r="BC550" s="1"/>
-      <c r="BD550" s="1" t="str">
+      <c r="BD550" s="1"/>
+      <c r="BE550" s="1"/>
+      <c r="BF550" s="1"/>
+      <c r="BG550" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38257,7 +40225,10 @@
       <c r="BA551" s="1"/>
       <c r="BB551" s="1"/>
       <c r="BC551" s="1"/>
-      <c r="BD551" s="1" t="str">
+      <c r="BD551" s="1"/>
+      <c r="BE551" s="1"/>
+      <c r="BF551" s="1"/>
+      <c r="BG551" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38321,7 +40292,10 @@
       <c r="BA552" s="1"/>
       <c r="BB552" s="1"/>
       <c r="BC552" s="1"/>
-      <c r="BD552" s="1" t="str">
+      <c r="BD552" s="1"/>
+      <c r="BE552" s="1"/>
+      <c r="BF552" s="1"/>
+      <c r="BG552" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38385,7 +40359,10 @@
       <c r="BA553" s="1"/>
       <c r="BB553" s="1"/>
       <c r="BC553" s="1"/>
-      <c r="BD553" s="1" t="str">
+      <c r="BD553" s="1"/>
+      <c r="BE553" s="1"/>
+      <c r="BF553" s="1"/>
+      <c r="BG553" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38449,7 +40426,10 @@
       <c r="BA554" s="1"/>
       <c r="BB554" s="1"/>
       <c r="BC554" s="1"/>
-      <c r="BD554" s="1" t="str">
+      <c r="BD554" s="1"/>
+      <c r="BE554" s="1"/>
+      <c r="BF554" s="1"/>
+      <c r="BG554" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38513,7 +40493,10 @@
       <c r="BA555" s="1"/>
       <c r="BB555" s="1"/>
       <c r="BC555" s="1"/>
-      <c r="BD555" s="1" t="str">
+      <c r="BD555" s="1"/>
+      <c r="BE555" s="1"/>
+      <c r="BF555" s="1"/>
+      <c r="BG555" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38577,7 +40560,10 @@
       <c r="BA556" s="1"/>
       <c r="BB556" s="1"/>
       <c r="BC556" s="1"/>
-      <c r="BD556" s="1" t="str">
+      <c r="BD556" s="1"/>
+      <c r="BE556" s="1"/>
+      <c r="BF556" s="1"/>
+      <c r="BG556" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38641,7 +40627,10 @@
       <c r="BA557" s="1"/>
       <c r="BB557" s="1"/>
       <c r="BC557" s="1"/>
-      <c r="BD557" s="1" t="str">
+      <c r="BD557" s="1"/>
+      <c r="BE557" s="1"/>
+      <c r="BF557" s="1"/>
+      <c r="BG557" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38705,7 +40694,10 @@
       <c r="BA558" s="1"/>
       <c r="BB558" s="1"/>
       <c r="BC558" s="1"/>
-      <c r="BD558" s="1" t="str">
+      <c r="BD558" s="1"/>
+      <c r="BE558" s="1"/>
+      <c r="BF558" s="1"/>
+      <c r="BG558" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38769,7 +40761,10 @@
       <c r="BA559" s="1"/>
       <c r="BB559" s="1"/>
       <c r="BC559" s="1"/>
-      <c r="BD559" s="1" t="str">
+      <c r="BD559" s="1"/>
+      <c r="BE559" s="1"/>
+      <c r="BF559" s="1"/>
+      <c r="BG559" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38833,7 +40828,10 @@
       <c r="BA560" s="1"/>
       <c r="BB560" s="1"/>
       <c r="BC560" s="1"/>
-      <c r="BD560" s="1" t="str">
+      <c r="BD560" s="1"/>
+      <c r="BE560" s="1"/>
+      <c r="BF560" s="1"/>
+      <c r="BG560" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38897,7 +40895,10 @@
       <c r="BA561" s="1"/>
       <c r="BB561" s="1"/>
       <c r="BC561" s="1"/>
-      <c r="BD561" s="1" t="str">
+      <c r="BD561" s="1"/>
+      <c r="BE561" s="1"/>
+      <c r="BF561" s="1"/>
+      <c r="BG561" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38961,7 +40962,10 @@
       <c r="BA562" s="1"/>
       <c r="BB562" s="1"/>
       <c r="BC562" s="1"/>
-      <c r="BD562" s="1" t="str">
+      <c r="BD562" s="1"/>
+      <c r="BE562" s="1"/>
+      <c r="BF562" s="1"/>
+      <c r="BG562" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39025,7 +41029,10 @@
       <c r="BA563" s="1"/>
       <c r="BB563" s="1"/>
       <c r="BC563" s="1"/>
-      <c r="BD563" s="1" t="str">
+      <c r="BD563" s="1"/>
+      <c r="BE563" s="1"/>
+      <c r="BF563" s="1"/>
+      <c r="BG563" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39089,7 +41096,10 @@
       <c r="BA564" s="1"/>
       <c r="BB564" s="1"/>
       <c r="BC564" s="1"/>
-      <c r="BD564" s="1" t="str">
+      <c r="BD564" s="1"/>
+      <c r="BE564" s="1"/>
+      <c r="BF564" s="1"/>
+      <c r="BG564" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39153,7 +41163,10 @@
       <c r="BA565" s="1"/>
       <c r="BB565" s="1"/>
       <c r="BC565" s="1"/>
-      <c r="BD565" s="1" t="str">
+      <c r="BD565" s="1"/>
+      <c r="BE565" s="1"/>
+      <c r="BF565" s="1"/>
+      <c r="BG565" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39217,7 +41230,10 @@
       <c r="BA566" s="1"/>
       <c r="BB566" s="1"/>
       <c r="BC566" s="1"/>
-      <c r="BD566" s="1" t="str">
+      <c r="BD566" s="1"/>
+      <c r="BE566" s="1"/>
+      <c r="BF566" s="1"/>
+      <c r="BG566" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39281,7 +41297,10 @@
       <c r="BA567" s="1"/>
       <c r="BB567" s="1"/>
       <c r="BC567" s="1"/>
-      <c r="BD567" s="1" t="str">
+      <c r="BD567" s="1"/>
+      <c r="BE567" s="1"/>
+      <c r="BF567" s="1"/>
+      <c r="BG567" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39345,7 +41364,10 @@
       <c r="BA568" s="1"/>
       <c r="BB568" s="1"/>
       <c r="BC568" s="1"/>
-      <c r="BD568" s="1" t="str">
+      <c r="BD568" s="1"/>
+      <c r="BE568" s="1"/>
+      <c r="BF568" s="1"/>
+      <c r="BG568" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39409,7 +41431,10 @@
       <c r="BA569" s="1"/>
       <c r="BB569" s="1"/>
       <c r="BC569" s="1"/>
-      <c r="BD569" s="1" t="str">
+      <c r="BD569" s="1"/>
+      <c r="BE569" s="1"/>
+      <c r="BF569" s="1"/>
+      <c r="BG569" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39473,7 +41498,10 @@
       <c r="BA570" s="1"/>
       <c r="BB570" s="1"/>
       <c r="BC570" s="1"/>
-      <c r="BD570" s="1" t="str">
+      <c r="BD570" s="1"/>
+      <c r="BE570" s="1"/>
+      <c r="BF570" s="1"/>
+      <c r="BG570" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39537,7 +41565,10 @@
       <c r="BA571" s="1"/>
       <c r="BB571" s="1"/>
       <c r="BC571" s="1"/>
-      <c r="BD571" s="1" t="str">
+      <c r="BD571" s="1"/>
+      <c r="BE571" s="1"/>
+      <c r="BF571" s="1"/>
+      <c r="BG571" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39601,7 +41632,10 @@
       <c r="BA572" s="1"/>
       <c r="BB572" s="1"/>
       <c r="BC572" s="1"/>
-      <c r="BD572" s="1" t="str">
+      <c r="BD572" s="1"/>
+      <c r="BE572" s="1"/>
+      <c r="BF572" s="1"/>
+      <c r="BG572" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39665,7 +41699,10 @@
       <c r="BA573" s="1"/>
       <c r="BB573" s="1"/>
       <c r="BC573" s="1"/>
-      <c r="BD573" s="1" t="str">
+      <c r="BD573" s="1"/>
+      <c r="BE573" s="1"/>
+      <c r="BF573" s="1"/>
+      <c r="BG573" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39729,7 +41766,10 @@
       <c r="BA574" s="1"/>
       <c r="BB574" s="1"/>
       <c r="BC574" s="1"/>
-      <c r="BD574" s="1" t="str">
+      <c r="BD574" s="1"/>
+      <c r="BE574" s="1"/>
+      <c r="BF574" s="1"/>
+      <c r="BG574" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39793,7 +41833,10 @@
       <c r="BA575" s="1"/>
       <c r="BB575" s="1"/>
       <c r="BC575" s="1"/>
-      <c r="BD575" s="1" t="str">
+      <c r="BD575" s="1"/>
+      <c r="BE575" s="1"/>
+      <c r="BF575" s="1"/>
+      <c r="BG575" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39857,7 +41900,10 @@
       <c r="BA576" s="1"/>
       <c r="BB576" s="1"/>
       <c r="BC576" s="1"/>
-      <c r="BD576" s="1" t="str">
+      <c r="BD576" s="1"/>
+      <c r="BE576" s="1"/>
+      <c r="BF576" s="1"/>
+      <c r="BG576" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39921,7 +41967,10 @@
       <c r="BA577" s="1"/>
       <c r="BB577" s="1"/>
       <c r="BC577" s="1"/>
-      <c r="BD577" s="1" t="str">
+      <c r="BD577" s="1"/>
+      <c r="BE577" s="1"/>
+      <c r="BF577" s="1"/>
+      <c r="BG577" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39985,7 +42034,10 @@
       <c r="BA578" s="1"/>
       <c r="BB578" s="1"/>
       <c r="BC578" s="1"/>
-      <c r="BD578" s="1" t="str">
+      <c r="BD578" s="1"/>
+      <c r="BE578" s="1"/>
+      <c r="BF578" s="1"/>
+      <c r="BG578" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40049,7 +42101,10 @@
       <c r="BA579" s="1"/>
       <c r="BB579" s="1"/>
       <c r="BC579" s="1"/>
-      <c r="BD579" s="1" t="str">
+      <c r="BD579" s="1"/>
+      <c r="BE579" s="1"/>
+      <c r="BF579" s="1"/>
+      <c r="BG579" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40113,7 +42168,10 @@
       <c r="BA580" s="1"/>
       <c r="BB580" s="1"/>
       <c r="BC580" s="1"/>
-      <c r="BD580" s="1" t="str">
+      <c r="BD580" s="1"/>
+      <c r="BE580" s="1"/>
+      <c r="BF580" s="1"/>
+      <c r="BG580" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40177,7 +42235,10 @@
       <c r="BA581" s="1"/>
       <c r="BB581" s="1"/>
       <c r="BC581" s="1"/>
-      <c r="BD581" s="1" t="str">
+      <c r="BD581" s="1"/>
+      <c r="BE581" s="1"/>
+      <c r="BF581" s="1"/>
+      <c r="BG581" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40241,7 +42302,10 @@
       <c r="BA582" s="1"/>
       <c r="BB582" s="1"/>
       <c r="BC582" s="1"/>
-      <c r="BD582" s="1" t="str">
+      <c r="BD582" s="1"/>
+      <c r="BE582" s="1"/>
+      <c r="BF582" s="1"/>
+      <c r="BG582" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40305,7 +42369,10 @@
       <c r="BA583" s="1"/>
       <c r="BB583" s="1"/>
       <c r="BC583" s="1"/>
-      <c r="BD583" s="1" t="str">
+      <c r="BD583" s="1"/>
+      <c r="BE583" s="1"/>
+      <c r="BF583" s="1"/>
+      <c r="BG583" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40369,7 +42436,10 @@
       <c r="BA584" s="1"/>
       <c r="BB584" s="1"/>
       <c r="BC584" s="1"/>
-      <c r="BD584" s="1" t="str">
+      <c r="BD584" s="1"/>
+      <c r="BE584" s="1"/>
+      <c r="BF584" s="1"/>
+      <c r="BG584" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40433,7 +42503,10 @@
       <c r="BA585" s="1"/>
       <c r="BB585" s="1"/>
       <c r="BC585" s="1"/>
-      <c r="BD585" s="1" t="str">
+      <c r="BD585" s="1"/>
+      <c r="BE585" s="1"/>
+      <c r="BF585" s="1"/>
+      <c r="BG585" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40497,7 +42570,10 @@
       <c r="BA586" s="1"/>
       <c r="BB586" s="1"/>
       <c r="BC586" s="1"/>
-      <c r="BD586" s="1" t="str">
+      <c r="BD586" s="1"/>
+      <c r="BE586" s="1"/>
+      <c r="BF586" s="1"/>
+      <c r="BG586" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40561,7 +42637,10 @@
       <c r="BA587" s="1"/>
       <c r="BB587" s="1"/>
       <c r="BC587" s="1"/>
-      <c r="BD587" s="1" t="str">
+      <c r="BD587" s="1"/>
+      <c r="BE587" s="1"/>
+      <c r="BF587" s="1"/>
+      <c r="BG587" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40625,7 +42704,10 @@
       <c r="BA588" s="1"/>
       <c r="BB588" s="1"/>
       <c r="BC588" s="1"/>
-      <c r="BD588" s="1" t="str">
+      <c r="BD588" s="1"/>
+      <c r="BE588" s="1"/>
+      <c r="BF588" s="1"/>
+      <c r="BG588" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40689,7 +42771,10 @@
       <c r="BA589" s="1"/>
       <c r="BB589" s="1"/>
       <c r="BC589" s="1"/>
-      <c r="BD589" s="1" t="str">
+      <c r="BD589" s="1"/>
+      <c r="BE589" s="1"/>
+      <c r="BF589" s="1"/>
+      <c r="BG589" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40753,7 +42838,10 @@
       <c r="BA590" s="1"/>
       <c r="BB590" s="1"/>
       <c r="BC590" s="1"/>
-      <c r="BD590" s="1" t="str">
+      <c r="BD590" s="1"/>
+      <c r="BE590" s="1"/>
+      <c r="BF590" s="1"/>
+      <c r="BG590" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40817,7 +42905,10 @@
       <c r="BA591" s="1"/>
       <c r="BB591" s="1"/>
       <c r="BC591" s="1"/>
-      <c r="BD591" s="1" t="str">
+      <c r="BD591" s="1"/>
+      <c r="BE591" s="1"/>
+      <c r="BF591" s="1"/>
+      <c r="BG591" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40881,7 +42972,10 @@
       <c r="BA592" s="1"/>
       <c r="BB592" s="1"/>
       <c r="BC592" s="1"/>
-      <c r="BD592" s="1" t="str">
+      <c r="BD592" s="1"/>
+      <c r="BE592" s="1"/>
+      <c r="BF592" s="1"/>
+      <c r="BG592" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40945,7 +43039,10 @@
       <c r="BA593" s="1"/>
       <c r="BB593" s="1"/>
       <c r="BC593" s="1"/>
-      <c r="BD593" s="1" t="str">
+      <c r="BD593" s="1"/>
+      <c r="BE593" s="1"/>
+      <c r="BF593" s="1"/>
+      <c r="BG593" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41009,7 +43106,10 @@
       <c r="BA594" s="1"/>
       <c r="BB594" s="1"/>
       <c r="BC594" s="1"/>
-      <c r="BD594" s="1" t="str">
+      <c r="BD594" s="1"/>
+      <c r="BE594" s="1"/>
+      <c r="BF594" s="1"/>
+      <c r="BG594" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41073,7 +43173,10 @@
       <c r="BA595" s="1"/>
       <c r="BB595" s="1"/>
       <c r="BC595" s="1"/>
-      <c r="BD595" s="1" t="str">
+      <c r="BD595" s="1"/>
+      <c r="BE595" s="1"/>
+      <c r="BF595" s="1"/>
+      <c r="BG595" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41137,7 +43240,10 @@
       <c r="BA596" s="1"/>
       <c r="BB596" s="1"/>
       <c r="BC596" s="1"/>
-      <c r="BD596" s="1" t="str">
+      <c r="BD596" s="1"/>
+      <c r="BE596" s="1"/>
+      <c r="BF596" s="1"/>
+      <c r="BG596" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41201,7 +43307,10 @@
       <c r="BA597" s="1"/>
       <c r="BB597" s="1"/>
       <c r="BC597" s="1"/>
-      <c r="BD597" s="1" t="str">
+      <c r="BD597" s="1"/>
+      <c r="BE597" s="1"/>
+      <c r="BF597" s="1"/>
+      <c r="BG597" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41265,7 +43374,10 @@
       <c r="BA598" s="1"/>
       <c r="BB598" s="1"/>
       <c r="BC598" s="1"/>
-      <c r="BD598" s="1" t="str">
+      <c r="BD598" s="1"/>
+      <c r="BE598" s="1"/>
+      <c r="BF598" s="1"/>
+      <c r="BG598" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41329,7 +43441,10 @@
       <c r="BA599" s="1"/>
       <c r="BB599" s="1"/>
       <c r="BC599" s="1"/>
-      <c r="BD599" s="1" t="str">
+      <c r="BD599" s="1"/>
+      <c r="BE599" s="1"/>
+      <c r="BF599" s="1"/>
+      <c r="BG599" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41393,7 +43508,10 @@
       <c r="BA600" s="1"/>
       <c r="BB600" s="1"/>
       <c r="BC600" s="1"/>
-      <c r="BD600" s="1" t="str">
+      <c r="BD600" s="1"/>
+      <c r="BE600" s="1"/>
+      <c r="BF600" s="1"/>
+      <c r="BG600" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41457,7 +43575,10 @@
       <c r="BA601" s="1"/>
       <c r="BB601" s="1"/>
       <c r="BC601" s="1"/>
-      <c r="BD601" s="1" t="str">
+      <c r="BD601" s="1"/>
+      <c r="BE601" s="1"/>
+      <c r="BF601" s="1"/>
+      <c r="BG601" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41521,7 +43642,10 @@
       <c r="BA602" s="1"/>
       <c r="BB602" s="1"/>
       <c r="BC602" s="1"/>
-      <c r="BD602" s="1" t="str">
+      <c r="BD602" s="1"/>
+      <c r="BE602" s="1"/>
+      <c r="BF602" s="1"/>
+      <c r="BG602" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41585,7 +43709,10 @@
       <c r="BA603" s="1"/>
       <c r="BB603" s="1"/>
       <c r="BC603" s="1"/>
-      <c r="BD603" s="1" t="str">
+      <c r="BD603" s="1"/>
+      <c r="BE603" s="1"/>
+      <c r="BF603" s="1"/>
+      <c r="BG603" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41649,7 +43776,10 @@
       <c r="BA604" s="1"/>
       <c r="BB604" s="1"/>
       <c r="BC604" s="1"/>
-      <c r="BD604" s="1" t="str">
+      <c r="BD604" s="1"/>
+      <c r="BE604" s="1"/>
+      <c r="BF604" s="1"/>
+      <c r="BG604" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41713,7 +43843,10 @@
       <c r="BA605" s="1"/>
       <c r="BB605" s="1"/>
       <c r="BC605" s="1"/>
-      <c r="BD605" s="1" t="str">
+      <c r="BD605" s="1"/>
+      <c r="BE605" s="1"/>
+      <c r="BF605" s="1"/>
+      <c r="BG605" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41777,7 +43910,10 @@
       <c r="BA606" s="1"/>
       <c r="BB606" s="1"/>
       <c r="BC606" s="1"/>
-      <c r="BD606" s="1" t="str">
+      <c r="BD606" s="1"/>
+      <c r="BE606" s="1"/>
+      <c r="BF606" s="1"/>
+      <c r="BG606" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41841,7 +43977,10 @@
       <c r="BA607" s="1"/>
       <c r="BB607" s="1"/>
       <c r="BC607" s="1"/>
-      <c r="BD607" s="1" t="str">
+      <c r="BD607" s="1"/>
+      <c r="BE607" s="1"/>
+      <c r="BF607" s="1"/>
+      <c r="BG607" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41905,7 +44044,10 @@
       <c r="BA608" s="1"/>
       <c r="BB608" s="1"/>
       <c r="BC608" s="1"/>
-      <c r="BD608" s="1" t="str">
+      <c r="BD608" s="1"/>
+      <c r="BE608" s="1"/>
+      <c r="BF608" s="1"/>
+      <c r="BG608" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41969,7 +44111,10 @@
       <c r="BA609" s="1"/>
       <c r="BB609" s="1"/>
       <c r="BC609" s="1"/>
-      <c r="BD609" s="1" t="str">
+      <c r="BD609" s="1"/>
+      <c r="BE609" s="1"/>
+      <c r="BF609" s="1"/>
+      <c r="BG609" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42033,7 +44178,10 @@
       <c r="BA610" s="1"/>
       <c r="BB610" s="1"/>
       <c r="BC610" s="1"/>
-      <c r="BD610" s="1" t="str">
+      <c r="BD610" s="1"/>
+      <c r="BE610" s="1"/>
+      <c r="BF610" s="1"/>
+      <c r="BG610" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42097,7 +44245,10 @@
       <c r="BA611" s="1"/>
       <c r="BB611" s="1"/>
       <c r="BC611" s="1"/>
-      <c r="BD611" s="1" t="str">
+      <c r="BD611" s="1"/>
+      <c r="BE611" s="1"/>
+      <c r="BF611" s="1"/>
+      <c r="BG611" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42161,7 +44312,10 @@
       <c r="BA612" s="1"/>
       <c r="BB612" s="1"/>
       <c r="BC612" s="1"/>
-      <c r="BD612" s="1" t="str">
+      <c r="BD612" s="1"/>
+      <c r="BE612" s="1"/>
+      <c r="BF612" s="1"/>
+      <c r="BG612" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42225,7 +44379,10 @@
       <c r="BA613" s="1"/>
       <c r="BB613" s="1"/>
       <c r="BC613" s="1"/>
-      <c r="BD613" s="1" t="str">
+      <c r="BD613" s="1"/>
+      <c r="BE613" s="1"/>
+      <c r="BF613" s="1"/>
+      <c r="BG613" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42289,7 +44446,10 @@
       <c r="BA614" s="1"/>
       <c r="BB614" s="1"/>
       <c r="BC614" s="1"/>
-      <c r="BD614" s="1" t="str">
+      <c r="BD614" s="1"/>
+      <c r="BE614" s="1"/>
+      <c r="BF614" s="1"/>
+      <c r="BG614" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42353,7 +44513,10 @@
       <c r="BA615" s="1"/>
       <c r="BB615" s="1"/>
       <c r="BC615" s="1"/>
-      <c r="BD615" s="1" t="str">
+      <c r="BD615" s="1"/>
+      <c r="BE615" s="1"/>
+      <c r="BF615" s="1"/>
+      <c r="BG615" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42417,7 +44580,10 @@
       <c r="BA616" s="1"/>
       <c r="BB616" s="1"/>
       <c r="BC616" s="1"/>
-      <c r="BD616" s="1" t="str">
+      <c r="BD616" s="1"/>
+      <c r="BE616" s="1"/>
+      <c r="BF616" s="1"/>
+      <c r="BG616" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42481,7 +44647,10 @@
       <c r="BA617" s="1"/>
       <c r="BB617" s="1"/>
       <c r="BC617" s="1"/>
-      <c r="BD617" s="1" t="str">
+      <c r="BD617" s="1"/>
+      <c r="BE617" s="1"/>
+      <c r="BF617" s="1"/>
+      <c r="BG617" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42545,7 +44714,10 @@
       <c r="BA618" s="1"/>
       <c r="BB618" s="1"/>
       <c r="BC618" s="1"/>
-      <c r="BD618" s="1" t="str">
+      <c r="BD618" s="1"/>
+      <c r="BE618" s="1"/>
+      <c r="BF618" s="1"/>
+      <c r="BG618" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42609,7 +44781,10 @@
       <c r="BA619" s="1"/>
       <c r="BB619" s="1"/>
       <c r="BC619" s="1"/>
-      <c r="BD619" s="1" t="str">
+      <c r="BD619" s="1"/>
+      <c r="BE619" s="1"/>
+      <c r="BF619" s="1"/>
+      <c r="BG619" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42673,7 +44848,10 @@
       <c r="BA620" s="1"/>
       <c r="BB620" s="1"/>
       <c r="BC620" s="1"/>
-      <c r="BD620" s="1" t="str">
+      <c r="BD620" s="1"/>
+      <c r="BE620" s="1"/>
+      <c r="BF620" s="1"/>
+      <c r="BG620" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42737,7 +44915,10 @@
       <c r="BA621" s="1"/>
       <c r="BB621" s="1"/>
       <c r="BC621" s="1"/>
-      <c r="BD621" s="1" t="str">
+      <c r="BD621" s="1"/>
+      <c r="BE621" s="1"/>
+      <c r="BF621" s="1"/>
+      <c r="BG621" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42801,7 +44982,10 @@
       <c r="BA622" s="1"/>
       <c r="BB622" s="1"/>
       <c r="BC622" s="1"/>
-      <c r="BD622" s="1" t="str">
+      <c r="BD622" s="1"/>
+      <c r="BE622" s="1"/>
+      <c r="BF622" s="1"/>
+      <c r="BG622" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42865,7 +45049,10 @@
       <c r="BA623" s="1"/>
       <c r="BB623" s="1"/>
       <c r="BC623" s="1"/>
-      <c r="BD623" s="1" t="str">
+      <c r="BD623" s="1"/>
+      <c r="BE623" s="1"/>
+      <c r="BF623" s="1"/>
+      <c r="BG623" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42929,7 +45116,10 @@
       <c r="BA624" s="1"/>
       <c r="BB624" s="1"/>
       <c r="BC624" s="1"/>
-      <c r="BD624" s="1" t="str">
+      <c r="BD624" s="1"/>
+      <c r="BE624" s="1"/>
+      <c r="BF624" s="1"/>
+      <c r="BG624" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42993,7 +45183,10 @@
       <c r="BA625" s="1"/>
       <c r="BB625" s="1"/>
       <c r="BC625" s="1"/>
-      <c r="BD625" s="1" t="str">
+      <c r="BD625" s="1"/>
+      <c r="BE625" s="1"/>
+      <c r="BF625" s="1"/>
+      <c r="BG625" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43057,7 +45250,10 @@
       <c r="BA626" s="1"/>
       <c r="BB626" s="1"/>
       <c r="BC626" s="1"/>
-      <c r="BD626" s="1" t="str">
+      <c r="BD626" s="1"/>
+      <c r="BE626" s="1"/>
+      <c r="BF626" s="1"/>
+      <c r="BG626" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43121,7 +45317,10 @@
       <c r="BA627" s="1"/>
       <c r="BB627" s="1"/>
       <c r="BC627" s="1"/>
-      <c r="BD627" s="1" t="str">
+      <c r="BD627" s="1"/>
+      <c r="BE627" s="1"/>
+      <c r="BF627" s="1"/>
+      <c r="BG627" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43185,7 +45384,10 @@
       <c r="BA628" s="1"/>
       <c r="BB628" s="1"/>
       <c r="BC628" s="1"/>
-      <c r="BD628" s="1" t="str">
+      <c r="BD628" s="1"/>
+      <c r="BE628" s="1"/>
+      <c r="BF628" s="1"/>
+      <c r="BG628" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43249,7 +45451,10 @@
       <c r="BA629" s="1"/>
       <c r="BB629" s="1"/>
       <c r="BC629" s="1"/>
-      <c r="BD629" s="1" t="str">
+      <c r="BD629" s="1"/>
+      <c r="BE629" s="1"/>
+      <c r="BF629" s="1"/>
+      <c r="BG629" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43313,7 +45518,10 @@
       <c r="BA630" s="1"/>
       <c r="BB630" s="1"/>
       <c r="BC630" s="1"/>
-      <c r="BD630" s="1" t="str">
+      <c r="BD630" s="1"/>
+      <c r="BE630" s="1"/>
+      <c r="BF630" s="1"/>
+      <c r="BG630" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43377,7 +45585,10 @@
       <c r="BA631" s="1"/>
       <c r="BB631" s="1"/>
       <c r="BC631" s="1"/>
-      <c r="BD631" s="1" t="str">
+      <c r="BD631" s="1"/>
+      <c r="BE631" s="1"/>
+      <c r="BF631" s="1"/>
+      <c r="BG631" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43441,7 +45652,10 @@
       <c r="BA632" s="1"/>
       <c r="BB632" s="1"/>
       <c r="BC632" s="1"/>
-      <c r="BD632" s="1" t="str">
+      <c r="BD632" s="1"/>
+      <c r="BE632" s="1"/>
+      <c r="BF632" s="1"/>
+      <c r="BG632" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43505,7 +45719,10 @@
       <c r="BA633" s="1"/>
       <c r="BB633" s="1"/>
       <c r="BC633" s="1"/>
-      <c r="BD633" s="1" t="str">
+      <c r="BD633" s="1"/>
+      <c r="BE633" s="1"/>
+      <c r="BF633" s="1"/>
+      <c r="BG633" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43569,7 +45786,10 @@
       <c r="BA634" s="1"/>
       <c r="BB634" s="1"/>
       <c r="BC634" s="1"/>
-      <c r="BD634" s="1" t="str">
+      <c r="BD634" s="1"/>
+      <c r="BE634" s="1"/>
+      <c r="BF634" s="1"/>
+      <c r="BG634" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43633,7 +45853,10 @@
       <c r="BA635" s="1"/>
       <c r="BB635" s="1"/>
       <c r="BC635" s="1"/>
-      <c r="BD635" s="1" t="str">
+      <c r="BD635" s="1"/>
+      <c r="BE635" s="1"/>
+      <c r="BF635" s="1"/>
+      <c r="BG635" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43697,7 +45920,10 @@
       <c r="BA636" s="1"/>
       <c r="BB636" s="1"/>
       <c r="BC636" s="1"/>
-      <c r="BD636" s="1" t="str">
+      <c r="BD636" s="1"/>
+      <c r="BE636" s="1"/>
+      <c r="BF636" s="1"/>
+      <c r="BG636" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43761,7 +45987,10 @@
       <c r="BA637" s="1"/>
       <c r="BB637" s="1"/>
       <c r="BC637" s="1"/>
-      <c r="BD637" s="1" t="str">
+      <c r="BD637" s="1"/>
+      <c r="BE637" s="1"/>
+      <c r="BF637" s="1"/>
+      <c r="BG637" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43825,7 +46054,10 @@
       <c r="BA638" s="1"/>
       <c r="BB638" s="1"/>
       <c r="BC638" s="1"/>
-      <c r="BD638" s="1" t="str">
+      <c r="BD638" s="1"/>
+      <c r="BE638" s="1"/>
+      <c r="BF638" s="1"/>
+      <c r="BG638" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43889,7 +46121,10 @@
       <c r="BA639" s="1"/>
       <c r="BB639" s="1"/>
       <c r="BC639" s="1"/>
-      <c r="BD639" s="1" t="str">
+      <c r="BD639" s="1"/>
+      <c r="BE639" s="1"/>
+      <c r="BF639" s="1"/>
+      <c r="BG639" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43953,7 +46188,10 @@
       <c r="BA640" s="1"/>
       <c r="BB640" s="1"/>
       <c r="BC640" s="1"/>
-      <c r="BD640" s="1" t="str">
+      <c r="BD640" s="1"/>
+      <c r="BE640" s="1"/>
+      <c r="BF640" s="1"/>
+      <c r="BG640" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44017,7 +46255,10 @@
       <c r="BA641" s="1"/>
       <c r="BB641" s="1"/>
       <c r="BC641" s="1"/>
-      <c r="BD641" s="1" t="str">
+      <c r="BD641" s="1"/>
+      <c r="BE641" s="1"/>
+      <c r="BF641" s="1"/>
+      <c r="BG641" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44081,7 +46322,10 @@
       <c r="BA642" s="1"/>
       <c r="BB642" s="1"/>
       <c r="BC642" s="1"/>
-      <c r="BD642" s="1" t="str">
+      <c r="BD642" s="1"/>
+      <c r="BE642" s="1"/>
+      <c r="BF642" s="1"/>
+      <c r="BG642" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44145,7 +46389,10 @@
       <c r="BA643" s="1"/>
       <c r="BB643" s="1"/>
       <c r="BC643" s="1"/>
-      <c r="BD643" s="1" t="str">
+      <c r="BD643" s="1"/>
+      <c r="BE643" s="1"/>
+      <c r="BF643" s="1"/>
+      <c r="BG643" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44209,7 +46456,10 @@
       <c r="BA644" s="1"/>
       <c r="BB644" s="1"/>
       <c r="BC644" s="1"/>
-      <c r="BD644" s="1" t="str">
+      <c r="BD644" s="1"/>
+      <c r="BE644" s="1"/>
+      <c r="BF644" s="1"/>
+      <c r="BG644" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44273,7 +46523,10 @@
       <c r="BA645" s="1"/>
       <c r="BB645" s="1"/>
       <c r="BC645" s="1"/>
-      <c r="BD645" s="1" t="str">
+      <c r="BD645" s="1"/>
+      <c r="BE645" s="1"/>
+      <c r="BF645" s="1"/>
+      <c r="BG645" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44337,7 +46590,10 @@
       <c r="BA646" s="1"/>
       <c r="BB646" s="1"/>
       <c r="BC646" s="1"/>
-      <c r="BD646" s="1" t="str">
+      <c r="BD646" s="1"/>
+      <c r="BE646" s="1"/>
+      <c r="BF646" s="1"/>
+      <c r="BG646" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44401,7 +46657,10 @@
       <c r="BA647" s="1"/>
       <c r="BB647" s="1"/>
       <c r="BC647" s="1"/>
-      <c r="BD647" s="1" t="str">
+      <c r="BD647" s="1"/>
+      <c r="BE647" s="1"/>
+      <c r="BF647" s="1"/>
+      <c r="BG647" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44465,7 +46724,10 @@
       <c r="BA648" s="1"/>
       <c r="BB648" s="1"/>
       <c r="BC648" s="1"/>
-      <c r="BD648" s="1" t="str">
+      <c r="BD648" s="1"/>
+      <c r="BE648" s="1"/>
+      <c r="BF648" s="1"/>
+      <c r="BG648" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44529,7 +46791,10 @@
       <c r="BA649" s="1"/>
       <c r="BB649" s="1"/>
       <c r="BC649" s="1"/>
-      <c r="BD649" s="1" t="str">
+      <c r="BD649" s="1"/>
+      <c r="BE649" s="1"/>
+      <c r="BF649" s="1"/>
+      <c r="BG649" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44593,7 +46858,10 @@
       <c r="BA650" s="1"/>
       <c r="BB650" s="1"/>
       <c r="BC650" s="1"/>
-      <c r="BD650" s="1" t="str">
+      <c r="BD650" s="1"/>
+      <c r="BE650" s="1"/>
+      <c r="BF650" s="1"/>
+      <c r="BG650" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44657,7 +46925,10 @@
       <c r="BA651" s="1"/>
       <c r="BB651" s="1"/>
       <c r="BC651" s="1"/>
-      <c r="BD651" s="1" t="str">
+      <c r="BD651" s="1"/>
+      <c r="BE651" s="1"/>
+      <c r="BF651" s="1"/>
+      <c r="BG651" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44721,7 +46992,10 @@
       <c r="BA652" s="1"/>
       <c r="BB652" s="1"/>
       <c r="BC652" s="1"/>
-      <c r="BD652" s="1" t="str">
+      <c r="BD652" s="1"/>
+      <c r="BE652" s="1"/>
+      <c r="BF652" s="1"/>
+      <c r="BG652" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44785,7 +47059,10 @@
       <c r="BA653" s="1"/>
       <c r="BB653" s="1"/>
       <c r="BC653" s="1"/>
-      <c r="BD653" s="1" t="str">
+      <c r="BD653" s="1"/>
+      <c r="BE653" s="1"/>
+      <c r="BF653" s="1"/>
+      <c r="BG653" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44849,7 +47126,10 @@
       <c r="BA654" s="1"/>
       <c r="BB654" s="1"/>
       <c r="BC654" s="1"/>
-      <c r="BD654" s="1" t="str">
+      <c r="BD654" s="1"/>
+      <c r="BE654" s="1"/>
+      <c r="BF654" s="1"/>
+      <c r="BG654" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44913,7 +47193,10 @@
       <c r="BA655" s="1"/>
       <c r="BB655" s="1"/>
       <c r="BC655" s="1"/>
-      <c r="BD655" s="1" t="str">
+      <c r="BD655" s="1"/>
+      <c r="BE655" s="1"/>
+      <c r="BF655" s="1"/>
+      <c r="BG655" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44977,7 +47260,10 @@
       <c r="BA656" s="1"/>
       <c r="BB656" s="1"/>
       <c r="BC656" s="1"/>
-      <c r="BD656" s="1" t="str">
+      <c r="BD656" s="1"/>
+      <c r="BE656" s="1"/>
+      <c r="BF656" s="1"/>
+      <c r="BG656" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45041,7 +47327,10 @@
       <c r="BA657" s="1"/>
       <c r="BB657" s="1"/>
       <c r="BC657" s="1"/>
-      <c r="BD657" s="1" t="str">
+      <c r="BD657" s="1"/>
+      <c r="BE657" s="1"/>
+      <c r="BF657" s="1"/>
+      <c r="BG657" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45105,7 +47394,10 @@
       <c r="BA658" s="1"/>
       <c r="BB658" s="1"/>
       <c r="BC658" s="1"/>
-      <c r="BD658" s="1" t="str">
+      <c r="BD658" s="1"/>
+      <c r="BE658" s="1"/>
+      <c r="BF658" s="1"/>
+      <c r="BG658" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45169,7 +47461,10 @@
       <c r="BA659" s="1"/>
       <c r="BB659" s="1"/>
       <c r="BC659" s="1"/>
-      <c r="BD659" s="1" t="str">
+      <c r="BD659" s="1"/>
+      <c r="BE659" s="1"/>
+      <c r="BF659" s="1"/>
+      <c r="BG659" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45233,7 +47528,10 @@
       <c r="BA660" s="1"/>
       <c r="BB660" s="1"/>
       <c r="BC660" s="1"/>
-      <c r="BD660" s="1" t="str">
+      <c r="BD660" s="1"/>
+      <c r="BE660" s="1"/>
+      <c r="BF660" s="1"/>
+      <c r="BG660" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45297,7 +47595,10 @@
       <c r="BA661" s="1"/>
       <c r="BB661" s="1"/>
       <c r="BC661" s="1"/>
-      <c r="BD661" s="1" t="str">
+      <c r="BD661" s="1"/>
+      <c r="BE661" s="1"/>
+      <c r="BF661" s="1"/>
+      <c r="BG661" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45361,7 +47662,10 @@
       <c r="BA662" s="1"/>
       <c r="BB662" s="1"/>
       <c r="BC662" s="1"/>
-      <c r="BD662" s="1" t="str">
+      <c r="BD662" s="1"/>
+      <c r="BE662" s="1"/>
+      <c r="BF662" s="1"/>
+      <c r="BG662" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45425,7 +47729,10 @@
       <c r="BA663" s="1"/>
       <c r="BB663" s="1"/>
       <c r="BC663" s="1"/>
-      <c r="BD663" s="1" t="str">
+      <c r="BD663" s="1"/>
+      <c r="BE663" s="1"/>
+      <c r="BF663" s="1"/>
+      <c r="BG663" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45489,7 +47796,10 @@
       <c r="BA664" s="1"/>
       <c r="BB664" s="1"/>
       <c r="BC664" s="1"/>
-      <c r="BD664" s="1" t="str">
+      <c r="BD664" s="1"/>
+      <c r="BE664" s="1"/>
+      <c r="BF664" s="1"/>
+      <c r="BG664" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45553,7 +47863,10 @@
       <c r="BA665" s="1"/>
       <c r="BB665" s="1"/>
       <c r="BC665" s="1"/>
-      <c r="BD665" s="1" t="str">
+      <c r="BD665" s="1"/>
+      <c r="BE665" s="1"/>
+      <c r="BF665" s="1"/>
+      <c r="BG665" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45617,7 +47930,10 @@
       <c r="BA666" s="1"/>
       <c r="BB666" s="1"/>
       <c r="BC666" s="1"/>
-      <c r="BD666" s="1" t="str">
+      <c r="BD666" s="1"/>
+      <c r="BE666" s="1"/>
+      <c r="BF666" s="1"/>
+      <c r="BG666" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45681,7 +47997,10 @@
       <c r="BA667" s="1"/>
       <c r="BB667" s="1"/>
       <c r="BC667" s="1"/>
-      <c r="BD667" s="1" t="str">
+      <c r="BD667" s="1"/>
+      <c r="BE667" s="1"/>
+      <c r="BF667" s="1"/>
+      <c r="BG667" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45745,7 +48064,10 @@
       <c r="BA668" s="1"/>
       <c r="BB668" s="1"/>
       <c r="BC668" s="1"/>
-      <c r="BD668" s="1" t="str">
+      <c r="BD668" s="1"/>
+      <c r="BE668" s="1"/>
+      <c r="BF668" s="1"/>
+      <c r="BG668" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45809,7 +48131,10 @@
       <c r="BA669" s="1"/>
       <c r="BB669" s="1"/>
       <c r="BC669" s="1"/>
-      <c r="BD669" s="1" t="str">
+      <c r="BD669" s="1"/>
+      <c r="BE669" s="1"/>
+      <c r="BF669" s="1"/>
+      <c r="BG669" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45873,7 +48198,10 @@
       <c r="BA670" s="1"/>
       <c r="BB670" s="1"/>
       <c r="BC670" s="1"/>
-      <c r="BD670" s="1" t="str">
+      <c r="BD670" s="1"/>
+      <c r="BE670" s="1"/>
+      <c r="BF670" s="1"/>
+      <c r="BG670" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45937,7 +48265,10 @@
       <c r="BA671" s="1"/>
       <c r="BB671" s="1"/>
       <c r="BC671" s="1"/>
-      <c r="BD671" s="1" t="str">
+      <c r="BD671" s="1"/>
+      <c r="BE671" s="1"/>
+      <c r="BF671" s="1"/>
+      <c r="BG671" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46001,7 +48332,10 @@
       <c r="BA672" s="1"/>
       <c r="BB672" s="1"/>
       <c r="BC672" s="1"/>
-      <c r="BD672" s="1" t="str">
+      <c r="BD672" s="1"/>
+      <c r="BE672" s="1"/>
+      <c r="BF672" s="1"/>
+      <c r="BG672" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46065,7 +48399,10 @@
       <c r="BA673" s="1"/>
       <c r="BB673" s="1"/>
       <c r="BC673" s="1"/>
-      <c r="BD673" s="1" t="str">
+      <c r="BD673" s="1"/>
+      <c r="BE673" s="1"/>
+      <c r="BF673" s="1"/>
+      <c r="BG673" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46129,7 +48466,10 @@
       <c r="BA674" s="1"/>
       <c r="BB674" s="1"/>
       <c r="BC674" s="1"/>
-      <c r="BD674" s="1" t="str">
+      <c r="BD674" s="1"/>
+      <c r="BE674" s="1"/>
+      <c r="BF674" s="1"/>
+      <c r="BG674" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46193,7 +48533,10 @@
       <c r="BA675" s="1"/>
       <c r="BB675" s="1"/>
       <c r="BC675" s="1"/>
-      <c r="BD675" s="1" t="str">
+      <c r="BD675" s="1"/>
+      <c r="BE675" s="1"/>
+      <c r="BF675" s="1"/>
+      <c r="BG675" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46257,7 +48600,10 @@
       <c r="BA676" s="1"/>
       <c r="BB676" s="1"/>
       <c r="BC676" s="1"/>
-      <c r="BD676" s="1" t="str">
+      <c r="BD676" s="1"/>
+      <c r="BE676" s="1"/>
+      <c r="BF676" s="1"/>
+      <c r="BG676" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46321,7 +48667,10 @@
       <c r="BA677" s="1"/>
       <c r="BB677" s="1"/>
       <c r="BC677" s="1"/>
-      <c r="BD677" s="1" t="str">
+      <c r="BD677" s="1"/>
+      <c r="BE677" s="1"/>
+      <c r="BF677" s="1"/>
+      <c r="BG677" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46385,7 +48734,10 @@
       <c r="BA678" s="1"/>
       <c r="BB678" s="1"/>
       <c r="BC678" s="1"/>
-      <c r="BD678" s="1" t="str">
+      <c r="BD678" s="1"/>
+      <c r="BE678" s="1"/>
+      <c r="BF678" s="1"/>
+      <c r="BG678" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46449,7 +48801,10 @@
       <c r="BA679" s="1"/>
       <c r="BB679" s="1"/>
       <c r="BC679" s="1"/>
-      <c r="BD679" s="1" t="str">
+      <c r="BD679" s="1"/>
+      <c r="BE679" s="1"/>
+      <c r="BF679" s="1"/>
+      <c r="BG679" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46513,7 +48868,10 @@
       <c r="BA680" s="1"/>
       <c r="BB680" s="1"/>
       <c r="BC680" s="1"/>
-      <c r="BD680" s="1" t="str">
+      <c r="BD680" s="1"/>
+      <c r="BE680" s="1"/>
+      <c r="BF680" s="1"/>
+      <c r="BG680" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46577,7 +48935,10 @@
       <c r="BA681" s="1"/>
       <c r="BB681" s="1"/>
       <c r="BC681" s="1"/>
-      <c r="BD681" s="1" t="str">
+      <c r="BD681" s="1"/>
+      <c r="BE681" s="1"/>
+      <c r="BF681" s="1"/>
+      <c r="BG681" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46641,7 +49002,10 @@
       <c r="BA682" s="1"/>
       <c r="BB682" s="1"/>
       <c r="BC682" s="1"/>
-      <c r="BD682" s="1" t="str">
+      <c r="BD682" s="1"/>
+      <c r="BE682" s="1"/>
+      <c r="BF682" s="1"/>
+      <c r="BG682" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46705,7 +49069,10 @@
       <c r="BA683" s="1"/>
       <c r="BB683" s="1"/>
       <c r="BC683" s="1"/>
-      <c r="BD683" s="1" t="str">
+      <c r="BD683" s="1"/>
+      <c r="BE683" s="1"/>
+      <c r="BF683" s="1"/>
+      <c r="BG683" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46769,7 +49136,10 @@
       <c r="BA684" s="1"/>
       <c r="BB684" s="1"/>
       <c r="BC684" s="1"/>
-      <c r="BD684" s="1" t="str">
+      <c r="BD684" s="1"/>
+      <c r="BE684" s="1"/>
+      <c r="BF684" s="1"/>
+      <c r="BG684" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46833,7 +49203,10 @@
       <c r="BA685" s="1"/>
       <c r="BB685" s="1"/>
       <c r="BC685" s="1"/>
-      <c r="BD685" s="1" t="str">
+      <c r="BD685" s="1"/>
+      <c r="BE685" s="1"/>
+      <c r="BF685" s="1"/>
+      <c r="BG685" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46897,7 +49270,10 @@
       <c r="BA686" s="1"/>
       <c r="BB686" s="1"/>
       <c r="BC686" s="1"/>
-      <c r="BD686" s="1" t="str">
+      <c r="BD686" s="1"/>
+      <c r="BE686" s="1"/>
+      <c r="BF686" s="1"/>
+      <c r="BG686" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46961,7 +49337,10 @@
       <c r="BA687" s="1"/>
       <c r="BB687" s="1"/>
       <c r="BC687" s="1"/>
-      <c r="BD687" s="1" t="str">
+      <c r="BD687" s="1"/>
+      <c r="BE687" s="1"/>
+      <c r="BF687" s="1"/>
+      <c r="BG687" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47025,7 +49404,10 @@
       <c r="BA688" s="1"/>
       <c r="BB688" s="1"/>
       <c r="BC688" s="1"/>
-      <c r="BD688" s="1" t="str">
+      <c r="BD688" s="1"/>
+      <c r="BE688" s="1"/>
+      <c r="BF688" s="1"/>
+      <c r="BG688" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47089,7 +49471,10 @@
       <c r="BA689" s="1"/>
       <c r="BB689" s="1"/>
       <c r="BC689" s="1"/>
-      <c r="BD689" s="1" t="str">
+      <c r="BD689" s="1"/>
+      <c r="BE689" s="1"/>
+      <c r="BF689" s="1"/>
+      <c r="BG689" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47153,7 +49538,10 @@
       <c r="BA690" s="1"/>
       <c r="BB690" s="1"/>
       <c r="BC690" s="1"/>
-      <c r="BD690" s="1" t="str">
+      <c r="BD690" s="1"/>
+      <c r="BE690" s="1"/>
+      <c r="BF690" s="1"/>
+      <c r="BG690" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47217,7 +49605,10 @@
       <c r="BA691" s="1"/>
       <c r="BB691" s="1"/>
       <c r="BC691" s="1"/>
-      <c r="BD691" s="1" t="str">
+      <c r="BD691" s="1"/>
+      <c r="BE691" s="1"/>
+      <c r="BF691" s="1"/>
+      <c r="BG691" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47281,7 +49672,10 @@
       <c r="BA692" s="1"/>
       <c r="BB692" s="1"/>
       <c r="BC692" s="1"/>
-      <c r="BD692" s="1" t="str">
+      <c r="BD692" s="1"/>
+      <c r="BE692" s="1"/>
+      <c r="BF692" s="1"/>
+      <c r="BG692" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47345,7 +49739,10 @@
       <c r="BA693" s="1"/>
       <c r="BB693" s="1"/>
       <c r="BC693" s="1"/>
-      <c r="BD693" s="1" t="str">
+      <c r="BD693" s="1"/>
+      <c r="BE693" s="1"/>
+      <c r="BF693" s="1"/>
+      <c r="BG693" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47409,7 +49806,10 @@
       <c r="BA694" s="1"/>
       <c r="BB694" s="1"/>
       <c r="BC694" s="1"/>
-      <c r="BD694" s="1" t="str">
+      <c r="BD694" s="1"/>
+      <c r="BE694" s="1"/>
+      <c r="BF694" s="1"/>
+      <c r="BG694" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47473,7 +49873,10 @@
       <c r="BA695" s="1"/>
       <c r="BB695" s="1"/>
       <c r="BC695" s="1"/>
-      <c r="BD695" s="1" t="str">
+      <c r="BD695" s="1"/>
+      <c r="BE695" s="1"/>
+      <c r="BF695" s="1"/>
+      <c r="BG695" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47537,7 +49940,10 @@
       <c r="BA696" s="1"/>
       <c r="BB696" s="1"/>
       <c r="BC696" s="1"/>
-      <c r="BD696" s="1" t="str">
+      <c r="BD696" s="1"/>
+      <c r="BE696" s="1"/>
+      <c r="BF696" s="1"/>
+      <c r="BG696" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47601,7 +50007,10 @@
       <c r="BA697" s="1"/>
       <c r="BB697" s="1"/>
       <c r="BC697" s="1"/>
-      <c r="BD697" s="1" t="str">
+      <c r="BD697" s="1"/>
+      <c r="BE697" s="1"/>
+      <c r="BF697" s="1"/>
+      <c r="BG697" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47665,7 +50074,10 @@
       <c r="BA698" s="1"/>
       <c r="BB698" s="1"/>
       <c r="BC698" s="1"/>
-      <c r="BD698" s="1" t="str">
+      <c r="BD698" s="1"/>
+      <c r="BE698" s="1"/>
+      <c r="BF698" s="1"/>
+      <c r="BG698" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47729,7 +50141,10 @@
       <c r="BA699" s="1"/>
       <c r="BB699" s="1"/>
       <c r="BC699" s="1"/>
-      <c r="BD699" s="1" t="str">
+      <c r="BD699" s="1"/>
+      <c r="BE699" s="1"/>
+      <c r="BF699" s="1"/>
+      <c r="BG699" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47793,7 +50208,10 @@
       <c r="BA700" s="1"/>
       <c r="BB700" s="1"/>
       <c r="BC700" s="1"/>
-      <c r="BD700" s="1" t="str">
+      <c r="BD700" s="1"/>
+      <c r="BE700" s="1"/>
+      <c r="BF700" s="1"/>
+      <c r="BG700" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>

--- a/DATA_VENTA26.1.xlsx
+++ b/DATA_VENTA26.1.xlsx
@@ -1203,8 +1203,8 @@
         <v>1450</v>
       </c>
       <c r="BC4" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="BD4" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
@@ -1911,8 +1911,8 @@
         <v>1050</v>
       </c>
       <c r="BC7" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="BD7" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
@@ -2149,8 +2149,8 @@
         <v>1215</v>
       </c>
       <c r="BC8" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="BD8" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
@@ -2625,8 +2625,8 @@
         <v>1600</v>
       </c>
       <c r="BC10" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="BD10" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
@@ -3696,8 +3696,8 @@
         <v>-</v>
       </c>
       <c r="AC15" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),850.0)</f>
-        <v>850</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="AD15" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -3884,8 +3884,8 @@
         <v>NINGUNO</v>
       </c>
       <c r="R16" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
-        <v>NINGUNO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"50% DSCTO. PRIMERA BOLETA")</f>
+        <v>50% DSCTO. PRIMERA BOLETA</v>
       </c>
       <c r="S16" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
@@ -3928,8 +3928,8 @@
         <v>-</v>
       </c>
       <c r="AC16" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
-        <v>50</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.0)</f>
+        <v>40</v>
       </c>
       <c r="AD16" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),95.0)</f>
@@ -4028,8 +4028,8 @@
         <v>1</v>
       </c>
       <c r="BB16" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1500.0)</f>
-        <v>1500</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1350.0)</f>
+        <v>1350</v>
       </c>
       <c r="BC16" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -4122,8 +4122,8 @@
         <v>NINGUNO</v>
       </c>
       <c r="R17" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
-        <v>NINGUNO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"50% DSCTO. PRIMERA BOLETA")</f>
+        <v>50% DSCTO. PRIMERA BOLETA</v>
       </c>
       <c r="S17" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
@@ -4266,8 +4266,8 @@
         <v>1</v>
       </c>
       <c r="BB17" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1350.0)</f>
-        <v>1350</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1215.0)</f>
+        <v>1215</v>
       </c>
       <c r="BC17" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -4360,8 +4360,8 @@
         <v>NINGUNO</v>
       </c>
       <c r="R18" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
-        <v>NINGUNO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"50% DSCTO. PRIMERA BOLETA")</f>
+        <v>50% DSCTO. PRIMERA BOLETA</v>
       </c>
       <c r="S18" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
@@ -4474,16 +4474,16 @@
         <v>10</v>
       </c>
       <c r="AV18" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIGITAL")</f>
-        <v>DIGITAL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TRADICIONAL")</f>
+        <v>TRADICIONAL</v>
       </c>
       <c r="AW18" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BIDIRECCIONAL")</f>
-        <v>BIDIRECCIONAL</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COLEGIOS")</f>
+        <v>COLEGIOS</v>
       </c>
       <c r="AX18" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ORGANICO")</f>
-        <v>ORGANICO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COLEGIOS")</f>
+        <v>COLEGIOS</v>
       </c>
       <c r="AY18" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
@@ -4498,8 +4498,8 @@
         <v>1</v>
       </c>
       <c r="BB18" s="7">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1500.0)</f>
-        <v>1500</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1350.0)</f>
+        <v>1350</v>
       </c>
       <c r="BC18" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -4523,201 +4523,708 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
-      <c r="R19" s="1"/>
-      <c r="S19" s="1"/>
-      <c r="T19" s="1"/>
-      <c r="U19" s="1"/>
-      <c r="V19" s="1"/>
-      <c r="W19" s="1"/>
-      <c r="X19" s="1"/>
-      <c r="Y19" s="1"/>
-      <c r="Z19" s="1"/>
-      <c r="AA19" s="1"/>
-      <c r="AB19" s="1"/>
-      <c r="AC19" s="1"/>
-      <c r="AD19" s="1"/>
-      <c r="AE19" s="1"/>
-      <c r="AF19" s="1"/>
-      <c r="AG19" s="1"/>
-      <c r="AH19" s="1"/>
-      <c r="AI19" s="1"/>
-      <c r="AJ19" s="1"/>
+      <c r="A19" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.0)</f>
+        <v>18</v>
+      </c>
+      <c r="B19" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2429874.0)</f>
+        <v>2429874</v>
+      </c>
+      <c r="C19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0000061985")</f>
+        <v>0000061985</v>
+      </c>
+      <c r="D19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BIANCA LETICIA ")</f>
+        <v>BIANCA LETICIA </v>
+      </c>
+      <c r="E19" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ZAMALLOA TRIVEÑO")</f>
+        <v>ZAMALLOA TRIVEÑO</v>
+      </c>
+      <c r="F19" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.3165759E7)</f>
+        <v>73165759</v>
+      </c>
+      <c r="G19" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.99408375E8)</f>
+        <v>999408375</v>
+      </c>
+      <c r="H19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"biancazamat@gmail.com")</f>
+        <v>biancazamat@gmail.com</v>
+      </c>
+      <c r="I19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Arquitectura de Interiores")</f>
+        <v>Arquitectura de Interiores</v>
+      </c>
+      <c r="J19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Arquitecturas")</f>
+        <v>Arquitecturas</v>
+      </c>
+      <c r="K19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Antigua")</f>
+        <v>Antigua</v>
+      </c>
+      <c r="L19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Admisión de Alto Rendimiento")</f>
+        <v>Admisión de Alto Rendimiento</v>
+      </c>
+      <c r="M19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Semi-presencial")</f>
+        <v>Semi-presencial</v>
+      </c>
+      <c r="N19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Diurno")</f>
+        <v>Diurno</v>
+      </c>
+      <c r="O19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NUEVO")</f>
+        <v>NUEVO</v>
+      </c>
+      <c r="P19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCALA REGULAR")</f>
+        <v>ESCALA REGULAR</v>
+      </c>
+      <c r="Q19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="R19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"50% DSCTO. PRIMERA BOLETA")</f>
+        <v>50% DSCTO. PRIMERA BOLETA</v>
+      </c>
+      <c r="S19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="T19" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45813.0)</f>
+        <v>45813</v>
+      </c>
+      <c r="U19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARGO")</f>
+        <v>CARGO</v>
+      </c>
+      <c r="V19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="W19" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="X19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="Y19" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45813.0)</f>
+        <v>45813</v>
+      </c>
+      <c r="Z19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="AA19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AB19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="AC19" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
+        <v>50</v>
+      </c>
+      <c r="AD19" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),95.0)</f>
+        <v>95</v>
+      </c>
+      <c r="AE19" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1250.0)</f>
+        <v>1250</v>
+      </c>
+      <c r="AF19" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1250.0)</f>
+        <v>1250</v>
+      </c>
+      <c r="AG19" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH19" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI19" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),325639.0)</f>
+        <v>325639</v>
+      </c>
       <c r="AK19" s="1"/>
       <c r="AL19" s="1"/>
-      <c r="AM19" s="1"/>
-      <c r="AN19" s="1"/>
-      <c r="AO19" s="1"/>
-      <c r="AP19" s="1"/>
-      <c r="AQ19" s="1"/>
-      <c r="AR19" s="1"/>
-      <c r="AS19" s="1"/>
-      <c r="AT19" s="1"/>
-      <c r="AU19" s="1"/>
-      <c r="AV19" s="1"/>
-      <c r="AW19" s="1"/>
-      <c r="AX19" s="1"/>
-      <c r="AY19" s="1"/>
-      <c r="AZ19" s="1"/>
-      <c r="BA19" s="1"/>
-      <c r="BB19" s="1"/>
-      <c r="BC19" s="1"/>
-      <c r="BD19" s="1"/>
-      <c r="BE19" s="1"/>
-      <c r="BF19" s="1"/>
+      <c r="AM19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0")</f>
+        <v>0</v>
+      </c>
+      <c r="AN19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="AO19" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2025.0)</f>
+        <v>2025</v>
+      </c>
+      <c r="AP19" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45809.0)</f>
+        <v>45809</v>
+      </c>
+      <c r="AQ19" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45803.0)</f>
+        <v>45803</v>
+      </c>
+      <c r="AR19" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45803.0)</f>
+        <v>45803</v>
+      </c>
+      <c r="AS19" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
+        <v>45778</v>
+      </c>
+      <c r="AT19" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45775.0)</f>
+        <v>45775</v>
+      </c>
+      <c r="AU19" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
+      </c>
+      <c r="AV19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TRADICIONAL")</f>
+        <v>TRADICIONAL</v>
+      </c>
+      <c r="AW19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COLEGIOS")</f>
+        <v>COLEGIOS</v>
+      </c>
+      <c r="AX19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"COLEGIOS")</f>
+        <v>COLEGIOS</v>
+      </c>
+      <c r="AY19" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Daniel Zapata")</f>
+        <v>Daniel Zapata</v>
+      </c>
+      <c r="BA19" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BB19" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1125.0)</f>
+        <v>1125</v>
+      </c>
+      <c r="BC19" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="BE19" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF19" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
+        <v>N/A</v>
+      </c>
       <c r="BG19" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-      <c r="Q20" s="1"/>
-      <c r="R20" s="1"/>
-      <c r="S20" s="1"/>
-      <c r="T20" s="1"/>
-      <c r="U20" s="1"/>
-      <c r="V20" s="1"/>
-      <c r="W20" s="1"/>
-      <c r="X20" s="1"/>
-      <c r="Y20" s="1"/>
-      <c r="Z20" s="1"/>
-      <c r="AA20" s="1"/>
-      <c r="AB20" s="1"/>
-      <c r="AC20" s="1"/>
-      <c r="AD20" s="1"/>
-      <c r="AE20" s="1"/>
-      <c r="AF20" s="1"/>
-      <c r="AG20" s="1"/>
-      <c r="AH20" s="1"/>
-      <c r="AI20" s="1"/>
-      <c r="AJ20" s="1"/>
-      <c r="AK20" s="1"/>
-      <c r="AL20" s="1"/>
-      <c r="AM20" s="1"/>
-      <c r="AN20" s="1"/>
-      <c r="AO20" s="1"/>
-      <c r="AP20" s="1"/>
-      <c r="AQ20" s="1"/>
-      <c r="AR20" s="1"/>
-      <c r="AS20" s="1"/>
-      <c r="AT20" s="1"/>
-      <c r="AU20" s="1"/>
-      <c r="AV20" s="1"/>
-      <c r="AW20" s="1"/>
-      <c r="AX20" s="1"/>
-      <c r="AY20" s="1"/>
-      <c r="AZ20" s="1"/>
-      <c r="BA20" s="1"/>
-      <c r="BB20" s="1"/>
-      <c r="BC20" s="1"/>
-      <c r="BD20" s="1"/>
-      <c r="BE20" s="1"/>
-      <c r="BF20" s="1"/>
+      <c r="A20" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.0)</f>
+        <v>19</v>
+      </c>
+      <c r="B20" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5003358.0)</f>
+        <v>5003358</v>
+      </c>
+      <c r="C20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0000427858")</f>
+        <v>0000427858</v>
+      </c>
+      <c r="D20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ARIADNA ")</f>
+        <v>ARIADNA </v>
+      </c>
+      <c r="E20" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SALAS LOZADA")</f>
+        <v>SALAS LOZADA</v>
+      </c>
+      <c r="F20" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.1669916E7)</f>
+        <v>71669916</v>
+      </c>
+      <c r="G20" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.32895414E8)</f>
+        <v>932895414</v>
+      </c>
+      <c r="H20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ariadnasalas1008@gmail.com")</f>
+        <v>ariadnasalas1008@gmail.com</v>
+      </c>
+      <c r="I20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Diseño Gráfico Publicitario")</f>
+        <v>Diseño Gráfico Publicitario</v>
+      </c>
+      <c r="J20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Diseño")</f>
+        <v>Diseño</v>
+      </c>
+      <c r="K20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Antigua")</f>
+        <v>Antigua</v>
+      </c>
+      <c r="L20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Admisión Ordinaria")</f>
+        <v>Admisión Ordinaria</v>
+      </c>
+      <c r="M20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Semi-presencial")</f>
+        <v>Semi-presencial</v>
+      </c>
+      <c r="N20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Diurno")</f>
+        <v>Diurno</v>
+      </c>
+      <c r="O20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NUEVO")</f>
+        <v>NUEVO</v>
+      </c>
+      <c r="P20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BECA")</f>
+        <v>BECA</v>
+      </c>
+      <c r="Q20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BECA DGP")</f>
+        <v>BECA DGP</v>
+      </c>
+      <c r="R20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="S20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FABIOLA")</f>
+        <v>FABIOLA</v>
+      </c>
+      <c r="T20" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45813.0)</f>
+        <v>45813</v>
+      </c>
+      <c r="U20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARGO")</f>
+        <v>CARGO</v>
+      </c>
+      <c r="V20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="W20" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="X20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="Y20" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45813.0)</f>
+        <v>45813</v>
+      </c>
+      <c r="Z20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="AA20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AB20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="AC20" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
+        <v>50</v>
+      </c>
+      <c r="AD20" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),95.0)</f>
+        <v>95</v>
+      </c>
+      <c r="AE20" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1600.0)</f>
+        <v>1600</v>
+      </c>
+      <c r="AF20" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1440.0)</f>
+        <v>1440</v>
+      </c>
+      <c r="AG20" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH20" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI20" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),588905.0)</f>
+        <v>588905</v>
+      </c>
+      <c r="AK20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"10 kms a 15 kms")</f>
+        <v>10 kms a 15 kms</v>
+      </c>
+      <c r="AL20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"06 551 a 800")</f>
+        <v>06 551 a 800</v>
+      </c>
+      <c r="AM20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0")</f>
+        <v>0</v>
+      </c>
+      <c r="AN20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="AO20" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2025.0)</f>
+        <v>2025</v>
+      </c>
+      <c r="AP20" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45809.0)</f>
+        <v>45809</v>
+      </c>
+      <c r="AQ20" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45803.0)</f>
+        <v>45803</v>
+      </c>
+      <c r="AR20" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45804.0)</f>
+        <v>45804</v>
+      </c>
+      <c r="AS20" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
+        <v>45778</v>
+      </c>
+      <c r="AT20" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45775.0)</f>
+        <v>45775</v>
+      </c>
+      <c r="AU20" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
+      </c>
+      <c r="AV20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIGITAL")</f>
+        <v>DIGITAL</v>
+      </c>
+      <c r="AW20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BIDIRECCIONAL")</f>
+        <v>BIDIRECCIONAL</v>
+      </c>
+      <c r="AX20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ORGANICO")</f>
+        <v>ORGANICO</v>
+      </c>
+      <c r="AY20" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cinthia Mariella Orosco")</f>
+        <v>Cinthia Mariella Orosco</v>
+      </c>
+      <c r="BA20" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BB20" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1440.0)</f>
+        <v>1440</v>
+      </c>
+      <c r="BC20" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="BE20" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF20" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
+        <v>N/A</v>
+      </c>
       <c r="BG20" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="1"/>
-      <c r="S21" s="1"/>
-      <c r="T21" s="1"/>
-      <c r="U21" s="1"/>
-      <c r="V21" s="1"/>
-      <c r="W21" s="1"/>
-      <c r="X21" s="1"/>
-      <c r="Y21" s="1"/>
-      <c r="Z21" s="1"/>
-      <c r="AA21" s="1"/>
-      <c r="AB21" s="1"/>
-      <c r="AC21" s="1"/>
-      <c r="AD21" s="1"/>
-      <c r="AE21" s="1"/>
-      <c r="AF21" s="1"/>
-      <c r="AG21" s="1"/>
-      <c r="AH21" s="1"/>
-      <c r="AI21" s="1"/>
-      <c r="AJ21" s="1"/>
-      <c r="AK21" s="1"/>
-      <c r="AL21" s="1"/>
-      <c r="AM21" s="1"/>
-      <c r="AN21" s="1"/>
-      <c r="AO21" s="1"/>
-      <c r="AP21" s="1"/>
-      <c r="AQ21" s="1"/>
-      <c r="AR21" s="1"/>
-      <c r="AS21" s="1"/>
-      <c r="AT21" s="1"/>
-      <c r="AU21" s="1"/>
-      <c r="AV21" s="1"/>
-      <c r="AW21" s="1"/>
-      <c r="AX21" s="1"/>
-      <c r="AY21" s="1"/>
-      <c r="AZ21" s="1"/>
-      <c r="BA21" s="1"/>
-      <c r="BB21" s="1"/>
-      <c r="BC21" s="1"/>
-      <c r="BD21" s="1"/>
-      <c r="BE21" s="1"/>
-      <c r="BF21" s="1"/>
+      <c r="A21" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.0)</f>
+        <v>20</v>
+      </c>
+      <c r="B21" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4644125.0)</f>
+        <v>4644125</v>
+      </c>
+      <c r="C21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0000428184")</f>
+        <v>0000428184</v>
+      </c>
+      <c r="D21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ARIAN GABRIEL ")</f>
+        <v>ARIAN GABRIEL </v>
+      </c>
+      <c r="E21" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FRANCO ALARCON")</f>
+        <v>FRANCO ALARCON</v>
+      </c>
+      <c r="F21" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.2586436E7)</f>
+        <v>72586436</v>
+      </c>
+      <c r="G21" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.18246384E8)</f>
+        <v>918246384</v>
+      </c>
+      <c r="H21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"jennyalarcon183@gmail.com")</f>
+        <v>jennyalarcon183@gmail.com</v>
+      </c>
+      <c r="I21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Comunicación Audiovisual y Cine")</f>
+        <v>Comunicación Audiovisual y Cine</v>
+      </c>
+      <c r="J21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Comunicaciones")</f>
+        <v>Comunicaciones</v>
+      </c>
+      <c r="K21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Antigua")</f>
+        <v>Antigua</v>
+      </c>
+      <c r="L21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Admisión de Alto Rendimiento")</f>
+        <v>Admisión de Alto Rendimiento</v>
+      </c>
+      <c r="M21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Semi-presencial")</f>
+        <v>Semi-presencial</v>
+      </c>
+      <c r="N21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Diurno")</f>
+        <v>Diurno</v>
+      </c>
+      <c r="O21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NUEVO")</f>
+        <v>NUEVO</v>
+      </c>
+      <c r="P21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCALA REGULAR")</f>
+        <v>ESCALA REGULAR</v>
+      </c>
+      <c r="Q21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="R21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"50% DSCTO. PRIMERA BOLETA")</f>
+        <v>50% DSCTO. PRIMERA BOLETA</v>
+      </c>
+      <c r="S21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="T21" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45814.0)</f>
+        <v>45814</v>
+      </c>
+      <c r="U21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"POS")</f>
+        <v>POS</v>
+      </c>
+      <c r="V21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="W21" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="X21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="Y21" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45814.0)</f>
+        <v>45814</v>
+      </c>
+      <c r="Z21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="AA21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AB21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="AC21" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
+        <v>50</v>
+      </c>
+      <c r="AD21" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),95.0)</f>
+        <v>95</v>
+      </c>
+      <c r="AE21" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1500.0)</f>
+        <v>1500</v>
+      </c>
+      <c r="AF21" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1500.0)</f>
+        <v>1500</v>
+      </c>
+      <c r="AG21" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH21" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI21" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ21" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1222355.0)</f>
+        <v>1222355</v>
+      </c>
+      <c r="AK21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Más de 15 kms")</f>
+        <v>Más de 15 kms</v>
+      </c>
+      <c r="AL21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"05 301 a 550")</f>
+        <v>05 301 a 550</v>
+      </c>
+      <c r="AM21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0")</f>
+        <v>0</v>
+      </c>
+      <c r="AN21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="AO21" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2025.0)</f>
+        <v>2025</v>
+      </c>
+      <c r="AP21" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45809.0)</f>
+        <v>45809</v>
+      </c>
+      <c r="AQ21" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45803.0)</f>
+        <v>45803</v>
+      </c>
+      <c r="AR21" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45805.0)</f>
+        <v>45805</v>
+      </c>
+      <c r="AS21" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
+        <v>45778</v>
+      </c>
+      <c r="AT21" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45775.0)</f>
+        <v>45775</v>
+      </c>
+      <c r="AU21" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
+      </c>
+      <c r="AV21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIGITAL")</f>
+        <v>DIGITAL</v>
+      </c>
+      <c r="AW21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BIDIRECCIONAL")</f>
+        <v>BIDIRECCIONAL</v>
+      </c>
+      <c r="AX21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEARCH CARRERA")</f>
+        <v>SEARCH CARRERA</v>
+      </c>
+      <c r="AY21" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Daniel Zapata")</f>
+        <v>Daniel Zapata</v>
+      </c>
+      <c r="BA21" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BB21" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1350.0)</f>
+        <v>1350</v>
+      </c>
+      <c r="BC21" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="BE21" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF21" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
+        <v>N/A</v>
+      </c>
       <c r="BG21" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>

--- a/DATA_VENTA26.1.xlsx
+++ b/DATA_VENTA26.1.xlsx
@@ -505,6 +505,14 @@
         <v>CONFIRMADO INICIA UCAL</v>
       </c>
       <c r="BG1" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FECHA PROGRAMACIÓN")</f>
+        <v>FECHA PROGRAMACIÓN</v>
+      </c>
+      <c r="BH1" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FECHA RINDIÓ")</f>
+        <v>FECHA RINDIÓ</v>
+      </c>
+      <c r="BI1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Respuestas NEE")</f>
         <v>Respuestas NEE</v>
       </c>
@@ -742,7 +750,12 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="BG2" s="1" t="str">
+      <c r="BG2" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45794.0)</f>
+        <v>45794</v>
+      </c>
+      <c r="BH2" s="1"/>
+      <c r="BI2" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -980,7 +993,15 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="BG3" s="1" t="str">
+      <c r="BG3" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45794.0)</f>
+        <v>45794</v>
+      </c>
+      <c r="BH3" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45794.0)</f>
+        <v>45794</v>
+      </c>
+      <c r="BI3" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -1218,7 +1239,15 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="BG4" s="1" t="str">
+      <c r="BG4" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45794.0)</f>
+        <v>45794</v>
+      </c>
+      <c r="BH4" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45815.0)</f>
+        <v>45815</v>
+      </c>
+      <c r="BI4" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -1450,7 +1479,12 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="BG5" s="1" t="str">
+      <c r="BG5" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45794.0)</f>
+        <v>45794</v>
+      </c>
+      <c r="BH5" s="1"/>
+      <c r="BI5" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -1688,7 +1722,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="BG6" s="1" t="str">
+      <c r="BG6" s="1"/>
+      <c r="BH6" s="1"/>
+      <c r="BI6" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -1926,7 +1962,15 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="BG7" s="1" t="str">
+      <c r="BG7" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45815.0)</f>
+        <v>45815</v>
+      </c>
+      <c r="BH7" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45815.0)</f>
+        <v>45815</v>
+      </c>
+      <c r="BI7" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -2164,7 +2208,15 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="BG8" s="1" t="str">
+      <c r="BG8" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45815.0)</f>
+        <v>45815</v>
+      </c>
+      <c r="BH8" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45815.0)</f>
+        <v>45815</v>
+      </c>
+      <c r="BI8" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -2402,7 +2454,12 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="BG9" s="1" t="str">
+      <c r="BG9" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45815.0)</f>
+        <v>45815</v>
+      </c>
+      <c r="BH9" s="1"/>
+      <c r="BI9" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -2640,7 +2697,15 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="BG10" s="1" t="str">
+      <c r="BG10" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45815.0)</f>
+        <v>45815</v>
+      </c>
+      <c r="BH10" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45815.0)</f>
+        <v>45815</v>
+      </c>
+      <c r="BI10" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -2875,7 +2940,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="BG11" s="1" t="str">
+      <c r="BG11" s="1"/>
+      <c r="BH11" s="1"/>
+      <c r="BI11" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -3110,7 +3177,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="BG12" s="1" t="str">
+      <c r="BG12" s="1"/>
+      <c r="BH12" s="1"/>
+      <c r="BI12" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -3339,7 +3408,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="BG13" s="1" t="str">
+      <c r="BG13" s="1"/>
+      <c r="BH13" s="1"/>
+      <c r="BI13" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -3577,7 +3648,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="BG14" s="1" t="str">
+      <c r="BG14" s="1"/>
+      <c r="BH14" s="1"/>
+      <c r="BI14" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -3809,7 +3882,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="BG15" s="1" t="str">
+      <c r="BG15" s="1"/>
+      <c r="BH15" s="1"/>
+      <c r="BI15" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4047,7 +4122,12 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="BG16" s="1" t="str">
+      <c r="BG16" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45815.0)</f>
+        <v>45815</v>
+      </c>
+      <c r="BH16" s="1"/>
+      <c r="BI16" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4285,7 +4365,12 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="BG17" s="1" t="str">
+      <c r="BG17" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45815.0)</f>
+        <v>45815</v>
+      </c>
+      <c r="BH17" s="1"/>
+      <c r="BI17" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4517,7 +4602,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="BG18" s="1" t="str">
+      <c r="BG18" s="1"/>
+      <c r="BH18" s="1"/>
+      <c r="BI18" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4749,7 +4836,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="BG19" s="1" t="str">
+      <c r="BG19" s="1"/>
+      <c r="BH19" s="1"/>
+      <c r="BI19" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4987,7 +5076,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="BG20" s="1" t="str">
+      <c r="BG20" s="1"/>
+      <c r="BH20" s="1"/>
+      <c r="BI20" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5225,7 +5316,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="BG21" s="1" t="str">
+      <c r="BG21" s="1"/>
+      <c r="BH21" s="1"/>
+      <c r="BI21" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5236,63 +5329,221 @@
         <v/>
       </c>
       <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
-      <c r="Q22" s="1"/>
-      <c r="R22" s="1"/>
-      <c r="S22" s="1"/>
-      <c r="T22" s="1"/>
-      <c r="U22" s="1"/>
-      <c r="V22" s="1"/>
-      <c r="W22" s="1"/>
-      <c r="X22" s="1"/>
-      <c r="Y22" s="1"/>
-      <c r="Z22" s="1"/>
-      <c r="AA22" s="1"/>
-      <c r="AB22" s="1"/>
-      <c r="AC22" s="1"/>
-      <c r="AD22" s="1"/>
-      <c r="AE22" s="1"/>
-      <c r="AF22" s="1"/>
-      <c r="AG22" s="1"/>
-      <c r="AH22" s="1"/>
-      <c r="AI22" s="1"/>
-      <c r="AJ22" s="1"/>
-      <c r="AK22" s="1"/>
+      <c r="C22" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0000428503")</f>
+        <v>0000428503</v>
+      </c>
+      <c r="D22" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ANA LUCIA ")</f>
+        <v>ANA LUCIA </v>
+      </c>
+      <c r="E22" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"QUIROZ FARIAS")</f>
+        <v>QUIROZ FARIAS</v>
+      </c>
+      <c r="F22" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0734727E7)</f>
+        <v>70734727</v>
+      </c>
+      <c r="G22" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.72770086E8)</f>
+        <v>972770086</v>
+      </c>
+      <c r="H22" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"analuquirozf@gmail.com")</f>
+        <v>analuquirozf@gmail.com</v>
+      </c>
+      <c r="I22" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Arquitectura de Interiores")</f>
+        <v>Arquitectura de Interiores</v>
+      </c>
+      <c r="J22" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Arquitecturas")</f>
+        <v>Arquitecturas</v>
+      </c>
+      <c r="K22" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Antigua")</f>
+        <v>Antigua</v>
+      </c>
+      <c r="L22" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Admisión Ordinaria")</f>
+        <v>Admisión Ordinaria</v>
+      </c>
+      <c r="M22" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Semi-presencial")</f>
+        <v>Semi-presencial</v>
+      </c>
+      <c r="N22" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Diurno")</f>
+        <v>Diurno</v>
+      </c>
+      <c r="O22" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NUEVO")</f>
+        <v>NUEVO</v>
+      </c>
+      <c r="P22" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BECA")</f>
+        <v>BECA</v>
+      </c>
+      <c r="Q22" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BECA CARRERAS CORE")</f>
+        <v>BECA CARRERAS CORE</v>
+      </c>
+      <c r="R22" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"50% DSCTO. PRIMERA BOLETA")</f>
+        <v>50% DSCTO. PRIMERA BOLETA</v>
+      </c>
+      <c r="S22" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FABIOLA")</f>
+        <v>FABIOLA</v>
+      </c>
+      <c r="T22" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45819.0)</f>
+        <v>45819</v>
+      </c>
+      <c r="U22" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"POS")</f>
+        <v>POS</v>
+      </c>
+      <c r="V22" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="W22" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="X22" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="Y22" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45819.0)</f>
+        <v>45819</v>
+      </c>
+      <c r="Z22" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="AA22" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AB22" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="AC22" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
+        <v>50</v>
+      </c>
+      <c r="AD22" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),95.0)</f>
+        <v>95</v>
+      </c>
+      <c r="AE22" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1250.0)</f>
+        <v>1250</v>
+      </c>
+      <c r="AF22" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1115.0)</f>
+        <v>1115</v>
+      </c>
+      <c r="AG22" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH22" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI22" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1242908.0)</f>
+        <v>1242908</v>
+      </c>
+      <c r="AK22" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
       <c r="AL22" s="1"/>
-      <c r="AM22" s="1"/>
-      <c r="AN22" s="1"/>
-      <c r="AO22" s="1"/>
-      <c r="AP22" s="1"/>
-      <c r="AQ22" s="1"/>
-      <c r="AR22" s="1"/>
-      <c r="AS22" s="1"/>
-      <c r="AT22" s="1"/>
-      <c r="AU22" s="1"/>
+      <c r="AM22" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0")</f>
+        <v>0</v>
+      </c>
+      <c r="AN22" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="AO22" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2025.0)</f>
+        <v>2025</v>
+      </c>
+      <c r="AP22" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45809.0)</f>
+        <v>45809</v>
+      </c>
+      <c r="AQ22" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45803.0)</f>
+        <v>45803</v>
+      </c>
+      <c r="AR22" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45806.0)</f>
+        <v>45806</v>
+      </c>
+      <c r="AS22" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
+        <v>45778</v>
+      </c>
+      <c r="AT22" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45775.0)</f>
+        <v>45775</v>
+      </c>
+      <c r="AU22" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.0)</f>
+        <v>13</v>
+      </c>
       <c r="AV22" s="1"/>
       <c r="AW22" s="1"/>
       <c r="AX22" s="1"/>
-      <c r="AY22" s="1"/>
-      <c r="AZ22" s="1"/>
-      <c r="BA22" s="1"/>
-      <c r="BB22" s="1"/>
-      <c r="BC22" s="1"/>
-      <c r="BD22" s="1"/>
-      <c r="BE22" s="1"/>
-      <c r="BF22" s="1"/>
-      <c r="BG22" s="1" t="str">
+      <c r="AY22" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ22" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cinthia Mariella Orosco")</f>
+        <v>Cinthia Mariella Orosco</v>
+      </c>
+      <c r="BA22" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BB22" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1003.5)</f>
+        <v>1003.5</v>
+      </c>
+      <c r="BC22" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD22" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="BE22" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF22" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="BG22" s="1"/>
+      <c r="BH22" s="1"/>
+      <c r="BI22" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5359,7 +5610,9 @@
       <c r="BD23" s="1"/>
       <c r="BE23" s="1"/>
       <c r="BF23" s="1"/>
-      <c r="BG23" s="1" t="str">
+      <c r="BG23" s="1"/>
+      <c r="BH23" s="1"/>
+      <c r="BI23" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5426,7 +5679,9 @@
       <c r="BD24" s="1"/>
       <c r="BE24" s="1"/>
       <c r="BF24" s="1"/>
-      <c r="BG24" s="1" t="str">
+      <c r="BG24" s="1"/>
+      <c r="BH24" s="1"/>
+      <c r="BI24" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5493,7 +5748,9 @@
       <c r="BD25" s="1"/>
       <c r="BE25" s="1"/>
       <c r="BF25" s="1"/>
-      <c r="BG25" s="1" t="str">
+      <c r="BG25" s="1"/>
+      <c r="BH25" s="1"/>
+      <c r="BI25" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5560,7 +5817,9 @@
       <c r="BD26" s="1"/>
       <c r="BE26" s="1"/>
       <c r="BF26" s="1"/>
-      <c r="BG26" s="1" t="str">
+      <c r="BG26" s="1"/>
+      <c r="BH26" s="1"/>
+      <c r="BI26" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5627,7 +5886,9 @@
       <c r="BD27" s="1"/>
       <c r="BE27" s="1"/>
       <c r="BF27" s="1"/>
-      <c r="BG27" s="1" t="str">
+      <c r="BG27" s="1"/>
+      <c r="BH27" s="1"/>
+      <c r="BI27" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5694,7 +5955,9 @@
       <c r="BD28" s="1"/>
       <c r="BE28" s="1"/>
       <c r="BF28" s="1"/>
-      <c r="BG28" s="1" t="str">
+      <c r="BG28" s="1"/>
+      <c r="BH28" s="1"/>
+      <c r="BI28" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5761,7 +6024,9 @@
       <c r="BD29" s="1"/>
       <c r="BE29" s="1"/>
       <c r="BF29" s="1"/>
-      <c r="BG29" s="1" t="str">
+      <c r="BG29" s="1"/>
+      <c r="BH29" s="1"/>
+      <c r="BI29" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5828,7 +6093,9 @@
       <c r="BD30" s="1"/>
       <c r="BE30" s="1"/>
       <c r="BF30" s="1"/>
-      <c r="BG30" s="1" t="str">
+      <c r="BG30" s="1"/>
+      <c r="BH30" s="1"/>
+      <c r="BI30" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5895,7 +6162,9 @@
       <c r="BD31" s="1"/>
       <c r="BE31" s="1"/>
       <c r="BF31" s="1"/>
-      <c r="BG31" s="1" t="str">
+      <c r="BG31" s="1"/>
+      <c r="BH31" s="1"/>
+      <c r="BI31" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5962,7 +6231,9 @@
       <c r="BD32" s="1"/>
       <c r="BE32" s="1"/>
       <c r="BF32" s="1"/>
-      <c r="BG32" s="1" t="str">
+      <c r="BG32" s="1"/>
+      <c r="BH32" s="1"/>
+      <c r="BI32" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6029,7 +6300,9 @@
       <c r="BD33" s="1"/>
       <c r="BE33" s="1"/>
       <c r="BF33" s="1"/>
-      <c r="BG33" s="1" t="str">
+      <c r="BG33" s="1"/>
+      <c r="BH33" s="1"/>
+      <c r="BI33" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6096,7 +6369,9 @@
       <c r="BD34" s="1"/>
       <c r="BE34" s="1"/>
       <c r="BF34" s="1"/>
-      <c r="BG34" s="1" t="str">
+      <c r="BG34" s="1"/>
+      <c r="BH34" s="1"/>
+      <c r="BI34" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6163,7 +6438,9 @@
       <c r="BD35" s="1"/>
       <c r="BE35" s="1"/>
       <c r="BF35" s="1"/>
-      <c r="BG35" s="1" t="str">
+      <c r="BG35" s="1"/>
+      <c r="BH35" s="1"/>
+      <c r="BI35" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6230,7 +6507,9 @@
       <c r="BD36" s="1"/>
       <c r="BE36" s="1"/>
       <c r="BF36" s="1"/>
-      <c r="BG36" s="1" t="str">
+      <c r="BG36" s="1"/>
+      <c r="BH36" s="1"/>
+      <c r="BI36" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6297,7 +6576,9 @@
       <c r="BD37" s="1"/>
       <c r="BE37" s="1"/>
       <c r="BF37" s="1"/>
-      <c r="BG37" s="1" t="str">
+      <c r="BG37" s="1"/>
+      <c r="BH37" s="1"/>
+      <c r="BI37" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6364,7 +6645,9 @@
       <c r="BD38" s="1"/>
       <c r="BE38" s="1"/>
       <c r="BF38" s="1"/>
-      <c r="BG38" s="1" t="str">
+      <c r="BG38" s="1"/>
+      <c r="BH38" s="1"/>
+      <c r="BI38" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6431,7 +6714,9 @@
       <c r="BD39" s="1"/>
       <c r="BE39" s="1"/>
       <c r="BF39" s="1"/>
-      <c r="BG39" s="1" t="str">
+      <c r="BG39" s="1"/>
+      <c r="BH39" s="1"/>
+      <c r="BI39" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6498,7 +6783,9 @@
       <c r="BD40" s="1"/>
       <c r="BE40" s="1"/>
       <c r="BF40" s="1"/>
-      <c r="BG40" s="1" t="str">
+      <c r="BG40" s="1"/>
+      <c r="BH40" s="1"/>
+      <c r="BI40" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6565,7 +6852,9 @@
       <c r="BD41" s="1"/>
       <c r="BE41" s="1"/>
       <c r="BF41" s="1"/>
-      <c r="BG41" s="1" t="str">
+      <c r="BG41" s="1"/>
+      <c r="BH41" s="1"/>
+      <c r="BI41" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6632,7 +6921,9 @@
       <c r="BD42" s="1"/>
       <c r="BE42" s="1"/>
       <c r="BF42" s="1"/>
-      <c r="BG42" s="1" t="str">
+      <c r="BG42" s="1"/>
+      <c r="BH42" s="1"/>
+      <c r="BI42" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6699,7 +6990,9 @@
       <c r="BD43" s="1"/>
       <c r="BE43" s="1"/>
       <c r="BF43" s="1"/>
-      <c r="BG43" s="1" t="str">
+      <c r="BG43" s="1"/>
+      <c r="BH43" s="1"/>
+      <c r="BI43" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6766,7 +7059,9 @@
       <c r="BD44" s="1"/>
       <c r="BE44" s="1"/>
       <c r="BF44" s="1"/>
-      <c r="BG44" s="1" t="str">
+      <c r="BG44" s="1"/>
+      <c r="BH44" s="1"/>
+      <c r="BI44" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6833,7 +7128,9 @@
       <c r="BD45" s="1"/>
       <c r="BE45" s="1"/>
       <c r="BF45" s="1"/>
-      <c r="BG45" s="1" t="str">
+      <c r="BG45" s="1"/>
+      <c r="BH45" s="1"/>
+      <c r="BI45" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6900,7 +7197,9 @@
       <c r="BD46" s="1"/>
       <c r="BE46" s="1"/>
       <c r="BF46" s="1"/>
-      <c r="BG46" s="1" t="str">
+      <c r="BG46" s="1"/>
+      <c r="BH46" s="1"/>
+      <c r="BI46" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6967,7 +7266,9 @@
       <c r="BD47" s="1"/>
       <c r="BE47" s="1"/>
       <c r="BF47" s="1"/>
-      <c r="BG47" s="1" t="str">
+      <c r="BG47" s="1"/>
+      <c r="BH47" s="1"/>
+      <c r="BI47" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7034,7 +7335,9 @@
       <c r="BD48" s="1"/>
       <c r="BE48" s="1"/>
       <c r="BF48" s="1"/>
-      <c r="BG48" s="1" t="str">
+      <c r="BG48" s="1"/>
+      <c r="BH48" s="1"/>
+      <c r="BI48" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7101,7 +7404,9 @@
       <c r="BD49" s="1"/>
       <c r="BE49" s="1"/>
       <c r="BF49" s="1"/>
-      <c r="BG49" s="1" t="str">
+      <c r="BG49" s="1"/>
+      <c r="BH49" s="1"/>
+      <c r="BI49" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7168,7 +7473,9 @@
       <c r="BD50" s="1"/>
       <c r="BE50" s="1"/>
       <c r="BF50" s="1"/>
-      <c r="BG50" s="1" t="str">
+      <c r="BG50" s="1"/>
+      <c r="BH50" s="1"/>
+      <c r="BI50" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7235,7 +7542,9 @@
       <c r="BD51" s="1"/>
       <c r="BE51" s="1"/>
       <c r="BF51" s="1"/>
-      <c r="BG51" s="1" t="str">
+      <c r="BG51" s="1"/>
+      <c r="BH51" s="1"/>
+      <c r="BI51" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7302,7 +7611,9 @@
       <c r="BD52" s="1"/>
       <c r="BE52" s="1"/>
       <c r="BF52" s="1"/>
-      <c r="BG52" s="1" t="str">
+      <c r="BG52" s="1"/>
+      <c r="BH52" s="1"/>
+      <c r="BI52" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7369,7 +7680,9 @@
       <c r="BD53" s="1"/>
       <c r="BE53" s="1"/>
       <c r="BF53" s="1"/>
-      <c r="BG53" s="1" t="str">
+      <c r="BG53" s="1"/>
+      <c r="BH53" s="1"/>
+      <c r="BI53" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7436,7 +7749,9 @@
       <c r="BD54" s="1"/>
       <c r="BE54" s="1"/>
       <c r="BF54" s="1"/>
-      <c r="BG54" s="1" t="str">
+      <c r="BG54" s="1"/>
+      <c r="BH54" s="1"/>
+      <c r="BI54" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7503,7 +7818,9 @@
       <c r="BD55" s="1"/>
       <c r="BE55" s="1"/>
       <c r="BF55" s="1"/>
-      <c r="BG55" s="1" t="str">
+      <c r="BG55" s="1"/>
+      <c r="BH55" s="1"/>
+      <c r="BI55" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7570,7 +7887,9 @@
       <c r="BD56" s="1"/>
       <c r="BE56" s="1"/>
       <c r="BF56" s="1"/>
-      <c r="BG56" s="1" t="str">
+      <c r="BG56" s="1"/>
+      <c r="BH56" s="1"/>
+      <c r="BI56" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7637,7 +7956,9 @@
       <c r="BD57" s="1"/>
       <c r="BE57" s="1"/>
       <c r="BF57" s="1"/>
-      <c r="BG57" s="1" t="str">
+      <c r="BG57" s="1"/>
+      <c r="BH57" s="1"/>
+      <c r="BI57" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7704,7 +8025,9 @@
       <c r="BD58" s="1"/>
       <c r="BE58" s="1"/>
       <c r="BF58" s="1"/>
-      <c r="BG58" s="1" t="str">
+      <c r="BG58" s="1"/>
+      <c r="BH58" s="1"/>
+      <c r="BI58" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7771,7 +8094,9 @@
       <c r="BD59" s="1"/>
       <c r="BE59" s="1"/>
       <c r="BF59" s="1"/>
-      <c r="BG59" s="1" t="str">
+      <c r="BG59" s="1"/>
+      <c r="BH59" s="1"/>
+      <c r="BI59" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7838,7 +8163,9 @@
       <c r="BD60" s="1"/>
       <c r="BE60" s="1"/>
       <c r="BF60" s="1"/>
-      <c r="BG60" s="1" t="str">
+      <c r="BG60" s="1"/>
+      <c r="BH60" s="1"/>
+      <c r="BI60" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7905,7 +8232,9 @@
       <c r="BD61" s="1"/>
       <c r="BE61" s="1"/>
       <c r="BF61" s="1"/>
-      <c r="BG61" s="1" t="str">
+      <c r="BG61" s="1"/>
+      <c r="BH61" s="1"/>
+      <c r="BI61" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7972,7 +8301,9 @@
       <c r="BD62" s="1"/>
       <c r="BE62" s="1"/>
       <c r="BF62" s="1"/>
-      <c r="BG62" s="1" t="str">
+      <c r="BG62" s="1"/>
+      <c r="BH62" s="1"/>
+      <c r="BI62" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8039,7 +8370,9 @@
       <c r="BD63" s="1"/>
       <c r="BE63" s="1"/>
       <c r="BF63" s="1"/>
-      <c r="BG63" s="1" t="str">
+      <c r="BG63" s="1"/>
+      <c r="BH63" s="1"/>
+      <c r="BI63" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8106,7 +8439,9 @@
       <c r="BD64" s="1"/>
       <c r="BE64" s="1"/>
       <c r="BF64" s="1"/>
-      <c r="BG64" s="1" t="str">
+      <c r="BG64" s="1"/>
+      <c r="BH64" s="1"/>
+      <c r="BI64" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8173,7 +8508,9 @@
       <c r="BD65" s="1"/>
       <c r="BE65" s="1"/>
       <c r="BF65" s="1"/>
-      <c r="BG65" s="1" t="str">
+      <c r="BG65" s="1"/>
+      <c r="BH65" s="1"/>
+      <c r="BI65" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8240,7 +8577,9 @@
       <c r="BD66" s="1"/>
       <c r="BE66" s="1"/>
       <c r="BF66" s="1"/>
-      <c r="BG66" s="1" t="str">
+      <c r="BG66" s="1"/>
+      <c r="BH66" s="1"/>
+      <c r="BI66" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8307,7 +8646,9 @@
       <c r="BD67" s="1"/>
       <c r="BE67" s="1"/>
       <c r="BF67" s="1"/>
-      <c r="BG67" s="1" t="str">
+      <c r="BG67" s="1"/>
+      <c r="BH67" s="1"/>
+      <c r="BI67" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8374,7 +8715,9 @@
       <c r="BD68" s="1"/>
       <c r="BE68" s="1"/>
       <c r="BF68" s="1"/>
-      <c r="BG68" s="1" t="str">
+      <c r="BG68" s="1"/>
+      <c r="BH68" s="1"/>
+      <c r="BI68" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8441,7 +8784,9 @@
       <c r="BD69" s="1"/>
       <c r="BE69" s="1"/>
       <c r="BF69" s="1"/>
-      <c r="BG69" s="1" t="str">
+      <c r="BG69" s="1"/>
+      <c r="BH69" s="1"/>
+      <c r="BI69" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8508,7 +8853,9 @@
       <c r="BD70" s="1"/>
       <c r="BE70" s="1"/>
       <c r="BF70" s="1"/>
-      <c r="BG70" s="1" t="str">
+      <c r="BG70" s="1"/>
+      <c r="BH70" s="1"/>
+      <c r="BI70" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8575,7 +8922,9 @@
       <c r="BD71" s="1"/>
       <c r="BE71" s="1"/>
       <c r="BF71" s="1"/>
-      <c r="BG71" s="1" t="str">
+      <c r="BG71" s="1"/>
+      <c r="BH71" s="1"/>
+      <c r="BI71" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8642,7 +8991,9 @@
       <c r="BD72" s="1"/>
       <c r="BE72" s="1"/>
       <c r="BF72" s="1"/>
-      <c r="BG72" s="1" t="str">
+      <c r="BG72" s="1"/>
+      <c r="BH72" s="1"/>
+      <c r="BI72" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8709,7 +9060,9 @@
       <c r="BD73" s="1"/>
       <c r="BE73" s="1"/>
       <c r="BF73" s="1"/>
-      <c r="BG73" s="1" t="str">
+      <c r="BG73" s="1"/>
+      <c r="BH73" s="1"/>
+      <c r="BI73" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8776,7 +9129,9 @@
       <c r="BD74" s="1"/>
       <c r="BE74" s="1"/>
       <c r="BF74" s="1"/>
-      <c r="BG74" s="1" t="str">
+      <c r="BG74" s="1"/>
+      <c r="BH74" s="1"/>
+      <c r="BI74" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8843,7 +9198,9 @@
       <c r="BD75" s="1"/>
       <c r="BE75" s="1"/>
       <c r="BF75" s="1"/>
-      <c r="BG75" s="1" t="str">
+      <c r="BG75" s="1"/>
+      <c r="BH75" s="1"/>
+      <c r="BI75" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8910,7 +9267,9 @@
       <c r="BD76" s="1"/>
       <c r="BE76" s="1"/>
       <c r="BF76" s="1"/>
-      <c r="BG76" s="1" t="str">
+      <c r="BG76" s="1"/>
+      <c r="BH76" s="1"/>
+      <c r="BI76" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8977,7 +9336,9 @@
       <c r="BD77" s="1"/>
       <c r="BE77" s="1"/>
       <c r="BF77" s="1"/>
-      <c r="BG77" s="1" t="str">
+      <c r="BG77" s="1"/>
+      <c r="BH77" s="1"/>
+      <c r="BI77" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9044,7 +9405,9 @@
       <c r="BD78" s="1"/>
       <c r="BE78" s="1"/>
       <c r="BF78" s="1"/>
-      <c r="BG78" s="1" t="str">
+      <c r="BG78" s="1"/>
+      <c r="BH78" s="1"/>
+      <c r="BI78" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9111,7 +9474,9 @@
       <c r="BD79" s="1"/>
       <c r="BE79" s="1"/>
       <c r="BF79" s="1"/>
-      <c r="BG79" s="1" t="str">
+      <c r="BG79" s="1"/>
+      <c r="BH79" s="1"/>
+      <c r="BI79" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9178,7 +9543,9 @@
       <c r="BD80" s="1"/>
       <c r="BE80" s="1"/>
       <c r="BF80" s="1"/>
-      <c r="BG80" s="1" t="str">
+      <c r="BG80" s="1"/>
+      <c r="BH80" s="1"/>
+      <c r="BI80" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9245,7 +9612,9 @@
       <c r="BD81" s="1"/>
       <c r="BE81" s="1"/>
       <c r="BF81" s="1"/>
-      <c r="BG81" s="1" t="str">
+      <c r="BG81" s="1"/>
+      <c r="BH81" s="1"/>
+      <c r="BI81" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9312,7 +9681,9 @@
       <c r="BD82" s="1"/>
       <c r="BE82" s="1"/>
       <c r="BF82" s="1"/>
-      <c r="BG82" s="1" t="str">
+      <c r="BG82" s="1"/>
+      <c r="BH82" s="1"/>
+      <c r="BI82" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9379,7 +9750,9 @@
       <c r="BD83" s="1"/>
       <c r="BE83" s="1"/>
       <c r="BF83" s="1"/>
-      <c r="BG83" s="1" t="str">
+      <c r="BG83" s="1"/>
+      <c r="BH83" s="1"/>
+      <c r="BI83" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9446,7 +9819,9 @@
       <c r="BD84" s="1"/>
       <c r="BE84" s="1"/>
       <c r="BF84" s="1"/>
-      <c r="BG84" s="1" t="str">
+      <c r="BG84" s="1"/>
+      <c r="BH84" s="1"/>
+      <c r="BI84" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9513,7 +9888,9 @@
       <c r="BD85" s="1"/>
       <c r="BE85" s="1"/>
       <c r="BF85" s="1"/>
-      <c r="BG85" s="1" t="str">
+      <c r="BG85" s="1"/>
+      <c r="BH85" s="1"/>
+      <c r="BI85" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9580,7 +9957,9 @@
       <c r="BD86" s="1"/>
       <c r="BE86" s="1"/>
       <c r="BF86" s="1"/>
-      <c r="BG86" s="1" t="str">
+      <c r="BG86" s="1"/>
+      <c r="BH86" s="1"/>
+      <c r="BI86" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9647,7 +10026,9 @@
       <c r="BD87" s="1"/>
       <c r="BE87" s="1"/>
       <c r="BF87" s="1"/>
-      <c r="BG87" s="1" t="str">
+      <c r="BG87" s="1"/>
+      <c r="BH87" s="1"/>
+      <c r="BI87" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9714,7 +10095,9 @@
       <c r="BD88" s="1"/>
       <c r="BE88" s="1"/>
       <c r="BF88" s="1"/>
-      <c r="BG88" s="1" t="str">
+      <c r="BG88" s="1"/>
+      <c r="BH88" s="1"/>
+      <c r="BI88" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9781,7 +10164,9 @@
       <c r="BD89" s="1"/>
       <c r="BE89" s="1"/>
       <c r="BF89" s="1"/>
-      <c r="BG89" s="1" t="str">
+      <c r="BG89" s="1"/>
+      <c r="BH89" s="1"/>
+      <c r="BI89" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9848,7 +10233,9 @@
       <c r="BD90" s="1"/>
       <c r="BE90" s="1"/>
       <c r="BF90" s="1"/>
-      <c r="BG90" s="1" t="str">
+      <c r="BG90" s="1"/>
+      <c r="BH90" s="1"/>
+      <c r="BI90" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9915,7 +10302,9 @@
       <c r="BD91" s="1"/>
       <c r="BE91" s="1"/>
       <c r="BF91" s="1"/>
-      <c r="BG91" s="1" t="str">
+      <c r="BG91" s="1"/>
+      <c r="BH91" s="1"/>
+      <c r="BI91" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9982,7 +10371,9 @@
       <c r="BD92" s="1"/>
       <c r="BE92" s="1"/>
       <c r="BF92" s="1"/>
-      <c r="BG92" s="1" t="str">
+      <c r="BG92" s="1"/>
+      <c r="BH92" s="1"/>
+      <c r="BI92" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10049,7 +10440,9 @@
       <c r="BD93" s="1"/>
       <c r="BE93" s="1"/>
       <c r="BF93" s="1"/>
-      <c r="BG93" s="1" t="str">
+      <c r="BG93" s="1"/>
+      <c r="BH93" s="1"/>
+      <c r="BI93" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10116,7 +10509,9 @@
       <c r="BD94" s="1"/>
       <c r="BE94" s="1"/>
       <c r="BF94" s="1"/>
-      <c r="BG94" s="1" t="str">
+      <c r="BG94" s="1"/>
+      <c r="BH94" s="1"/>
+      <c r="BI94" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10183,7 +10578,9 @@
       <c r="BD95" s="1"/>
       <c r="BE95" s="1"/>
       <c r="BF95" s="1"/>
-      <c r="BG95" s="1" t="str">
+      <c r="BG95" s="1"/>
+      <c r="BH95" s="1"/>
+      <c r="BI95" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10250,7 +10647,9 @@
       <c r="BD96" s="1"/>
       <c r="BE96" s="1"/>
       <c r="BF96" s="1"/>
-      <c r="BG96" s="1" t="str">
+      <c r="BG96" s="1"/>
+      <c r="BH96" s="1"/>
+      <c r="BI96" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10317,7 +10716,9 @@
       <c r="BD97" s="1"/>
       <c r="BE97" s="1"/>
       <c r="BF97" s="1"/>
-      <c r="BG97" s="1" t="str">
+      <c r="BG97" s="1"/>
+      <c r="BH97" s="1"/>
+      <c r="BI97" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10384,7 +10785,9 @@
       <c r="BD98" s="1"/>
       <c r="BE98" s="1"/>
       <c r="BF98" s="1"/>
-      <c r="BG98" s="1" t="str">
+      <c r="BG98" s="1"/>
+      <c r="BH98" s="1"/>
+      <c r="BI98" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10451,7 +10854,9 @@
       <c r="BD99" s="1"/>
       <c r="BE99" s="1"/>
       <c r="BF99" s="1"/>
-      <c r="BG99" s="1" t="str">
+      <c r="BG99" s="1"/>
+      <c r="BH99" s="1"/>
+      <c r="BI99" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10518,7 +10923,9 @@
       <c r="BD100" s="1"/>
       <c r="BE100" s="1"/>
       <c r="BF100" s="1"/>
-      <c r="BG100" s="1" t="str">
+      <c r="BG100" s="1"/>
+      <c r="BH100" s="1"/>
+      <c r="BI100" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10585,7 +10992,9 @@
       <c r="BD101" s="1"/>
       <c r="BE101" s="1"/>
       <c r="BF101" s="1"/>
-      <c r="BG101" s="1" t="str">
+      <c r="BG101" s="1"/>
+      <c r="BH101" s="1"/>
+      <c r="BI101" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10652,7 +11061,9 @@
       <c r="BD102" s="1"/>
       <c r="BE102" s="1"/>
       <c r="BF102" s="1"/>
-      <c r="BG102" s="1" t="str">
+      <c r="BG102" s="1"/>
+      <c r="BH102" s="1"/>
+      <c r="BI102" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10719,7 +11130,9 @@
       <c r="BD103" s="1"/>
       <c r="BE103" s="1"/>
       <c r="BF103" s="1"/>
-      <c r="BG103" s="1" t="str">
+      <c r="BG103" s="1"/>
+      <c r="BH103" s="1"/>
+      <c r="BI103" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10786,7 +11199,9 @@
       <c r="BD104" s="1"/>
       <c r="BE104" s="1"/>
       <c r="BF104" s="1"/>
-      <c r="BG104" s="1" t="str">
+      <c r="BG104" s="1"/>
+      <c r="BH104" s="1"/>
+      <c r="BI104" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10853,7 +11268,9 @@
       <c r="BD105" s="1"/>
       <c r="BE105" s="1"/>
       <c r="BF105" s="1"/>
-      <c r="BG105" s="1" t="str">
+      <c r="BG105" s="1"/>
+      <c r="BH105" s="1"/>
+      <c r="BI105" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10920,7 +11337,9 @@
       <c r="BD106" s="1"/>
       <c r="BE106" s="1"/>
       <c r="BF106" s="1"/>
-      <c r="BG106" s="1" t="str">
+      <c r="BG106" s="1"/>
+      <c r="BH106" s="1"/>
+      <c r="BI106" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10987,7 +11406,9 @@
       <c r="BD107" s="1"/>
       <c r="BE107" s="1"/>
       <c r="BF107" s="1"/>
-      <c r="BG107" s="1" t="str">
+      <c r="BG107" s="1"/>
+      <c r="BH107" s="1"/>
+      <c r="BI107" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11054,7 +11475,9 @@
       <c r="BD108" s="1"/>
       <c r="BE108" s="1"/>
       <c r="BF108" s="1"/>
-      <c r="BG108" s="1" t="str">
+      <c r="BG108" s="1"/>
+      <c r="BH108" s="1"/>
+      <c r="BI108" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11121,7 +11544,9 @@
       <c r="BD109" s="1"/>
       <c r="BE109" s="1"/>
       <c r="BF109" s="1"/>
-      <c r="BG109" s="1" t="str">
+      <c r="BG109" s="1"/>
+      <c r="BH109" s="1"/>
+      <c r="BI109" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11188,7 +11613,9 @@
       <c r="BD110" s="1"/>
       <c r="BE110" s="1"/>
       <c r="BF110" s="1"/>
-      <c r="BG110" s="1" t="str">
+      <c r="BG110" s="1"/>
+      <c r="BH110" s="1"/>
+      <c r="BI110" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11255,7 +11682,9 @@
       <c r="BD111" s="1"/>
       <c r="BE111" s="1"/>
       <c r="BF111" s="1"/>
-      <c r="BG111" s="1" t="str">
+      <c r="BG111" s="1"/>
+      <c r="BH111" s="1"/>
+      <c r="BI111" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11322,7 +11751,9 @@
       <c r="BD112" s="1"/>
       <c r="BE112" s="1"/>
       <c r="BF112" s="1"/>
-      <c r="BG112" s="1" t="str">
+      <c r="BG112" s="1"/>
+      <c r="BH112" s="1"/>
+      <c r="BI112" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11389,7 +11820,9 @@
       <c r="BD113" s="1"/>
       <c r="BE113" s="1"/>
       <c r="BF113" s="1"/>
-      <c r="BG113" s="1" t="str">
+      <c r="BG113" s="1"/>
+      <c r="BH113" s="1"/>
+      <c r="BI113" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11456,7 +11889,9 @@
       <c r="BD114" s="1"/>
       <c r="BE114" s="1"/>
       <c r="BF114" s="1"/>
-      <c r="BG114" s="1" t="str">
+      <c r="BG114" s="1"/>
+      <c r="BH114" s="1"/>
+      <c r="BI114" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11523,7 +11958,9 @@
       <c r="BD115" s="1"/>
       <c r="BE115" s="1"/>
       <c r="BF115" s="1"/>
-      <c r="BG115" s="1" t="str">
+      <c r="BG115" s="1"/>
+      <c r="BH115" s="1"/>
+      <c r="BI115" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11590,7 +12027,9 @@
       <c r="BD116" s="1"/>
       <c r="BE116" s="1"/>
       <c r="BF116" s="1"/>
-      <c r="BG116" s="1" t="str">
+      <c r="BG116" s="1"/>
+      <c r="BH116" s="1"/>
+      <c r="BI116" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11657,7 +12096,9 @@
       <c r="BD117" s="1"/>
       <c r="BE117" s="1"/>
       <c r="BF117" s="1"/>
-      <c r="BG117" s="1" t="str">
+      <c r="BG117" s="1"/>
+      <c r="BH117" s="1"/>
+      <c r="BI117" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11724,7 +12165,9 @@
       <c r="BD118" s="1"/>
       <c r="BE118" s="1"/>
       <c r="BF118" s="1"/>
-      <c r="BG118" s="1" t="str">
+      <c r="BG118" s="1"/>
+      <c r="BH118" s="1"/>
+      <c r="BI118" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11791,7 +12234,9 @@
       <c r="BD119" s="1"/>
       <c r="BE119" s="1"/>
       <c r="BF119" s="1"/>
-      <c r="BG119" s="1" t="str">
+      <c r="BG119" s="1"/>
+      <c r="BH119" s="1"/>
+      <c r="BI119" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11858,7 +12303,9 @@
       <c r="BD120" s="1"/>
       <c r="BE120" s="1"/>
       <c r="BF120" s="1"/>
-      <c r="BG120" s="1" t="str">
+      <c r="BG120" s="1"/>
+      <c r="BH120" s="1"/>
+      <c r="BI120" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11925,7 +12372,9 @@
       <c r="BD121" s="1"/>
       <c r="BE121" s="1"/>
       <c r="BF121" s="1"/>
-      <c r="BG121" s="1" t="str">
+      <c r="BG121" s="1"/>
+      <c r="BH121" s="1"/>
+      <c r="BI121" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11992,7 +12441,9 @@
       <c r="BD122" s="1"/>
       <c r="BE122" s="1"/>
       <c r="BF122" s="1"/>
-      <c r="BG122" s="1" t="str">
+      <c r="BG122" s="1"/>
+      <c r="BH122" s="1"/>
+      <c r="BI122" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12059,7 +12510,9 @@
       <c r="BD123" s="1"/>
       <c r="BE123" s="1"/>
       <c r="BF123" s="1"/>
-      <c r="BG123" s="1" t="str">
+      <c r="BG123" s="1"/>
+      <c r="BH123" s="1"/>
+      <c r="BI123" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12126,7 +12579,9 @@
       <c r="BD124" s="1"/>
       <c r="BE124" s="1"/>
       <c r="BF124" s="1"/>
-      <c r="BG124" s="1" t="str">
+      <c r="BG124" s="1"/>
+      <c r="BH124" s="1"/>
+      <c r="BI124" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12193,7 +12648,9 @@
       <c r="BD125" s="1"/>
       <c r="BE125" s="1"/>
       <c r="BF125" s="1"/>
-      <c r="BG125" s="1" t="str">
+      <c r="BG125" s="1"/>
+      <c r="BH125" s="1"/>
+      <c r="BI125" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12260,7 +12717,9 @@
       <c r="BD126" s="1"/>
       <c r="BE126" s="1"/>
       <c r="BF126" s="1"/>
-      <c r="BG126" s="1" t="str">
+      <c r="BG126" s="1"/>
+      <c r="BH126" s="1"/>
+      <c r="BI126" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12327,7 +12786,9 @@
       <c r="BD127" s="1"/>
       <c r="BE127" s="1"/>
       <c r="BF127" s="1"/>
-      <c r="BG127" s="1" t="str">
+      <c r="BG127" s="1"/>
+      <c r="BH127" s="1"/>
+      <c r="BI127" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12394,7 +12855,9 @@
       <c r="BD128" s="1"/>
       <c r="BE128" s="1"/>
       <c r="BF128" s="1"/>
-      <c r="BG128" s="1" t="str">
+      <c r="BG128" s="1"/>
+      <c r="BH128" s="1"/>
+      <c r="BI128" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12461,7 +12924,9 @@
       <c r="BD129" s="1"/>
       <c r="BE129" s="1"/>
       <c r="BF129" s="1"/>
-      <c r="BG129" s="1" t="str">
+      <c r="BG129" s="1"/>
+      <c r="BH129" s="1"/>
+      <c r="BI129" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12528,7 +12993,9 @@
       <c r="BD130" s="1"/>
       <c r="BE130" s="1"/>
       <c r="BF130" s="1"/>
-      <c r="BG130" s="1" t="str">
+      <c r="BG130" s="1"/>
+      <c r="BH130" s="1"/>
+      <c r="BI130" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12595,7 +13062,9 @@
       <c r="BD131" s="1"/>
       <c r="BE131" s="1"/>
       <c r="BF131" s="1"/>
-      <c r="BG131" s="1" t="str">
+      <c r="BG131" s="1"/>
+      <c r="BH131" s="1"/>
+      <c r="BI131" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12662,7 +13131,9 @@
       <c r="BD132" s="1"/>
       <c r="BE132" s="1"/>
       <c r="BF132" s="1"/>
-      <c r="BG132" s="1" t="str">
+      <c r="BG132" s="1"/>
+      <c r="BH132" s="1"/>
+      <c r="BI132" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12729,7 +13200,9 @@
       <c r="BD133" s="1"/>
       <c r="BE133" s="1"/>
       <c r="BF133" s="1"/>
-      <c r="BG133" s="1" t="str">
+      <c r="BG133" s="1"/>
+      <c r="BH133" s="1"/>
+      <c r="BI133" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12796,7 +13269,9 @@
       <c r="BD134" s="1"/>
       <c r="BE134" s="1"/>
       <c r="BF134" s="1"/>
-      <c r="BG134" s="1" t="str">
+      <c r="BG134" s="1"/>
+      <c r="BH134" s="1"/>
+      <c r="BI134" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12863,7 +13338,9 @@
       <c r="BD135" s="1"/>
       <c r="BE135" s="1"/>
       <c r="BF135" s="1"/>
-      <c r="BG135" s="1" t="str">
+      <c r="BG135" s="1"/>
+      <c r="BH135" s="1"/>
+      <c r="BI135" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12930,7 +13407,9 @@
       <c r="BD136" s="1"/>
       <c r="BE136" s="1"/>
       <c r="BF136" s="1"/>
-      <c r="BG136" s="1" t="str">
+      <c r="BG136" s="1"/>
+      <c r="BH136" s="1"/>
+      <c r="BI136" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12997,7 +13476,9 @@
       <c r="BD137" s="1"/>
       <c r="BE137" s="1"/>
       <c r="BF137" s="1"/>
-      <c r="BG137" s="1" t="str">
+      <c r="BG137" s="1"/>
+      <c r="BH137" s="1"/>
+      <c r="BI137" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13064,7 +13545,9 @@
       <c r="BD138" s="1"/>
       <c r="BE138" s="1"/>
       <c r="BF138" s="1"/>
-      <c r="BG138" s="1" t="str">
+      <c r="BG138" s="1"/>
+      <c r="BH138" s="1"/>
+      <c r="BI138" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13131,7 +13614,9 @@
       <c r="BD139" s="1"/>
       <c r="BE139" s="1"/>
       <c r="BF139" s="1"/>
-      <c r="BG139" s="1" t="str">
+      <c r="BG139" s="1"/>
+      <c r="BH139" s="1"/>
+      <c r="BI139" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13198,7 +13683,9 @@
       <c r="BD140" s="1"/>
       <c r="BE140" s="1"/>
       <c r="BF140" s="1"/>
-      <c r="BG140" s="1" t="str">
+      <c r="BG140" s="1"/>
+      <c r="BH140" s="1"/>
+      <c r="BI140" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13265,7 +13752,9 @@
       <c r="BD141" s="1"/>
       <c r="BE141" s="1"/>
       <c r="BF141" s="1"/>
-      <c r="BG141" s="1" t="str">
+      <c r="BG141" s="1"/>
+      <c r="BH141" s="1"/>
+      <c r="BI141" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13332,7 +13821,9 @@
       <c r="BD142" s="1"/>
       <c r="BE142" s="1"/>
       <c r="BF142" s="1"/>
-      <c r="BG142" s="1" t="str">
+      <c r="BG142" s="1"/>
+      <c r="BH142" s="1"/>
+      <c r="BI142" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13399,7 +13890,9 @@
       <c r="BD143" s="1"/>
       <c r="BE143" s="1"/>
       <c r="BF143" s="1"/>
-      <c r="BG143" s="1" t="str">
+      <c r="BG143" s="1"/>
+      <c r="BH143" s="1"/>
+      <c r="BI143" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13466,7 +13959,9 @@
       <c r="BD144" s="1"/>
       <c r="BE144" s="1"/>
       <c r="BF144" s="1"/>
-      <c r="BG144" s="1" t="str">
+      <c r="BG144" s="1"/>
+      <c r="BH144" s="1"/>
+      <c r="BI144" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13533,7 +14028,9 @@
       <c r="BD145" s="1"/>
       <c r="BE145" s="1"/>
       <c r="BF145" s="1"/>
-      <c r="BG145" s="1" t="str">
+      <c r="BG145" s="1"/>
+      <c r="BH145" s="1"/>
+      <c r="BI145" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13600,7 +14097,9 @@
       <c r="BD146" s="1"/>
       <c r="BE146" s="1"/>
       <c r="BF146" s="1"/>
-      <c r="BG146" s="1" t="str">
+      <c r="BG146" s="1"/>
+      <c r="BH146" s="1"/>
+      <c r="BI146" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13667,7 +14166,9 @@
       <c r="BD147" s="1"/>
       <c r="BE147" s="1"/>
       <c r="BF147" s="1"/>
-      <c r="BG147" s="1" t="str">
+      <c r="BG147" s="1"/>
+      <c r="BH147" s="1"/>
+      <c r="BI147" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13734,7 +14235,9 @@
       <c r="BD148" s="1"/>
       <c r="BE148" s="1"/>
       <c r="BF148" s="1"/>
-      <c r="BG148" s="1" t="str">
+      <c r="BG148" s="1"/>
+      <c r="BH148" s="1"/>
+      <c r="BI148" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13801,7 +14304,9 @@
       <c r="BD149" s="1"/>
       <c r="BE149" s="1"/>
       <c r="BF149" s="1"/>
-      <c r="BG149" s="1" t="str">
+      <c r="BG149" s="1"/>
+      <c r="BH149" s="1"/>
+      <c r="BI149" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13868,7 +14373,9 @@
       <c r="BD150" s="1"/>
       <c r="BE150" s="1"/>
       <c r="BF150" s="1"/>
-      <c r="BG150" s="1" t="str">
+      <c r="BG150" s="1"/>
+      <c r="BH150" s="1"/>
+      <c r="BI150" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13935,7 +14442,9 @@
       <c r="BD151" s="1"/>
       <c r="BE151" s="1"/>
       <c r="BF151" s="1"/>
-      <c r="BG151" s="1" t="str">
+      <c r="BG151" s="1"/>
+      <c r="BH151" s="1"/>
+      <c r="BI151" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14002,7 +14511,9 @@
       <c r="BD152" s="1"/>
       <c r="BE152" s="1"/>
       <c r="BF152" s="1"/>
-      <c r="BG152" s="1" t="str">
+      <c r="BG152" s="1"/>
+      <c r="BH152" s="1"/>
+      <c r="BI152" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14069,7 +14580,9 @@
       <c r="BD153" s="1"/>
       <c r="BE153" s="1"/>
       <c r="BF153" s="1"/>
-      <c r="BG153" s="1" t="str">
+      <c r="BG153" s="1"/>
+      <c r="BH153" s="1"/>
+      <c r="BI153" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14136,7 +14649,9 @@
       <c r="BD154" s="1"/>
       <c r="BE154" s="1"/>
       <c r="BF154" s="1"/>
-      <c r="BG154" s="1" t="str">
+      <c r="BG154" s="1"/>
+      <c r="BH154" s="1"/>
+      <c r="BI154" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14203,7 +14718,9 @@
       <c r="BD155" s="1"/>
       <c r="BE155" s="1"/>
       <c r="BF155" s="1"/>
-      <c r="BG155" s="1" t="str">
+      <c r="BG155" s="1"/>
+      <c r="BH155" s="1"/>
+      <c r="BI155" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14270,7 +14787,9 @@
       <c r="BD156" s="1"/>
       <c r="BE156" s="1"/>
       <c r="BF156" s="1"/>
-      <c r="BG156" s="1" t="str">
+      <c r="BG156" s="1"/>
+      <c r="BH156" s="1"/>
+      <c r="BI156" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14337,7 +14856,9 @@
       <c r="BD157" s="1"/>
       <c r="BE157" s="1"/>
       <c r="BF157" s="1"/>
-      <c r="BG157" s="1" t="str">
+      <c r="BG157" s="1"/>
+      <c r="BH157" s="1"/>
+      <c r="BI157" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14404,7 +14925,9 @@
       <c r="BD158" s="1"/>
       <c r="BE158" s="1"/>
       <c r="BF158" s="1"/>
-      <c r="BG158" s="1" t="str">
+      <c r="BG158" s="1"/>
+      <c r="BH158" s="1"/>
+      <c r="BI158" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14471,7 +14994,9 @@
       <c r="BD159" s="1"/>
       <c r="BE159" s="1"/>
       <c r="BF159" s="1"/>
-      <c r="BG159" s="1" t="str">
+      <c r="BG159" s="1"/>
+      <c r="BH159" s="1"/>
+      <c r="BI159" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14538,7 +15063,9 @@
       <c r="BD160" s="1"/>
       <c r="BE160" s="1"/>
       <c r="BF160" s="1"/>
-      <c r="BG160" s="1" t="str">
+      <c r="BG160" s="1"/>
+      <c r="BH160" s="1"/>
+      <c r="BI160" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14605,7 +15132,9 @@
       <c r="BD161" s="1"/>
       <c r="BE161" s="1"/>
       <c r="BF161" s="1"/>
-      <c r="BG161" s="1" t="str">
+      <c r="BG161" s="1"/>
+      <c r="BH161" s="1"/>
+      <c r="BI161" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14672,7 +15201,9 @@
       <c r="BD162" s="1"/>
       <c r="BE162" s="1"/>
       <c r="BF162" s="1"/>
-      <c r="BG162" s="1" t="str">
+      <c r="BG162" s="1"/>
+      <c r="BH162" s="1"/>
+      <c r="BI162" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14739,7 +15270,9 @@
       <c r="BD163" s="1"/>
       <c r="BE163" s="1"/>
       <c r="BF163" s="1"/>
-      <c r="BG163" s="1" t="str">
+      <c r="BG163" s="1"/>
+      <c r="BH163" s="1"/>
+      <c r="BI163" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14806,7 +15339,9 @@
       <c r="BD164" s="1"/>
       <c r="BE164" s="1"/>
       <c r="BF164" s="1"/>
-      <c r="BG164" s="1" t="str">
+      <c r="BG164" s="1"/>
+      <c r="BH164" s="1"/>
+      <c r="BI164" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14873,7 +15408,9 @@
       <c r="BD165" s="1"/>
       <c r="BE165" s="1"/>
       <c r="BF165" s="1"/>
-      <c r="BG165" s="1" t="str">
+      <c r="BG165" s="1"/>
+      <c r="BH165" s="1"/>
+      <c r="BI165" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14940,7 +15477,9 @@
       <c r="BD166" s="1"/>
       <c r="BE166" s="1"/>
       <c r="BF166" s="1"/>
-      <c r="BG166" s="1" t="str">
+      <c r="BG166" s="1"/>
+      <c r="BH166" s="1"/>
+      <c r="BI166" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15007,7 +15546,9 @@
       <c r="BD167" s="1"/>
       <c r="BE167" s="1"/>
       <c r="BF167" s="1"/>
-      <c r="BG167" s="1" t="str">
+      <c r="BG167" s="1"/>
+      <c r="BH167" s="1"/>
+      <c r="BI167" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15074,7 +15615,9 @@
       <c r="BD168" s="1"/>
       <c r="BE168" s="1"/>
       <c r="BF168" s="1"/>
-      <c r="BG168" s="1" t="str">
+      <c r="BG168" s="1"/>
+      <c r="BH168" s="1"/>
+      <c r="BI168" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15141,7 +15684,9 @@
       <c r="BD169" s="1"/>
       <c r="BE169" s="1"/>
       <c r="BF169" s="1"/>
-      <c r="BG169" s="1" t="str">
+      <c r="BG169" s="1"/>
+      <c r="BH169" s="1"/>
+      <c r="BI169" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15208,7 +15753,9 @@
       <c r="BD170" s="1"/>
       <c r="BE170" s="1"/>
       <c r="BF170" s="1"/>
-      <c r="BG170" s="1" t="str">
+      <c r="BG170" s="1"/>
+      <c r="BH170" s="1"/>
+      <c r="BI170" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15275,7 +15822,9 @@
       <c r="BD171" s="1"/>
       <c r="BE171" s="1"/>
       <c r="BF171" s="1"/>
-      <c r="BG171" s="1" t="str">
+      <c r="BG171" s="1"/>
+      <c r="BH171" s="1"/>
+      <c r="BI171" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15342,7 +15891,9 @@
       <c r="BD172" s="1"/>
       <c r="BE172" s="1"/>
       <c r="BF172" s="1"/>
-      <c r="BG172" s="1" t="str">
+      <c r="BG172" s="1"/>
+      <c r="BH172" s="1"/>
+      <c r="BI172" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15409,7 +15960,9 @@
       <c r="BD173" s="1"/>
       <c r="BE173" s="1"/>
       <c r="BF173" s="1"/>
-      <c r="BG173" s="1" t="str">
+      <c r="BG173" s="1"/>
+      <c r="BH173" s="1"/>
+      <c r="BI173" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15476,7 +16029,9 @@
       <c r="BD174" s="1"/>
       <c r="BE174" s="1"/>
       <c r="BF174" s="1"/>
-      <c r="BG174" s="1" t="str">
+      <c r="BG174" s="1"/>
+      <c r="BH174" s="1"/>
+      <c r="BI174" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15543,7 +16098,9 @@
       <c r="BD175" s="1"/>
       <c r="BE175" s="1"/>
       <c r="BF175" s="1"/>
-      <c r="BG175" s="1" t="str">
+      <c r="BG175" s="1"/>
+      <c r="BH175" s="1"/>
+      <c r="BI175" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15610,7 +16167,9 @@
       <c r="BD176" s="1"/>
       <c r="BE176" s="1"/>
       <c r="BF176" s="1"/>
-      <c r="BG176" s="1" t="str">
+      <c r="BG176" s="1"/>
+      <c r="BH176" s="1"/>
+      <c r="BI176" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15677,7 +16236,9 @@
       <c r="BD177" s="1"/>
       <c r="BE177" s="1"/>
       <c r="BF177" s="1"/>
-      <c r="BG177" s="1" t="str">
+      <c r="BG177" s="1"/>
+      <c r="BH177" s="1"/>
+      <c r="BI177" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15744,7 +16305,9 @@
       <c r="BD178" s="1"/>
       <c r="BE178" s="1"/>
       <c r="BF178" s="1"/>
-      <c r="BG178" s="1" t="str">
+      <c r="BG178" s="1"/>
+      <c r="BH178" s="1"/>
+      <c r="BI178" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15811,7 +16374,9 @@
       <c r="BD179" s="1"/>
       <c r="BE179" s="1"/>
       <c r="BF179" s="1"/>
-      <c r="BG179" s="1" t="str">
+      <c r="BG179" s="1"/>
+      <c r="BH179" s="1"/>
+      <c r="BI179" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15878,7 +16443,9 @@
       <c r="BD180" s="1"/>
       <c r="BE180" s="1"/>
       <c r="BF180" s="1"/>
-      <c r="BG180" s="1" t="str">
+      <c r="BG180" s="1"/>
+      <c r="BH180" s="1"/>
+      <c r="BI180" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15945,7 +16512,9 @@
       <c r="BD181" s="1"/>
       <c r="BE181" s="1"/>
       <c r="BF181" s="1"/>
-      <c r="BG181" s="1" t="str">
+      <c r="BG181" s="1"/>
+      <c r="BH181" s="1"/>
+      <c r="BI181" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16012,7 +16581,9 @@
       <c r="BD182" s="1"/>
       <c r="BE182" s="1"/>
       <c r="BF182" s="1"/>
-      <c r="BG182" s="1" t="str">
+      <c r="BG182" s="1"/>
+      <c r="BH182" s="1"/>
+      <c r="BI182" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16079,7 +16650,9 @@
       <c r="BD183" s="1"/>
       <c r="BE183" s="1"/>
       <c r="BF183" s="1"/>
-      <c r="BG183" s="1" t="str">
+      <c r="BG183" s="1"/>
+      <c r="BH183" s="1"/>
+      <c r="BI183" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16146,7 +16719,9 @@
       <c r="BD184" s="1"/>
       <c r="BE184" s="1"/>
       <c r="BF184" s="1"/>
-      <c r="BG184" s="1" t="str">
+      <c r="BG184" s="1"/>
+      <c r="BH184" s="1"/>
+      <c r="BI184" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16213,7 +16788,9 @@
       <c r="BD185" s="1"/>
       <c r="BE185" s="1"/>
       <c r="BF185" s="1"/>
-      <c r="BG185" s="1" t="str">
+      <c r="BG185" s="1"/>
+      <c r="BH185" s="1"/>
+      <c r="BI185" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16280,7 +16857,9 @@
       <c r="BD186" s="1"/>
       <c r="BE186" s="1"/>
       <c r="BF186" s="1"/>
-      <c r="BG186" s="1" t="str">
+      <c r="BG186" s="1"/>
+      <c r="BH186" s="1"/>
+      <c r="BI186" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16347,7 +16926,9 @@
       <c r="BD187" s="1"/>
       <c r="BE187" s="1"/>
       <c r="BF187" s="1"/>
-      <c r="BG187" s="1" t="str">
+      <c r="BG187" s="1"/>
+      <c r="BH187" s="1"/>
+      <c r="BI187" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16414,7 +16995,9 @@
       <c r="BD188" s="1"/>
       <c r="BE188" s="1"/>
       <c r="BF188" s="1"/>
-      <c r="BG188" s="1" t="str">
+      <c r="BG188" s="1"/>
+      <c r="BH188" s="1"/>
+      <c r="BI188" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16481,7 +17064,9 @@
       <c r="BD189" s="1"/>
       <c r="BE189" s="1"/>
       <c r="BF189" s="1"/>
-      <c r="BG189" s="1" t="str">
+      <c r="BG189" s="1"/>
+      <c r="BH189" s="1"/>
+      <c r="BI189" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16548,7 +17133,9 @@
       <c r="BD190" s="1"/>
       <c r="BE190" s="1"/>
       <c r="BF190" s="1"/>
-      <c r="BG190" s="1" t="str">
+      <c r="BG190" s="1"/>
+      <c r="BH190" s="1"/>
+      <c r="BI190" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16615,7 +17202,9 @@
       <c r="BD191" s="1"/>
       <c r="BE191" s="1"/>
       <c r="BF191" s="1"/>
-      <c r="BG191" s="1" t="str">
+      <c r="BG191" s="1"/>
+      <c r="BH191" s="1"/>
+      <c r="BI191" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16682,7 +17271,9 @@
       <c r="BD192" s="1"/>
       <c r="BE192" s="1"/>
       <c r="BF192" s="1"/>
-      <c r="BG192" s="1" t="str">
+      <c r="BG192" s="1"/>
+      <c r="BH192" s="1"/>
+      <c r="BI192" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16749,7 +17340,9 @@
       <c r="BD193" s="1"/>
       <c r="BE193" s="1"/>
       <c r="BF193" s="1"/>
-      <c r="BG193" s="1" t="str">
+      <c r="BG193" s="1"/>
+      <c r="BH193" s="1"/>
+      <c r="BI193" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16816,7 +17409,9 @@
       <c r="BD194" s="1"/>
       <c r="BE194" s="1"/>
       <c r="BF194" s="1"/>
-      <c r="BG194" s="1" t="str">
+      <c r="BG194" s="1"/>
+      <c r="BH194" s="1"/>
+      <c r="BI194" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16883,7 +17478,9 @@
       <c r="BD195" s="1"/>
       <c r="BE195" s="1"/>
       <c r="BF195" s="1"/>
-      <c r="BG195" s="1" t="str">
+      <c r="BG195" s="1"/>
+      <c r="BH195" s="1"/>
+      <c r="BI195" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16950,7 +17547,9 @@
       <c r="BD196" s="1"/>
       <c r="BE196" s="1"/>
       <c r="BF196" s="1"/>
-      <c r="BG196" s="1" t="str">
+      <c r="BG196" s="1"/>
+      <c r="BH196" s="1"/>
+      <c r="BI196" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17017,7 +17616,9 @@
       <c r="BD197" s="1"/>
       <c r="BE197" s="1"/>
       <c r="BF197" s="1"/>
-      <c r="BG197" s="1" t="str">
+      <c r="BG197" s="1"/>
+      <c r="BH197" s="1"/>
+      <c r="BI197" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17084,7 +17685,9 @@
       <c r="BD198" s="1"/>
       <c r="BE198" s="1"/>
       <c r="BF198" s="1"/>
-      <c r="BG198" s="1" t="str">
+      <c r="BG198" s="1"/>
+      <c r="BH198" s="1"/>
+      <c r="BI198" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17151,7 +17754,9 @@
       <c r="BD199" s="1"/>
       <c r="BE199" s="1"/>
       <c r="BF199" s="1"/>
-      <c r="BG199" s="1" t="str">
+      <c r="BG199" s="1"/>
+      <c r="BH199" s="1"/>
+      <c r="BI199" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17218,7 +17823,9 @@
       <c r="BD200" s="1"/>
       <c r="BE200" s="1"/>
       <c r="BF200" s="1"/>
-      <c r="BG200" s="1" t="str">
+      <c r="BG200" s="1"/>
+      <c r="BH200" s="1"/>
+      <c r="BI200" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17285,7 +17892,9 @@
       <c r="BD201" s="1"/>
       <c r="BE201" s="1"/>
       <c r="BF201" s="1"/>
-      <c r="BG201" s="1" t="str">
+      <c r="BG201" s="1"/>
+      <c r="BH201" s="1"/>
+      <c r="BI201" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17352,7 +17961,9 @@
       <c r="BD202" s="1"/>
       <c r="BE202" s="1"/>
       <c r="BF202" s="1"/>
-      <c r="BG202" s="1" t="str">
+      <c r="BG202" s="1"/>
+      <c r="BH202" s="1"/>
+      <c r="BI202" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17419,7 +18030,9 @@
       <c r="BD203" s="1"/>
       <c r="BE203" s="1"/>
       <c r="BF203" s="1"/>
-      <c r="BG203" s="1" t="str">
+      <c r="BG203" s="1"/>
+      <c r="BH203" s="1"/>
+      <c r="BI203" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17486,7 +18099,9 @@
       <c r="BD204" s="1"/>
       <c r="BE204" s="1"/>
       <c r="BF204" s="1"/>
-      <c r="BG204" s="1" t="str">
+      <c r="BG204" s="1"/>
+      <c r="BH204" s="1"/>
+      <c r="BI204" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17553,7 +18168,9 @@
       <c r="BD205" s="1"/>
       <c r="BE205" s="1"/>
       <c r="BF205" s="1"/>
-      <c r="BG205" s="1" t="str">
+      <c r="BG205" s="1"/>
+      <c r="BH205" s="1"/>
+      <c r="BI205" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17620,7 +18237,9 @@
       <c r="BD206" s="1"/>
       <c r="BE206" s="1"/>
       <c r="BF206" s="1"/>
-      <c r="BG206" s="1" t="str">
+      <c r="BG206" s="1"/>
+      <c r="BH206" s="1"/>
+      <c r="BI206" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17687,7 +18306,9 @@
       <c r="BD207" s="1"/>
       <c r="BE207" s="1"/>
       <c r="BF207" s="1"/>
-      <c r="BG207" s="1" t="str">
+      <c r="BG207" s="1"/>
+      <c r="BH207" s="1"/>
+      <c r="BI207" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17754,7 +18375,9 @@
       <c r="BD208" s="1"/>
       <c r="BE208" s="1"/>
       <c r="BF208" s="1"/>
-      <c r="BG208" s="1" t="str">
+      <c r="BG208" s="1"/>
+      <c r="BH208" s="1"/>
+      <c r="BI208" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17821,7 +18444,9 @@
       <c r="BD209" s="1"/>
       <c r="BE209" s="1"/>
       <c r="BF209" s="1"/>
-      <c r="BG209" s="1" t="str">
+      <c r="BG209" s="1"/>
+      <c r="BH209" s="1"/>
+      <c r="BI209" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17888,7 +18513,9 @@
       <c r="BD210" s="1"/>
       <c r="BE210" s="1"/>
       <c r="BF210" s="1"/>
-      <c r="BG210" s="1" t="str">
+      <c r="BG210" s="1"/>
+      <c r="BH210" s="1"/>
+      <c r="BI210" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17955,7 +18582,9 @@
       <c r="BD211" s="1"/>
       <c r="BE211" s="1"/>
       <c r="BF211" s="1"/>
-      <c r="BG211" s="1" t="str">
+      <c r="BG211" s="1"/>
+      <c r="BH211" s="1"/>
+      <c r="BI211" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18022,7 +18651,9 @@
       <c r="BD212" s="1"/>
       <c r="BE212" s="1"/>
       <c r="BF212" s="1"/>
-      <c r="BG212" s="1" t="str">
+      <c r="BG212" s="1"/>
+      <c r="BH212" s="1"/>
+      <c r="BI212" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18089,7 +18720,9 @@
       <c r="BD213" s="1"/>
       <c r="BE213" s="1"/>
       <c r="BF213" s="1"/>
-      <c r="BG213" s="1" t="str">
+      <c r="BG213" s="1"/>
+      <c r="BH213" s="1"/>
+      <c r="BI213" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18156,7 +18789,9 @@
       <c r="BD214" s="1"/>
       <c r="BE214" s="1"/>
       <c r="BF214" s="1"/>
-      <c r="BG214" s="1" t="str">
+      <c r="BG214" s="1"/>
+      <c r="BH214" s="1"/>
+      <c r="BI214" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18223,7 +18858,9 @@
       <c r="BD215" s="1"/>
       <c r="BE215" s="1"/>
       <c r="BF215" s="1"/>
-      <c r="BG215" s="1" t="str">
+      <c r="BG215" s="1"/>
+      <c r="BH215" s="1"/>
+      <c r="BI215" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18290,7 +18927,9 @@
       <c r="BD216" s="1"/>
       <c r="BE216" s="1"/>
       <c r="BF216" s="1"/>
-      <c r="BG216" s="1" t="str">
+      <c r="BG216" s="1"/>
+      <c r="BH216" s="1"/>
+      <c r="BI216" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18357,7 +18996,9 @@
       <c r="BD217" s="1"/>
       <c r="BE217" s="1"/>
       <c r="BF217" s="1"/>
-      <c r="BG217" s="1" t="str">
+      <c r="BG217" s="1"/>
+      <c r="BH217" s="1"/>
+      <c r="BI217" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18424,7 +19065,9 @@
       <c r="BD218" s="1"/>
       <c r="BE218" s="1"/>
       <c r="BF218" s="1"/>
-      <c r="BG218" s="1" t="str">
+      <c r="BG218" s="1"/>
+      <c r="BH218" s="1"/>
+      <c r="BI218" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18491,7 +19134,9 @@
       <c r="BD219" s="1"/>
       <c r="BE219" s="1"/>
       <c r="BF219" s="1"/>
-      <c r="BG219" s="1" t="str">
+      <c r="BG219" s="1"/>
+      <c r="BH219" s="1"/>
+      <c r="BI219" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18558,7 +19203,9 @@
       <c r="BD220" s="1"/>
       <c r="BE220" s="1"/>
       <c r="BF220" s="1"/>
-      <c r="BG220" s="1" t="str">
+      <c r="BG220" s="1"/>
+      <c r="BH220" s="1"/>
+      <c r="BI220" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18625,7 +19272,9 @@
       <c r="BD221" s="1"/>
       <c r="BE221" s="1"/>
       <c r="BF221" s="1"/>
-      <c r="BG221" s="1" t="str">
+      <c r="BG221" s="1"/>
+      <c r="BH221" s="1"/>
+      <c r="BI221" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18692,7 +19341,9 @@
       <c r="BD222" s="1"/>
       <c r="BE222" s="1"/>
       <c r="BF222" s="1"/>
-      <c r="BG222" s="1" t="str">
+      <c r="BG222" s="1"/>
+      <c r="BH222" s="1"/>
+      <c r="BI222" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18759,7 +19410,9 @@
       <c r="BD223" s="1"/>
       <c r="BE223" s="1"/>
       <c r="BF223" s="1"/>
-      <c r="BG223" s="1" t="str">
+      <c r="BG223" s="1"/>
+      <c r="BH223" s="1"/>
+      <c r="BI223" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18826,7 +19479,9 @@
       <c r="BD224" s="1"/>
       <c r="BE224" s="1"/>
       <c r="BF224" s="1"/>
-      <c r="BG224" s="1" t="str">
+      <c r="BG224" s="1"/>
+      <c r="BH224" s="1"/>
+      <c r="BI224" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18893,7 +19548,9 @@
       <c r="BD225" s="1"/>
       <c r="BE225" s="1"/>
       <c r="BF225" s="1"/>
-      <c r="BG225" s="1" t="str">
+      <c r="BG225" s="1"/>
+      <c r="BH225" s="1"/>
+      <c r="BI225" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18960,7 +19617,9 @@
       <c r="BD226" s="1"/>
       <c r="BE226" s="1"/>
       <c r="BF226" s="1"/>
-      <c r="BG226" s="1" t="str">
+      <c r="BG226" s="1"/>
+      <c r="BH226" s="1"/>
+      <c r="BI226" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19027,7 +19686,9 @@
       <c r="BD227" s="1"/>
       <c r="BE227" s="1"/>
       <c r="BF227" s="1"/>
-      <c r="BG227" s="1" t="str">
+      <c r="BG227" s="1"/>
+      <c r="BH227" s="1"/>
+      <c r="BI227" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19094,7 +19755,9 @@
       <c r="BD228" s="1"/>
       <c r="BE228" s="1"/>
       <c r="BF228" s="1"/>
-      <c r="BG228" s="1" t="str">
+      <c r="BG228" s="1"/>
+      <c r="BH228" s="1"/>
+      <c r="BI228" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19161,7 +19824,9 @@
       <c r="BD229" s="1"/>
       <c r="BE229" s="1"/>
       <c r="BF229" s="1"/>
-      <c r="BG229" s="1" t="str">
+      <c r="BG229" s="1"/>
+      <c r="BH229" s="1"/>
+      <c r="BI229" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19228,7 +19893,9 @@
       <c r="BD230" s="1"/>
       <c r="BE230" s="1"/>
       <c r="BF230" s="1"/>
-      <c r="BG230" s="1" t="str">
+      <c r="BG230" s="1"/>
+      <c r="BH230" s="1"/>
+      <c r="BI230" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19295,7 +19962,9 @@
       <c r="BD231" s="1"/>
       <c r="BE231" s="1"/>
       <c r="BF231" s="1"/>
-      <c r="BG231" s="1" t="str">
+      <c r="BG231" s="1"/>
+      <c r="BH231" s="1"/>
+      <c r="BI231" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19362,7 +20031,9 @@
       <c r="BD232" s="1"/>
       <c r="BE232" s="1"/>
       <c r="BF232" s="1"/>
-      <c r="BG232" s="1" t="str">
+      <c r="BG232" s="1"/>
+      <c r="BH232" s="1"/>
+      <c r="BI232" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19429,7 +20100,9 @@
       <c r="BD233" s="1"/>
       <c r="BE233" s="1"/>
       <c r="BF233" s="1"/>
-      <c r="BG233" s="1" t="str">
+      <c r="BG233" s="1"/>
+      <c r="BH233" s="1"/>
+      <c r="BI233" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19496,7 +20169,9 @@
       <c r="BD234" s="1"/>
       <c r="BE234" s="1"/>
       <c r="BF234" s="1"/>
-      <c r="BG234" s="1" t="str">
+      <c r="BG234" s="1"/>
+      <c r="BH234" s="1"/>
+      <c r="BI234" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19563,7 +20238,9 @@
       <c r="BD235" s="1"/>
       <c r="BE235" s="1"/>
       <c r="BF235" s="1"/>
-      <c r="BG235" s="1" t="str">
+      <c r="BG235" s="1"/>
+      <c r="BH235" s="1"/>
+      <c r="BI235" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19630,7 +20307,9 @@
       <c r="BD236" s="1"/>
       <c r="BE236" s="1"/>
       <c r="BF236" s="1"/>
-      <c r="BG236" s="1" t="str">
+      <c r="BG236" s="1"/>
+      <c r="BH236" s="1"/>
+      <c r="BI236" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19697,7 +20376,9 @@
       <c r="BD237" s="1"/>
       <c r="BE237" s="1"/>
       <c r="BF237" s="1"/>
-      <c r="BG237" s="1" t="str">
+      <c r="BG237" s="1"/>
+      <c r="BH237" s="1"/>
+      <c r="BI237" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19764,7 +20445,9 @@
       <c r="BD238" s="1"/>
       <c r="BE238" s="1"/>
       <c r="BF238" s="1"/>
-      <c r="BG238" s="1" t="str">
+      <c r="BG238" s="1"/>
+      <c r="BH238" s="1"/>
+      <c r="BI238" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19831,7 +20514,9 @@
       <c r="BD239" s="1"/>
       <c r="BE239" s="1"/>
       <c r="BF239" s="1"/>
-      <c r="BG239" s="1" t="str">
+      <c r="BG239" s="1"/>
+      <c r="BH239" s="1"/>
+      <c r="BI239" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19898,7 +20583,9 @@
       <c r="BD240" s="1"/>
       <c r="BE240" s="1"/>
       <c r="BF240" s="1"/>
-      <c r="BG240" s="1" t="str">
+      <c r="BG240" s="1"/>
+      <c r="BH240" s="1"/>
+      <c r="BI240" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19965,7 +20652,9 @@
       <c r="BD241" s="1"/>
       <c r="BE241" s="1"/>
       <c r="BF241" s="1"/>
-      <c r="BG241" s="1" t="str">
+      <c r="BG241" s="1"/>
+      <c r="BH241" s="1"/>
+      <c r="BI241" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20032,7 +20721,9 @@
       <c r="BD242" s="1"/>
       <c r="BE242" s="1"/>
       <c r="BF242" s="1"/>
-      <c r="BG242" s="1" t="str">
+      <c r="BG242" s="1"/>
+      <c r="BH242" s="1"/>
+      <c r="BI242" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20099,7 +20790,9 @@
       <c r="BD243" s="1"/>
       <c r="BE243" s="1"/>
       <c r="BF243" s="1"/>
-      <c r="BG243" s="1" t="str">
+      <c r="BG243" s="1"/>
+      <c r="BH243" s="1"/>
+      <c r="BI243" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20166,7 +20859,9 @@
       <c r="BD244" s="1"/>
       <c r="BE244" s="1"/>
       <c r="BF244" s="1"/>
-      <c r="BG244" s="1" t="str">
+      <c r="BG244" s="1"/>
+      <c r="BH244" s="1"/>
+      <c r="BI244" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20233,7 +20928,9 @@
       <c r="BD245" s="1"/>
       <c r="BE245" s="1"/>
       <c r="BF245" s="1"/>
-      <c r="BG245" s="1" t="str">
+      <c r="BG245" s="1"/>
+      <c r="BH245" s="1"/>
+      <c r="BI245" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20300,7 +20997,9 @@
       <c r="BD246" s="1"/>
       <c r="BE246" s="1"/>
       <c r="BF246" s="1"/>
-      <c r="BG246" s="1" t="str">
+      <c r="BG246" s="1"/>
+      <c r="BH246" s="1"/>
+      <c r="BI246" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20367,7 +21066,9 @@
       <c r="BD247" s="1"/>
       <c r="BE247" s="1"/>
       <c r="BF247" s="1"/>
-      <c r="BG247" s="1" t="str">
+      <c r="BG247" s="1"/>
+      <c r="BH247" s="1"/>
+      <c r="BI247" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20434,7 +21135,9 @@
       <c r="BD248" s="1"/>
       <c r="BE248" s="1"/>
       <c r="BF248" s="1"/>
-      <c r="BG248" s="1" t="str">
+      <c r="BG248" s="1"/>
+      <c r="BH248" s="1"/>
+      <c r="BI248" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20501,7 +21204,9 @@
       <c r="BD249" s="1"/>
       <c r="BE249" s="1"/>
       <c r="BF249" s="1"/>
-      <c r="BG249" s="1" t="str">
+      <c r="BG249" s="1"/>
+      <c r="BH249" s="1"/>
+      <c r="BI249" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20568,7 +21273,9 @@
       <c r="BD250" s="1"/>
       <c r="BE250" s="1"/>
       <c r="BF250" s="1"/>
-      <c r="BG250" s="1" t="str">
+      <c r="BG250" s="1"/>
+      <c r="BH250" s="1"/>
+      <c r="BI250" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20635,7 +21342,9 @@
       <c r="BD251" s="1"/>
       <c r="BE251" s="1"/>
       <c r="BF251" s="1"/>
-      <c r="BG251" s="1" t="str">
+      <c r="BG251" s="1"/>
+      <c r="BH251" s="1"/>
+      <c r="BI251" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20702,7 +21411,9 @@
       <c r="BD252" s="1"/>
       <c r="BE252" s="1"/>
       <c r="BF252" s="1"/>
-      <c r="BG252" s="1" t="str">
+      <c r="BG252" s="1"/>
+      <c r="BH252" s="1"/>
+      <c r="BI252" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20769,7 +21480,9 @@
       <c r="BD253" s="1"/>
       <c r="BE253" s="1"/>
       <c r="BF253" s="1"/>
-      <c r="BG253" s="1" t="str">
+      <c r="BG253" s="1"/>
+      <c r="BH253" s="1"/>
+      <c r="BI253" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20836,7 +21549,9 @@
       <c r="BD254" s="1"/>
       <c r="BE254" s="1"/>
       <c r="BF254" s="1"/>
-      <c r="BG254" s="1" t="str">
+      <c r="BG254" s="1"/>
+      <c r="BH254" s="1"/>
+      <c r="BI254" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20903,7 +21618,9 @@
       <c r="BD255" s="1"/>
       <c r="BE255" s="1"/>
       <c r="BF255" s="1"/>
-      <c r="BG255" s="1" t="str">
+      <c r="BG255" s="1"/>
+      <c r="BH255" s="1"/>
+      <c r="BI255" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20970,7 +21687,9 @@
       <c r="BD256" s="1"/>
       <c r="BE256" s="1"/>
       <c r="BF256" s="1"/>
-      <c r="BG256" s="1" t="str">
+      <c r="BG256" s="1"/>
+      <c r="BH256" s="1"/>
+      <c r="BI256" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21037,7 +21756,9 @@
       <c r="BD257" s="1"/>
       <c r="BE257" s="1"/>
       <c r="BF257" s="1"/>
-      <c r="BG257" s="1" t="str">
+      <c r="BG257" s="1"/>
+      <c r="BH257" s="1"/>
+      <c r="BI257" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21104,7 +21825,9 @@
       <c r="BD258" s="1"/>
       <c r="BE258" s="1"/>
       <c r="BF258" s="1"/>
-      <c r="BG258" s="1" t="str">
+      <c r="BG258" s="1"/>
+      <c r="BH258" s="1"/>
+      <c r="BI258" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21171,7 +21894,9 @@
       <c r="BD259" s="1"/>
       <c r="BE259" s="1"/>
       <c r="BF259" s="1"/>
-      <c r="BG259" s="1" t="str">
+      <c r="BG259" s="1"/>
+      <c r="BH259" s="1"/>
+      <c r="BI259" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21238,7 +21963,9 @@
       <c r="BD260" s="1"/>
       <c r="BE260" s="1"/>
       <c r="BF260" s="1"/>
-      <c r="BG260" s="1" t="str">
+      <c r="BG260" s="1"/>
+      <c r="BH260" s="1"/>
+      <c r="BI260" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21305,7 +22032,9 @@
       <c r="BD261" s="1"/>
       <c r="BE261" s="1"/>
       <c r="BF261" s="1"/>
-      <c r="BG261" s="1" t="str">
+      <c r="BG261" s="1"/>
+      <c r="BH261" s="1"/>
+      <c r="BI261" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21372,7 +22101,9 @@
       <c r="BD262" s="1"/>
       <c r="BE262" s="1"/>
       <c r="BF262" s="1"/>
-      <c r="BG262" s="1" t="str">
+      <c r="BG262" s="1"/>
+      <c r="BH262" s="1"/>
+      <c r="BI262" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21439,7 +22170,9 @@
       <c r="BD263" s="1"/>
       <c r="BE263" s="1"/>
       <c r="BF263" s="1"/>
-      <c r="BG263" s="1" t="str">
+      <c r="BG263" s="1"/>
+      <c r="BH263" s="1"/>
+      <c r="BI263" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21506,7 +22239,9 @@
       <c r="BD264" s="1"/>
       <c r="BE264" s="1"/>
       <c r="BF264" s="1"/>
-      <c r="BG264" s="1" t="str">
+      <c r="BG264" s="1"/>
+      <c r="BH264" s="1"/>
+      <c r="BI264" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21573,7 +22308,9 @@
       <c r="BD265" s="1"/>
       <c r="BE265" s="1"/>
       <c r="BF265" s="1"/>
-      <c r="BG265" s="1" t="str">
+      <c r="BG265" s="1"/>
+      <c r="BH265" s="1"/>
+      <c r="BI265" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21640,7 +22377,9 @@
       <c r="BD266" s="1"/>
       <c r="BE266" s="1"/>
       <c r="BF266" s="1"/>
-      <c r="BG266" s="1" t="str">
+      <c r="BG266" s="1"/>
+      <c r="BH266" s="1"/>
+      <c r="BI266" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21707,7 +22446,9 @@
       <c r="BD267" s="1"/>
       <c r="BE267" s="1"/>
       <c r="BF267" s="1"/>
-      <c r="BG267" s="1" t="str">
+      <c r="BG267" s="1"/>
+      <c r="BH267" s="1"/>
+      <c r="BI267" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21774,7 +22515,9 @@
       <c r="BD268" s="1"/>
       <c r="BE268" s="1"/>
       <c r="BF268" s="1"/>
-      <c r="BG268" s="1" t="str">
+      <c r="BG268" s="1"/>
+      <c r="BH268" s="1"/>
+      <c r="BI268" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21841,7 +22584,9 @@
       <c r="BD269" s="1"/>
       <c r="BE269" s="1"/>
       <c r="BF269" s="1"/>
-      <c r="BG269" s="1" t="str">
+      <c r="BG269" s="1"/>
+      <c r="BH269" s="1"/>
+      <c r="BI269" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21908,7 +22653,9 @@
       <c r="BD270" s="1"/>
       <c r="BE270" s="1"/>
       <c r="BF270" s="1"/>
-      <c r="BG270" s="1" t="str">
+      <c r="BG270" s="1"/>
+      <c r="BH270" s="1"/>
+      <c r="BI270" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21975,7 +22722,9 @@
       <c r="BD271" s="1"/>
       <c r="BE271" s="1"/>
       <c r="BF271" s="1"/>
-      <c r="BG271" s="1" t="str">
+      <c r="BG271" s="1"/>
+      <c r="BH271" s="1"/>
+      <c r="BI271" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22042,7 +22791,9 @@
       <c r="BD272" s="1"/>
       <c r="BE272" s="1"/>
       <c r="BF272" s="1"/>
-      <c r="BG272" s="1" t="str">
+      <c r="BG272" s="1"/>
+      <c r="BH272" s="1"/>
+      <c r="BI272" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22109,7 +22860,9 @@
       <c r="BD273" s="1"/>
       <c r="BE273" s="1"/>
       <c r="BF273" s="1"/>
-      <c r="BG273" s="1" t="str">
+      <c r="BG273" s="1"/>
+      <c r="BH273" s="1"/>
+      <c r="BI273" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22176,7 +22929,9 @@
       <c r="BD274" s="1"/>
       <c r="BE274" s="1"/>
       <c r="BF274" s="1"/>
-      <c r="BG274" s="1" t="str">
+      <c r="BG274" s="1"/>
+      <c r="BH274" s="1"/>
+      <c r="BI274" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22243,7 +22998,9 @@
       <c r="BD275" s="1"/>
       <c r="BE275" s="1"/>
       <c r="BF275" s="1"/>
-      <c r="BG275" s="1" t="str">
+      <c r="BG275" s="1"/>
+      <c r="BH275" s="1"/>
+      <c r="BI275" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22310,7 +23067,9 @@
       <c r="BD276" s="1"/>
       <c r="BE276" s="1"/>
       <c r="BF276" s="1"/>
-      <c r="BG276" s="1" t="str">
+      <c r="BG276" s="1"/>
+      <c r="BH276" s="1"/>
+      <c r="BI276" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22377,7 +23136,9 @@
       <c r="BD277" s="1"/>
       <c r="BE277" s="1"/>
       <c r="BF277" s="1"/>
-      <c r="BG277" s="1" t="str">
+      <c r="BG277" s="1"/>
+      <c r="BH277" s="1"/>
+      <c r="BI277" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22444,7 +23205,9 @@
       <c r="BD278" s="1"/>
       <c r="BE278" s="1"/>
       <c r="BF278" s="1"/>
-      <c r="BG278" s="1" t="str">
+      <c r="BG278" s="1"/>
+      <c r="BH278" s="1"/>
+      <c r="BI278" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22511,7 +23274,9 @@
       <c r="BD279" s="1"/>
       <c r="BE279" s="1"/>
       <c r="BF279" s="1"/>
-      <c r="BG279" s="1" t="str">
+      <c r="BG279" s="1"/>
+      <c r="BH279" s="1"/>
+      <c r="BI279" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22578,7 +23343,9 @@
       <c r="BD280" s="1"/>
       <c r="BE280" s="1"/>
       <c r="BF280" s="1"/>
-      <c r="BG280" s="1" t="str">
+      <c r="BG280" s="1"/>
+      <c r="BH280" s="1"/>
+      <c r="BI280" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22645,7 +23412,9 @@
       <c r="BD281" s="1"/>
       <c r="BE281" s="1"/>
       <c r="BF281" s="1"/>
-      <c r="BG281" s="1" t="str">
+      <c r="BG281" s="1"/>
+      <c r="BH281" s="1"/>
+      <c r="BI281" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22712,7 +23481,9 @@
       <c r="BD282" s="1"/>
       <c r="BE282" s="1"/>
       <c r="BF282" s="1"/>
-      <c r="BG282" s="1" t="str">
+      <c r="BG282" s="1"/>
+      <c r="BH282" s="1"/>
+      <c r="BI282" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22779,7 +23550,9 @@
       <c r="BD283" s="1"/>
       <c r="BE283" s="1"/>
       <c r="BF283" s="1"/>
-      <c r="BG283" s="1" t="str">
+      <c r="BG283" s="1"/>
+      <c r="BH283" s="1"/>
+      <c r="BI283" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22846,7 +23619,9 @@
       <c r="BD284" s="1"/>
       <c r="BE284" s="1"/>
       <c r="BF284" s="1"/>
-      <c r="BG284" s="1" t="str">
+      <c r="BG284" s="1"/>
+      <c r="BH284" s="1"/>
+      <c r="BI284" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22913,7 +23688,9 @@
       <c r="BD285" s="1"/>
       <c r="BE285" s="1"/>
       <c r="BF285" s="1"/>
-      <c r="BG285" s="1" t="str">
+      <c r="BG285" s="1"/>
+      <c r="BH285" s="1"/>
+      <c r="BI285" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22980,7 +23757,9 @@
       <c r="BD286" s="1"/>
       <c r="BE286" s="1"/>
       <c r="BF286" s="1"/>
-      <c r="BG286" s="1" t="str">
+      <c r="BG286" s="1"/>
+      <c r="BH286" s="1"/>
+      <c r="BI286" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23047,7 +23826,9 @@
       <c r="BD287" s="1"/>
       <c r="BE287" s="1"/>
       <c r="BF287" s="1"/>
-      <c r="BG287" s="1" t="str">
+      <c r="BG287" s="1"/>
+      <c r="BH287" s="1"/>
+      <c r="BI287" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23114,7 +23895,9 @@
       <c r="BD288" s="1"/>
       <c r="BE288" s="1"/>
       <c r="BF288" s="1"/>
-      <c r="BG288" s="1" t="str">
+      <c r="BG288" s="1"/>
+      <c r="BH288" s="1"/>
+      <c r="BI288" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23181,7 +23964,9 @@
       <c r="BD289" s="1"/>
       <c r="BE289" s="1"/>
       <c r="BF289" s="1"/>
-      <c r="BG289" s="1" t="str">
+      <c r="BG289" s="1"/>
+      <c r="BH289" s="1"/>
+      <c r="BI289" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23248,7 +24033,9 @@
       <c r="BD290" s="1"/>
       <c r="BE290" s="1"/>
       <c r="BF290" s="1"/>
-      <c r="BG290" s="1" t="str">
+      <c r="BG290" s="1"/>
+      <c r="BH290" s="1"/>
+      <c r="BI290" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23315,7 +24102,9 @@
       <c r="BD291" s="1"/>
       <c r="BE291" s="1"/>
       <c r="BF291" s="1"/>
-      <c r="BG291" s="1" t="str">
+      <c r="BG291" s="1"/>
+      <c r="BH291" s="1"/>
+      <c r="BI291" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23382,7 +24171,9 @@
       <c r="BD292" s="1"/>
       <c r="BE292" s="1"/>
       <c r="BF292" s="1"/>
-      <c r="BG292" s="1" t="str">
+      <c r="BG292" s="1"/>
+      <c r="BH292" s="1"/>
+      <c r="BI292" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23449,7 +24240,9 @@
       <c r="BD293" s="1"/>
       <c r="BE293" s="1"/>
       <c r="BF293" s="1"/>
-      <c r="BG293" s="1" t="str">
+      <c r="BG293" s="1"/>
+      <c r="BH293" s="1"/>
+      <c r="BI293" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23516,7 +24309,9 @@
       <c r="BD294" s="1"/>
       <c r="BE294" s="1"/>
       <c r="BF294" s="1"/>
-      <c r="BG294" s="1" t="str">
+      <c r="BG294" s="1"/>
+      <c r="BH294" s="1"/>
+      <c r="BI294" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23583,7 +24378,9 @@
       <c r="BD295" s="1"/>
       <c r="BE295" s="1"/>
       <c r="BF295" s="1"/>
-      <c r="BG295" s="1" t="str">
+      <c r="BG295" s="1"/>
+      <c r="BH295" s="1"/>
+      <c r="BI295" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23650,7 +24447,9 @@
       <c r="BD296" s="1"/>
       <c r="BE296" s="1"/>
       <c r="BF296" s="1"/>
-      <c r="BG296" s="1" t="str">
+      <c r="BG296" s="1"/>
+      <c r="BH296" s="1"/>
+      <c r="BI296" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23717,7 +24516,9 @@
       <c r="BD297" s="1"/>
       <c r="BE297" s="1"/>
       <c r="BF297" s="1"/>
-      <c r="BG297" s="1" t="str">
+      <c r="BG297" s="1"/>
+      <c r="BH297" s="1"/>
+      <c r="BI297" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23784,7 +24585,9 @@
       <c r="BD298" s="1"/>
       <c r="BE298" s="1"/>
       <c r="BF298" s="1"/>
-      <c r="BG298" s="1" t="str">
+      <c r="BG298" s="1"/>
+      <c r="BH298" s="1"/>
+      <c r="BI298" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23851,7 +24654,9 @@
       <c r="BD299" s="1"/>
       <c r="BE299" s="1"/>
       <c r="BF299" s="1"/>
-      <c r="BG299" s="1" t="str">
+      <c r="BG299" s="1"/>
+      <c r="BH299" s="1"/>
+      <c r="BI299" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23918,7 +24723,9 @@
       <c r="BD300" s="1"/>
       <c r="BE300" s="1"/>
       <c r="BF300" s="1"/>
-      <c r="BG300" s="1" t="str">
+      <c r="BG300" s="1"/>
+      <c r="BH300" s="1"/>
+      <c r="BI300" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23985,7 +24792,9 @@
       <c r="BD301" s="1"/>
       <c r="BE301" s="1"/>
       <c r="BF301" s="1"/>
-      <c r="BG301" s="1" t="str">
+      <c r="BG301" s="1"/>
+      <c r="BH301" s="1"/>
+      <c r="BI301" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24052,7 +24861,9 @@
       <c r="BD302" s="1"/>
       <c r="BE302" s="1"/>
       <c r="BF302" s="1"/>
-      <c r="BG302" s="1" t="str">
+      <c r="BG302" s="1"/>
+      <c r="BH302" s="1"/>
+      <c r="BI302" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24119,7 +24930,9 @@
       <c r="BD303" s="1"/>
       <c r="BE303" s="1"/>
       <c r="BF303" s="1"/>
-      <c r="BG303" s="1" t="str">
+      <c r="BG303" s="1"/>
+      <c r="BH303" s="1"/>
+      <c r="BI303" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24186,7 +24999,9 @@
       <c r="BD304" s="1"/>
       <c r="BE304" s="1"/>
       <c r="BF304" s="1"/>
-      <c r="BG304" s="1" t="str">
+      <c r="BG304" s="1"/>
+      <c r="BH304" s="1"/>
+      <c r="BI304" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24253,7 +25068,9 @@
       <c r="BD305" s="1"/>
       <c r="BE305" s="1"/>
       <c r="BF305" s="1"/>
-      <c r="BG305" s="1" t="str">
+      <c r="BG305" s="1"/>
+      <c r="BH305" s="1"/>
+      <c r="BI305" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24320,7 +25137,9 @@
       <c r="BD306" s="1"/>
       <c r="BE306" s="1"/>
       <c r="BF306" s="1"/>
-      <c r="BG306" s="1" t="str">
+      <c r="BG306" s="1"/>
+      <c r="BH306" s="1"/>
+      <c r="BI306" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24387,7 +25206,9 @@
       <c r="BD307" s="1"/>
       <c r="BE307" s="1"/>
       <c r="BF307" s="1"/>
-      <c r="BG307" s="1" t="str">
+      <c r="BG307" s="1"/>
+      <c r="BH307" s="1"/>
+      <c r="BI307" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24454,7 +25275,9 @@
       <c r="BD308" s="1"/>
       <c r="BE308" s="1"/>
       <c r="BF308" s="1"/>
-      <c r="BG308" s="1" t="str">
+      <c r="BG308" s="1"/>
+      <c r="BH308" s="1"/>
+      <c r="BI308" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24521,7 +25344,9 @@
       <c r="BD309" s="1"/>
       <c r="BE309" s="1"/>
       <c r="BF309" s="1"/>
-      <c r="BG309" s="1" t="str">
+      <c r="BG309" s="1"/>
+      <c r="BH309" s="1"/>
+      <c r="BI309" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24588,7 +25413,9 @@
       <c r="BD310" s="1"/>
       <c r="BE310" s="1"/>
       <c r="BF310" s="1"/>
-      <c r="BG310" s="1" t="str">
+      <c r="BG310" s="1"/>
+      <c r="BH310" s="1"/>
+      <c r="BI310" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24655,7 +25482,9 @@
       <c r="BD311" s="1"/>
       <c r="BE311" s="1"/>
       <c r="BF311" s="1"/>
-      <c r="BG311" s="1" t="str">
+      <c r="BG311" s="1"/>
+      <c r="BH311" s="1"/>
+      <c r="BI311" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24722,7 +25551,9 @@
       <c r="BD312" s="1"/>
       <c r="BE312" s="1"/>
       <c r="BF312" s="1"/>
-      <c r="BG312" s="1" t="str">
+      <c r="BG312" s="1"/>
+      <c r="BH312" s="1"/>
+      <c r="BI312" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24789,7 +25620,9 @@
       <c r="BD313" s="1"/>
       <c r="BE313" s="1"/>
       <c r="BF313" s="1"/>
-      <c r="BG313" s="1" t="str">
+      <c r="BG313" s="1"/>
+      <c r="BH313" s="1"/>
+      <c r="BI313" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24856,7 +25689,9 @@
       <c r="BD314" s="1"/>
       <c r="BE314" s="1"/>
       <c r="BF314" s="1"/>
-      <c r="BG314" s="1" t="str">
+      <c r="BG314" s="1"/>
+      <c r="BH314" s="1"/>
+      <c r="BI314" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24923,7 +25758,9 @@
       <c r="BD315" s="1"/>
       <c r="BE315" s="1"/>
       <c r="BF315" s="1"/>
-      <c r="BG315" s="1" t="str">
+      <c r="BG315" s="1"/>
+      <c r="BH315" s="1"/>
+      <c r="BI315" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24990,7 +25827,9 @@
       <c r="BD316" s="1"/>
       <c r="BE316" s="1"/>
       <c r="BF316" s="1"/>
-      <c r="BG316" s="1" t="str">
+      <c r="BG316" s="1"/>
+      <c r="BH316" s="1"/>
+      <c r="BI316" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25057,7 +25896,9 @@
       <c r="BD317" s="1"/>
       <c r="BE317" s="1"/>
       <c r="BF317" s="1"/>
-      <c r="BG317" s="1" t="str">
+      <c r="BG317" s="1"/>
+      <c r="BH317" s="1"/>
+      <c r="BI317" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25124,7 +25965,9 @@
       <c r="BD318" s="1"/>
       <c r="BE318" s="1"/>
       <c r="BF318" s="1"/>
-      <c r="BG318" s="1" t="str">
+      <c r="BG318" s="1"/>
+      <c r="BH318" s="1"/>
+      <c r="BI318" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25191,7 +26034,9 @@
       <c r="BD319" s="1"/>
       <c r="BE319" s="1"/>
       <c r="BF319" s="1"/>
-      <c r="BG319" s="1" t="str">
+      <c r="BG319" s="1"/>
+      <c r="BH319" s="1"/>
+      <c r="BI319" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25258,7 +26103,9 @@
       <c r="BD320" s="1"/>
       <c r="BE320" s="1"/>
       <c r="BF320" s="1"/>
-      <c r="BG320" s="1" t="str">
+      <c r="BG320" s="1"/>
+      <c r="BH320" s="1"/>
+      <c r="BI320" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25325,7 +26172,9 @@
       <c r="BD321" s="1"/>
       <c r="BE321" s="1"/>
       <c r="BF321" s="1"/>
-      <c r="BG321" s="1" t="str">
+      <c r="BG321" s="1"/>
+      <c r="BH321" s="1"/>
+      <c r="BI321" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25392,7 +26241,9 @@
       <c r="BD322" s="1"/>
       <c r="BE322" s="1"/>
       <c r="BF322" s="1"/>
-      <c r="BG322" s="1" t="str">
+      <c r="BG322" s="1"/>
+      <c r="BH322" s="1"/>
+      <c r="BI322" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25459,7 +26310,9 @@
       <c r="BD323" s="1"/>
       <c r="BE323" s="1"/>
       <c r="BF323" s="1"/>
-      <c r="BG323" s="1" t="str">
+      <c r="BG323" s="1"/>
+      <c r="BH323" s="1"/>
+      <c r="BI323" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25526,7 +26379,9 @@
       <c r="BD324" s="1"/>
       <c r="BE324" s="1"/>
       <c r="BF324" s="1"/>
-      <c r="BG324" s="1" t="str">
+      <c r="BG324" s="1"/>
+      <c r="BH324" s="1"/>
+      <c r="BI324" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25593,7 +26448,9 @@
       <c r="BD325" s="1"/>
       <c r="BE325" s="1"/>
       <c r="BF325" s="1"/>
-      <c r="BG325" s="1" t="str">
+      <c r="BG325" s="1"/>
+      <c r="BH325" s="1"/>
+      <c r="BI325" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25660,7 +26517,9 @@
       <c r="BD326" s="1"/>
       <c r="BE326" s="1"/>
       <c r="BF326" s="1"/>
-      <c r="BG326" s="1" t="str">
+      <c r="BG326" s="1"/>
+      <c r="BH326" s="1"/>
+      <c r="BI326" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25727,7 +26586,9 @@
       <c r="BD327" s="1"/>
       <c r="BE327" s="1"/>
       <c r="BF327" s="1"/>
-      <c r="BG327" s="1" t="str">
+      <c r="BG327" s="1"/>
+      <c r="BH327" s="1"/>
+      <c r="BI327" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25794,7 +26655,9 @@
       <c r="BD328" s="1"/>
       <c r="BE328" s="1"/>
       <c r="BF328" s="1"/>
-      <c r="BG328" s="1" t="str">
+      <c r="BG328" s="1"/>
+      <c r="BH328" s="1"/>
+      <c r="BI328" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25861,7 +26724,9 @@
       <c r="BD329" s="1"/>
       <c r="BE329" s="1"/>
       <c r="BF329" s="1"/>
-      <c r="BG329" s="1" t="str">
+      <c r="BG329" s="1"/>
+      <c r="BH329" s="1"/>
+      <c r="BI329" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25928,7 +26793,9 @@
       <c r="BD330" s="1"/>
       <c r="BE330" s="1"/>
       <c r="BF330" s="1"/>
-      <c r="BG330" s="1" t="str">
+      <c r="BG330" s="1"/>
+      <c r="BH330" s="1"/>
+      <c r="BI330" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25995,7 +26862,9 @@
       <c r="BD331" s="1"/>
       <c r="BE331" s="1"/>
       <c r="BF331" s="1"/>
-      <c r="BG331" s="1" t="str">
+      <c r="BG331" s="1"/>
+      <c r="BH331" s="1"/>
+      <c r="BI331" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26062,7 +26931,9 @@
       <c r="BD332" s="1"/>
       <c r="BE332" s="1"/>
       <c r="BF332" s="1"/>
-      <c r="BG332" s="1" t="str">
+      <c r="BG332" s="1"/>
+      <c r="BH332" s="1"/>
+      <c r="BI332" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26129,7 +27000,9 @@
       <c r="BD333" s="1"/>
       <c r="BE333" s="1"/>
       <c r="BF333" s="1"/>
-      <c r="BG333" s="1" t="str">
+      <c r="BG333" s="1"/>
+      <c r="BH333" s="1"/>
+      <c r="BI333" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26196,7 +27069,9 @@
       <c r="BD334" s="1"/>
       <c r="BE334" s="1"/>
       <c r="BF334" s="1"/>
-      <c r="BG334" s="1" t="str">
+      <c r="BG334" s="1"/>
+      <c r="BH334" s="1"/>
+      <c r="BI334" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26263,7 +27138,9 @@
       <c r="BD335" s="1"/>
       <c r="BE335" s="1"/>
       <c r="BF335" s="1"/>
-      <c r="BG335" s="1" t="str">
+      <c r="BG335" s="1"/>
+      <c r="BH335" s="1"/>
+      <c r="BI335" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26330,7 +27207,9 @@
       <c r="BD336" s="1"/>
       <c r="BE336" s="1"/>
       <c r="BF336" s="1"/>
-      <c r="BG336" s="1" t="str">
+      <c r="BG336" s="1"/>
+      <c r="BH336" s="1"/>
+      <c r="BI336" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26397,7 +27276,9 @@
       <c r="BD337" s="1"/>
       <c r="BE337" s="1"/>
       <c r="BF337" s="1"/>
-      <c r="BG337" s="1" t="str">
+      <c r="BG337" s="1"/>
+      <c r="BH337" s="1"/>
+      <c r="BI337" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26464,7 +27345,9 @@
       <c r="BD338" s="1"/>
       <c r="BE338" s="1"/>
       <c r="BF338" s="1"/>
-      <c r="BG338" s="1" t="str">
+      <c r="BG338" s="1"/>
+      <c r="BH338" s="1"/>
+      <c r="BI338" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26531,7 +27414,9 @@
       <c r="BD339" s="1"/>
       <c r="BE339" s="1"/>
       <c r="BF339" s="1"/>
-      <c r="BG339" s="1" t="str">
+      <c r="BG339" s="1"/>
+      <c r="BH339" s="1"/>
+      <c r="BI339" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26598,7 +27483,9 @@
       <c r="BD340" s="1"/>
       <c r="BE340" s="1"/>
       <c r="BF340" s="1"/>
-      <c r="BG340" s="1" t="str">
+      <c r="BG340" s="1"/>
+      <c r="BH340" s="1"/>
+      <c r="BI340" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26665,7 +27552,9 @@
       <c r="BD341" s="1"/>
       <c r="BE341" s="1"/>
       <c r="BF341" s="1"/>
-      <c r="BG341" s="1" t="str">
+      <c r="BG341" s="1"/>
+      <c r="BH341" s="1"/>
+      <c r="BI341" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26732,7 +27621,9 @@
       <c r="BD342" s="1"/>
       <c r="BE342" s="1"/>
       <c r="BF342" s="1"/>
-      <c r="BG342" s="1" t="str">
+      <c r="BG342" s="1"/>
+      <c r="BH342" s="1"/>
+      <c r="BI342" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26799,7 +27690,9 @@
       <c r="BD343" s="1"/>
       <c r="BE343" s="1"/>
       <c r="BF343" s="1"/>
-      <c r="BG343" s="1" t="str">
+      <c r="BG343" s="1"/>
+      <c r="BH343" s="1"/>
+      <c r="BI343" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26866,7 +27759,9 @@
       <c r="BD344" s="1"/>
       <c r="BE344" s="1"/>
       <c r="BF344" s="1"/>
-      <c r="BG344" s="1" t="str">
+      <c r="BG344" s="1"/>
+      <c r="BH344" s="1"/>
+      <c r="BI344" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26933,7 +27828,9 @@
       <c r="BD345" s="1"/>
       <c r="BE345" s="1"/>
       <c r="BF345" s="1"/>
-      <c r="BG345" s="1" t="str">
+      <c r="BG345" s="1"/>
+      <c r="BH345" s="1"/>
+      <c r="BI345" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27000,7 +27897,9 @@
       <c r="BD346" s="1"/>
       <c r="BE346" s="1"/>
       <c r="BF346" s="1"/>
-      <c r="BG346" s="1" t="str">
+      <c r="BG346" s="1"/>
+      <c r="BH346" s="1"/>
+      <c r="BI346" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27067,7 +27966,9 @@
       <c r="BD347" s="1"/>
       <c r="BE347" s="1"/>
       <c r="BF347" s="1"/>
-      <c r="BG347" s="1" t="str">
+      <c r="BG347" s="1"/>
+      <c r="BH347" s="1"/>
+      <c r="BI347" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27134,7 +28035,9 @@
       <c r="BD348" s="1"/>
       <c r="BE348" s="1"/>
       <c r="BF348" s="1"/>
-      <c r="BG348" s="1" t="str">
+      <c r="BG348" s="1"/>
+      <c r="BH348" s="1"/>
+      <c r="BI348" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27201,7 +28104,9 @@
       <c r="BD349" s="1"/>
       <c r="BE349" s="1"/>
       <c r="BF349" s="1"/>
-      <c r="BG349" s="1" t="str">
+      <c r="BG349" s="1"/>
+      <c r="BH349" s="1"/>
+      <c r="BI349" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27268,7 +28173,9 @@
       <c r="BD350" s="1"/>
       <c r="BE350" s="1"/>
       <c r="BF350" s="1"/>
-      <c r="BG350" s="1" t="str">
+      <c r="BG350" s="1"/>
+      <c r="BH350" s="1"/>
+      <c r="BI350" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27335,7 +28242,9 @@
       <c r="BD351" s="1"/>
       <c r="BE351" s="1"/>
       <c r="BF351" s="1"/>
-      <c r="BG351" s="1" t="str">
+      <c r="BG351" s="1"/>
+      <c r="BH351" s="1"/>
+      <c r="BI351" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27402,7 +28311,9 @@
       <c r="BD352" s="1"/>
       <c r="BE352" s="1"/>
       <c r="BF352" s="1"/>
-      <c r="BG352" s="1" t="str">
+      <c r="BG352" s="1"/>
+      <c r="BH352" s="1"/>
+      <c r="BI352" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27469,7 +28380,9 @@
       <c r="BD353" s="1"/>
       <c r="BE353" s="1"/>
       <c r="BF353" s="1"/>
-      <c r="BG353" s="1" t="str">
+      <c r="BG353" s="1"/>
+      <c r="BH353" s="1"/>
+      <c r="BI353" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27536,7 +28449,9 @@
       <c r="BD354" s="1"/>
       <c r="BE354" s="1"/>
       <c r="BF354" s="1"/>
-      <c r="BG354" s="1" t="str">
+      <c r="BG354" s="1"/>
+      <c r="BH354" s="1"/>
+      <c r="BI354" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27603,7 +28518,9 @@
       <c r="BD355" s="1"/>
       <c r="BE355" s="1"/>
       <c r="BF355" s="1"/>
-      <c r="BG355" s="1" t="str">
+      <c r="BG355" s="1"/>
+      <c r="BH355" s="1"/>
+      <c r="BI355" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27670,7 +28587,9 @@
       <c r="BD356" s="1"/>
       <c r="BE356" s="1"/>
       <c r="BF356" s="1"/>
-      <c r="BG356" s="1" t="str">
+      <c r="BG356" s="1"/>
+      <c r="BH356" s="1"/>
+      <c r="BI356" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27737,7 +28656,9 @@
       <c r="BD357" s="1"/>
       <c r="BE357" s="1"/>
       <c r="BF357" s="1"/>
-      <c r="BG357" s="1" t="str">
+      <c r="BG357" s="1"/>
+      <c r="BH357" s="1"/>
+      <c r="BI357" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27804,7 +28725,9 @@
       <c r="BD358" s="1"/>
       <c r="BE358" s="1"/>
       <c r="BF358" s="1"/>
-      <c r="BG358" s="1" t="str">
+      <c r="BG358" s="1"/>
+      <c r="BH358" s="1"/>
+      <c r="BI358" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27871,7 +28794,9 @@
       <c r="BD359" s="1"/>
       <c r="BE359" s="1"/>
       <c r="BF359" s="1"/>
-      <c r="BG359" s="1" t="str">
+      <c r="BG359" s="1"/>
+      <c r="BH359" s="1"/>
+      <c r="BI359" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27938,7 +28863,9 @@
       <c r="BD360" s="1"/>
       <c r="BE360" s="1"/>
       <c r="BF360" s="1"/>
-      <c r="BG360" s="1" t="str">
+      <c r="BG360" s="1"/>
+      <c r="BH360" s="1"/>
+      <c r="BI360" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28005,7 +28932,9 @@
       <c r="BD361" s="1"/>
       <c r="BE361" s="1"/>
       <c r="BF361" s="1"/>
-      <c r="BG361" s="1" t="str">
+      <c r="BG361" s="1"/>
+      <c r="BH361" s="1"/>
+      <c r="BI361" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28072,7 +29001,9 @@
       <c r="BD362" s="1"/>
       <c r="BE362" s="1"/>
       <c r="BF362" s="1"/>
-      <c r="BG362" s="1" t="str">
+      <c r="BG362" s="1"/>
+      <c r="BH362" s="1"/>
+      <c r="BI362" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28139,7 +29070,9 @@
       <c r="BD363" s="1"/>
       <c r="BE363" s="1"/>
       <c r="BF363" s="1"/>
-      <c r="BG363" s="1" t="str">
+      <c r="BG363" s="1"/>
+      <c r="BH363" s="1"/>
+      <c r="BI363" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28206,7 +29139,9 @@
       <c r="BD364" s="1"/>
       <c r="BE364" s="1"/>
       <c r="BF364" s="1"/>
-      <c r="BG364" s="1" t="str">
+      <c r="BG364" s="1"/>
+      <c r="BH364" s="1"/>
+      <c r="BI364" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28273,7 +29208,9 @@
       <c r="BD365" s="1"/>
       <c r="BE365" s="1"/>
       <c r="BF365" s="1"/>
-      <c r="BG365" s="1" t="str">
+      <c r="BG365" s="1"/>
+      <c r="BH365" s="1"/>
+      <c r="BI365" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28340,7 +29277,9 @@
       <c r="BD366" s="1"/>
       <c r="BE366" s="1"/>
       <c r="BF366" s="1"/>
-      <c r="BG366" s="1" t="str">
+      <c r="BG366" s="1"/>
+      <c r="BH366" s="1"/>
+      <c r="BI366" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28407,7 +29346,9 @@
       <c r="BD367" s="1"/>
       <c r="BE367" s="1"/>
       <c r="BF367" s="1"/>
-      <c r="BG367" s="1" t="str">
+      <c r="BG367" s="1"/>
+      <c r="BH367" s="1"/>
+      <c r="BI367" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28474,7 +29415,9 @@
       <c r="BD368" s="1"/>
       <c r="BE368" s="1"/>
       <c r="BF368" s="1"/>
-      <c r="BG368" s="1" t="str">
+      <c r="BG368" s="1"/>
+      <c r="BH368" s="1"/>
+      <c r="BI368" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28541,7 +29484,9 @@
       <c r="BD369" s="1"/>
       <c r="BE369" s="1"/>
       <c r="BF369" s="1"/>
-      <c r="BG369" s="1" t="str">
+      <c r="BG369" s="1"/>
+      <c r="BH369" s="1"/>
+      <c r="BI369" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28608,7 +29553,9 @@
       <c r="BD370" s="1"/>
       <c r="BE370" s="1"/>
       <c r="BF370" s="1"/>
-      <c r="BG370" s="1" t="str">
+      <c r="BG370" s="1"/>
+      <c r="BH370" s="1"/>
+      <c r="BI370" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28675,7 +29622,9 @@
       <c r="BD371" s="1"/>
       <c r="BE371" s="1"/>
       <c r="BF371" s="1"/>
-      <c r="BG371" s="1" t="str">
+      <c r="BG371" s="1"/>
+      <c r="BH371" s="1"/>
+      <c r="BI371" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28742,7 +29691,9 @@
       <c r="BD372" s="1"/>
       <c r="BE372" s="1"/>
       <c r="BF372" s="1"/>
-      <c r="BG372" s="1" t="str">
+      <c r="BG372" s="1"/>
+      <c r="BH372" s="1"/>
+      <c r="BI372" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28809,7 +29760,9 @@
       <c r="BD373" s="1"/>
       <c r="BE373" s="1"/>
       <c r="BF373" s="1"/>
-      <c r="BG373" s="1" t="str">
+      <c r="BG373" s="1"/>
+      <c r="BH373" s="1"/>
+      <c r="BI373" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28876,7 +29829,9 @@
       <c r="BD374" s="1"/>
       <c r="BE374" s="1"/>
       <c r="BF374" s="1"/>
-      <c r="BG374" s="1" t="str">
+      <c r="BG374" s="1"/>
+      <c r="BH374" s="1"/>
+      <c r="BI374" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28943,7 +29898,9 @@
       <c r="BD375" s="1"/>
       <c r="BE375" s="1"/>
       <c r="BF375" s="1"/>
-      <c r="BG375" s="1" t="str">
+      <c r="BG375" s="1"/>
+      <c r="BH375" s="1"/>
+      <c r="BI375" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29010,7 +29967,9 @@
       <c r="BD376" s="1"/>
       <c r="BE376" s="1"/>
       <c r="BF376" s="1"/>
-      <c r="BG376" s="1" t="str">
+      <c r="BG376" s="1"/>
+      <c r="BH376" s="1"/>
+      <c r="BI376" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29077,7 +30036,9 @@
       <c r="BD377" s="1"/>
       <c r="BE377" s="1"/>
       <c r="BF377" s="1"/>
-      <c r="BG377" s="1" t="str">
+      <c r="BG377" s="1"/>
+      <c r="BH377" s="1"/>
+      <c r="BI377" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29144,7 +30105,9 @@
       <c r="BD378" s="1"/>
       <c r="BE378" s="1"/>
       <c r="BF378" s="1"/>
-      <c r="BG378" s="1" t="str">
+      <c r="BG378" s="1"/>
+      <c r="BH378" s="1"/>
+      <c r="BI378" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29211,7 +30174,9 @@
       <c r="BD379" s="1"/>
       <c r="BE379" s="1"/>
       <c r="BF379" s="1"/>
-      <c r="BG379" s="1" t="str">
+      <c r="BG379" s="1"/>
+      <c r="BH379" s="1"/>
+      <c r="BI379" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29278,7 +30243,9 @@
       <c r="BD380" s="1"/>
       <c r="BE380" s="1"/>
       <c r="BF380" s="1"/>
-      <c r="BG380" s="1" t="str">
+      <c r="BG380" s="1"/>
+      <c r="BH380" s="1"/>
+      <c r="BI380" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29345,7 +30312,9 @@
       <c r="BD381" s="1"/>
       <c r="BE381" s="1"/>
       <c r="BF381" s="1"/>
-      <c r="BG381" s="1" t="str">
+      <c r="BG381" s="1"/>
+      <c r="BH381" s="1"/>
+      <c r="BI381" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29412,7 +30381,9 @@
       <c r="BD382" s="1"/>
       <c r="BE382" s="1"/>
       <c r="BF382" s="1"/>
-      <c r="BG382" s="1" t="str">
+      <c r="BG382" s="1"/>
+      <c r="BH382" s="1"/>
+      <c r="BI382" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29479,7 +30450,9 @@
       <c r="BD383" s="1"/>
       <c r="BE383" s="1"/>
       <c r="BF383" s="1"/>
-      <c r="BG383" s="1" t="str">
+      <c r="BG383" s="1"/>
+      <c r="BH383" s="1"/>
+      <c r="BI383" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29546,7 +30519,9 @@
       <c r="BD384" s="1"/>
       <c r="BE384" s="1"/>
       <c r="BF384" s="1"/>
-      <c r="BG384" s="1" t="str">
+      <c r="BG384" s="1"/>
+      <c r="BH384" s="1"/>
+      <c r="BI384" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29613,7 +30588,9 @@
       <c r="BD385" s="1"/>
       <c r="BE385" s="1"/>
       <c r="BF385" s="1"/>
-      <c r="BG385" s="1" t="str">
+      <c r="BG385" s="1"/>
+      <c r="BH385" s="1"/>
+      <c r="BI385" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29680,7 +30657,9 @@
       <c r="BD386" s="1"/>
       <c r="BE386" s="1"/>
       <c r="BF386" s="1"/>
-      <c r="BG386" s="1" t="str">
+      <c r="BG386" s="1"/>
+      <c r="BH386" s="1"/>
+      <c r="BI386" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29747,7 +30726,9 @@
       <c r="BD387" s="1"/>
       <c r="BE387" s="1"/>
       <c r="BF387" s="1"/>
-      <c r="BG387" s="1" t="str">
+      <c r="BG387" s="1"/>
+      <c r="BH387" s="1"/>
+      <c r="BI387" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29814,7 +30795,9 @@
       <c r="BD388" s="1"/>
       <c r="BE388" s="1"/>
       <c r="BF388" s="1"/>
-      <c r="BG388" s="1" t="str">
+      <c r="BG388" s="1"/>
+      <c r="BH388" s="1"/>
+      <c r="BI388" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29881,7 +30864,9 @@
       <c r="BD389" s="1"/>
       <c r="BE389" s="1"/>
       <c r="BF389" s="1"/>
-      <c r="BG389" s="1" t="str">
+      <c r="BG389" s="1"/>
+      <c r="BH389" s="1"/>
+      <c r="BI389" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29948,7 +30933,9 @@
       <c r="BD390" s="1"/>
       <c r="BE390" s="1"/>
       <c r="BF390" s="1"/>
-      <c r="BG390" s="1" t="str">
+      <c r="BG390" s="1"/>
+      <c r="BH390" s="1"/>
+      <c r="BI390" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30015,7 +31002,9 @@
       <c r="BD391" s="1"/>
       <c r="BE391" s="1"/>
       <c r="BF391" s="1"/>
-      <c r="BG391" s="1" t="str">
+      <c r="BG391" s="1"/>
+      <c r="BH391" s="1"/>
+      <c r="BI391" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30082,7 +31071,9 @@
       <c r="BD392" s="1"/>
       <c r="BE392" s="1"/>
       <c r="BF392" s="1"/>
-      <c r="BG392" s="1" t="str">
+      <c r="BG392" s="1"/>
+      <c r="BH392" s="1"/>
+      <c r="BI392" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30149,7 +31140,9 @@
       <c r="BD393" s="1"/>
       <c r="BE393" s="1"/>
       <c r="BF393" s="1"/>
-      <c r="BG393" s="1" t="str">
+      <c r="BG393" s="1"/>
+      <c r="BH393" s="1"/>
+      <c r="BI393" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30216,7 +31209,9 @@
       <c r="BD394" s="1"/>
       <c r="BE394" s="1"/>
       <c r="BF394" s="1"/>
-      <c r="BG394" s="1" t="str">
+      <c r="BG394" s="1"/>
+      <c r="BH394" s="1"/>
+      <c r="BI394" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30283,7 +31278,9 @@
       <c r="BD395" s="1"/>
       <c r="BE395" s="1"/>
       <c r="BF395" s="1"/>
-      <c r="BG395" s="1" t="str">
+      <c r="BG395" s="1"/>
+      <c r="BH395" s="1"/>
+      <c r="BI395" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30350,7 +31347,9 @@
       <c r="BD396" s="1"/>
       <c r="BE396" s="1"/>
       <c r="BF396" s="1"/>
-      <c r="BG396" s="1" t="str">
+      <c r="BG396" s="1"/>
+      <c r="BH396" s="1"/>
+      <c r="BI396" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30417,7 +31416,9 @@
       <c r="BD397" s="1"/>
       <c r="BE397" s="1"/>
       <c r="BF397" s="1"/>
-      <c r="BG397" s="1" t="str">
+      <c r="BG397" s="1"/>
+      <c r="BH397" s="1"/>
+      <c r="BI397" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30484,7 +31485,9 @@
       <c r="BD398" s="1"/>
       <c r="BE398" s="1"/>
       <c r="BF398" s="1"/>
-      <c r="BG398" s="1" t="str">
+      <c r="BG398" s="1"/>
+      <c r="BH398" s="1"/>
+      <c r="BI398" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30551,7 +31554,9 @@
       <c r="BD399" s="1"/>
       <c r="BE399" s="1"/>
       <c r="BF399" s="1"/>
-      <c r="BG399" s="1" t="str">
+      <c r="BG399" s="1"/>
+      <c r="BH399" s="1"/>
+      <c r="BI399" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30618,7 +31623,9 @@
       <c r="BD400" s="1"/>
       <c r="BE400" s="1"/>
       <c r="BF400" s="1"/>
-      <c r="BG400" s="1" t="str">
+      <c r="BG400" s="1"/>
+      <c r="BH400" s="1"/>
+      <c r="BI400" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30685,7 +31692,9 @@
       <c r="BD401" s="1"/>
       <c r="BE401" s="1"/>
       <c r="BF401" s="1"/>
-      <c r="BG401" s="1" t="str">
+      <c r="BG401" s="1"/>
+      <c r="BH401" s="1"/>
+      <c r="BI401" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30752,7 +31761,9 @@
       <c r="BD402" s="1"/>
       <c r="BE402" s="1"/>
       <c r="BF402" s="1"/>
-      <c r="BG402" s="1" t="str">
+      <c r="BG402" s="1"/>
+      <c r="BH402" s="1"/>
+      <c r="BI402" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30819,7 +31830,9 @@
       <c r="BD403" s="1"/>
       <c r="BE403" s="1"/>
       <c r="BF403" s="1"/>
-      <c r="BG403" s="1" t="str">
+      <c r="BG403" s="1"/>
+      <c r="BH403" s="1"/>
+      <c r="BI403" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30886,7 +31899,9 @@
       <c r="BD404" s="1"/>
       <c r="BE404" s="1"/>
       <c r="BF404" s="1"/>
-      <c r="BG404" s="1" t="str">
+      <c r="BG404" s="1"/>
+      <c r="BH404" s="1"/>
+      <c r="BI404" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30953,7 +31968,9 @@
       <c r="BD405" s="1"/>
       <c r="BE405" s="1"/>
       <c r="BF405" s="1"/>
-      <c r="BG405" s="1" t="str">
+      <c r="BG405" s="1"/>
+      <c r="BH405" s="1"/>
+      <c r="BI405" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31020,7 +32037,9 @@
       <c r="BD406" s="1"/>
       <c r="BE406" s="1"/>
       <c r="BF406" s="1"/>
-      <c r="BG406" s="1" t="str">
+      <c r="BG406" s="1"/>
+      <c r="BH406" s="1"/>
+      <c r="BI406" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31087,7 +32106,9 @@
       <c r="BD407" s="1"/>
       <c r="BE407" s="1"/>
       <c r="BF407" s="1"/>
-      <c r="BG407" s="1" t="str">
+      <c r="BG407" s="1"/>
+      <c r="BH407" s="1"/>
+      <c r="BI407" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31154,7 +32175,9 @@
       <c r="BD408" s="1"/>
       <c r="BE408" s="1"/>
       <c r="BF408" s="1"/>
-      <c r="BG408" s="1" t="str">
+      <c r="BG408" s="1"/>
+      <c r="BH408" s="1"/>
+      <c r="BI408" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31221,7 +32244,9 @@
       <c r="BD409" s="1"/>
       <c r="BE409" s="1"/>
       <c r="BF409" s="1"/>
-      <c r="BG409" s="1" t="str">
+      <c r="BG409" s="1"/>
+      <c r="BH409" s="1"/>
+      <c r="BI409" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31288,7 +32313,9 @@
       <c r="BD410" s="1"/>
       <c r="BE410" s="1"/>
       <c r="BF410" s="1"/>
-      <c r="BG410" s="1" t="str">
+      <c r="BG410" s="1"/>
+      <c r="BH410" s="1"/>
+      <c r="BI410" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31355,7 +32382,9 @@
       <c r="BD411" s="1"/>
       <c r="BE411" s="1"/>
       <c r="BF411" s="1"/>
-      <c r="BG411" s="1" t="str">
+      <c r="BG411" s="1"/>
+      <c r="BH411" s="1"/>
+      <c r="BI411" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31422,7 +32451,9 @@
       <c r="BD412" s="1"/>
       <c r="BE412" s="1"/>
       <c r="BF412" s="1"/>
-      <c r="BG412" s="1" t="str">
+      <c r="BG412" s="1"/>
+      <c r="BH412" s="1"/>
+      <c r="BI412" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31489,7 +32520,9 @@
       <c r="BD413" s="1"/>
       <c r="BE413" s="1"/>
       <c r="BF413" s="1"/>
-      <c r="BG413" s="1" t="str">
+      <c r="BG413" s="1"/>
+      <c r="BH413" s="1"/>
+      <c r="BI413" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31556,7 +32589,9 @@
       <c r="BD414" s="1"/>
       <c r="BE414" s="1"/>
       <c r="BF414" s="1"/>
-      <c r="BG414" s="1" t="str">
+      <c r="BG414" s="1"/>
+      <c r="BH414" s="1"/>
+      <c r="BI414" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31623,7 +32658,9 @@
       <c r="BD415" s="1"/>
       <c r="BE415" s="1"/>
       <c r="BF415" s="1"/>
-      <c r="BG415" s="1" t="str">
+      <c r="BG415" s="1"/>
+      <c r="BH415" s="1"/>
+      <c r="BI415" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31690,7 +32727,9 @@
       <c r="BD416" s="1"/>
       <c r="BE416" s="1"/>
       <c r="BF416" s="1"/>
-      <c r="BG416" s="1" t="str">
+      <c r="BG416" s="1"/>
+      <c r="BH416" s="1"/>
+      <c r="BI416" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31757,7 +32796,9 @@
       <c r="BD417" s="1"/>
       <c r="BE417" s="1"/>
       <c r="BF417" s="1"/>
-      <c r="BG417" s="1" t="str">
+      <c r="BG417" s="1"/>
+      <c r="BH417" s="1"/>
+      <c r="BI417" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31824,7 +32865,9 @@
       <c r="BD418" s="1"/>
       <c r="BE418" s="1"/>
       <c r="BF418" s="1"/>
-      <c r="BG418" s="1" t="str">
+      <c r="BG418" s="1"/>
+      <c r="BH418" s="1"/>
+      <c r="BI418" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31891,7 +32934,9 @@
       <c r="BD419" s="1"/>
       <c r="BE419" s="1"/>
       <c r="BF419" s="1"/>
-      <c r="BG419" s="1" t="str">
+      <c r="BG419" s="1"/>
+      <c r="BH419" s="1"/>
+      <c r="BI419" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31958,7 +33003,9 @@
       <c r="BD420" s="1"/>
       <c r="BE420" s="1"/>
       <c r="BF420" s="1"/>
-      <c r="BG420" s="1" t="str">
+      <c r="BG420" s="1"/>
+      <c r="BH420" s="1"/>
+      <c r="BI420" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32025,7 +33072,9 @@
       <c r="BD421" s="1"/>
       <c r="BE421" s="1"/>
       <c r="BF421" s="1"/>
-      <c r="BG421" s="1" t="str">
+      <c r="BG421" s="1"/>
+      <c r="BH421" s="1"/>
+      <c r="BI421" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32092,7 +33141,9 @@
       <c r="BD422" s="1"/>
       <c r="BE422" s="1"/>
       <c r="BF422" s="1"/>
-      <c r="BG422" s="1" t="str">
+      <c r="BG422" s="1"/>
+      <c r="BH422" s="1"/>
+      <c r="BI422" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32159,7 +33210,9 @@
       <c r="BD423" s="1"/>
       <c r="BE423" s="1"/>
       <c r="BF423" s="1"/>
-      <c r="BG423" s="1" t="str">
+      <c r="BG423" s="1"/>
+      <c r="BH423" s="1"/>
+      <c r="BI423" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32226,7 +33279,9 @@
       <c r="BD424" s="1"/>
       <c r="BE424" s="1"/>
       <c r="BF424" s="1"/>
-      <c r="BG424" s="1" t="str">
+      <c r="BG424" s="1"/>
+      <c r="BH424" s="1"/>
+      <c r="BI424" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32293,7 +33348,9 @@
       <c r="BD425" s="1"/>
       <c r="BE425" s="1"/>
       <c r="BF425" s="1"/>
-      <c r="BG425" s="1" t="str">
+      <c r="BG425" s="1"/>
+      <c r="BH425" s="1"/>
+      <c r="BI425" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32360,7 +33417,9 @@
       <c r="BD426" s="1"/>
       <c r="BE426" s="1"/>
       <c r="BF426" s="1"/>
-      <c r="BG426" s="1" t="str">
+      <c r="BG426" s="1"/>
+      <c r="BH426" s="1"/>
+      <c r="BI426" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32427,7 +33486,9 @@
       <c r="BD427" s="1"/>
       <c r="BE427" s="1"/>
       <c r="BF427" s="1"/>
-      <c r="BG427" s="1" t="str">
+      <c r="BG427" s="1"/>
+      <c r="BH427" s="1"/>
+      <c r="BI427" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32494,7 +33555,9 @@
       <c r="BD428" s="1"/>
       <c r="BE428" s="1"/>
       <c r="BF428" s="1"/>
-      <c r="BG428" s="1" t="str">
+      <c r="BG428" s="1"/>
+      <c r="BH428" s="1"/>
+      <c r="BI428" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32561,7 +33624,9 @@
       <c r="BD429" s="1"/>
       <c r="BE429" s="1"/>
       <c r="BF429" s="1"/>
-      <c r="BG429" s="1" t="str">
+      <c r="BG429" s="1"/>
+      <c r="BH429" s="1"/>
+      <c r="BI429" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32628,7 +33693,9 @@
       <c r="BD430" s="1"/>
       <c r="BE430" s="1"/>
       <c r="BF430" s="1"/>
-      <c r="BG430" s="1" t="str">
+      <c r="BG430" s="1"/>
+      <c r="BH430" s="1"/>
+      <c r="BI430" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32695,7 +33762,9 @@
       <c r="BD431" s="1"/>
       <c r="BE431" s="1"/>
       <c r="BF431" s="1"/>
-      <c r="BG431" s="1" t="str">
+      <c r="BG431" s="1"/>
+      <c r="BH431" s="1"/>
+      <c r="BI431" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32762,7 +33831,9 @@
       <c r="BD432" s="1"/>
       <c r="BE432" s="1"/>
       <c r="BF432" s="1"/>
-      <c r="BG432" s="1" t="str">
+      <c r="BG432" s="1"/>
+      <c r="BH432" s="1"/>
+      <c r="BI432" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32829,7 +33900,9 @@
       <c r="BD433" s="1"/>
       <c r="BE433" s="1"/>
       <c r="BF433" s="1"/>
-      <c r="BG433" s="1" t="str">
+      <c r="BG433" s="1"/>
+      <c r="BH433" s="1"/>
+      <c r="BI433" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32896,7 +33969,9 @@
       <c r="BD434" s="1"/>
       <c r="BE434" s="1"/>
       <c r="BF434" s="1"/>
-      <c r="BG434" s="1" t="str">
+      <c r="BG434" s="1"/>
+      <c r="BH434" s="1"/>
+      <c r="BI434" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32963,7 +34038,9 @@
       <c r="BD435" s="1"/>
       <c r="BE435" s="1"/>
       <c r="BF435" s="1"/>
-      <c r="BG435" s="1" t="str">
+      <c r="BG435" s="1"/>
+      <c r="BH435" s="1"/>
+      <c r="BI435" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33030,7 +34107,9 @@
       <c r="BD436" s="1"/>
       <c r="BE436" s="1"/>
       <c r="BF436" s="1"/>
-      <c r="BG436" s="1" t="str">
+      <c r="BG436" s="1"/>
+      <c r="BH436" s="1"/>
+      <c r="BI436" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33097,7 +34176,9 @@
       <c r="BD437" s="1"/>
       <c r="BE437" s="1"/>
       <c r="BF437" s="1"/>
-      <c r="BG437" s="1" t="str">
+      <c r="BG437" s="1"/>
+      <c r="BH437" s="1"/>
+      <c r="BI437" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33164,7 +34245,9 @@
       <c r="BD438" s="1"/>
       <c r="BE438" s="1"/>
       <c r="BF438" s="1"/>
-      <c r="BG438" s="1" t="str">
+      <c r="BG438" s="1"/>
+      <c r="BH438" s="1"/>
+      <c r="BI438" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33231,7 +34314,9 @@
       <c r="BD439" s="1"/>
       <c r="BE439" s="1"/>
       <c r="BF439" s="1"/>
-      <c r="BG439" s="1" t="str">
+      <c r="BG439" s="1"/>
+      <c r="BH439" s="1"/>
+      <c r="BI439" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33298,7 +34383,9 @@
       <c r="BD440" s="1"/>
       <c r="BE440" s="1"/>
       <c r="BF440" s="1"/>
-      <c r="BG440" s="1" t="str">
+      <c r="BG440" s="1"/>
+      <c r="BH440" s="1"/>
+      <c r="BI440" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33365,7 +34452,9 @@
       <c r="BD441" s="1"/>
       <c r="BE441" s="1"/>
       <c r="BF441" s="1"/>
-      <c r="BG441" s="1" t="str">
+      <c r="BG441" s="1"/>
+      <c r="BH441" s="1"/>
+      <c r="BI441" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33432,7 +34521,9 @@
       <c r="BD442" s="1"/>
       <c r="BE442" s="1"/>
       <c r="BF442" s="1"/>
-      <c r="BG442" s="1" t="str">
+      <c r="BG442" s="1"/>
+      <c r="BH442" s="1"/>
+      <c r="BI442" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33499,7 +34590,9 @@
       <c r="BD443" s="1"/>
       <c r="BE443" s="1"/>
       <c r="BF443" s="1"/>
-      <c r="BG443" s="1" t="str">
+      <c r="BG443" s="1"/>
+      <c r="BH443" s="1"/>
+      <c r="BI443" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33566,7 +34659,9 @@
       <c r="BD444" s="1"/>
       <c r="BE444" s="1"/>
       <c r="BF444" s="1"/>
-      <c r="BG444" s="1" t="str">
+      <c r="BG444" s="1"/>
+      <c r="BH444" s="1"/>
+      <c r="BI444" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33633,7 +34728,9 @@
       <c r="BD445" s="1"/>
       <c r="BE445" s="1"/>
       <c r="BF445" s="1"/>
-      <c r="BG445" s="1" t="str">
+      <c r="BG445" s="1"/>
+      <c r="BH445" s="1"/>
+      <c r="BI445" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33700,7 +34797,9 @@
       <c r="BD446" s="1"/>
       <c r="BE446" s="1"/>
       <c r="BF446" s="1"/>
-      <c r="BG446" s="1" t="str">
+      <c r="BG446" s="1"/>
+      <c r="BH446" s="1"/>
+      <c r="BI446" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33767,7 +34866,9 @@
       <c r="BD447" s="1"/>
       <c r="BE447" s="1"/>
       <c r="BF447" s="1"/>
-      <c r="BG447" s="1" t="str">
+      <c r="BG447" s="1"/>
+      <c r="BH447" s="1"/>
+      <c r="BI447" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33834,7 +34935,9 @@
       <c r="BD448" s="1"/>
       <c r="BE448" s="1"/>
       <c r="BF448" s="1"/>
-      <c r="BG448" s="1" t="str">
+      <c r="BG448" s="1"/>
+      <c r="BH448" s="1"/>
+      <c r="BI448" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33901,7 +35004,9 @@
       <c r="BD449" s="1"/>
       <c r="BE449" s="1"/>
       <c r="BF449" s="1"/>
-      <c r="BG449" s="1" t="str">
+      <c r="BG449" s="1"/>
+      <c r="BH449" s="1"/>
+      <c r="BI449" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33968,7 +35073,9 @@
       <c r="BD450" s="1"/>
       <c r="BE450" s="1"/>
       <c r="BF450" s="1"/>
-      <c r="BG450" s="1" t="str">
+      <c r="BG450" s="1"/>
+      <c r="BH450" s="1"/>
+      <c r="BI450" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34035,7 +35142,9 @@
       <c r="BD451" s="1"/>
       <c r="BE451" s="1"/>
       <c r="BF451" s="1"/>
-      <c r="BG451" s="1" t="str">
+      <c r="BG451" s="1"/>
+      <c r="BH451" s="1"/>
+      <c r="BI451" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34102,7 +35211,9 @@
       <c r="BD452" s="1"/>
       <c r="BE452" s="1"/>
       <c r="BF452" s="1"/>
-      <c r="BG452" s="1" t="str">
+      <c r="BG452" s="1"/>
+      <c r="BH452" s="1"/>
+      <c r="BI452" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34169,7 +35280,9 @@
       <c r="BD453" s="1"/>
       <c r="BE453" s="1"/>
       <c r="BF453" s="1"/>
-      <c r="BG453" s="1" t="str">
+      <c r="BG453" s="1"/>
+      <c r="BH453" s="1"/>
+      <c r="BI453" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34236,7 +35349,9 @@
       <c r="BD454" s="1"/>
       <c r="BE454" s="1"/>
       <c r="BF454" s="1"/>
-      <c r="BG454" s="1" t="str">
+      <c r="BG454" s="1"/>
+      <c r="BH454" s="1"/>
+      <c r="BI454" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34303,7 +35418,9 @@
       <c r="BD455" s="1"/>
       <c r="BE455" s="1"/>
       <c r="BF455" s="1"/>
-      <c r="BG455" s="1" t="str">
+      <c r="BG455" s="1"/>
+      <c r="BH455" s="1"/>
+      <c r="BI455" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34370,7 +35487,9 @@
       <c r="BD456" s="1"/>
       <c r="BE456" s="1"/>
       <c r="BF456" s="1"/>
-      <c r="BG456" s="1" t="str">
+      <c r="BG456" s="1"/>
+      <c r="BH456" s="1"/>
+      <c r="BI456" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34437,7 +35556,9 @@
       <c r="BD457" s="1"/>
       <c r="BE457" s="1"/>
       <c r="BF457" s="1"/>
-      <c r="BG457" s="1" t="str">
+      <c r="BG457" s="1"/>
+      <c r="BH457" s="1"/>
+      <c r="BI457" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34504,7 +35625,9 @@
       <c r="BD458" s="1"/>
       <c r="BE458" s="1"/>
       <c r="BF458" s="1"/>
-      <c r="BG458" s="1" t="str">
+      <c r="BG458" s="1"/>
+      <c r="BH458" s="1"/>
+      <c r="BI458" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34571,7 +35694,9 @@
       <c r="BD459" s="1"/>
       <c r="BE459" s="1"/>
       <c r="BF459" s="1"/>
-      <c r="BG459" s="1" t="str">
+      <c r="BG459" s="1"/>
+      <c r="BH459" s="1"/>
+      <c r="BI459" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34638,7 +35763,9 @@
       <c r="BD460" s="1"/>
       <c r="BE460" s="1"/>
       <c r="BF460" s="1"/>
-      <c r="BG460" s="1" t="str">
+      <c r="BG460" s="1"/>
+      <c r="BH460" s="1"/>
+      <c r="BI460" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34705,7 +35832,9 @@
       <c r="BD461" s="1"/>
       <c r="BE461" s="1"/>
       <c r="BF461" s="1"/>
-      <c r="BG461" s="1" t="str">
+      <c r="BG461" s="1"/>
+      <c r="BH461" s="1"/>
+      <c r="BI461" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34772,7 +35901,9 @@
       <c r="BD462" s="1"/>
       <c r="BE462" s="1"/>
       <c r="BF462" s="1"/>
-      <c r="BG462" s="1" t="str">
+      <c r="BG462" s="1"/>
+      <c r="BH462" s="1"/>
+      <c r="BI462" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34839,7 +35970,9 @@
       <c r="BD463" s="1"/>
       <c r="BE463" s="1"/>
       <c r="BF463" s="1"/>
-      <c r="BG463" s="1" t="str">
+      <c r="BG463" s="1"/>
+      <c r="BH463" s="1"/>
+      <c r="BI463" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34906,7 +36039,9 @@
       <c r="BD464" s="1"/>
       <c r="BE464" s="1"/>
       <c r="BF464" s="1"/>
-      <c r="BG464" s="1" t="str">
+      <c r="BG464" s="1"/>
+      <c r="BH464" s="1"/>
+      <c r="BI464" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34973,7 +36108,9 @@
       <c r="BD465" s="1"/>
       <c r="BE465" s="1"/>
       <c r="BF465" s="1"/>
-      <c r="BG465" s="1" t="str">
+      <c r="BG465" s="1"/>
+      <c r="BH465" s="1"/>
+      <c r="BI465" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35040,7 +36177,9 @@
       <c r="BD466" s="1"/>
       <c r="BE466" s="1"/>
       <c r="BF466" s="1"/>
-      <c r="BG466" s="1" t="str">
+      <c r="BG466" s="1"/>
+      <c r="BH466" s="1"/>
+      <c r="BI466" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35107,7 +36246,9 @@
       <c r="BD467" s="1"/>
       <c r="BE467" s="1"/>
       <c r="BF467" s="1"/>
-      <c r="BG467" s="1" t="str">
+      <c r="BG467" s="1"/>
+      <c r="BH467" s="1"/>
+      <c r="BI467" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35174,7 +36315,9 @@
       <c r="BD468" s="1"/>
       <c r="BE468" s="1"/>
       <c r="BF468" s="1"/>
-      <c r="BG468" s="1" t="str">
+      <c r="BG468" s="1"/>
+      <c r="BH468" s="1"/>
+      <c r="BI468" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35241,7 +36384,9 @@
       <c r="BD469" s="1"/>
       <c r="BE469" s="1"/>
       <c r="BF469" s="1"/>
-      <c r="BG469" s="1" t="str">
+      <c r="BG469" s="1"/>
+      <c r="BH469" s="1"/>
+      <c r="BI469" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35308,7 +36453,9 @@
       <c r="BD470" s="1"/>
       <c r="BE470" s="1"/>
       <c r="BF470" s="1"/>
-      <c r="BG470" s="1" t="str">
+      <c r="BG470" s="1"/>
+      <c r="BH470" s="1"/>
+      <c r="BI470" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35375,7 +36522,9 @@
       <c r="BD471" s="1"/>
       <c r="BE471" s="1"/>
       <c r="BF471" s="1"/>
-      <c r="BG471" s="1" t="str">
+      <c r="BG471" s="1"/>
+      <c r="BH471" s="1"/>
+      <c r="BI471" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35442,7 +36591,9 @@
       <c r="BD472" s="1"/>
       <c r="BE472" s="1"/>
       <c r="BF472" s="1"/>
-      <c r="BG472" s="1" t="str">
+      <c r="BG472" s="1"/>
+      <c r="BH472" s="1"/>
+      <c r="BI472" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35509,7 +36660,9 @@
       <c r="BD473" s="1"/>
       <c r="BE473" s="1"/>
       <c r="BF473" s="1"/>
-      <c r="BG473" s="1" t="str">
+      <c r="BG473" s="1"/>
+      <c r="BH473" s="1"/>
+      <c r="BI473" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35576,7 +36729,9 @@
       <c r="BD474" s="1"/>
       <c r="BE474" s="1"/>
       <c r="BF474" s="1"/>
-      <c r="BG474" s="1" t="str">
+      <c r="BG474" s="1"/>
+      <c r="BH474" s="1"/>
+      <c r="BI474" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35643,7 +36798,9 @@
       <c r="BD475" s="1"/>
       <c r="BE475" s="1"/>
       <c r="BF475" s="1"/>
-      <c r="BG475" s="1" t="str">
+      <c r="BG475" s="1"/>
+      <c r="BH475" s="1"/>
+      <c r="BI475" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35710,7 +36867,9 @@
       <c r="BD476" s="1"/>
       <c r="BE476" s="1"/>
       <c r="BF476" s="1"/>
-      <c r="BG476" s="1" t="str">
+      <c r="BG476" s="1"/>
+      <c r="BH476" s="1"/>
+      <c r="BI476" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35777,7 +36936,9 @@
       <c r="BD477" s="1"/>
       <c r="BE477" s="1"/>
       <c r="BF477" s="1"/>
-      <c r="BG477" s="1" t="str">
+      <c r="BG477" s="1"/>
+      <c r="BH477" s="1"/>
+      <c r="BI477" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35844,7 +37005,9 @@
       <c r="BD478" s="1"/>
       <c r="BE478" s="1"/>
       <c r="BF478" s="1"/>
-      <c r="BG478" s="1" t="str">
+      <c r="BG478" s="1"/>
+      <c r="BH478" s="1"/>
+      <c r="BI478" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35911,7 +37074,9 @@
       <c r="BD479" s="1"/>
       <c r="BE479" s="1"/>
       <c r="BF479" s="1"/>
-      <c r="BG479" s="1" t="str">
+      <c r="BG479" s="1"/>
+      <c r="BH479" s="1"/>
+      <c r="BI479" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35978,7 +37143,9 @@
       <c r="BD480" s="1"/>
       <c r="BE480" s="1"/>
       <c r="BF480" s="1"/>
-      <c r="BG480" s="1" t="str">
+      <c r="BG480" s="1"/>
+      <c r="BH480" s="1"/>
+      <c r="BI480" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36045,7 +37212,9 @@
       <c r="BD481" s="1"/>
       <c r="BE481" s="1"/>
       <c r="BF481" s="1"/>
-      <c r="BG481" s="1" t="str">
+      <c r="BG481" s="1"/>
+      <c r="BH481" s="1"/>
+      <c r="BI481" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36112,7 +37281,9 @@
       <c r="BD482" s="1"/>
       <c r="BE482" s="1"/>
       <c r="BF482" s="1"/>
-      <c r="BG482" s="1" t="str">
+      <c r="BG482" s="1"/>
+      <c r="BH482" s="1"/>
+      <c r="BI482" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36179,7 +37350,9 @@
       <c r="BD483" s="1"/>
       <c r="BE483" s="1"/>
       <c r="BF483" s="1"/>
-      <c r="BG483" s="1" t="str">
+      <c r="BG483" s="1"/>
+      <c r="BH483" s="1"/>
+      <c r="BI483" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36246,7 +37419,9 @@
       <c r="BD484" s="1"/>
       <c r="BE484" s="1"/>
       <c r="BF484" s="1"/>
-      <c r="BG484" s="1" t="str">
+      <c r="BG484" s="1"/>
+      <c r="BH484" s="1"/>
+      <c r="BI484" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36313,7 +37488,9 @@
       <c r="BD485" s="1"/>
       <c r="BE485" s="1"/>
       <c r="BF485" s="1"/>
-      <c r="BG485" s="1" t="str">
+      <c r="BG485" s="1"/>
+      <c r="BH485" s="1"/>
+      <c r="BI485" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36380,7 +37557,9 @@
       <c r="BD486" s="1"/>
       <c r="BE486" s="1"/>
       <c r="BF486" s="1"/>
-      <c r="BG486" s="1" t="str">
+      <c r="BG486" s="1"/>
+      <c r="BH486" s="1"/>
+      <c r="BI486" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36447,7 +37626,9 @@
       <c r="BD487" s="1"/>
       <c r="BE487" s="1"/>
       <c r="BF487" s="1"/>
-      <c r="BG487" s="1" t="str">
+      <c r="BG487" s="1"/>
+      <c r="BH487" s="1"/>
+      <c r="BI487" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36514,7 +37695,9 @@
       <c r="BD488" s="1"/>
       <c r="BE488" s="1"/>
       <c r="BF488" s="1"/>
-      <c r="BG488" s="1" t="str">
+      <c r="BG488" s="1"/>
+      <c r="BH488" s="1"/>
+      <c r="BI488" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36581,7 +37764,9 @@
       <c r="BD489" s="1"/>
       <c r="BE489" s="1"/>
       <c r="BF489" s="1"/>
-      <c r="BG489" s="1" t="str">
+      <c r="BG489" s="1"/>
+      <c r="BH489" s="1"/>
+      <c r="BI489" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36648,7 +37833,9 @@
       <c r="BD490" s="1"/>
       <c r="BE490" s="1"/>
       <c r="BF490" s="1"/>
-      <c r="BG490" s="1" t="str">
+      <c r="BG490" s="1"/>
+      <c r="BH490" s="1"/>
+      <c r="BI490" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36715,7 +37902,9 @@
       <c r="BD491" s="1"/>
       <c r="BE491" s="1"/>
       <c r="BF491" s="1"/>
-      <c r="BG491" s="1" t="str">
+      <c r="BG491" s="1"/>
+      <c r="BH491" s="1"/>
+      <c r="BI491" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36782,7 +37971,9 @@
       <c r="BD492" s="1"/>
       <c r="BE492" s="1"/>
       <c r="BF492" s="1"/>
-      <c r="BG492" s="1" t="str">
+      <c r="BG492" s="1"/>
+      <c r="BH492" s="1"/>
+      <c r="BI492" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36849,7 +38040,9 @@
       <c r="BD493" s="1"/>
       <c r="BE493" s="1"/>
       <c r="BF493" s="1"/>
-      <c r="BG493" s="1" t="str">
+      <c r="BG493" s="1"/>
+      <c r="BH493" s="1"/>
+      <c r="BI493" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36916,7 +38109,9 @@
       <c r="BD494" s="1"/>
       <c r="BE494" s="1"/>
       <c r="BF494" s="1"/>
-      <c r="BG494" s="1" t="str">
+      <c r="BG494" s="1"/>
+      <c r="BH494" s="1"/>
+      <c r="BI494" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36983,7 +38178,9 @@
       <c r="BD495" s="1"/>
       <c r="BE495" s="1"/>
       <c r="BF495" s="1"/>
-      <c r="BG495" s="1" t="str">
+      <c r="BG495" s="1"/>
+      <c r="BH495" s="1"/>
+      <c r="BI495" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37050,7 +38247,9 @@
       <c r="BD496" s="1"/>
       <c r="BE496" s="1"/>
       <c r="BF496" s="1"/>
-      <c r="BG496" s="1" t="str">
+      <c r="BG496" s="1"/>
+      <c r="BH496" s="1"/>
+      <c r="BI496" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37117,7 +38316,9 @@
       <c r="BD497" s="1"/>
       <c r="BE497" s="1"/>
       <c r="BF497" s="1"/>
-      <c r="BG497" s="1" t="str">
+      <c r="BG497" s="1"/>
+      <c r="BH497" s="1"/>
+      <c r="BI497" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37184,7 +38385,9 @@
       <c r="BD498" s="1"/>
       <c r="BE498" s="1"/>
       <c r="BF498" s="1"/>
-      <c r="BG498" s="1" t="str">
+      <c r="BG498" s="1"/>
+      <c r="BH498" s="1"/>
+      <c r="BI498" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37251,7 +38454,9 @@
       <c r="BD499" s="1"/>
       <c r="BE499" s="1"/>
       <c r="BF499" s="1"/>
-      <c r="BG499" s="1" t="str">
+      <c r="BG499" s="1"/>
+      <c r="BH499" s="1"/>
+      <c r="BI499" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37318,7 +38523,9 @@
       <c r="BD500" s="1"/>
       <c r="BE500" s="1"/>
       <c r="BF500" s="1"/>
-      <c r="BG500" s="1" t="str">
+      <c r="BG500" s="1"/>
+      <c r="BH500" s="1"/>
+      <c r="BI500" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37385,7 +38592,9 @@
       <c r="BD501" s="1"/>
       <c r="BE501" s="1"/>
       <c r="BF501" s="1"/>
-      <c r="BG501" s="1" t="str">
+      <c r="BG501" s="1"/>
+      <c r="BH501" s="1"/>
+      <c r="BI501" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37452,7 +38661,9 @@
       <c r="BD502" s="1"/>
       <c r="BE502" s="1"/>
       <c r="BF502" s="1"/>
-      <c r="BG502" s="1" t="str">
+      <c r="BG502" s="1"/>
+      <c r="BH502" s="1"/>
+      <c r="BI502" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37519,7 +38730,9 @@
       <c r="BD503" s="1"/>
       <c r="BE503" s="1"/>
       <c r="BF503" s="1"/>
-      <c r="BG503" s="1" t="str">
+      <c r="BG503" s="1"/>
+      <c r="BH503" s="1"/>
+      <c r="BI503" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37586,7 +38799,9 @@
       <c r="BD504" s="1"/>
       <c r="BE504" s="1"/>
       <c r="BF504" s="1"/>
-      <c r="BG504" s="1" t="str">
+      <c r="BG504" s="1"/>
+      <c r="BH504" s="1"/>
+      <c r="BI504" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37653,7 +38868,9 @@
       <c r="BD505" s="1"/>
       <c r="BE505" s="1"/>
       <c r="BF505" s="1"/>
-      <c r="BG505" s="1" t="str">
+      <c r="BG505" s="1"/>
+      <c r="BH505" s="1"/>
+      <c r="BI505" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37720,7 +38937,9 @@
       <c r="BD506" s="1"/>
       <c r="BE506" s="1"/>
       <c r="BF506" s="1"/>
-      <c r="BG506" s="1" t="str">
+      <c r="BG506" s="1"/>
+      <c r="BH506" s="1"/>
+      <c r="BI506" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37787,7 +39006,9 @@
       <c r="BD507" s="1"/>
       <c r="BE507" s="1"/>
       <c r="BF507" s="1"/>
-      <c r="BG507" s="1" t="str">
+      <c r="BG507" s="1"/>
+      <c r="BH507" s="1"/>
+      <c r="BI507" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37854,7 +39075,9 @@
       <c r="BD508" s="1"/>
       <c r="BE508" s="1"/>
       <c r="BF508" s="1"/>
-      <c r="BG508" s="1" t="str">
+      <c r="BG508" s="1"/>
+      <c r="BH508" s="1"/>
+      <c r="BI508" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37921,7 +39144,9 @@
       <c r="BD509" s="1"/>
       <c r="BE509" s="1"/>
       <c r="BF509" s="1"/>
-      <c r="BG509" s="1" t="str">
+      <c r="BG509" s="1"/>
+      <c r="BH509" s="1"/>
+      <c r="BI509" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37988,7 +39213,9 @@
       <c r="BD510" s="1"/>
       <c r="BE510" s="1"/>
       <c r="BF510" s="1"/>
-      <c r="BG510" s="1" t="str">
+      <c r="BG510" s="1"/>
+      <c r="BH510" s="1"/>
+      <c r="BI510" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38055,7 +39282,9 @@
       <c r="BD511" s="1"/>
       <c r="BE511" s="1"/>
       <c r="BF511" s="1"/>
-      <c r="BG511" s="1" t="str">
+      <c r="BG511" s="1"/>
+      <c r="BH511" s="1"/>
+      <c r="BI511" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38122,7 +39351,9 @@
       <c r="BD512" s="1"/>
       <c r="BE512" s="1"/>
       <c r="BF512" s="1"/>
-      <c r="BG512" s="1" t="str">
+      <c r="BG512" s="1"/>
+      <c r="BH512" s="1"/>
+      <c r="BI512" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38189,7 +39420,9 @@
       <c r="BD513" s="1"/>
       <c r="BE513" s="1"/>
       <c r="BF513" s="1"/>
-      <c r="BG513" s="1" t="str">
+      <c r="BG513" s="1"/>
+      <c r="BH513" s="1"/>
+      <c r="BI513" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38256,7 +39489,9 @@
       <c r="BD514" s="1"/>
       <c r="BE514" s="1"/>
       <c r="BF514" s="1"/>
-      <c r="BG514" s="1" t="str">
+      <c r="BG514" s="1"/>
+      <c r="BH514" s="1"/>
+      <c r="BI514" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38323,7 +39558,9 @@
       <c r="BD515" s="1"/>
       <c r="BE515" s="1"/>
       <c r="BF515" s="1"/>
-      <c r="BG515" s="1" t="str">
+      <c r="BG515" s="1"/>
+      <c r="BH515" s="1"/>
+      <c r="BI515" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38390,7 +39627,9 @@
       <c r="BD516" s="1"/>
       <c r="BE516" s="1"/>
       <c r="BF516" s="1"/>
-      <c r="BG516" s="1" t="str">
+      <c r="BG516" s="1"/>
+      <c r="BH516" s="1"/>
+      <c r="BI516" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38457,7 +39696,9 @@
       <c r="BD517" s="1"/>
       <c r="BE517" s="1"/>
       <c r="BF517" s="1"/>
-      <c r="BG517" s="1" t="str">
+      <c r="BG517" s="1"/>
+      <c r="BH517" s="1"/>
+      <c r="BI517" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38524,7 +39765,9 @@
       <c r="BD518" s="1"/>
       <c r="BE518" s="1"/>
       <c r="BF518" s="1"/>
-      <c r="BG518" s="1" t="str">
+      <c r="BG518" s="1"/>
+      <c r="BH518" s="1"/>
+      <c r="BI518" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38591,7 +39834,9 @@
       <c r="BD519" s="1"/>
       <c r="BE519" s="1"/>
       <c r="BF519" s="1"/>
-      <c r="BG519" s="1" t="str">
+      <c r="BG519" s="1"/>
+      <c r="BH519" s="1"/>
+      <c r="BI519" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38658,7 +39903,9 @@
       <c r="BD520" s="1"/>
       <c r="BE520" s="1"/>
       <c r="BF520" s="1"/>
-      <c r="BG520" s="1" t="str">
+      <c r="BG520" s="1"/>
+      <c r="BH520" s="1"/>
+      <c r="BI520" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38725,7 +39972,9 @@
       <c r="BD521" s="1"/>
       <c r="BE521" s="1"/>
       <c r="BF521" s="1"/>
-      <c r="BG521" s="1" t="str">
+      <c r="BG521" s="1"/>
+      <c r="BH521" s="1"/>
+      <c r="BI521" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38792,7 +40041,9 @@
       <c r="BD522" s="1"/>
       <c r="BE522" s="1"/>
       <c r="BF522" s="1"/>
-      <c r="BG522" s="1" t="str">
+      <c r="BG522" s="1"/>
+      <c r="BH522" s="1"/>
+      <c r="BI522" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38859,7 +40110,9 @@
       <c r="BD523" s="1"/>
       <c r="BE523" s="1"/>
       <c r="BF523" s="1"/>
-      <c r="BG523" s="1" t="str">
+      <c r="BG523" s="1"/>
+      <c r="BH523" s="1"/>
+      <c r="BI523" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38926,7 +40179,9 @@
       <c r="BD524" s="1"/>
       <c r="BE524" s="1"/>
       <c r="BF524" s="1"/>
-      <c r="BG524" s="1" t="str">
+      <c r="BG524" s="1"/>
+      <c r="BH524" s="1"/>
+      <c r="BI524" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38993,7 +40248,9 @@
       <c r="BD525" s="1"/>
       <c r="BE525" s="1"/>
       <c r="BF525" s="1"/>
-      <c r="BG525" s="1" t="str">
+      <c r="BG525" s="1"/>
+      <c r="BH525" s="1"/>
+      <c r="BI525" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39060,7 +40317,9 @@
       <c r="BD526" s="1"/>
       <c r="BE526" s="1"/>
       <c r="BF526" s="1"/>
-      <c r="BG526" s="1" t="str">
+      <c r="BG526" s="1"/>
+      <c r="BH526" s="1"/>
+      <c r="BI526" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39127,7 +40386,9 @@
       <c r="BD527" s="1"/>
       <c r="BE527" s="1"/>
       <c r="BF527" s="1"/>
-      <c r="BG527" s="1" t="str">
+      <c r="BG527" s="1"/>
+      <c r="BH527" s="1"/>
+      <c r="BI527" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39194,7 +40455,9 @@
       <c r="BD528" s="1"/>
       <c r="BE528" s="1"/>
       <c r="BF528" s="1"/>
-      <c r="BG528" s="1" t="str">
+      <c r="BG528" s="1"/>
+      <c r="BH528" s="1"/>
+      <c r="BI528" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39261,7 +40524,9 @@
       <c r="BD529" s="1"/>
       <c r="BE529" s="1"/>
       <c r="BF529" s="1"/>
-      <c r="BG529" s="1" t="str">
+      <c r="BG529" s="1"/>
+      <c r="BH529" s="1"/>
+      <c r="BI529" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39328,7 +40593,9 @@
       <c r="BD530" s="1"/>
       <c r="BE530" s="1"/>
       <c r="BF530" s="1"/>
-      <c r="BG530" s="1" t="str">
+      <c r="BG530" s="1"/>
+      <c r="BH530" s="1"/>
+      <c r="BI530" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39395,7 +40662,9 @@
       <c r="BD531" s="1"/>
       <c r="BE531" s="1"/>
       <c r="BF531" s="1"/>
-      <c r="BG531" s="1" t="str">
+      <c r="BG531" s="1"/>
+      <c r="BH531" s="1"/>
+      <c r="BI531" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39462,7 +40731,9 @@
       <c r="BD532" s="1"/>
       <c r="BE532" s="1"/>
       <c r="BF532" s="1"/>
-      <c r="BG532" s="1" t="str">
+      <c r="BG532" s="1"/>
+      <c r="BH532" s="1"/>
+      <c r="BI532" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39529,7 +40800,9 @@
       <c r="BD533" s="1"/>
       <c r="BE533" s="1"/>
       <c r="BF533" s="1"/>
-      <c r="BG533" s="1" t="str">
+      <c r="BG533" s="1"/>
+      <c r="BH533" s="1"/>
+      <c r="BI533" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39596,7 +40869,9 @@
       <c r="BD534" s="1"/>
       <c r="BE534" s="1"/>
       <c r="BF534" s="1"/>
-      <c r="BG534" s="1" t="str">
+      <c r="BG534" s="1"/>
+      <c r="BH534" s="1"/>
+      <c r="BI534" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39663,7 +40938,9 @@
       <c r="BD535" s="1"/>
       <c r="BE535" s="1"/>
       <c r="BF535" s="1"/>
-      <c r="BG535" s="1" t="str">
+      <c r="BG535" s="1"/>
+      <c r="BH535" s="1"/>
+      <c r="BI535" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39730,7 +41007,9 @@
       <c r="BD536" s="1"/>
       <c r="BE536" s="1"/>
       <c r="BF536" s="1"/>
-      <c r="BG536" s="1" t="str">
+      <c r="BG536" s="1"/>
+      <c r="BH536" s="1"/>
+      <c r="BI536" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39797,7 +41076,9 @@
       <c r="BD537" s="1"/>
       <c r="BE537" s="1"/>
       <c r="BF537" s="1"/>
-      <c r="BG537" s="1" t="str">
+      <c r="BG537" s="1"/>
+      <c r="BH537" s="1"/>
+      <c r="BI537" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39864,7 +41145,9 @@
       <c r="BD538" s="1"/>
       <c r="BE538" s="1"/>
       <c r="BF538" s="1"/>
-      <c r="BG538" s="1" t="str">
+      <c r="BG538" s="1"/>
+      <c r="BH538" s="1"/>
+      <c r="BI538" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39931,7 +41214,9 @@
       <c r="BD539" s="1"/>
       <c r="BE539" s="1"/>
       <c r="BF539" s="1"/>
-      <c r="BG539" s="1" t="str">
+      <c r="BG539" s="1"/>
+      <c r="BH539" s="1"/>
+      <c r="BI539" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39998,7 +41283,9 @@
       <c r="BD540" s="1"/>
       <c r="BE540" s="1"/>
       <c r="BF540" s="1"/>
-      <c r="BG540" s="1" t="str">
+      <c r="BG540" s="1"/>
+      <c r="BH540" s="1"/>
+      <c r="BI540" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40065,7 +41352,9 @@
       <c r="BD541" s="1"/>
       <c r="BE541" s="1"/>
       <c r="BF541" s="1"/>
-      <c r="BG541" s="1" t="str">
+      <c r="BG541" s="1"/>
+      <c r="BH541" s="1"/>
+      <c r="BI541" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40132,7 +41421,9 @@
       <c r="BD542" s="1"/>
       <c r="BE542" s="1"/>
       <c r="BF542" s="1"/>
-      <c r="BG542" s="1" t="str">
+      <c r="BG542" s="1"/>
+      <c r="BH542" s="1"/>
+      <c r="BI542" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40199,7 +41490,9 @@
       <c r="BD543" s="1"/>
       <c r="BE543" s="1"/>
       <c r="BF543" s="1"/>
-      <c r="BG543" s="1" t="str">
+      <c r="BG543" s="1"/>
+      <c r="BH543" s="1"/>
+      <c r="BI543" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40266,7 +41559,9 @@
       <c r="BD544" s="1"/>
       <c r="BE544" s="1"/>
       <c r="BF544" s="1"/>
-      <c r="BG544" s="1" t="str">
+      <c r="BG544" s="1"/>
+      <c r="BH544" s="1"/>
+      <c r="BI544" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40333,7 +41628,9 @@
       <c r="BD545" s="1"/>
       <c r="BE545" s="1"/>
       <c r="BF545" s="1"/>
-      <c r="BG545" s="1" t="str">
+      <c r="BG545" s="1"/>
+      <c r="BH545" s="1"/>
+      <c r="BI545" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40400,7 +41697,9 @@
       <c r="BD546" s="1"/>
       <c r="BE546" s="1"/>
       <c r="BF546" s="1"/>
-      <c r="BG546" s="1" t="str">
+      <c r="BG546" s="1"/>
+      <c r="BH546" s="1"/>
+      <c r="BI546" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40467,7 +41766,9 @@
       <c r="BD547" s="1"/>
       <c r="BE547" s="1"/>
       <c r="BF547" s="1"/>
-      <c r="BG547" s="1" t="str">
+      <c r="BG547" s="1"/>
+      <c r="BH547" s="1"/>
+      <c r="BI547" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40534,7 +41835,9 @@
       <c r="BD548" s="1"/>
       <c r="BE548" s="1"/>
       <c r="BF548" s="1"/>
-      <c r="BG548" s="1" t="str">
+      <c r="BG548" s="1"/>
+      <c r="BH548" s="1"/>
+      <c r="BI548" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40601,7 +41904,9 @@
       <c r="BD549" s="1"/>
       <c r="BE549" s="1"/>
       <c r="BF549" s="1"/>
-      <c r="BG549" s="1" t="str">
+      <c r="BG549" s="1"/>
+      <c r="BH549" s="1"/>
+      <c r="BI549" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40668,7 +41973,9 @@
       <c r="BD550" s="1"/>
       <c r="BE550" s="1"/>
       <c r="BF550" s="1"/>
-      <c r="BG550" s="1" t="str">
+      <c r="BG550" s="1"/>
+      <c r="BH550" s="1"/>
+      <c r="BI550" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40735,7 +42042,9 @@
       <c r="BD551" s="1"/>
       <c r="BE551" s="1"/>
       <c r="BF551" s="1"/>
-      <c r="BG551" s="1" t="str">
+      <c r="BG551" s="1"/>
+      <c r="BH551" s="1"/>
+      <c r="BI551" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40802,7 +42111,9 @@
       <c r="BD552" s="1"/>
       <c r="BE552" s="1"/>
       <c r="BF552" s="1"/>
-      <c r="BG552" s="1" t="str">
+      <c r="BG552" s="1"/>
+      <c r="BH552" s="1"/>
+      <c r="BI552" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40869,7 +42180,9 @@
       <c r="BD553" s="1"/>
       <c r="BE553" s="1"/>
       <c r="BF553" s="1"/>
-      <c r="BG553" s="1" t="str">
+      <c r="BG553" s="1"/>
+      <c r="BH553" s="1"/>
+      <c r="BI553" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40936,7 +42249,9 @@
       <c r="BD554" s="1"/>
       <c r="BE554" s="1"/>
       <c r="BF554" s="1"/>
-      <c r="BG554" s="1" t="str">
+      <c r="BG554" s="1"/>
+      <c r="BH554" s="1"/>
+      <c r="BI554" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41003,7 +42318,9 @@
       <c r="BD555" s="1"/>
       <c r="BE555" s="1"/>
       <c r="BF555" s="1"/>
-      <c r="BG555" s="1" t="str">
+      <c r="BG555" s="1"/>
+      <c r="BH555" s="1"/>
+      <c r="BI555" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41070,7 +42387,9 @@
       <c r="BD556" s="1"/>
       <c r="BE556" s="1"/>
       <c r="BF556" s="1"/>
-      <c r="BG556" s="1" t="str">
+      <c r="BG556" s="1"/>
+      <c r="BH556" s="1"/>
+      <c r="BI556" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41137,7 +42456,9 @@
       <c r="BD557" s="1"/>
       <c r="BE557" s="1"/>
       <c r="BF557" s="1"/>
-      <c r="BG557" s="1" t="str">
+      <c r="BG557" s="1"/>
+      <c r="BH557" s="1"/>
+      <c r="BI557" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41204,7 +42525,9 @@
       <c r="BD558" s="1"/>
       <c r="BE558" s="1"/>
       <c r="BF558" s="1"/>
-      <c r="BG558" s="1" t="str">
+      <c r="BG558" s="1"/>
+      <c r="BH558" s="1"/>
+      <c r="BI558" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41271,7 +42594,9 @@
       <c r="BD559" s="1"/>
       <c r="BE559" s="1"/>
       <c r="BF559" s="1"/>
-      <c r="BG559" s="1" t="str">
+      <c r="BG559" s="1"/>
+      <c r="BH559" s="1"/>
+      <c r="BI559" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41338,7 +42663,9 @@
       <c r="BD560" s="1"/>
       <c r="BE560" s="1"/>
       <c r="BF560" s="1"/>
-      <c r="BG560" s="1" t="str">
+      <c r="BG560" s="1"/>
+      <c r="BH560" s="1"/>
+      <c r="BI560" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41405,7 +42732,9 @@
       <c r="BD561" s="1"/>
       <c r="BE561" s="1"/>
       <c r="BF561" s="1"/>
-      <c r="BG561" s="1" t="str">
+      <c r="BG561" s="1"/>
+      <c r="BH561" s="1"/>
+      <c r="BI561" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41472,7 +42801,9 @@
       <c r="BD562" s="1"/>
       <c r="BE562" s="1"/>
       <c r="BF562" s="1"/>
-      <c r="BG562" s="1" t="str">
+      <c r="BG562" s="1"/>
+      <c r="BH562" s="1"/>
+      <c r="BI562" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41539,7 +42870,9 @@
       <c r="BD563" s="1"/>
       <c r="BE563" s="1"/>
       <c r="BF563" s="1"/>
-      <c r="BG563" s="1" t="str">
+      <c r="BG563" s="1"/>
+      <c r="BH563" s="1"/>
+      <c r="BI563" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41606,7 +42939,9 @@
       <c r="BD564" s="1"/>
       <c r="BE564" s="1"/>
       <c r="BF564" s="1"/>
-      <c r="BG564" s="1" t="str">
+      <c r="BG564" s="1"/>
+      <c r="BH564" s="1"/>
+      <c r="BI564" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41673,7 +43008,9 @@
       <c r="BD565" s="1"/>
       <c r="BE565" s="1"/>
       <c r="BF565" s="1"/>
-      <c r="BG565" s="1" t="str">
+      <c r="BG565" s="1"/>
+      <c r="BH565" s="1"/>
+      <c r="BI565" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41740,7 +43077,9 @@
       <c r="BD566" s="1"/>
       <c r="BE566" s="1"/>
       <c r="BF566" s="1"/>
-      <c r="BG566" s="1" t="str">
+      <c r="BG566" s="1"/>
+      <c r="BH566" s="1"/>
+      <c r="BI566" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41807,7 +43146,9 @@
       <c r="BD567" s="1"/>
       <c r="BE567" s="1"/>
       <c r="BF567" s="1"/>
-      <c r="BG567" s="1" t="str">
+      <c r="BG567" s="1"/>
+      <c r="BH567" s="1"/>
+      <c r="BI567" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41874,7 +43215,9 @@
       <c r="BD568" s="1"/>
       <c r="BE568" s="1"/>
       <c r="BF568" s="1"/>
-      <c r="BG568" s="1" t="str">
+      <c r="BG568" s="1"/>
+      <c r="BH568" s="1"/>
+      <c r="BI568" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41941,7 +43284,9 @@
       <c r="BD569" s="1"/>
       <c r="BE569" s="1"/>
       <c r="BF569" s="1"/>
-      <c r="BG569" s="1" t="str">
+      <c r="BG569" s="1"/>
+      <c r="BH569" s="1"/>
+      <c r="BI569" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42008,7 +43353,9 @@
       <c r="BD570" s="1"/>
       <c r="BE570" s="1"/>
       <c r="BF570" s="1"/>
-      <c r="BG570" s="1" t="str">
+      <c r="BG570" s="1"/>
+      <c r="BH570" s="1"/>
+      <c r="BI570" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42075,7 +43422,9 @@
       <c r="BD571" s="1"/>
       <c r="BE571" s="1"/>
       <c r="BF571" s="1"/>
-      <c r="BG571" s="1" t="str">
+      <c r="BG571" s="1"/>
+      <c r="BH571" s="1"/>
+      <c r="BI571" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42142,7 +43491,9 @@
       <c r="BD572" s="1"/>
       <c r="BE572" s="1"/>
       <c r="BF572" s="1"/>
-      <c r="BG572" s="1" t="str">
+      <c r="BG572" s="1"/>
+      <c r="BH572" s="1"/>
+      <c r="BI572" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42209,7 +43560,9 @@
       <c r="BD573" s="1"/>
       <c r="BE573" s="1"/>
       <c r="BF573" s="1"/>
-      <c r="BG573" s="1" t="str">
+      <c r="BG573" s="1"/>
+      <c r="BH573" s="1"/>
+      <c r="BI573" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42276,7 +43629,9 @@
       <c r="BD574" s="1"/>
       <c r="BE574" s="1"/>
       <c r="BF574" s="1"/>
-      <c r="BG574" s="1" t="str">
+      <c r="BG574" s="1"/>
+      <c r="BH574" s="1"/>
+      <c r="BI574" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42343,7 +43698,9 @@
       <c r="BD575" s="1"/>
       <c r="BE575" s="1"/>
       <c r="BF575" s="1"/>
-      <c r="BG575" s="1" t="str">
+      <c r="BG575" s="1"/>
+      <c r="BH575" s="1"/>
+      <c r="BI575" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42410,7 +43767,9 @@
       <c r="BD576" s="1"/>
       <c r="BE576" s="1"/>
       <c r="BF576" s="1"/>
-      <c r="BG576" s="1" t="str">
+      <c r="BG576" s="1"/>
+      <c r="BH576" s="1"/>
+      <c r="BI576" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42477,7 +43836,9 @@
       <c r="BD577" s="1"/>
       <c r="BE577" s="1"/>
       <c r="BF577" s="1"/>
-      <c r="BG577" s="1" t="str">
+      <c r="BG577" s="1"/>
+      <c r="BH577" s="1"/>
+      <c r="BI577" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42544,7 +43905,9 @@
       <c r="BD578" s="1"/>
       <c r="BE578" s="1"/>
       <c r="BF578" s="1"/>
-      <c r="BG578" s="1" t="str">
+      <c r="BG578" s="1"/>
+      <c r="BH578" s="1"/>
+      <c r="BI578" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42611,7 +43974,9 @@
       <c r="BD579" s="1"/>
       <c r="BE579" s="1"/>
       <c r="BF579" s="1"/>
-      <c r="BG579" s="1" t="str">
+      <c r="BG579" s="1"/>
+      <c r="BH579" s="1"/>
+      <c r="BI579" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42678,7 +44043,9 @@
       <c r="BD580" s="1"/>
       <c r="BE580" s="1"/>
       <c r="BF580" s="1"/>
-      <c r="BG580" s="1" t="str">
+      <c r="BG580" s="1"/>
+      <c r="BH580" s="1"/>
+      <c r="BI580" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42745,7 +44112,9 @@
       <c r="BD581" s="1"/>
       <c r="BE581" s="1"/>
       <c r="BF581" s="1"/>
-      <c r="BG581" s="1" t="str">
+      <c r="BG581" s="1"/>
+      <c r="BH581" s="1"/>
+      <c r="BI581" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42812,7 +44181,9 @@
       <c r="BD582" s="1"/>
       <c r="BE582" s="1"/>
       <c r="BF582" s="1"/>
-      <c r="BG582" s="1" t="str">
+      <c r="BG582" s="1"/>
+      <c r="BH582" s="1"/>
+      <c r="BI582" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42879,7 +44250,9 @@
       <c r="BD583" s="1"/>
       <c r="BE583" s="1"/>
       <c r="BF583" s="1"/>
-      <c r="BG583" s="1" t="str">
+      <c r="BG583" s="1"/>
+      <c r="BH583" s="1"/>
+      <c r="BI583" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42946,7 +44319,9 @@
       <c r="BD584" s="1"/>
       <c r="BE584" s="1"/>
       <c r="BF584" s="1"/>
-      <c r="BG584" s="1" t="str">
+      <c r="BG584" s="1"/>
+      <c r="BH584" s="1"/>
+      <c r="BI584" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43013,7 +44388,9 @@
       <c r="BD585" s="1"/>
       <c r="BE585" s="1"/>
       <c r="BF585" s="1"/>
-      <c r="BG585" s="1" t="str">
+      <c r="BG585" s="1"/>
+      <c r="BH585" s="1"/>
+      <c r="BI585" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43080,7 +44457,9 @@
       <c r="BD586" s="1"/>
       <c r="BE586" s="1"/>
       <c r="BF586" s="1"/>
-      <c r="BG586" s="1" t="str">
+      <c r="BG586" s="1"/>
+      <c r="BH586" s="1"/>
+      <c r="BI586" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43147,7 +44526,9 @@
       <c r="BD587" s="1"/>
       <c r="BE587" s="1"/>
       <c r="BF587" s="1"/>
-      <c r="BG587" s="1" t="str">
+      <c r="BG587" s="1"/>
+      <c r="BH587" s="1"/>
+      <c r="BI587" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43214,7 +44595,9 @@
       <c r="BD588" s="1"/>
       <c r="BE588" s="1"/>
       <c r="BF588" s="1"/>
-      <c r="BG588" s="1" t="str">
+      <c r="BG588" s="1"/>
+      <c r="BH588" s="1"/>
+      <c r="BI588" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43281,7 +44664,9 @@
       <c r="BD589" s="1"/>
       <c r="BE589" s="1"/>
       <c r="BF589" s="1"/>
-      <c r="BG589" s="1" t="str">
+      <c r="BG589" s="1"/>
+      <c r="BH589" s="1"/>
+      <c r="BI589" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43348,7 +44733,9 @@
       <c r="BD590" s="1"/>
       <c r="BE590" s="1"/>
       <c r="BF590" s="1"/>
-      <c r="BG590" s="1" t="str">
+      <c r="BG590" s="1"/>
+      <c r="BH590" s="1"/>
+      <c r="BI590" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43415,7 +44802,9 @@
       <c r="BD591" s="1"/>
       <c r="BE591" s="1"/>
       <c r="BF591" s="1"/>
-      <c r="BG591" s="1" t="str">
+      <c r="BG591" s="1"/>
+      <c r="BH591" s="1"/>
+      <c r="BI591" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43482,7 +44871,9 @@
       <c r="BD592" s="1"/>
       <c r="BE592" s="1"/>
       <c r="BF592" s="1"/>
-      <c r="BG592" s="1" t="str">
+      <c r="BG592" s="1"/>
+      <c r="BH592" s="1"/>
+      <c r="BI592" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43549,7 +44940,9 @@
       <c r="BD593" s="1"/>
       <c r="BE593" s="1"/>
       <c r="BF593" s="1"/>
-      <c r="BG593" s="1" t="str">
+      <c r="BG593" s="1"/>
+      <c r="BH593" s="1"/>
+      <c r="BI593" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43616,7 +45009,9 @@
       <c r="BD594" s="1"/>
       <c r="BE594" s="1"/>
       <c r="BF594" s="1"/>
-      <c r="BG594" s="1" t="str">
+      <c r="BG594" s="1"/>
+      <c r="BH594" s="1"/>
+      <c r="BI594" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43683,7 +45078,9 @@
       <c r="BD595" s="1"/>
       <c r="BE595" s="1"/>
       <c r="BF595" s="1"/>
-      <c r="BG595" s="1" t="str">
+      <c r="BG595" s="1"/>
+      <c r="BH595" s="1"/>
+      <c r="BI595" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43750,7 +45147,9 @@
       <c r="BD596" s="1"/>
       <c r="BE596" s="1"/>
       <c r="BF596" s="1"/>
-      <c r="BG596" s="1" t="str">
+      <c r="BG596" s="1"/>
+      <c r="BH596" s="1"/>
+      <c r="BI596" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43817,7 +45216,9 @@
       <c r="BD597" s="1"/>
       <c r="BE597" s="1"/>
       <c r="BF597" s="1"/>
-      <c r="BG597" s="1" t="str">
+      <c r="BG597" s="1"/>
+      <c r="BH597" s="1"/>
+      <c r="BI597" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43884,7 +45285,9 @@
       <c r="BD598" s="1"/>
       <c r="BE598" s="1"/>
       <c r="BF598" s="1"/>
-      <c r="BG598" s="1" t="str">
+      <c r="BG598" s="1"/>
+      <c r="BH598" s="1"/>
+      <c r="BI598" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43951,7 +45354,9 @@
       <c r="BD599" s="1"/>
       <c r="BE599" s="1"/>
       <c r="BF599" s="1"/>
-      <c r="BG599" s="1" t="str">
+      <c r="BG599" s="1"/>
+      <c r="BH599" s="1"/>
+      <c r="BI599" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44018,7 +45423,9 @@
       <c r="BD600" s="1"/>
       <c r="BE600" s="1"/>
       <c r="BF600" s="1"/>
-      <c r="BG600" s="1" t="str">
+      <c r="BG600" s="1"/>
+      <c r="BH600" s="1"/>
+      <c r="BI600" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44085,7 +45492,9 @@
       <c r="BD601" s="1"/>
       <c r="BE601" s="1"/>
       <c r="BF601" s="1"/>
-      <c r="BG601" s="1" t="str">
+      <c r="BG601" s="1"/>
+      <c r="BH601" s="1"/>
+      <c r="BI601" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44152,7 +45561,9 @@
       <c r="BD602" s="1"/>
       <c r="BE602" s="1"/>
       <c r="BF602" s="1"/>
-      <c r="BG602" s="1" t="str">
+      <c r="BG602" s="1"/>
+      <c r="BH602" s="1"/>
+      <c r="BI602" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44219,7 +45630,9 @@
       <c r="BD603" s="1"/>
       <c r="BE603" s="1"/>
       <c r="BF603" s="1"/>
-      <c r="BG603" s="1" t="str">
+      <c r="BG603" s="1"/>
+      <c r="BH603" s="1"/>
+      <c r="BI603" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44286,7 +45699,9 @@
       <c r="BD604" s="1"/>
       <c r="BE604" s="1"/>
       <c r="BF604" s="1"/>
-      <c r="BG604" s="1" t="str">
+      <c r="BG604" s="1"/>
+      <c r="BH604" s="1"/>
+      <c r="BI604" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44353,7 +45768,9 @@
       <c r="BD605" s="1"/>
       <c r="BE605" s="1"/>
       <c r="BF605" s="1"/>
-      <c r="BG605" s="1" t="str">
+      <c r="BG605" s="1"/>
+      <c r="BH605" s="1"/>
+      <c r="BI605" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44420,7 +45837,9 @@
       <c r="BD606" s="1"/>
       <c r="BE606" s="1"/>
       <c r="BF606" s="1"/>
-      <c r="BG606" s="1" t="str">
+      <c r="BG606" s="1"/>
+      <c r="BH606" s="1"/>
+      <c r="BI606" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44487,7 +45906,9 @@
       <c r="BD607" s="1"/>
       <c r="BE607" s="1"/>
       <c r="BF607" s="1"/>
-      <c r="BG607" s="1" t="str">
+      <c r="BG607" s="1"/>
+      <c r="BH607" s="1"/>
+      <c r="BI607" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44554,7 +45975,9 @@
       <c r="BD608" s="1"/>
       <c r="BE608" s="1"/>
       <c r="BF608" s="1"/>
-      <c r="BG608" s="1" t="str">
+      <c r="BG608" s="1"/>
+      <c r="BH608" s="1"/>
+      <c r="BI608" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44621,7 +46044,9 @@
       <c r="BD609" s="1"/>
       <c r="BE609" s="1"/>
       <c r="BF609" s="1"/>
-      <c r="BG609" s="1" t="str">
+      <c r="BG609" s="1"/>
+      <c r="BH609" s="1"/>
+      <c r="BI609" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44688,7 +46113,9 @@
       <c r="BD610" s="1"/>
       <c r="BE610" s="1"/>
       <c r="BF610" s="1"/>
-      <c r="BG610" s="1" t="str">
+      <c r="BG610" s="1"/>
+      <c r="BH610" s="1"/>
+      <c r="BI610" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44755,7 +46182,9 @@
       <c r="BD611" s="1"/>
       <c r="BE611" s="1"/>
       <c r="BF611" s="1"/>
-      <c r="BG611" s="1" t="str">
+      <c r="BG611" s="1"/>
+      <c r="BH611" s="1"/>
+      <c r="BI611" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44822,7 +46251,9 @@
       <c r="BD612" s="1"/>
       <c r="BE612" s="1"/>
       <c r="BF612" s="1"/>
-      <c r="BG612" s="1" t="str">
+      <c r="BG612" s="1"/>
+      <c r="BH612" s="1"/>
+      <c r="BI612" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44889,7 +46320,9 @@
       <c r="BD613" s="1"/>
       <c r="BE613" s="1"/>
       <c r="BF613" s="1"/>
-      <c r="BG613" s="1" t="str">
+      <c r="BG613" s="1"/>
+      <c r="BH613" s="1"/>
+      <c r="BI613" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44956,7 +46389,9 @@
       <c r="BD614" s="1"/>
       <c r="BE614" s="1"/>
       <c r="BF614" s="1"/>
-      <c r="BG614" s="1" t="str">
+      <c r="BG614" s="1"/>
+      <c r="BH614" s="1"/>
+      <c r="BI614" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45023,7 +46458,9 @@
       <c r="BD615" s="1"/>
       <c r="BE615" s="1"/>
       <c r="BF615" s="1"/>
-      <c r="BG615" s="1" t="str">
+      <c r="BG615" s="1"/>
+      <c r="BH615" s="1"/>
+      <c r="BI615" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45090,7 +46527,9 @@
       <c r="BD616" s="1"/>
       <c r="BE616" s="1"/>
       <c r="BF616" s="1"/>
-      <c r="BG616" s="1" t="str">
+      <c r="BG616" s="1"/>
+      <c r="BH616" s="1"/>
+      <c r="BI616" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45157,7 +46596,9 @@
       <c r="BD617" s="1"/>
       <c r="BE617" s="1"/>
       <c r="BF617" s="1"/>
-      <c r="BG617" s="1" t="str">
+      <c r="BG617" s="1"/>
+      <c r="BH617" s="1"/>
+      <c r="BI617" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45224,7 +46665,9 @@
       <c r="BD618" s="1"/>
       <c r="BE618" s="1"/>
       <c r="BF618" s="1"/>
-      <c r="BG618" s="1" t="str">
+      <c r="BG618" s="1"/>
+      <c r="BH618" s="1"/>
+      <c r="BI618" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45291,7 +46734,9 @@
       <c r="BD619" s="1"/>
       <c r="BE619" s="1"/>
       <c r="BF619" s="1"/>
-      <c r="BG619" s="1" t="str">
+      <c r="BG619" s="1"/>
+      <c r="BH619" s="1"/>
+      <c r="BI619" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45358,7 +46803,9 @@
       <c r="BD620" s="1"/>
       <c r="BE620" s="1"/>
       <c r="BF620" s="1"/>
-      <c r="BG620" s="1" t="str">
+      <c r="BG620" s="1"/>
+      <c r="BH620" s="1"/>
+      <c r="BI620" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45425,7 +46872,9 @@
       <c r="BD621" s="1"/>
       <c r="BE621" s="1"/>
       <c r="BF621" s="1"/>
-      <c r="BG621" s="1" t="str">
+      <c r="BG621" s="1"/>
+      <c r="BH621" s="1"/>
+      <c r="BI621" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45492,7 +46941,9 @@
       <c r="BD622" s="1"/>
       <c r="BE622" s="1"/>
       <c r="BF622" s="1"/>
-      <c r="BG622" s="1" t="str">
+      <c r="BG622" s="1"/>
+      <c r="BH622" s="1"/>
+      <c r="BI622" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45559,7 +47010,9 @@
       <c r="BD623" s="1"/>
       <c r="BE623" s="1"/>
       <c r="BF623" s="1"/>
-      <c r="BG623" s="1" t="str">
+      <c r="BG623" s="1"/>
+      <c r="BH623" s="1"/>
+      <c r="BI623" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45626,7 +47079,9 @@
       <c r="BD624" s="1"/>
       <c r="BE624" s="1"/>
       <c r="BF624" s="1"/>
-      <c r="BG624" s="1" t="str">
+      <c r="BG624" s="1"/>
+      <c r="BH624" s="1"/>
+      <c r="BI624" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45693,7 +47148,9 @@
       <c r="BD625" s="1"/>
       <c r="BE625" s="1"/>
       <c r="BF625" s="1"/>
-      <c r="BG625" s="1" t="str">
+      <c r="BG625" s="1"/>
+      <c r="BH625" s="1"/>
+      <c r="BI625" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45760,7 +47217,9 @@
       <c r="BD626" s="1"/>
       <c r="BE626" s="1"/>
       <c r="BF626" s="1"/>
-      <c r="BG626" s="1" t="str">
+      <c r="BG626" s="1"/>
+      <c r="BH626" s="1"/>
+      <c r="BI626" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45827,7 +47286,9 @@
       <c r="BD627" s="1"/>
       <c r="BE627" s="1"/>
       <c r="BF627" s="1"/>
-      <c r="BG627" s="1" t="str">
+      <c r="BG627" s="1"/>
+      <c r="BH627" s="1"/>
+      <c r="BI627" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45894,7 +47355,9 @@
       <c r="BD628" s="1"/>
       <c r="BE628" s="1"/>
       <c r="BF628" s="1"/>
-      <c r="BG628" s="1" t="str">
+      <c r="BG628" s="1"/>
+      <c r="BH628" s="1"/>
+      <c r="BI628" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45961,7 +47424,9 @@
       <c r="BD629" s="1"/>
       <c r="BE629" s="1"/>
       <c r="BF629" s="1"/>
-      <c r="BG629" s="1" t="str">
+      <c r="BG629" s="1"/>
+      <c r="BH629" s="1"/>
+      <c r="BI629" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46028,7 +47493,9 @@
       <c r="BD630" s="1"/>
       <c r="BE630" s="1"/>
       <c r="BF630" s="1"/>
-      <c r="BG630" s="1" t="str">
+      <c r="BG630" s="1"/>
+      <c r="BH630" s="1"/>
+      <c r="BI630" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46095,7 +47562,9 @@
       <c r="BD631" s="1"/>
       <c r="BE631" s="1"/>
       <c r="BF631" s="1"/>
-      <c r="BG631" s="1" t="str">
+      <c r="BG631" s="1"/>
+      <c r="BH631" s="1"/>
+      <c r="BI631" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46162,7 +47631,9 @@
       <c r="BD632" s="1"/>
       <c r="BE632" s="1"/>
       <c r="BF632" s="1"/>
-      <c r="BG632" s="1" t="str">
+      <c r="BG632" s="1"/>
+      <c r="BH632" s="1"/>
+      <c r="BI632" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46229,7 +47700,9 @@
       <c r="BD633" s="1"/>
       <c r="BE633" s="1"/>
       <c r="BF633" s="1"/>
-      <c r="BG633" s="1" t="str">
+      <c r="BG633" s="1"/>
+      <c r="BH633" s="1"/>
+      <c r="BI633" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46296,7 +47769,9 @@
       <c r="BD634" s="1"/>
       <c r="BE634" s="1"/>
       <c r="BF634" s="1"/>
-      <c r="BG634" s="1" t="str">
+      <c r="BG634" s="1"/>
+      <c r="BH634" s="1"/>
+      <c r="BI634" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46363,7 +47838,9 @@
       <c r="BD635" s="1"/>
       <c r="BE635" s="1"/>
       <c r="BF635" s="1"/>
-      <c r="BG635" s="1" t="str">
+      <c r="BG635" s="1"/>
+      <c r="BH635" s="1"/>
+      <c r="BI635" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46430,7 +47907,9 @@
       <c r="BD636" s="1"/>
       <c r="BE636" s="1"/>
       <c r="BF636" s="1"/>
-      <c r="BG636" s="1" t="str">
+      <c r="BG636" s="1"/>
+      <c r="BH636" s="1"/>
+      <c r="BI636" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46497,7 +47976,9 @@
       <c r="BD637" s="1"/>
       <c r="BE637" s="1"/>
       <c r="BF637" s="1"/>
-      <c r="BG637" s="1" t="str">
+      <c r="BG637" s="1"/>
+      <c r="BH637" s="1"/>
+      <c r="BI637" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46564,7 +48045,9 @@
       <c r="BD638" s="1"/>
       <c r="BE638" s="1"/>
       <c r="BF638" s="1"/>
-      <c r="BG638" s="1" t="str">
+      <c r="BG638" s="1"/>
+      <c r="BH638" s="1"/>
+      <c r="BI638" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46631,7 +48114,9 @@
       <c r="BD639" s="1"/>
       <c r="BE639" s="1"/>
       <c r="BF639" s="1"/>
-      <c r="BG639" s="1" t="str">
+      <c r="BG639" s="1"/>
+      <c r="BH639" s="1"/>
+      <c r="BI639" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46698,7 +48183,9 @@
       <c r="BD640" s="1"/>
       <c r="BE640" s="1"/>
       <c r="BF640" s="1"/>
-      <c r="BG640" s="1" t="str">
+      <c r="BG640" s="1"/>
+      <c r="BH640" s="1"/>
+      <c r="BI640" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46765,7 +48252,9 @@
       <c r="BD641" s="1"/>
       <c r="BE641" s="1"/>
       <c r="BF641" s="1"/>
-      <c r="BG641" s="1" t="str">
+      <c r="BG641" s="1"/>
+      <c r="BH641" s="1"/>
+      <c r="BI641" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46832,7 +48321,9 @@
       <c r="BD642" s="1"/>
       <c r="BE642" s="1"/>
       <c r="BF642" s="1"/>
-      <c r="BG642" s="1" t="str">
+      <c r="BG642" s="1"/>
+      <c r="BH642" s="1"/>
+      <c r="BI642" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46899,7 +48390,9 @@
       <c r="BD643" s="1"/>
       <c r="BE643" s="1"/>
       <c r="BF643" s="1"/>
-      <c r="BG643" s="1" t="str">
+      <c r="BG643" s="1"/>
+      <c r="BH643" s="1"/>
+      <c r="BI643" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46966,7 +48459,9 @@
       <c r="BD644" s="1"/>
       <c r="BE644" s="1"/>
       <c r="BF644" s="1"/>
-      <c r="BG644" s="1" t="str">
+      <c r="BG644" s="1"/>
+      <c r="BH644" s="1"/>
+      <c r="BI644" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47033,7 +48528,9 @@
       <c r="BD645" s="1"/>
       <c r="BE645" s="1"/>
       <c r="BF645" s="1"/>
-      <c r="BG645" s="1" t="str">
+      <c r="BG645" s="1"/>
+      <c r="BH645" s="1"/>
+      <c r="BI645" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47100,7 +48597,9 @@
       <c r="BD646" s="1"/>
       <c r="BE646" s="1"/>
       <c r="BF646" s="1"/>
-      <c r="BG646" s="1" t="str">
+      <c r="BG646" s="1"/>
+      <c r="BH646" s="1"/>
+      <c r="BI646" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47167,7 +48666,9 @@
       <c r="BD647" s="1"/>
       <c r="BE647" s="1"/>
       <c r="BF647" s="1"/>
-      <c r="BG647" s="1" t="str">
+      <c r="BG647" s="1"/>
+      <c r="BH647" s="1"/>
+      <c r="BI647" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47234,7 +48735,9 @@
       <c r="BD648" s="1"/>
       <c r="BE648" s="1"/>
       <c r="BF648" s="1"/>
-      <c r="BG648" s="1" t="str">
+      <c r="BG648" s="1"/>
+      <c r="BH648" s="1"/>
+      <c r="BI648" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47301,7 +48804,9 @@
       <c r="BD649" s="1"/>
       <c r="BE649" s="1"/>
       <c r="BF649" s="1"/>
-      <c r="BG649" s="1" t="str">
+      <c r="BG649" s="1"/>
+      <c r="BH649" s="1"/>
+      <c r="BI649" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47368,7 +48873,9 @@
       <c r="BD650" s="1"/>
       <c r="BE650" s="1"/>
       <c r="BF650" s="1"/>
-      <c r="BG650" s="1" t="str">
+      <c r="BG650" s="1"/>
+      <c r="BH650" s="1"/>
+      <c r="BI650" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47435,7 +48942,9 @@
       <c r="BD651" s="1"/>
       <c r="BE651" s="1"/>
       <c r="BF651" s="1"/>
-      <c r="BG651" s="1" t="str">
+      <c r="BG651" s="1"/>
+      <c r="BH651" s="1"/>
+      <c r="BI651" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47502,7 +49011,9 @@
       <c r="BD652" s="1"/>
       <c r="BE652" s="1"/>
       <c r="BF652" s="1"/>
-      <c r="BG652" s="1" t="str">
+      <c r="BG652" s="1"/>
+      <c r="BH652" s="1"/>
+      <c r="BI652" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47569,7 +49080,9 @@
       <c r="BD653" s="1"/>
       <c r="BE653" s="1"/>
       <c r="BF653" s="1"/>
-      <c r="BG653" s="1" t="str">
+      <c r="BG653" s="1"/>
+      <c r="BH653" s="1"/>
+      <c r="BI653" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47636,7 +49149,9 @@
       <c r="BD654" s="1"/>
       <c r="BE654" s="1"/>
       <c r="BF654" s="1"/>
-      <c r="BG654" s="1" t="str">
+      <c r="BG654" s="1"/>
+      <c r="BH654" s="1"/>
+      <c r="BI654" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47703,7 +49218,9 @@
       <c r="BD655" s="1"/>
       <c r="BE655" s="1"/>
       <c r="BF655" s="1"/>
-      <c r="BG655" s="1" t="str">
+      <c r="BG655" s="1"/>
+      <c r="BH655" s="1"/>
+      <c r="BI655" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47770,7 +49287,9 @@
       <c r="BD656" s="1"/>
       <c r="BE656" s="1"/>
       <c r="BF656" s="1"/>
-      <c r="BG656" s="1" t="str">
+      <c r="BG656" s="1"/>
+      <c r="BH656" s="1"/>
+      <c r="BI656" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47837,7 +49356,9 @@
       <c r="BD657" s="1"/>
       <c r="BE657" s="1"/>
       <c r="BF657" s="1"/>
-      <c r="BG657" s="1" t="str">
+      <c r="BG657" s="1"/>
+      <c r="BH657" s="1"/>
+      <c r="BI657" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47904,7 +49425,9 @@
       <c r="BD658" s="1"/>
       <c r="BE658" s="1"/>
       <c r="BF658" s="1"/>
-      <c r="BG658" s="1" t="str">
+      <c r="BG658" s="1"/>
+      <c r="BH658" s="1"/>
+      <c r="BI658" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47971,7 +49494,9 @@
       <c r="BD659" s="1"/>
       <c r="BE659" s="1"/>
       <c r="BF659" s="1"/>
-      <c r="BG659" s="1" t="str">
+      <c r="BG659" s="1"/>
+      <c r="BH659" s="1"/>
+      <c r="BI659" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48038,7 +49563,9 @@
       <c r="BD660" s="1"/>
       <c r="BE660" s="1"/>
       <c r="BF660" s="1"/>
-      <c r="BG660" s="1" t="str">
+      <c r="BG660" s="1"/>
+      <c r="BH660" s="1"/>
+      <c r="BI660" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48105,7 +49632,9 @@
       <c r="BD661" s="1"/>
       <c r="BE661" s="1"/>
       <c r="BF661" s="1"/>
-      <c r="BG661" s="1" t="str">
+      <c r="BG661" s="1"/>
+      <c r="BH661" s="1"/>
+      <c r="BI661" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48172,7 +49701,9 @@
       <c r="BD662" s="1"/>
       <c r="BE662" s="1"/>
       <c r="BF662" s="1"/>
-      <c r="BG662" s="1" t="str">
+      <c r="BG662" s="1"/>
+      <c r="BH662" s="1"/>
+      <c r="BI662" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48239,7 +49770,9 @@
       <c r="BD663" s="1"/>
       <c r="BE663" s="1"/>
       <c r="BF663" s="1"/>
-      <c r="BG663" s="1" t="str">
+      <c r="BG663" s="1"/>
+      <c r="BH663" s="1"/>
+      <c r="BI663" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48306,7 +49839,9 @@
       <c r="BD664" s="1"/>
       <c r="BE664" s="1"/>
       <c r="BF664" s="1"/>
-      <c r="BG664" s="1" t="str">
+      <c r="BG664" s="1"/>
+      <c r="BH664" s="1"/>
+      <c r="BI664" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48373,7 +49908,9 @@
       <c r="BD665" s="1"/>
       <c r="BE665" s="1"/>
       <c r="BF665" s="1"/>
-      <c r="BG665" s="1" t="str">
+      <c r="BG665" s="1"/>
+      <c r="BH665" s="1"/>
+      <c r="BI665" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48440,7 +49977,9 @@
       <c r="BD666" s="1"/>
       <c r="BE666" s="1"/>
       <c r="BF666" s="1"/>
-      <c r="BG666" s="1" t="str">
+      <c r="BG666" s="1"/>
+      <c r="BH666" s="1"/>
+      <c r="BI666" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48507,7 +50046,9 @@
       <c r="BD667" s="1"/>
       <c r="BE667" s="1"/>
       <c r="BF667" s="1"/>
-      <c r="BG667" s="1" t="str">
+      <c r="BG667" s="1"/>
+      <c r="BH667" s="1"/>
+      <c r="BI667" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48574,7 +50115,9 @@
       <c r="BD668" s="1"/>
       <c r="BE668" s="1"/>
       <c r="BF668" s="1"/>
-      <c r="BG668" s="1" t="str">
+      <c r="BG668" s="1"/>
+      <c r="BH668" s="1"/>
+      <c r="BI668" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48641,7 +50184,9 @@
       <c r="BD669" s="1"/>
       <c r="BE669" s="1"/>
       <c r="BF669" s="1"/>
-      <c r="BG669" s="1" t="str">
+      <c r="BG669" s="1"/>
+      <c r="BH669" s="1"/>
+      <c r="BI669" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48708,7 +50253,9 @@
       <c r="BD670" s="1"/>
       <c r="BE670" s="1"/>
       <c r="BF670" s="1"/>
-      <c r="BG670" s="1" t="str">
+      <c r="BG670" s="1"/>
+      <c r="BH670" s="1"/>
+      <c r="BI670" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48775,7 +50322,9 @@
       <c r="BD671" s="1"/>
       <c r="BE671" s="1"/>
       <c r="BF671" s="1"/>
-      <c r="BG671" s="1" t="str">
+      <c r="BG671" s="1"/>
+      <c r="BH671" s="1"/>
+      <c r="BI671" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48842,7 +50391,9 @@
       <c r="BD672" s="1"/>
       <c r="BE672" s="1"/>
       <c r="BF672" s="1"/>
-      <c r="BG672" s="1" t="str">
+      <c r="BG672" s="1"/>
+      <c r="BH672" s="1"/>
+      <c r="BI672" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48909,7 +50460,9 @@
       <c r="BD673" s="1"/>
       <c r="BE673" s="1"/>
       <c r="BF673" s="1"/>
-      <c r="BG673" s="1" t="str">
+      <c r="BG673" s="1"/>
+      <c r="BH673" s="1"/>
+      <c r="BI673" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48976,7 +50529,9 @@
       <c r="BD674" s="1"/>
       <c r="BE674" s="1"/>
       <c r="BF674" s="1"/>
-      <c r="BG674" s="1" t="str">
+      <c r="BG674" s="1"/>
+      <c r="BH674" s="1"/>
+      <c r="BI674" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49043,7 +50598,9 @@
       <c r="BD675" s="1"/>
       <c r="BE675" s="1"/>
       <c r="BF675" s="1"/>
-      <c r="BG675" s="1" t="str">
+      <c r="BG675" s="1"/>
+      <c r="BH675" s="1"/>
+      <c r="BI675" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49110,7 +50667,9 @@
       <c r="BD676" s="1"/>
       <c r="BE676" s="1"/>
       <c r="BF676" s="1"/>
-      <c r="BG676" s="1" t="str">
+      <c r="BG676" s="1"/>
+      <c r="BH676" s="1"/>
+      <c r="BI676" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49177,7 +50736,9 @@
       <c r="BD677" s="1"/>
       <c r="BE677" s="1"/>
       <c r="BF677" s="1"/>
-      <c r="BG677" s="1" t="str">
+      <c r="BG677" s="1"/>
+      <c r="BH677" s="1"/>
+      <c r="BI677" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49244,7 +50805,9 @@
       <c r="BD678" s="1"/>
       <c r="BE678" s="1"/>
       <c r="BF678" s="1"/>
-      <c r="BG678" s="1" t="str">
+      <c r="BG678" s="1"/>
+      <c r="BH678" s="1"/>
+      <c r="BI678" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49311,7 +50874,9 @@
       <c r="BD679" s="1"/>
       <c r="BE679" s="1"/>
       <c r="BF679" s="1"/>
-      <c r="BG679" s="1" t="str">
+      <c r="BG679" s="1"/>
+      <c r="BH679" s="1"/>
+      <c r="BI679" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49378,7 +50943,9 @@
       <c r="BD680" s="1"/>
       <c r="BE680" s="1"/>
       <c r="BF680" s="1"/>
-      <c r="BG680" s="1" t="str">
+      <c r="BG680" s="1"/>
+      <c r="BH680" s="1"/>
+      <c r="BI680" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49445,7 +51012,9 @@
       <c r="BD681" s="1"/>
       <c r="BE681" s="1"/>
       <c r="BF681" s="1"/>
-      <c r="BG681" s="1" t="str">
+      <c r="BG681" s="1"/>
+      <c r="BH681" s="1"/>
+      <c r="BI681" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49512,7 +51081,9 @@
       <c r="BD682" s="1"/>
       <c r="BE682" s="1"/>
       <c r="BF682" s="1"/>
-      <c r="BG682" s="1" t="str">
+      <c r="BG682" s="1"/>
+      <c r="BH682" s="1"/>
+      <c r="BI682" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49579,7 +51150,9 @@
       <c r="BD683" s="1"/>
       <c r="BE683" s="1"/>
       <c r="BF683" s="1"/>
-      <c r="BG683" s="1" t="str">
+      <c r="BG683" s="1"/>
+      <c r="BH683" s="1"/>
+      <c r="BI683" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49646,7 +51219,9 @@
       <c r="BD684" s="1"/>
       <c r="BE684" s="1"/>
       <c r="BF684" s="1"/>
-      <c r="BG684" s="1" t="str">
+      <c r="BG684" s="1"/>
+      <c r="BH684" s="1"/>
+      <c r="BI684" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49713,7 +51288,9 @@
       <c r="BD685" s="1"/>
       <c r="BE685" s="1"/>
       <c r="BF685" s="1"/>
-      <c r="BG685" s="1" t="str">
+      <c r="BG685" s="1"/>
+      <c r="BH685" s="1"/>
+      <c r="BI685" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49780,7 +51357,9 @@
       <c r="BD686" s="1"/>
       <c r="BE686" s="1"/>
       <c r="BF686" s="1"/>
-      <c r="BG686" s="1" t="str">
+      <c r="BG686" s="1"/>
+      <c r="BH686" s="1"/>
+      <c r="BI686" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49847,7 +51426,9 @@
       <c r="BD687" s="1"/>
       <c r="BE687" s="1"/>
       <c r="BF687" s="1"/>
-      <c r="BG687" s="1" t="str">
+      <c r="BG687" s="1"/>
+      <c r="BH687" s="1"/>
+      <c r="BI687" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49914,7 +51495,9 @@
       <c r="BD688" s="1"/>
       <c r="BE688" s="1"/>
       <c r="BF688" s="1"/>
-      <c r="BG688" s="1" t="str">
+      <c r="BG688" s="1"/>
+      <c r="BH688" s="1"/>
+      <c r="BI688" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49981,7 +51564,9 @@
       <c r="BD689" s="1"/>
       <c r="BE689" s="1"/>
       <c r="BF689" s="1"/>
-      <c r="BG689" s="1" t="str">
+      <c r="BG689" s="1"/>
+      <c r="BH689" s="1"/>
+      <c r="BI689" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50048,7 +51633,9 @@
       <c r="BD690" s="1"/>
       <c r="BE690" s="1"/>
       <c r="BF690" s="1"/>
-      <c r="BG690" s="1" t="str">
+      <c r="BG690" s="1"/>
+      <c r="BH690" s="1"/>
+      <c r="BI690" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50115,7 +51702,9 @@
       <c r="BD691" s="1"/>
       <c r="BE691" s="1"/>
       <c r="BF691" s="1"/>
-      <c r="BG691" s="1" t="str">
+      <c r="BG691" s="1"/>
+      <c r="BH691" s="1"/>
+      <c r="BI691" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50182,7 +51771,9 @@
       <c r="BD692" s="1"/>
       <c r="BE692" s="1"/>
       <c r="BF692" s="1"/>
-      <c r="BG692" s="1" t="str">
+      <c r="BG692" s="1"/>
+      <c r="BH692" s="1"/>
+      <c r="BI692" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50249,7 +51840,9 @@
       <c r="BD693" s="1"/>
       <c r="BE693" s="1"/>
       <c r="BF693" s="1"/>
-      <c r="BG693" s="1" t="str">
+      <c r="BG693" s="1"/>
+      <c r="BH693" s="1"/>
+      <c r="BI693" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50316,7 +51909,9 @@
       <c r="BD694" s="1"/>
       <c r="BE694" s="1"/>
       <c r="BF694" s="1"/>
-      <c r="BG694" s="1" t="str">
+      <c r="BG694" s="1"/>
+      <c r="BH694" s="1"/>
+      <c r="BI694" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50383,7 +51978,9 @@
       <c r="BD695" s="1"/>
       <c r="BE695" s="1"/>
       <c r="BF695" s="1"/>
-      <c r="BG695" s="1" t="str">
+      <c r="BG695" s="1"/>
+      <c r="BH695" s="1"/>
+      <c r="BI695" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50450,7 +52047,9 @@
       <c r="BD696" s="1"/>
       <c r="BE696" s="1"/>
       <c r="BF696" s="1"/>
-      <c r="BG696" s="1" t="str">
+      <c r="BG696" s="1"/>
+      <c r="BH696" s="1"/>
+      <c r="BI696" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50517,7 +52116,9 @@
       <c r="BD697" s="1"/>
       <c r="BE697" s="1"/>
       <c r="BF697" s="1"/>
-      <c r="BG697" s="1" t="str">
+      <c r="BG697" s="1"/>
+      <c r="BH697" s="1"/>
+      <c r="BI697" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50584,7 +52185,9 @@
       <c r="BD698" s="1"/>
       <c r="BE698" s="1"/>
       <c r="BF698" s="1"/>
-      <c r="BG698" s="1" t="str">
+      <c r="BG698" s="1"/>
+      <c r="BH698" s="1"/>
+      <c r="BI698" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50651,7 +52254,9 @@
       <c r="BD699" s="1"/>
       <c r="BE699" s="1"/>
       <c r="BF699" s="1"/>
-      <c r="BG699" s="1" t="str">
+      <c r="BG699" s="1"/>
+      <c r="BH699" s="1"/>
+      <c r="BI699" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50718,7 +52323,9 @@
       <c r="BD700" s="1"/>
       <c r="BE700" s="1"/>
       <c r="BF700" s="1"/>
-      <c r="BG700" s="1" t="str">
+      <c r="BG700" s="1"/>
+      <c r="BH700" s="1"/>
+      <c r="BI700" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
